--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605839</v>
+        <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447574</v>
+        <v>448020</v>
       </c>
       <c r="R2" t="n">
-        <v>6814884</v>
+        <v>6815080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605860</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
         <v>79083</v>
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448020</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6815080</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605858</v>
+        <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>78840</v>
+        <v>57682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +982,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448017</v>
+        <v>447574</v>
       </c>
       <c r="R5" t="n">
-        <v>6814944</v>
+        <v>6814884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R9" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605849</v>
+        <v>128605829</v>
       </c>
       <c r="B10" t="n">
-        <v>78840</v>
+        <v>79702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447655</v>
+        <v>447634</v>
       </c>
       <c r="R10" t="n">
-        <v>6814988</v>
+        <v>6814941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605886</v>
+        <v>128605849</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447905</v>
+        <v>447655</v>
       </c>
       <c r="R11" t="n">
-        <v>6815066</v>
+        <v>6814988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128605833</v>
+        <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>78840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,42 +1771,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447771</v>
+        <v>447783</v>
       </c>
       <c r="R13" t="n">
-        <v>6814844</v>
+        <v>6814852</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,7 +1857,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605837</v>
+        <v>128605833</v>
       </c>
       <c r="B14" t="n">
         <v>57682</v>
@@ -1898,7 +1890,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1908,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447740</v>
+        <v>447771</v>
       </c>
       <c r="R14" t="n">
-        <v>6814822</v>
+        <v>6814844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,10 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605852</v>
+        <v>128605837</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>57682</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,34 +1973,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447783</v>
+        <v>447740</v>
       </c>
       <c r="R15" t="n">
-        <v>6814852</v>
+        <v>6814822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605853</v>
+        <v>128605885</v>
       </c>
       <c r="B16" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447773</v>
+        <v>447840</v>
       </c>
       <c r="R16" t="n">
-        <v>6814906</v>
+        <v>6815104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605832</v>
+        <v>128605888</v>
       </c>
       <c r="B17" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,42 +2175,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448062</v>
+        <v>447929</v>
       </c>
       <c r="R17" t="n">
-        <v>6815199</v>
+        <v>6815007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,6 +2235,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605885</v>
+        <v>128605853</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2280,21 +2277,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2301,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447840</v>
+        <v>447773</v>
       </c>
       <c r="R18" t="n">
-        <v>6815104</v>
+        <v>6814906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605888</v>
+        <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2377,34 +2374,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447929</v>
+        <v>448062</v>
       </c>
       <c r="R19" t="n">
-        <v>6815007</v>
+        <v>6815199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,11 +2442,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605830</v>
+        <v>128605889</v>
       </c>
       <c r="B33" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3773,21 +3773,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447941</v>
+        <v>447989</v>
       </c>
       <c r="R33" t="n">
-        <v>6814981</v>
+        <v>6814944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,6 +3833,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3859,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,21 +3875,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3894,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R34" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3930,11 +3935,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605847</v>
+        <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448022</v>
+        <v>447910</v>
       </c>
       <c r="R41" t="n">
-        <v>6814932</v>
+        <v>6815145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B42" t="n">
         <v>79083</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R42" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4752,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605893</v>
+        <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,21 +4768,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447907</v>
+        <v>447950</v>
       </c>
       <c r="R43" t="n">
-        <v>6815150</v>
+        <v>6814974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,11 +4828,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R44" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R45" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,6 +5022,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R46" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5119,11 +5124,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605884</v>
+        <v>128605851</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447831</v>
+        <v>447628</v>
       </c>
       <c r="R55" t="n">
-        <v>6815067</v>
+        <v>6814833</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605870</v>
+        <v>128605884</v>
       </c>
       <c r="B56" t="n">
         <v>79083</v>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447670</v>
+        <v>447831</v>
       </c>
       <c r="R56" t="n">
-        <v>6814996</v>
+        <v>6815067</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605872</v>
+        <v>128605870</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447594</v>
+        <v>447670</v>
       </c>
       <c r="R57" t="n">
-        <v>6814977</v>
+        <v>6814996</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605851</v>
+        <v>128605872</v>
       </c>
       <c r="B58" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447628</v>
+        <v>447594</v>
       </c>
       <c r="R58" t="n">
-        <v>6814833</v>
+        <v>6814977</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605841</v>
+        <v>128605881</v>
       </c>
       <c r="B60" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447636</v>
+        <v>447753</v>
       </c>
       <c r="R60" t="n">
-        <v>6814937</v>
+        <v>6814819</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605843</v>
+        <v>128605880</v>
       </c>
       <c r="B61" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447744</v>
+        <v>447716</v>
       </c>
       <c r="R61" t="n">
-        <v>6814896</v>
+        <v>6814847</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605881</v>
+        <v>128605882</v>
       </c>
       <c r="B62" t="n">
         <v>79083</v>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447753</v>
+        <v>447789</v>
       </c>
       <c r="R62" t="n">
-        <v>6814819</v>
+        <v>6814910</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605880</v>
+        <v>128605841</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447716</v>
+        <v>447636</v>
       </c>
       <c r="R63" t="n">
-        <v>6814847</v>
+        <v>6814937</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6812,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605882</v>
+        <v>128605843</v>
       </c>
       <c r="B64" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6823,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447789</v>
+        <v>447744</v>
       </c>
       <c r="R64" t="n">
-        <v>6814910</v>
+        <v>6814896</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6883,11 +6888,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605835</v>
+        <v>128605844</v>
       </c>
       <c r="B29" t="n">
-        <v>57682</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,42 +3376,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447581</v>
+        <v>447771</v>
       </c>
       <c r="R29" t="n">
-        <v>6814933</v>
+        <v>6814896</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3462,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605844</v>
+        <v>128605835</v>
       </c>
       <c r="B30" t="n">
-        <v>78841</v>
+        <v>57682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,34 +3473,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447771</v>
+        <v>447581</v>
       </c>
       <c r="R30" t="n">
-        <v>6814896</v>
+        <v>6814933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605894</v>
+        <v>128605847</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447910</v>
+        <v>448022</v>
       </c>
       <c r="R41" t="n">
-        <v>6815145</v>
+        <v>6814932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B42" t="n">
         <v>79083</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605856</v>
+        <v>128605893</v>
       </c>
       <c r="B43" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4763,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447950</v>
+        <v>447907</v>
       </c>
       <c r="R43" t="n">
-        <v>6814974</v>
+        <v>6815150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,6 +4823,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605847</v>
+        <v>128605856</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448022</v>
+        <v>447950</v>
       </c>
       <c r="R44" t="n">
-        <v>6814932</v>
+        <v>6814974</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R45" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B46" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5059,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R46" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5124,6 +5119,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605838</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5748,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447770</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5842,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605890</v>
+        <v>128605871</v>
       </c>
       <c r="B54" t="n">
         <v>79083</v>
@@ -5869,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448003</v>
+        <v>447606</v>
       </c>
       <c r="R54" t="n">
-        <v>6814939</v>
+        <v>6814958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605851</v>
+        <v>128605890</v>
       </c>
       <c r="B55" t="n">
-        <v>78840</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,21 +5950,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5966,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447628</v>
+        <v>448003</v>
       </c>
       <c r="R55" t="n">
-        <v>6814833</v>
+        <v>6814939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,10 +6036,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605884</v>
+        <v>128605851</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>78840</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447831</v>
+        <v>447628</v>
       </c>
       <c r="R56" t="n">
-        <v>6815067</v>
+        <v>6814833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605870</v>
+        <v>128605884</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6160,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447670</v>
+        <v>447831</v>
       </c>
       <c r="R57" t="n">
-        <v>6814996</v>
+        <v>6815067</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,7 +6230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605872</v>
+        <v>128605870</v>
       </c>
       <c r="B58" t="n">
         <v>79083</v>
@@ -6257,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447594</v>
+        <v>447670</v>
       </c>
       <c r="R58" t="n">
-        <v>6814977</v>
+        <v>6814996</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6319,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605838</v>
+        <v>128605872</v>
       </c>
       <c r="B59" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6330,42 +6338,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447770</v>
+        <v>447594</v>
       </c>
       <c r="R59" t="n">
-        <v>6814909</v>
+        <v>6814977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6912,6 +6912,107 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128629773</v>
+      </c>
+      <c r="B65" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skrikberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>448022</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6814932</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605855</v>
+        <v>128605892</v>
       </c>
       <c r="B7" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447946</v>
+        <v>447931</v>
       </c>
       <c r="R7" t="n">
-        <v>6814990</v>
+        <v>6815092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1244,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605892</v>
+        <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447931</v>
+        <v>447946</v>
       </c>
       <c r="R8" t="n">
-        <v>6815092</v>
+        <v>6814990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,11 +1346,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605829</v>
+        <v>128605849</v>
       </c>
       <c r="B10" t="n">
-        <v>79702</v>
+        <v>78844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447634</v>
+        <v>447655</v>
       </c>
       <c r="R10" t="n">
-        <v>6814941</v>
+        <v>6814988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605849</v>
+        <v>128605886</v>
       </c>
       <c r="B11" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447655</v>
+        <v>447905</v>
       </c>
       <c r="R11" t="n">
-        <v>6814988</v>
+        <v>6815066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
         <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128605833</v>
       </c>
       <c r="B14" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>128605837</v>
       </c>
       <c r="B15" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605885</v>
+        <v>128605853</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447840</v>
+        <v>447773</v>
       </c>
       <c r="R16" t="n">
-        <v>6815104</v>
+        <v>6814906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R17" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,11 +2235,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605853</v>
+        <v>128605888</v>
       </c>
       <c r="B18" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447773</v>
+        <v>447929</v>
       </c>
       <c r="R18" t="n">
-        <v>6814906</v>
+        <v>6815007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2366,7 +2366,7 @@
         <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605861</v>
+        <v>128605865</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448113</v>
+        <v>447930</v>
       </c>
       <c r="R23" t="n">
-        <v>6815152</v>
+        <v>6815173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2849,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,10 +2875,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605865</v>
+        <v>128605861</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447930</v>
+        <v>448113</v>
       </c>
       <c r="R24" t="n">
-        <v>6815173</v>
+        <v>6815152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,6 +2946,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,7 +2980,7 @@
         <v>128605873</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>128605879</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>128605862</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605844</v>
+        <v>128605835</v>
       </c>
       <c r="B29" t="n">
-        <v>78841</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447771</v>
+        <v>447581</v>
       </c>
       <c r="R29" t="n">
-        <v>6814896</v>
+        <v>6814933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605835</v>
+        <v>128605844</v>
       </c>
       <c r="B30" t="n">
-        <v>57682</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3473,42 +3481,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447581</v>
+        <v>447771</v>
       </c>
       <c r="R30" t="n">
-        <v>6814933</v>
+        <v>6814896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605846</v>
+        <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448039</v>
+        <v>447989</v>
       </c>
       <c r="R32" t="n">
-        <v>6814941</v>
+        <v>6814944</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,10 +3767,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605889</v>
+        <v>128605891</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447989</v>
+        <v>447935</v>
       </c>
       <c r="R33" t="n">
-        <v>6814944</v>
+        <v>6815088</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3837,7 +3842,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3867,7 +3872,7 @@
         <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3961,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128605891</v>
+        <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>78845</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3996,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447935</v>
+        <v>448039</v>
       </c>
       <c r="R35" t="n">
-        <v>6815088</v>
+        <v>6814941</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4032,11 +4037,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4066,7 +4066,7 @@
         <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605847</v>
+        <v>128605893</v>
       </c>
       <c r="B41" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448022</v>
+        <v>447907</v>
       </c>
       <c r="R41" t="n">
-        <v>6814932</v>
+        <v>6815150</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,6 +4629,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605894</v>
+        <v>128605856</v>
       </c>
       <c r="B42" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4666,21 +4671,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4695,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447910</v>
+        <v>447950</v>
       </c>
       <c r="R42" t="n">
-        <v>6815145</v>
+        <v>6814974</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4752,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R43" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,11 +4828,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78840</v>
+        <v>78845</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R44" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>128605842</v>
       </c>
       <c r="B45" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128605864</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128605883</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>128605877</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>128605857</v>
       </c>
       <c r="B49" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605838</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447770</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814909</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605871</v>
+        <v>128605890</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447606</v>
+        <v>448003</v>
       </c>
       <c r="R54" t="n">
-        <v>6814958</v>
+        <v>6814939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605890</v>
+        <v>128605884</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5974,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448003</v>
+        <v>447831</v>
       </c>
       <c r="R55" t="n">
-        <v>6814939</v>
+        <v>6815067</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605851</v>
+        <v>128605870</v>
       </c>
       <c r="B56" t="n">
-        <v>78840</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6039,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447628</v>
+        <v>447670</v>
       </c>
       <c r="R56" t="n">
-        <v>6814833</v>
+        <v>6814996</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605884</v>
+        <v>128605872</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6168,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447831</v>
+        <v>447594</v>
       </c>
       <c r="R57" t="n">
-        <v>6815067</v>
+        <v>6814977</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605870</v>
+        <v>128605838</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,34 +6233,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447670</v>
+        <v>447770</v>
       </c>
       <c r="R58" t="n">
-        <v>6814996</v>
+        <v>6814909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605872</v>
+        <v>128605851</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>78844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447594</v>
+        <v>447628</v>
       </c>
       <c r="R59" t="n">
-        <v>6814977</v>
+        <v>6814833</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,7 +6427,7 @@
         <v>128605881</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605880</v>
+        <v>128605882</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447716</v>
+        <v>447789</v>
       </c>
       <c r="R61" t="n">
-        <v>6814847</v>
+        <v>6814910</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,6 +6592,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6618,10 +6623,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605882</v>
+        <v>128605880</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447789</v>
+        <v>447716</v>
       </c>
       <c r="R62" t="n">
-        <v>6814910</v>
+        <v>6814847</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6694,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6723,7 +6723,7 @@
         <v>128605841</v>
       </c>
       <c r="B63" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128605843</v>
       </c>
       <c r="B64" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128629773</v>
       </c>
       <c r="B65" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605860</v>
+        <v>128605839</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448020</v>
+        <v>447574</v>
       </c>
       <c r="R2" t="n">
-        <v>6815080</v>
+        <v>6814884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605860</v>
       </c>
       <c r="B3" t="n">
         <v>79087</v>
@@ -812,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>448020</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6815080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605839</v>
+        <v>128605858</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447574</v>
+        <v>448017</v>
       </c>
       <c r="R5" t="n">
-        <v>6814884</v>
+        <v>6814944</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605876</v>
+        <v>128605855</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447585</v>
+        <v>447946</v>
       </c>
       <c r="R6" t="n">
-        <v>6814852</v>
+        <v>6814990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605892</v>
+        <v>128605876</v>
       </c>
       <c r="B7" t="n">
         <v>79087</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447931</v>
+        <v>447585</v>
       </c>
       <c r="R7" t="n">
-        <v>6815092</v>
+        <v>6814852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605855</v>
+        <v>128605892</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447946</v>
+        <v>447931</v>
       </c>
       <c r="R8" t="n">
-        <v>6814990</v>
+        <v>6815092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1341,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R9" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R10" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R11" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605887</v>
+        <v>128605849</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447907</v>
+        <v>447655</v>
       </c>
       <c r="R12" t="n">
-        <v>6815070</v>
+        <v>6814988</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605853</v>
+        <v>128605832</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,34 +2078,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447773</v>
+        <v>448062</v>
       </c>
       <c r="R16" t="n">
-        <v>6814906</v>
+        <v>6815199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605832</v>
+        <v>128605853</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>78844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,42 +2382,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448062</v>
+        <v>447773</v>
       </c>
       <c r="R19" t="n">
-        <v>6815199</v>
+        <v>6814906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R21" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R22" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605865</v>
+        <v>128605861</v>
       </c>
       <c r="B23" t="n">
         <v>79087</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447930</v>
+        <v>448113</v>
       </c>
       <c r="R23" t="n">
-        <v>6815173</v>
+        <v>6815152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2875,7 +2880,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605861</v>
+        <v>128605865</v>
       </c>
       <c r="B24" t="n">
         <v>79087</v>
@@ -2910,10 +2915,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448113</v>
+        <v>447930</v>
       </c>
       <c r="R24" t="n">
-        <v>6815152</v>
+        <v>6815173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,11 +2951,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B41" t="n">
         <v>79087</v>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R41" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,11 +4629,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4660,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605856</v>
+        <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4671,21 +4666,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4695,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447950</v>
+        <v>447907</v>
       </c>
       <c r="R42" t="n">
-        <v>6814974</v>
+        <v>6815150</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4731,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605894</v>
+        <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4768,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447910</v>
+        <v>447950</v>
       </c>
       <c r="R43" t="n">
-        <v>6815145</v>
+        <v>6814974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605838</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5748,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447770</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5842,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605890</v>
+        <v>128605871</v>
       </c>
       <c r="B54" t="n">
         <v>79087</v>
@@ -5869,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448003</v>
+        <v>447606</v>
       </c>
       <c r="R54" t="n">
-        <v>6814939</v>
+        <v>6814958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,7 +5939,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605884</v>
+        <v>128605890</v>
       </c>
       <c r="B55" t="n">
         <v>79087</v>
@@ -5966,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447831</v>
+        <v>448003</v>
       </c>
       <c r="R55" t="n">
-        <v>6815067</v>
+        <v>6814939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6036,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605870</v>
+        <v>128605884</v>
       </c>
       <c r="B56" t="n">
         <v>79087</v>
@@ -6063,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447670</v>
+        <v>447831</v>
       </c>
       <c r="R56" t="n">
-        <v>6814996</v>
+        <v>6815067</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605872</v>
+        <v>128605870</v>
       </c>
       <c r="B57" t="n">
         <v>79087</v>
@@ -6160,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447594</v>
+        <v>447670</v>
       </c>
       <c r="R57" t="n">
-        <v>6814977</v>
+        <v>6814996</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605838</v>
+        <v>128605872</v>
       </c>
       <c r="B58" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,42 +6241,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447770</v>
+        <v>447594</v>
       </c>
       <c r="R58" t="n">
-        <v>6814909</v>
+        <v>6814977</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605882</v>
+        <v>128605880</v>
       </c>
       <c r="B61" t="n">
         <v>79087</v>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447789</v>
+        <v>447716</v>
       </c>
       <c r="R61" t="n">
-        <v>6814910</v>
+        <v>6814847</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,11 +6592,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6623,7 +6618,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605880</v>
+        <v>128605882</v>
       </c>
       <c r="B62" t="n">
         <v>79087</v>
@@ -6658,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447716</v>
+        <v>447789</v>
       </c>
       <c r="R62" t="n">
-        <v>6814847</v>
+        <v>6814910</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6694,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R6" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605876</v>
+        <v>128605892</v>
       </c>
       <c r="B7" t="n">
         <v>79087</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447585</v>
+        <v>447931</v>
       </c>
       <c r="R7" t="n">
-        <v>6814852</v>
+        <v>6815092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1244,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605892</v>
+        <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447931</v>
+        <v>447946</v>
       </c>
       <c r="R8" t="n">
-        <v>6815092</v>
+        <v>6814990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,11 +1346,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605879</v>
+        <v>128605835</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,34 +3182,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447664</v>
+        <v>447581</v>
       </c>
       <c r="R27" t="n">
-        <v>6814830</v>
+        <v>6814933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605862</v>
+        <v>128605844</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3279,21 +3287,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448085</v>
+        <v>447771</v>
       </c>
       <c r="R28" t="n">
-        <v>6815187</v>
+        <v>6814896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605835</v>
+        <v>128605879</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,42 +3384,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447581</v>
+        <v>447664</v>
       </c>
       <c r="R29" t="n">
-        <v>6814933</v>
+        <v>6814830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605844</v>
+        <v>128605862</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447771</v>
+        <v>448085</v>
       </c>
       <c r="R30" t="n">
-        <v>6814896</v>
+        <v>6815187</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R45" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,6 +5022,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R46" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5119,11 +5124,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605839</v>
+        <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447574</v>
+        <v>448020</v>
       </c>
       <c r="R2" t="n">
-        <v>6814884</v>
+        <v>6815080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605860</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448020</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6815080</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605858</v>
+        <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +982,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448017</v>
+        <v>447574</v>
       </c>
       <c r="R5" t="n">
-        <v>6814944</v>
+        <v>6814884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128605892</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605887</v>
+        <v>128605849</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447907</v>
+        <v>447655</v>
       </c>
       <c r="R10" t="n">
-        <v>6815070</v>
+        <v>6814988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R11" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R12" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128605852</v>
+        <v>128605833</v>
       </c>
       <c r="B13" t="n">
-        <v>78844</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,34 +1771,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447783</v>
+        <v>447771</v>
       </c>
       <c r="R13" t="n">
-        <v>6814852</v>
+        <v>6814844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1865,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605833</v>
+        <v>128605837</v>
       </c>
       <c r="B14" t="n">
         <v>57686</v>
@@ -1890,7 +1898,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1900,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447771</v>
+        <v>447740</v>
       </c>
       <c r="R14" t="n">
-        <v>6814844</v>
+        <v>6814822</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,10 +1970,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605837</v>
+        <v>128605852</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,42 +1981,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447740</v>
+        <v>447783</v>
       </c>
       <c r="R15" t="n">
-        <v>6814822</v>
+        <v>6814852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2175,7 @@
         <v>128605885</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128605888</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>128605853</v>
       </c>
       <c r="B19" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R22" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,7 +2781,7 @@
         <v>128605861</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128605865</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>128605873</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605835</v>
+        <v>128605879</v>
       </c>
       <c r="B27" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,42 +3182,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447581</v>
+        <v>447664</v>
       </c>
       <c r="R27" t="n">
-        <v>6814933</v>
+        <v>6814830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605844</v>
+        <v>128605862</v>
       </c>
       <c r="B28" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,21 +3279,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447771</v>
+        <v>448085</v>
       </c>
       <c r="R28" t="n">
-        <v>6814896</v>
+        <v>6815187</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605879</v>
+        <v>128605835</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447664</v>
+        <v>447581</v>
       </c>
       <c r="R29" t="n">
-        <v>6814830</v>
+        <v>6814933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605862</v>
+        <v>128605844</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448085</v>
+        <v>447771</v>
       </c>
       <c r="R30" t="n">
-        <v>6815187</v>
+        <v>6814896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128605891</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128605883</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>128605877</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>128605857</v>
       </c>
       <c r="B49" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605838</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447770</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814909</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605871</v>
+        <v>128605890</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447606</v>
+        <v>448003</v>
       </c>
       <c r="R54" t="n">
-        <v>6814958</v>
+        <v>6814939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605890</v>
+        <v>128605884</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5974,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448003</v>
+        <v>447831</v>
       </c>
       <c r="R55" t="n">
-        <v>6814939</v>
+        <v>6815067</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605884</v>
+        <v>128605870</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6071,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447831</v>
+        <v>447670</v>
       </c>
       <c r="R56" t="n">
-        <v>6815067</v>
+        <v>6814996</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605870</v>
+        <v>128605872</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6168,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447670</v>
+        <v>447594</v>
       </c>
       <c r="R57" t="n">
-        <v>6814996</v>
+        <v>6814977</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605872</v>
+        <v>128605838</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,34 +6233,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447594</v>
+        <v>447770</v>
       </c>
       <c r="R58" t="n">
-        <v>6814977</v>
+        <v>6814909</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6330,7 +6330,7 @@
         <v>128605851</v>
       </c>
       <c r="B59" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605881</v>
+        <v>128605841</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447753</v>
+        <v>447636</v>
       </c>
       <c r="R60" t="n">
-        <v>6814819</v>
+        <v>6814937</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605880</v>
+        <v>128605843</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447716</v>
+        <v>447744</v>
       </c>
       <c r="R61" t="n">
-        <v>6814847</v>
+        <v>6814896</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605882</v>
+        <v>128605881</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447789</v>
+        <v>447753</v>
       </c>
       <c r="R62" t="n">
-        <v>6814910</v>
+        <v>6814819</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6689,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605841</v>
+        <v>128605880</v>
       </c>
       <c r="B63" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447636</v>
+        <v>447716</v>
       </c>
       <c r="R63" t="n">
-        <v>6814937</v>
+        <v>6814847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6817,10 +6812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605843</v>
+        <v>128605882</v>
       </c>
       <c r="B64" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6823,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447744</v>
+        <v>447789</v>
       </c>
       <c r="R64" t="n">
-        <v>6814896</v>
+        <v>6814910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6888,6 +6883,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605860</v>
+        <v>128605858</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448020</v>
+        <v>448017</v>
       </c>
       <c r="R2" t="n">
-        <v>6815080</v>
+        <v>6814944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605860</v>
       </c>
       <c r="B3" t="n">
         <v>79089</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>448020</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6815080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605876</v>
+        <v>128605855</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447585</v>
+        <v>447946</v>
       </c>
       <c r="R6" t="n">
-        <v>6814852</v>
+        <v>6814990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R8" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R9" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605849</v>
+        <v>128605829</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447655</v>
+        <v>447634</v>
       </c>
       <c r="R10" t="n">
-        <v>6814988</v>
+        <v>6814941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605886</v>
+        <v>128605849</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447905</v>
+        <v>447655</v>
       </c>
       <c r="R11" t="n">
-        <v>6815066</v>
+        <v>6814988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605885</v>
+        <v>128605888</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447840</v>
+        <v>447929</v>
       </c>
       <c r="R17" t="n">
-        <v>6815104</v>
+        <v>6815007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,6 +2243,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,7 +2274,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B18" t="n">
         <v>79089</v>
@@ -2304,10 +2309,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R18" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,11 +2345,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2778,7 +2778,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R23" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2849,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,7 +2875,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605865</v>
+        <v>128605873</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -2915,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447930</v>
+        <v>447570</v>
       </c>
       <c r="R24" t="n">
-        <v>6815173</v>
+        <v>6814915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,7 +2972,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B25" t="n">
         <v>79089</v>
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R25" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,7 +3069,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605863</v>
+        <v>128605861</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3109,10 +3104,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448048</v>
+        <v>448113</v>
       </c>
       <c r="R26" t="n">
-        <v>6815201</v>
+        <v>6815152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,6 +3140,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605879</v>
+        <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447664</v>
+        <v>447771</v>
       </c>
       <c r="R27" t="n">
-        <v>6814830</v>
+        <v>6814896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605862</v>
+        <v>128605879</v>
       </c>
       <c r="B28" t="n">
         <v>79089</v>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448085</v>
+        <v>447664</v>
       </c>
       <c r="R28" t="n">
-        <v>6815187</v>
+        <v>6814830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605835</v>
+        <v>128605862</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,42 +3376,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447581</v>
+        <v>448085</v>
       </c>
       <c r="R29" t="n">
-        <v>6814933</v>
+        <v>6815187</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3462,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605844</v>
+        <v>128605835</v>
       </c>
       <c r="B30" t="n">
-        <v>78847</v>
+        <v>57686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,34 +3473,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447771</v>
+        <v>447581</v>
       </c>
       <c r="R30" t="n">
-        <v>6814896</v>
+        <v>6814933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R32" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3869,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605830</v>
+        <v>128605889</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3875,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447941</v>
+        <v>447989</v>
       </c>
       <c r="R34" t="n">
-        <v>6814981</v>
+        <v>6814944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,6 +3935,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4063,7 +4063,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605878</v>
+        <v>128605867</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447619</v>
+        <v>447749</v>
       </c>
       <c r="R36" t="n">
-        <v>6814842</v>
+        <v>6815028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,6 +4134,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4160,7 +4165,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605867</v>
+        <v>128605878</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4195,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447749</v>
+        <v>447619</v>
       </c>
       <c r="R37" t="n">
-        <v>6815028</v>
+        <v>6814842</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4231,11 +4236,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4558,7 +4558,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R41" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,6 +4629,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4655,7 +4660,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B42" t="n">
         <v>79089</v>
@@ -4690,10 +4695,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4731,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605883</v>
+        <v>128605857</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447840</v>
+        <v>447992</v>
       </c>
       <c r="R47" t="n">
-        <v>6815052</v>
+        <v>6814945</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,11 +5221,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5349,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605857</v>
+        <v>128605883</v>
       </c>
       <c r="B49" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447992</v>
+        <v>447840</v>
       </c>
       <c r="R49" t="n">
-        <v>6814945</v>
+        <v>6815052</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5420,6 +5415,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605890</v>
+        <v>128605838</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448003</v>
+        <v>447770</v>
       </c>
       <c r="R54" t="n">
-        <v>6814939</v>
+        <v>6814909</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,7 +5939,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605884</v>
+        <v>128605872</v>
       </c>
       <c r="B55" t="n">
         <v>79089</v>
@@ -5966,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447831</v>
+        <v>447594</v>
       </c>
       <c r="R55" t="n">
-        <v>6815067</v>
+        <v>6814977</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6125,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605872</v>
+        <v>128605884</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -6160,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447594</v>
+        <v>447831</v>
       </c>
       <c r="R57" t="n">
-        <v>6814977</v>
+        <v>6815067</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605838</v>
+        <v>128605871</v>
       </c>
       <c r="B58" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,42 +6241,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447770</v>
+        <v>447606</v>
       </c>
       <c r="R58" t="n">
-        <v>6814909</v>
+        <v>6814958</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605851</v>
+        <v>128605890</v>
       </c>
       <c r="B59" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447628</v>
+        <v>448003</v>
       </c>
       <c r="R59" t="n">
-        <v>6814833</v>
+        <v>6814939</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605841</v>
+        <v>128605881</v>
       </c>
       <c r="B60" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447636</v>
+        <v>447753</v>
       </c>
       <c r="R60" t="n">
-        <v>6814937</v>
+        <v>6814819</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605843</v>
+        <v>128605882</v>
       </c>
       <c r="B61" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447744</v>
+        <v>447789</v>
       </c>
       <c r="R61" t="n">
-        <v>6814896</v>
+        <v>6814910</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,6 +6592,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6618,7 +6623,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605881</v>
+        <v>128605880</v>
       </c>
       <c r="B62" t="n">
         <v>79089</v>
@@ -6653,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447753</v>
+        <v>447716</v>
       </c>
       <c r="R62" t="n">
-        <v>6814819</v>
+        <v>6814847</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605880</v>
+        <v>128605841</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447716</v>
+        <v>447636</v>
       </c>
       <c r="R63" t="n">
-        <v>6814847</v>
+        <v>6814937</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6812,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605882</v>
+        <v>128605843</v>
       </c>
       <c r="B64" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6823,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447789</v>
+        <v>447744</v>
       </c>
       <c r="R64" t="n">
-        <v>6814910</v>
+        <v>6814896</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6883,11 +6888,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605829</v>
+        <v>128605849</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447634</v>
+        <v>447655</v>
       </c>
       <c r="R10" t="n">
-        <v>6814941</v>
+        <v>6814988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R11" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605887</v>
+        <v>128605886</v>
       </c>
       <c r="B12" t="n">
         <v>79089</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447907</v>
+        <v>447905</v>
       </c>
       <c r="R12" t="n">
-        <v>6815070</v>
+        <v>6815066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605832</v>
+        <v>128605853</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,42 +2078,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448062</v>
+        <v>447773</v>
       </c>
       <c r="R16" t="n">
-        <v>6815199</v>
+        <v>6814906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2207,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R17" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,11 +2235,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605885</v>
+        <v>128605832</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2285,34 +2272,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447840</v>
+        <v>448062</v>
       </c>
       <c r="R18" t="n">
-        <v>6815104</v>
+        <v>6815199</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,10 +2366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605853</v>
+        <v>128605888</v>
       </c>
       <c r="B19" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2382,21 +2377,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2406,10 +2401,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447773</v>
+        <v>447929</v>
       </c>
       <c r="R19" t="n">
-        <v>6814906</v>
+        <v>6815007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3268,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605879</v>
+        <v>128605835</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3279,34 +3279,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447664</v>
+        <v>447581</v>
       </c>
       <c r="R28" t="n">
-        <v>6814830</v>
+        <v>6814933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,7 +3373,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605862</v>
+        <v>128605879</v>
       </c>
       <c r="B29" t="n">
         <v>79089</v>
@@ -3400,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448085</v>
+        <v>447664</v>
       </c>
       <c r="R29" t="n">
-        <v>6815187</v>
+        <v>6814830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605835</v>
+        <v>128605862</v>
       </c>
       <c r="B30" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3473,42 +3481,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447581</v>
+        <v>448085</v>
       </c>
       <c r="R30" t="n">
-        <v>6814933</v>
+        <v>6815187</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605867</v>
+        <v>128605878</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447749</v>
+        <v>447619</v>
       </c>
       <c r="R36" t="n">
-        <v>6815028</v>
+        <v>6814842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,11 +4134,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4165,7 +4160,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605878</v>
+        <v>128605866</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4200,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447619</v>
+        <v>447839</v>
       </c>
       <c r="R37" t="n">
-        <v>6814842</v>
+        <v>6815058</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4236,6 +4231,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4262,7 +4262,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128605866</v>
+        <v>128605867</v>
       </c>
       <c r="B38" t="n">
         <v>79089</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447839</v>
+        <v>447749</v>
       </c>
       <c r="R38" t="n">
-        <v>6815058</v>
+        <v>6815028</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605857</v>
+        <v>128605877</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447992</v>
+        <v>447607</v>
       </c>
       <c r="R47" t="n">
-        <v>6814945</v>
+        <v>6814835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5247,7 +5247,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605877</v>
+        <v>128605883</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447607</v>
+        <v>447840</v>
       </c>
       <c r="R48" t="n">
-        <v>6814835</v>
+        <v>6815052</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,6 +5318,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605883</v>
+        <v>128605857</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447840</v>
+        <v>447992</v>
       </c>
       <c r="R49" t="n">
-        <v>6815052</v>
+        <v>6814945</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5415,11 +5420,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605851</v>
+        <v>128605838</v>
       </c>
       <c r="B53" t="n">
-        <v>78846</v>
+        <v>57686</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5748,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447628</v>
+        <v>447770</v>
       </c>
       <c r="R53" t="n">
-        <v>6814833</v>
+        <v>6814909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5842,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605838</v>
+        <v>128605870</v>
       </c>
       <c r="B54" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,42 +5853,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447770</v>
+        <v>447670</v>
       </c>
       <c r="R54" t="n">
-        <v>6814909</v>
+        <v>6814996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605872</v>
+        <v>128605884</v>
       </c>
       <c r="B55" t="n">
         <v>79089</v>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447594</v>
+        <v>447831</v>
       </c>
       <c r="R55" t="n">
-        <v>6814977</v>
+        <v>6815067</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605870</v>
+        <v>128605871</v>
       </c>
       <c r="B56" t="n">
         <v>79089</v>
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447670</v>
+        <v>447606</v>
       </c>
       <c r="R56" t="n">
-        <v>6814996</v>
+        <v>6814958</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605884</v>
+        <v>128605890</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447831</v>
+        <v>448003</v>
       </c>
       <c r="R57" t="n">
-        <v>6815067</v>
+        <v>6814939</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6241,21 +6241,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R58" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605890</v>
+        <v>128605872</v>
       </c>
       <c r="B59" t="n">
         <v>79089</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>448003</v>
+        <v>447594</v>
       </c>
       <c r="R59" t="n">
-        <v>6814939</v>
+        <v>6814977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605858</v>
+        <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448017</v>
+        <v>448020</v>
       </c>
       <c r="R2" t="n">
-        <v>6814944</v>
+        <v>6815080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605860</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
         <v>79089</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448020</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6815080</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R6" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605876</v>
+        <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447585</v>
+        <v>447946</v>
       </c>
       <c r="R8" t="n">
-        <v>6814852</v>
+        <v>6814990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R9" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R10" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605887</v>
+        <v>128605829</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447907</v>
+        <v>447634</v>
       </c>
       <c r="R11" t="n">
-        <v>6815070</v>
+        <v>6814941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605886</v>
+        <v>128605849</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447905</v>
+        <v>447655</v>
       </c>
       <c r="R12" t="n">
-        <v>6815066</v>
+        <v>6814988</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605853</v>
+        <v>128605832</v>
       </c>
       <c r="B16" t="n">
-        <v>78846</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,34 +2078,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447773</v>
+        <v>448062</v>
       </c>
       <c r="R16" t="n">
-        <v>6814906</v>
+        <v>6815199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,10 +2269,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605832</v>
+        <v>128605888</v>
       </c>
       <c r="B18" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,42 +2280,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448062</v>
+        <v>447929</v>
       </c>
       <c r="R18" t="n">
-        <v>6815199</v>
+        <v>6815007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,6 +2340,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2366,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605888</v>
+        <v>128605853</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2377,21 +2382,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2401,10 +2406,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447929</v>
+        <v>447773</v>
       </c>
       <c r="R19" t="n">
-        <v>6815007</v>
+        <v>6814906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,11 +2442,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B21" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R21" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R22" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605863</v>
+        <v>128605861</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448048</v>
+        <v>448113</v>
       </c>
       <c r="R23" t="n">
-        <v>6815201</v>
+        <v>6815152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2875,7 +2880,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -2910,10 +2915,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R24" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605865</v>
+        <v>128605873</v>
       </c>
       <c r="B25" t="n">
         <v>79089</v>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447930</v>
+        <v>447570</v>
       </c>
       <c r="R25" t="n">
-        <v>6815173</v>
+        <v>6814915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,7 +3074,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R26" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,11 +3145,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605844</v>
+        <v>128605879</v>
       </c>
       <c r="B27" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447771</v>
+        <v>447664</v>
       </c>
       <c r="R27" t="n">
-        <v>6814896</v>
+        <v>6814830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605835</v>
+        <v>128605862</v>
       </c>
       <c r="B28" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3279,42 +3279,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447581</v>
+        <v>448085</v>
       </c>
       <c r="R28" t="n">
-        <v>6814933</v>
+        <v>6815187</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605879</v>
+        <v>128605835</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447664</v>
+        <v>447581</v>
       </c>
       <c r="R29" t="n">
-        <v>6814830</v>
+        <v>6814933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605862</v>
+        <v>128605844</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448085</v>
+        <v>447771</v>
       </c>
       <c r="R30" t="n">
-        <v>6815187</v>
+        <v>6814896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605830</v>
+        <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447941</v>
+        <v>447989</v>
       </c>
       <c r="R32" t="n">
-        <v>6814981</v>
+        <v>6814944</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3875,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R34" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,11 +3940,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4160,7 +4160,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605866</v>
+        <v>128605867</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447839</v>
+        <v>447749</v>
       </c>
       <c r="R37" t="n">
-        <v>6815058</v>
+        <v>6815028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4262,7 +4262,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128605867</v>
+        <v>128605866</v>
       </c>
       <c r="B38" t="n">
         <v>79089</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447749</v>
+        <v>447839</v>
       </c>
       <c r="R38" t="n">
-        <v>6815028</v>
+        <v>6815058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4558,7 +4558,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B41" t="n">
         <v>79089</v>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R41" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,11 +4629,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4660,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B42" t="n">
         <v>79089</v>
@@ -4695,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R42" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4731,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5150,7 +5150,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605877</v>
+        <v>128605883</v>
       </c>
       <c r="B47" t="n">
         <v>79089</v>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447607</v>
+        <v>447840</v>
       </c>
       <c r="R47" t="n">
-        <v>6814835</v>
+        <v>6815052</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,6 +5221,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,7 +5252,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605883</v>
+        <v>128605877</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -5282,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447840</v>
+        <v>447607</v>
       </c>
       <c r="R48" t="n">
-        <v>6815052</v>
+        <v>6814835</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,11 +5323,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605838</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447770</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814909</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,7 +5834,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605870</v>
+        <v>128605890</v>
       </c>
       <c r="B54" t="n">
         <v>79089</v>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447670</v>
+        <v>448003</v>
       </c>
       <c r="R54" t="n">
-        <v>6814996</v>
+        <v>6814939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605871</v>
+        <v>128605870</v>
       </c>
       <c r="B56" t="n">
         <v>79089</v>
@@ -6071,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447606</v>
+        <v>447670</v>
       </c>
       <c r="R56" t="n">
-        <v>6814958</v>
+        <v>6814996</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,7 +6125,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605890</v>
+        <v>128605872</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -6168,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>448003</v>
+        <v>447594</v>
       </c>
       <c r="R57" t="n">
-        <v>6814939</v>
+        <v>6814977</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6327,10 +6319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605872</v>
+        <v>128605838</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,34 +6330,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447594</v>
+        <v>447770</v>
       </c>
       <c r="R59" t="n">
-        <v>6814977</v>
+        <v>6814909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128605892</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128605887</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128605829</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128605849</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128605833</v>
+        <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>78873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,42 +1771,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447771</v>
+        <v>447783</v>
       </c>
       <c r="R13" t="n">
-        <v>6814844</v>
+        <v>6814852</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,7 +1860,7 @@
         <v>128605837</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,10 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605852</v>
+        <v>128605833</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,34 +1973,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447783</v>
+        <v>447771</v>
       </c>
       <c r="R15" t="n">
-        <v>6814852</v>
+        <v>6814844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605832</v>
+        <v>128605853</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>78873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,42 +2078,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448062</v>
+        <v>447773</v>
       </c>
       <c r="R16" t="n">
-        <v>6815199</v>
+        <v>6814906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,7 +2167,7 @@
         <v>128605885</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2264,7 @@
         <v>128605888</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605853</v>
+        <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>78846</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2382,34 +2374,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447773</v>
+        <v>448062</v>
       </c>
       <c r="R19" t="n">
-        <v>6814906</v>
+        <v>6815199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128605840</v>
+        <v>128605868</v>
       </c>
       <c r="B20" t="n">
-        <v>80195</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,37 +2479,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447610</v>
+        <v>447751</v>
       </c>
       <c r="R20" t="n">
-        <v>6814943</v>
+        <v>6815024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,24 +2547,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2584,10 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605840</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>80222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,34 +2576,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447610</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6814943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2663,8 +2647,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2684,7 +2684,7 @@
         <v>128605854</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128605861</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128605865</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>128605873</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605879</v>
+        <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447664</v>
+        <v>447771</v>
       </c>
       <c r="R27" t="n">
-        <v>6814830</v>
+        <v>6814896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605862</v>
+        <v>128605879</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448085</v>
+        <v>447664</v>
       </c>
       <c r="R28" t="n">
-        <v>6815187</v>
+        <v>6814830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605835</v>
+        <v>128605862</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,42 +3376,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447581</v>
+        <v>448085</v>
       </c>
       <c r="R29" t="n">
-        <v>6814933</v>
+        <v>6815187</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3462,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605844</v>
+        <v>128605835</v>
       </c>
       <c r="B30" t="n">
-        <v>78847</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,34 +3473,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447771</v>
+        <v>447581</v>
       </c>
       <c r="R30" t="n">
-        <v>6814896</v>
+        <v>6814933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128605891</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605883</v>
+        <v>128605857</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447840</v>
+        <v>447992</v>
       </c>
       <c r="R47" t="n">
-        <v>6815052</v>
+        <v>6814945</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,11 +5221,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5252,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605877</v>
+        <v>128605883</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5287,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447607</v>
+        <v>447840</v>
       </c>
       <c r="R48" t="n">
-        <v>6814835</v>
+        <v>6815052</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5323,6 +5318,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605857</v>
+        <v>128605877</v>
       </c>
       <c r="B49" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447992</v>
+        <v>447607</v>
       </c>
       <c r="R49" t="n">
-        <v>6814945</v>
+        <v>6814835</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,7 +5449,7 @@
         <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>78873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605890</v>
+        <v>128605838</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448003</v>
+        <v>447770</v>
       </c>
       <c r="R54" t="n">
-        <v>6814939</v>
+        <v>6814909</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605884</v>
+        <v>128605871</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5966,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447831</v>
+        <v>447606</v>
       </c>
       <c r="R55" t="n">
-        <v>6815067</v>
+        <v>6814958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,10 +6036,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605870</v>
+        <v>128605890</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6063,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447670</v>
+        <v>448003</v>
       </c>
       <c r="R56" t="n">
-        <v>6814996</v>
+        <v>6814939</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605872</v>
+        <v>128605884</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6160,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447594</v>
+        <v>447831</v>
       </c>
       <c r="R57" t="n">
-        <v>6814977</v>
+        <v>6815067</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605851</v>
+        <v>128605870</v>
       </c>
       <c r="B58" t="n">
-        <v>78846</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,21 +6241,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6257,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447628</v>
+        <v>447670</v>
       </c>
       <c r="R58" t="n">
-        <v>6814833</v>
+        <v>6814996</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6319,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605838</v>
+        <v>128605872</v>
       </c>
       <c r="B59" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6330,42 +6338,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447770</v>
+        <v>447594</v>
       </c>
       <c r="R59" t="n">
-        <v>6814909</v>
+        <v>6814977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605881</v>
+        <v>128605841</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447753</v>
+        <v>447636</v>
       </c>
       <c r="R60" t="n">
-        <v>6814819</v>
+        <v>6814937</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605882</v>
+        <v>128605843</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447789</v>
+        <v>447744</v>
       </c>
       <c r="R61" t="n">
-        <v>6814910</v>
+        <v>6814896</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,11 +6592,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6623,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605880</v>
+        <v>128605881</v>
       </c>
       <c r="B62" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6658,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447716</v>
+        <v>447753</v>
       </c>
       <c r="R62" t="n">
-        <v>6814847</v>
+        <v>6814819</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605841</v>
+        <v>128605880</v>
       </c>
       <c r="B63" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447636</v>
+        <v>447716</v>
       </c>
       <c r="R63" t="n">
-        <v>6814937</v>
+        <v>6814847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6817,10 +6812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605843</v>
+        <v>128605882</v>
       </c>
       <c r="B64" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6823,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447744</v>
+        <v>447789</v>
       </c>
       <c r="R64" t="n">
-        <v>6814896</v>
+        <v>6814910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6888,6 +6883,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6917,7 +6917,7 @@
         <v>128629773</v>
       </c>
       <c r="B65" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605853</v>
+        <v>128605885</v>
       </c>
       <c r="B16" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447773</v>
+        <v>447840</v>
       </c>
       <c r="R16" t="n">
-        <v>6814906</v>
+        <v>6815104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605885</v>
+        <v>128605888</v>
       </c>
       <c r="B17" t="n">
         <v>79116</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447840</v>
+        <v>447929</v>
       </c>
       <c r="R17" t="n">
-        <v>6815104</v>
+        <v>6815007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,6 +2235,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2261,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605888</v>
+        <v>128605853</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2277,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2301,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447929</v>
+        <v>447773</v>
       </c>
       <c r="R18" t="n">
-        <v>6815007</v>
+        <v>6814906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2337,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,10 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605840</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>80222</v>
+        <v>78873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2576,37 +2576,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447610</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6814943</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,24 +2644,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2681,10 +2662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605854</v>
+        <v>128605840</v>
       </c>
       <c r="B22" t="n">
-        <v>78873</v>
+        <v>80222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,34 +2673,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447840</v>
+        <v>447610</v>
       </c>
       <c r="R22" t="n">
-        <v>6815042</v>
+        <v>6814943</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,8 +2744,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128605850</v>
+        <v>128605874</v>
       </c>
       <c r="B39" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447632</v>
+        <v>447564</v>
       </c>
       <c r="R39" t="n">
-        <v>6814941</v>
+        <v>6814901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128605874</v>
+        <v>128605850</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447564</v>
+        <v>447632</v>
       </c>
       <c r="R40" t="n">
-        <v>6814901</v>
+        <v>6814941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605851</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>78873</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447628</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814833</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605838</v>
+        <v>128605870</v>
       </c>
       <c r="B54" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,42 +5845,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447770</v>
+        <v>447670</v>
       </c>
       <c r="R54" t="n">
-        <v>6814909</v>
+        <v>6814996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,7 +5931,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605871</v>
+        <v>128605872</v>
       </c>
       <c r="B55" t="n">
         <v>79116</v>
@@ -5974,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447606</v>
+        <v>447594</v>
       </c>
       <c r="R55" t="n">
-        <v>6814958</v>
+        <v>6814977</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605890</v>
+        <v>128605851</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>78873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6039,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448003</v>
+        <v>447628</v>
       </c>
       <c r="R56" t="n">
-        <v>6814939</v>
+        <v>6814833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605884</v>
+        <v>128605838</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6144,34 +6136,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447831</v>
+        <v>447770</v>
       </c>
       <c r="R57" t="n">
-        <v>6815067</v>
+        <v>6814909</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605870</v>
+        <v>128605890</v>
       </c>
       <c r="B58" t="n">
         <v>79116</v>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447670</v>
+        <v>448003</v>
       </c>
       <c r="R58" t="n">
-        <v>6814996</v>
+        <v>6814939</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605872</v>
+        <v>128605884</v>
       </c>
       <c r="B59" t="n">
         <v>79116</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447594</v>
+        <v>447831</v>
       </c>
       <c r="R59" t="n">
-        <v>6814977</v>
+        <v>6815067</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605860</v>
+        <v>128605858</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448020</v>
+        <v>448017</v>
       </c>
       <c r="R2" t="n">
-        <v>6815080</v>
+        <v>6814944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605860</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>448020</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6815080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128605892</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128605887</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128605829</v>
       </c>
       <c r="B11" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128605849</v>
       </c>
       <c r="B12" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605837</v>
+        <v>128605833</v>
       </c>
       <c r="B14" t="n">
         <v>57713</v>
@@ -1890,7 +1890,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447740</v>
+        <v>447771</v>
       </c>
       <c r="R14" t="n">
-        <v>6814822</v>
+        <v>6814844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605833</v>
+        <v>128605837</v>
       </c>
       <c r="B15" t="n">
         <v>57713</v>
@@ -1995,7 +1995,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447771</v>
+        <v>447740</v>
       </c>
       <c r="R15" t="n">
-        <v>6814844</v>
+        <v>6814822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605885</v>
+        <v>128605853</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447840</v>
+        <v>447773</v>
       </c>
       <c r="R16" t="n">
-        <v>6815104</v>
+        <v>6814906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605888</v>
+        <v>128605832</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,34 +2175,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447929</v>
+        <v>448062</v>
       </c>
       <c r="R17" t="n">
-        <v>6815007</v>
+        <v>6815199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,11 +2243,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,10 +2269,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605853</v>
+        <v>128605885</v>
       </c>
       <c r="B18" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,21 +2280,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2301,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447773</v>
+        <v>447840</v>
       </c>
       <c r="R18" t="n">
-        <v>6814906</v>
+        <v>6815104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,10 +2366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605832</v>
+        <v>128605888</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,42 +2377,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448062</v>
+        <v>447929</v>
       </c>
       <c r="R19" t="n">
-        <v>6815199</v>
+        <v>6815007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R20" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B21" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R21" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,7 +2665,7 @@
         <v>128605840</v>
       </c>
       <c r="B22" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128605861</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>128605865</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>128605873</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>128605879</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>128605862</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128605891</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128605874</v>
+        <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447564</v>
+        <v>447632</v>
       </c>
       <c r="R39" t="n">
-        <v>6814901</v>
+        <v>6814941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128605850</v>
+        <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447632</v>
+        <v>447564</v>
       </c>
       <c r="R40" t="n">
-        <v>6814941</v>
+        <v>6814901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4561,7 +4561,7 @@
         <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B43" t="n">
-        <v>78873</v>
+        <v>78878</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4768,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R43" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605847</v>
+        <v>128605856</v>
       </c>
       <c r="B44" t="n">
-        <v>78874</v>
+        <v>78877</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448022</v>
+        <v>447950</v>
       </c>
       <c r="R44" t="n">
-        <v>6814932</v>
+        <v>6814974</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605857</v>
+        <v>128605877</v>
       </c>
       <c r="B47" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447992</v>
+        <v>447607</v>
       </c>
       <c r="R47" t="n">
-        <v>6814945</v>
+        <v>6814835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605883</v>
+        <v>128605857</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447840</v>
+        <v>447992</v>
       </c>
       <c r="R48" t="n">
-        <v>6815052</v>
+        <v>6814945</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,11 +5318,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5349,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605877</v>
+        <v>128605883</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5384,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447607</v>
+        <v>447840</v>
       </c>
       <c r="R49" t="n">
-        <v>6814835</v>
+        <v>6815052</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5420,6 +5415,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>79739</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79735</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>78877</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605870</v>
+        <v>128605838</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,34 +5845,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447670</v>
+        <v>447770</v>
       </c>
       <c r="R54" t="n">
-        <v>6814996</v>
+        <v>6814909</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605872</v>
+        <v>128605871</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5966,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447594</v>
+        <v>447606</v>
       </c>
       <c r="R55" t="n">
-        <v>6814977</v>
+        <v>6814958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,10 +6036,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605851</v>
+        <v>128605890</v>
       </c>
       <c r="B56" t="n">
-        <v>78873</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447628</v>
+        <v>448003</v>
       </c>
       <c r="R56" t="n">
-        <v>6814833</v>
+        <v>6814939</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605838</v>
+        <v>128605884</v>
       </c>
       <c r="B57" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,42 +6144,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447770</v>
+        <v>447831</v>
       </c>
       <c r="R57" t="n">
-        <v>6814909</v>
+        <v>6815067</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605890</v>
+        <v>128605870</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>448003</v>
+        <v>447670</v>
       </c>
       <c r="R58" t="n">
-        <v>6814939</v>
+        <v>6814996</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605884</v>
+        <v>128605872</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447831</v>
+        <v>447594</v>
       </c>
       <c r="R59" t="n">
-        <v>6815067</v>
+        <v>6814977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,7 +6427,7 @@
         <v>128605841</v>
       </c>
       <c r="B60" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>128605843</v>
       </c>
       <c r="B61" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128605881</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>128605880</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>128605882</v>
       </c>
       <c r="B64" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605860</v>
+        <v>128605839</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448020</v>
+        <v>447574</v>
       </c>
       <c r="R3" t="n">
-        <v>6815080</v>
+        <v>6814884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +851,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605869</v>
+        <v>128605860</v>
       </c>
       <c r="B4" t="n">
         <v>79120</v>
@@ -909,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447681</v>
+        <v>448020</v>
       </c>
       <c r="R4" t="n">
-        <v>6815015</v>
+        <v>6815080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605839</v>
+        <v>128605869</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447574</v>
+        <v>447681</v>
       </c>
       <c r="R5" t="n">
-        <v>6814884</v>
+        <v>6815015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605876</v>
+        <v>128605855</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447585</v>
+        <v>447946</v>
       </c>
       <c r="R6" t="n">
-        <v>6814852</v>
+        <v>6814990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605892</v>
+        <v>128605876</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447931</v>
+        <v>447585</v>
       </c>
       <c r="R7" t="n">
-        <v>6815092</v>
+        <v>6814852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605855</v>
+        <v>128605892</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447946</v>
+        <v>447931</v>
       </c>
       <c r="R8" t="n">
-        <v>6814990</v>
+        <v>6815092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1341,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605887</v>
+        <v>128605849</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447907</v>
+        <v>447655</v>
       </c>
       <c r="R10" t="n">
-        <v>6815070</v>
+        <v>6814988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R11" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R12" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605832</v>
+        <v>128605885</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,42 +2175,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448062</v>
+        <v>447840</v>
       </c>
       <c r="R17" t="n">
-        <v>6815199</v>
+        <v>6815104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2269,7 +2261,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605885</v>
+        <v>128605888</v>
       </c>
       <c r="B18" t="n">
         <v>79120</v>
@@ -2304,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447840</v>
+        <v>447929</v>
       </c>
       <c r="R18" t="n">
-        <v>6815104</v>
+        <v>6815007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2366,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605888</v>
+        <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2377,34 +2374,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447929</v>
+        <v>448062</v>
       </c>
       <c r="R19" t="n">
-        <v>6815007</v>
+        <v>6815199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,11 +2442,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128605854</v>
+        <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>80226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,34 +2479,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447840</v>
+        <v>447610</v>
       </c>
       <c r="R20" t="n">
-        <v>6815042</v>
+        <v>6814943</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,8 +2550,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2565,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2576,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2600,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2662,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605840</v>
+        <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>80226</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2673,37 +2692,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447610</v>
+        <v>447751</v>
       </c>
       <c r="R22" t="n">
-        <v>6814943</v>
+        <v>6815024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,24 +2760,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605844</v>
+        <v>128605879</v>
       </c>
       <c r="B27" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447771</v>
+        <v>447664</v>
       </c>
       <c r="R27" t="n">
-        <v>6814896</v>
+        <v>6814830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605879</v>
+        <v>128605862</v>
       </c>
       <c r="B28" t="n">
         <v>79120</v>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447664</v>
+        <v>448085</v>
       </c>
       <c r="R28" t="n">
-        <v>6814830</v>
+        <v>6815187</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605862</v>
+        <v>128605835</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448085</v>
+        <v>447581</v>
       </c>
       <c r="R29" t="n">
-        <v>6815187</v>
+        <v>6814933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605835</v>
+        <v>128605844</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3473,42 +3481,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447581</v>
+        <v>447771</v>
       </c>
       <c r="R30" t="n">
-        <v>6814933</v>
+        <v>6814896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R32" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3767,7 +3762,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605891</v>
+        <v>128605889</v>
       </c>
       <c r="B33" t="n">
         <v>79120</v>
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447935</v>
+        <v>447989</v>
       </c>
       <c r="R33" t="n">
-        <v>6815088</v>
+        <v>6814944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3842,7 +3837,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605830</v>
+        <v>128605891</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3875,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447941</v>
+        <v>447935</v>
       </c>
       <c r="R34" t="n">
-        <v>6814981</v>
+        <v>6815088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,6 +3935,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605894</v>
+        <v>128605856</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447910</v>
+        <v>447950</v>
       </c>
       <c r="R41" t="n">
-        <v>6815145</v>
+        <v>6814974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B42" t="n">
         <v>79120</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605847</v>
+        <v>128605893</v>
       </c>
       <c r="B43" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4763,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448022</v>
+        <v>447907</v>
       </c>
       <c r="R43" t="n">
-        <v>6814932</v>
+        <v>6815150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,6 +4823,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R44" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605877</v>
+        <v>128605857</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447607</v>
+        <v>447992</v>
       </c>
       <c r="R47" t="n">
-        <v>6814835</v>
+        <v>6814945</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605857</v>
+        <v>128605883</v>
       </c>
       <c r="B48" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447992</v>
+        <v>447840</v>
       </c>
       <c r="R48" t="n">
-        <v>6814945</v>
+        <v>6815052</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,6 +5318,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,7 +5349,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605883</v>
+        <v>128605877</v>
       </c>
       <c r="B49" t="n">
         <v>79120</v>
@@ -5379,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447840</v>
+        <v>447607</v>
       </c>
       <c r="R49" t="n">
-        <v>6815052</v>
+        <v>6814835</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5415,11 +5420,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605851</v>
+        <v>128605838</v>
       </c>
       <c r="B53" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5748,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447628</v>
+        <v>447770</v>
       </c>
       <c r="R53" t="n">
-        <v>6814833</v>
+        <v>6814909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5842,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605838</v>
+        <v>128605851</v>
       </c>
       <c r="B54" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5845,42 +5853,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447770</v>
+        <v>447628</v>
       </c>
       <c r="R54" t="n">
-        <v>6814909</v>
+        <v>6814833</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B2" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R2" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605839</v>
+        <v>128605860</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447574</v>
+        <v>448020</v>
       </c>
       <c r="R3" t="n">
-        <v>6814884</v>
+        <v>6815080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605860</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448020</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815080</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605869</v>
+        <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +982,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447681</v>
+        <v>447574</v>
       </c>
       <c r="R5" t="n">
-        <v>6815015</v>
+        <v>6814884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R6" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605876</v>
+        <v>128605855</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447585</v>
+        <v>447946</v>
       </c>
       <c r="R7" t="n">
-        <v>6814852</v>
+        <v>6814990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605829</v>
+        <v>128605887</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447634</v>
+        <v>447907</v>
       </c>
       <c r="R9" t="n">
-        <v>6814941</v>
+        <v>6815070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605849</v>
+        <v>128605886</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447655</v>
+        <v>447905</v>
       </c>
       <c r="R10" t="n">
-        <v>6814988</v>
+        <v>6815066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R11" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605887</v>
+        <v>128605849</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447907</v>
+        <v>447655</v>
       </c>
       <c r="R12" t="n">
-        <v>6815070</v>
+        <v>6814988</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605885</v>
+        <v>128605832</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,34 +2175,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447840</v>
+        <v>448062</v>
       </c>
       <c r="R17" t="n">
-        <v>6815104</v>
+        <v>6815199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,7 +2269,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B18" t="n">
         <v>79120</v>
@@ -2296,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R18" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2340,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605832</v>
+        <v>128605888</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,42 +2377,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448062</v>
+        <v>447929</v>
       </c>
       <c r="R19" t="n">
-        <v>6815199</v>
+        <v>6815007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B21" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R21" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R22" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B23" t="n">
         <v>79120</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R23" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2849,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,7 +2875,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605865</v>
+        <v>128605873</v>
       </c>
       <c r="B24" t="n">
         <v>79120</v>
@@ -2915,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447930</v>
+        <v>447570</v>
       </c>
       <c r="R24" t="n">
-        <v>6815173</v>
+        <v>6814915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,7 +2972,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B25" t="n">
         <v>79120</v>
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R25" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,7 +3069,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605863</v>
+        <v>128605861</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3109,10 +3104,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448048</v>
+        <v>448113</v>
       </c>
       <c r="R26" t="n">
-        <v>6815201</v>
+        <v>6815152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,6 +3140,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605830</v>
+        <v>128605891</v>
       </c>
       <c r="B32" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447941</v>
+        <v>447935</v>
       </c>
       <c r="R32" t="n">
-        <v>6814981</v>
+        <v>6815088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,10 +3767,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3773,21 +3778,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R33" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,11 +3838,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3864,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605891</v>
+        <v>128605889</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447935</v>
+        <v>447989</v>
       </c>
       <c r="R34" t="n">
-        <v>6815088</v>
+        <v>6814944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4063,7 +4063,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605878</v>
+        <v>128605867</v>
       </c>
       <c r="B36" t="n">
         <v>79120</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447619</v>
+        <v>447749</v>
       </c>
       <c r="R36" t="n">
-        <v>6814842</v>
+        <v>6815028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,6 +4134,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4160,7 +4165,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605867</v>
+        <v>128605866</v>
       </c>
       <c r="B37" t="n">
         <v>79120</v>
@@ -4195,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447749</v>
+        <v>447839</v>
       </c>
       <c r="R37" t="n">
-        <v>6815028</v>
+        <v>6815058</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4235,7 +4240,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4262,7 +4267,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128605866</v>
+        <v>128605878</v>
       </c>
       <c r="B38" t="n">
         <v>79120</v>
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447839</v>
+        <v>447619</v>
       </c>
       <c r="R38" t="n">
-        <v>6815058</v>
+        <v>6814842</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4333,11 +4338,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128605850</v>
+        <v>128605874</v>
       </c>
       <c r="B39" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447632</v>
+        <v>447564</v>
       </c>
       <c r="R39" t="n">
-        <v>6814941</v>
+        <v>6814901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128605874</v>
+        <v>128605850</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447564</v>
+        <v>447632</v>
       </c>
       <c r="R40" t="n">
-        <v>6814901</v>
+        <v>6814941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605856</v>
+        <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447950</v>
+        <v>447910</v>
       </c>
       <c r="R41" t="n">
-        <v>6814974</v>
+        <v>6815145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B42" t="n">
         <v>79120</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R42" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4752,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605893</v>
+        <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,21 +4768,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447907</v>
+        <v>447950</v>
       </c>
       <c r="R43" t="n">
-        <v>6815150</v>
+        <v>6814974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,11 +4828,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R45" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B46" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5059,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R46" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5124,6 +5119,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605857</v>
+        <v>128605883</v>
       </c>
       <c r="B47" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447992</v>
+        <v>447840</v>
       </c>
       <c r="R47" t="n">
-        <v>6814945</v>
+        <v>6815052</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,6 +5221,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,7 +5252,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605883</v>
+        <v>128605877</v>
       </c>
       <c r="B48" t="n">
         <v>79120</v>
@@ -5282,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447840</v>
+        <v>447607</v>
       </c>
       <c r="R48" t="n">
-        <v>6815052</v>
+        <v>6814835</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,11 +5323,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605877</v>
+        <v>128605857</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447607</v>
+        <v>447992</v>
       </c>
       <c r="R49" t="n">
-        <v>6814835</v>
+        <v>6814945</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605838</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447770</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814909</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605851</v>
+        <v>128605890</v>
       </c>
       <c r="B54" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5853,21 +5845,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447628</v>
+        <v>448003</v>
       </c>
       <c r="R54" t="n">
-        <v>6814833</v>
+        <v>6814939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,7 +5931,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605871</v>
+        <v>128605884</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -5974,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447606</v>
+        <v>447831</v>
       </c>
       <c r="R55" t="n">
-        <v>6814958</v>
+        <v>6815067</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605890</v>
+        <v>128605838</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,34 +6039,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448003</v>
+        <v>447770</v>
       </c>
       <c r="R56" t="n">
-        <v>6814939</v>
+        <v>6814909</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605884</v>
+        <v>128605851</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447831</v>
+        <v>447628</v>
       </c>
       <c r="R57" t="n">
-        <v>6815067</v>
+        <v>6814833</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605870</v>
+        <v>128605872</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447670</v>
+        <v>447594</v>
       </c>
       <c r="R58" t="n">
-        <v>6814996</v>
+        <v>6814977</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605872</v>
+        <v>128605870</v>
       </c>
       <c r="B59" t="n">
         <v>79120</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447594</v>
+        <v>447670</v>
       </c>
       <c r="R59" t="n">
-        <v>6814977</v>
+        <v>6814996</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605881</v>
+        <v>128605880</v>
       </c>
       <c r="B62" t="n">
         <v>79120</v>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447753</v>
+        <v>447716</v>
       </c>
       <c r="R62" t="n">
-        <v>6814819</v>
+        <v>6814847</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605880</v>
+        <v>128605882</v>
       </c>
       <c r="B63" t="n">
         <v>79120</v>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447716</v>
+        <v>447789</v>
       </c>
       <c r="R63" t="n">
-        <v>6814847</v>
+        <v>6814910</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6786,6 +6786,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6812,7 +6817,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605882</v>
+        <v>128605881</v>
       </c>
       <c r="B64" t="n">
         <v>79120</v>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447789</v>
+        <v>447753</v>
       </c>
       <c r="R64" t="n">
-        <v>6814910</v>
+        <v>6814819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6883,11 +6888,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605887</v>
+        <v>128605886</v>
       </c>
       <c r="B9" t="n">
         <v>79120</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447907</v>
+        <v>447905</v>
       </c>
       <c r="R9" t="n">
-        <v>6815070</v>
+        <v>6815066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605886</v>
+        <v>128605887</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447905</v>
+        <v>447907</v>
       </c>
       <c r="R10" t="n">
-        <v>6815066</v>
+        <v>6815070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605879</v>
+        <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447664</v>
+        <v>447771</v>
       </c>
       <c r="R27" t="n">
-        <v>6814830</v>
+        <v>6814896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605835</v>
+        <v>128605879</v>
       </c>
       <c r="B29" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,42 +3376,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447581</v>
+        <v>447664</v>
       </c>
       <c r="R29" t="n">
-        <v>6814933</v>
+        <v>6814830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3462,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605844</v>
+        <v>128605835</v>
       </c>
       <c r="B30" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,34 +3473,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447771</v>
+        <v>447581</v>
       </c>
       <c r="R30" t="n">
-        <v>6814896</v>
+        <v>6814933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605894</v>
+        <v>128605847</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447910</v>
+        <v>448022</v>
       </c>
       <c r="R41" t="n">
-        <v>6815145</v>
+        <v>6814932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B42" t="n">
         <v>79120</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605856</v>
+        <v>128605893</v>
       </c>
       <c r="B43" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4763,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447950</v>
+        <v>447907</v>
       </c>
       <c r="R43" t="n">
-        <v>6814974</v>
+        <v>6815150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,6 +4823,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605847</v>
+        <v>128605856</v>
       </c>
       <c r="B44" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448022</v>
+        <v>447950</v>
       </c>
       <c r="R44" t="n">
-        <v>6814932</v>
+        <v>6814974</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R45" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,6 +5022,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R46" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5119,11 +5124,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605883</v>
+        <v>128605857</v>
       </c>
       <c r="B47" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447840</v>
+        <v>447992</v>
       </c>
       <c r="R47" t="n">
-        <v>6815052</v>
+        <v>6814945</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,11 +5221,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5252,7 +5247,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605877</v>
+        <v>128605883</v>
       </c>
       <c r="B48" t="n">
         <v>79120</v>
@@ -5287,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447607</v>
+        <v>447840</v>
       </c>
       <c r="R48" t="n">
-        <v>6814835</v>
+        <v>6815052</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5323,6 +5318,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605857</v>
+        <v>128605877</v>
       </c>
       <c r="B49" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447992</v>
+        <v>447607</v>
       </c>
       <c r="R49" t="n">
-        <v>6814945</v>
+        <v>6814835</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605890</v>
+        <v>128605872</v>
       </c>
       <c r="B54" t="n">
         <v>79120</v>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448003</v>
+        <v>447594</v>
       </c>
       <c r="R54" t="n">
-        <v>6814939</v>
+        <v>6814977</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,7 +5931,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605884</v>
+        <v>128605870</v>
       </c>
       <c r="B55" t="n">
         <v>79120</v>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447831</v>
+        <v>447670</v>
       </c>
       <c r="R55" t="n">
-        <v>6815067</v>
+        <v>6814996</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6133,10 +6133,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605851</v>
+        <v>128605871</v>
       </c>
       <c r="B57" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447628</v>
+        <v>447606</v>
       </c>
       <c r="R57" t="n">
-        <v>6814833</v>
+        <v>6814958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605872</v>
+        <v>128605890</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447594</v>
+        <v>448003</v>
       </c>
       <c r="R58" t="n">
-        <v>6814977</v>
+        <v>6814939</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605870</v>
+        <v>128605884</v>
       </c>
       <c r="B59" t="n">
         <v>79120</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447670</v>
+        <v>447831</v>
       </c>
       <c r="R59" t="n">
-        <v>6814996</v>
+        <v>6815067</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605869</v>
+        <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447681</v>
+        <v>448020</v>
       </c>
       <c r="R2" t="n">
-        <v>6815015</v>
+        <v>6815080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605860</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448020</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6815080</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>128605855</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128605892</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605887</v>
+        <v>128605829</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447907</v>
+        <v>447634</v>
       </c>
       <c r="R10" t="n">
-        <v>6815070</v>
+        <v>6814941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605829</v>
+        <v>128605849</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447634</v>
+        <v>447655</v>
       </c>
       <c r="R11" t="n">
-        <v>6814941</v>
+        <v>6814988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R12" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>128605833</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>128605837</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605853</v>
+        <v>128605885</v>
       </c>
       <c r="B16" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447773</v>
+        <v>447840</v>
       </c>
       <c r="R16" t="n">
-        <v>6814906</v>
+        <v>6815104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605832</v>
+        <v>128605888</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,42 +2175,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448062</v>
+        <v>447929</v>
       </c>
       <c r="R17" t="n">
-        <v>6815199</v>
+        <v>6815007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,6 +2235,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605885</v>
+        <v>128605853</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2280,21 +2277,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2301,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447840</v>
+        <v>447773</v>
       </c>
       <c r="R18" t="n">
-        <v>6815104</v>
+        <v>6814906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605888</v>
+        <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2377,34 +2374,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447929</v>
+        <v>448062</v>
       </c>
       <c r="R19" t="n">
-        <v>6815007</v>
+        <v>6815199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2437,11 +2442,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,7 +2471,7 @@
         <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R22" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605863</v>
+        <v>128605861</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448048</v>
+        <v>448113</v>
       </c>
       <c r="R23" t="n">
-        <v>6815201</v>
+        <v>6815152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2875,10 +2880,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,10 +2915,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R24" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,10 +2977,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605865</v>
+        <v>128605873</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447930</v>
+        <v>447570</v>
       </c>
       <c r="R25" t="n">
-        <v>6815173</v>
+        <v>6814915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,10 +3074,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R26" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,11 +3145,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3174,7 +3174,7 @@
         <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605862</v>
+        <v>128605879</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448085</v>
+        <v>447664</v>
       </c>
       <c r="R28" t="n">
-        <v>6815187</v>
+        <v>6814830</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605879</v>
+        <v>128605862</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447664</v>
+        <v>448085</v>
       </c>
       <c r="R29" t="n">
-        <v>6814830</v>
+        <v>6815187</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
         <v>128605835</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605891</v>
+        <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447935</v>
+        <v>447989</v>
       </c>
       <c r="R32" t="n">
-        <v>6815088</v>
+        <v>6814944</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3770,7 +3770,7 @@
         <v>128605830</v>
       </c>
       <c r="B33" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605889</v>
+        <v>128605891</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447989</v>
+        <v>447935</v>
       </c>
       <c r="R34" t="n">
-        <v>6814944</v>
+        <v>6815088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3969,7 +3969,7 @@
         <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605867</v>
+        <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447749</v>
+        <v>447619</v>
       </c>
       <c r="R36" t="n">
-        <v>6815028</v>
+        <v>6814842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,11 +4134,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4165,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605866</v>
+        <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4200,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447839</v>
+        <v>447749</v>
       </c>
       <c r="R37" t="n">
-        <v>6815058</v>
+        <v>6815028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,7 +4235,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4267,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128605878</v>
+        <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447619</v>
+        <v>447839</v>
       </c>
       <c r="R38" t="n">
-        <v>6814842</v>
+        <v>6815058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4338,6 +4333,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128605874</v>
+        <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447564</v>
+        <v>447632</v>
       </c>
       <c r="R39" t="n">
-        <v>6814901</v>
+        <v>6814941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128605850</v>
+        <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447632</v>
+        <v>447564</v>
       </c>
       <c r="R40" t="n">
-        <v>6814941</v>
+        <v>6814901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605847</v>
+        <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448022</v>
+        <v>447910</v>
       </c>
       <c r="R41" t="n">
-        <v>6814932</v>
+        <v>6815145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R42" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4752,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605893</v>
+        <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,21 +4768,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447907</v>
+        <v>447950</v>
       </c>
       <c r="R43" t="n">
-        <v>6815150</v>
+        <v>6814974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,11 +4828,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R44" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605857</v>
+        <v>128605883</v>
       </c>
       <c r="B47" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447992</v>
+        <v>447840</v>
       </c>
       <c r="R47" t="n">
-        <v>6814945</v>
+        <v>6815052</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,6 +5221,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,10 +5252,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605883</v>
+        <v>128605877</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447840</v>
+        <v>447607</v>
       </c>
       <c r="R48" t="n">
-        <v>6815052</v>
+        <v>6814835</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,11 +5323,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605877</v>
+        <v>128605857</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447607</v>
+        <v>447992</v>
       </c>
       <c r="R49" t="n">
-        <v>6814835</v>
+        <v>6814945</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605851</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447628</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814833</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605872</v>
+        <v>128605890</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447594</v>
+        <v>448003</v>
       </c>
       <c r="R54" t="n">
-        <v>6814977</v>
+        <v>6814939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605870</v>
+        <v>128605851</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447670</v>
+        <v>447628</v>
       </c>
       <c r="R55" t="n">
-        <v>6814996</v>
+        <v>6814833</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605838</v>
+        <v>128605884</v>
       </c>
       <c r="B56" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,42 +6039,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447770</v>
+        <v>447831</v>
       </c>
       <c r="R56" t="n">
-        <v>6814909</v>
+        <v>6815067</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605871</v>
+        <v>128605870</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6168,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447606</v>
+        <v>447670</v>
       </c>
       <c r="R57" t="n">
-        <v>6814958</v>
+        <v>6814996</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605890</v>
+        <v>128605872</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6265,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>448003</v>
+        <v>447594</v>
       </c>
       <c r="R58" t="n">
-        <v>6814939</v>
+        <v>6814977</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605884</v>
+        <v>128605838</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,34 +6330,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447831</v>
+        <v>447770</v>
       </c>
       <c r="R59" t="n">
-        <v>6815067</v>
+        <v>6814909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,7 +6427,7 @@
         <v>128605841</v>
       </c>
       <c r="B60" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>128605843</v>
       </c>
       <c r="B61" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605880</v>
+        <v>128605881</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447716</v>
+        <v>447753</v>
       </c>
       <c r="R62" t="n">
-        <v>6814847</v>
+        <v>6814819</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605882</v>
+        <v>128605880</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6750,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447789</v>
+        <v>447716</v>
       </c>
       <c r="R63" t="n">
-        <v>6814910</v>
+        <v>6814847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6786,11 +6786,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,10 +6812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605881</v>
+        <v>128605882</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447753</v>
+        <v>447789</v>
       </c>
       <c r="R64" t="n">
-        <v>6814819</v>
+        <v>6814910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6888,6 +6883,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6917,7 +6917,7 @@
         <v>128629773</v>
       </c>
       <c r="B65" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605876</v>
+        <v>128605892</v>
       </c>
       <c r="B6" t="n">
         <v>79124</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447585</v>
+        <v>447931</v>
       </c>
       <c r="R6" t="n">
-        <v>6814852</v>
+        <v>6815092</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1147,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1189,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R7" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605892</v>
+        <v>128605855</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447931</v>
+        <v>447946</v>
       </c>
       <c r="R8" t="n">
-        <v>6815092</v>
+        <v>6814990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1341,11 +1346,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B10" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R10" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128605840</v>
+        <v>128605868</v>
       </c>
       <c r="B20" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,37 +2479,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447610</v>
+        <v>447751</v>
       </c>
       <c r="R20" t="n">
-        <v>6814943</v>
+        <v>6815024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,24 +2547,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2681,10 +2662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605868</v>
+        <v>128605840</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,34 +2673,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447751</v>
+        <v>447610</v>
       </c>
       <c r="R22" t="n">
-        <v>6815024</v>
+        <v>6814943</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,8 +2744,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2778,7 +2778,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B23" t="n">
         <v>79124</v>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R23" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,11 +2849,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2880,7 +2875,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605865</v>
+        <v>128605861</v>
       </c>
       <c r="B24" t="n">
         <v>79124</v>
@@ -2915,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447930</v>
+        <v>448113</v>
       </c>
       <c r="R24" t="n">
-        <v>6815173</v>
+        <v>6815152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,6 +2946,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B25" t="n">
         <v>79124</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R25" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605863</v>
+        <v>128605873</v>
       </c>
       <c r="B26" t="n">
         <v>79124</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448048</v>
+        <v>447570</v>
       </c>
       <c r="R26" t="n">
-        <v>6815201</v>
+        <v>6814915</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605844</v>
+        <v>128605862</v>
       </c>
       <c r="B27" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,21 +3182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447771</v>
+        <v>448085</v>
       </c>
       <c r="R27" t="n">
-        <v>6814896</v>
+        <v>6815187</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605862</v>
+        <v>128605835</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448085</v>
+        <v>447581</v>
       </c>
       <c r="R29" t="n">
-        <v>6815187</v>
+        <v>6814933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605835</v>
+        <v>128605844</v>
       </c>
       <c r="B30" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3473,42 +3481,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447581</v>
+        <v>447771</v>
       </c>
       <c r="R30" t="n">
-        <v>6814933</v>
+        <v>6814896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605830</v>
+        <v>128605891</v>
       </c>
       <c r="B33" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447941</v>
+        <v>447935</v>
       </c>
       <c r="R33" t="n">
-        <v>6814981</v>
+        <v>6815088</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,6 +3838,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3864,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605891</v>
+        <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3875,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447935</v>
+        <v>447941</v>
       </c>
       <c r="R34" t="n">
-        <v>6815088</v>
+        <v>6814981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,11 +3940,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4063,7 +4063,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605878</v>
+        <v>128605867</v>
       </c>
       <c r="B36" t="n">
         <v>79124</v>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447619</v>
+        <v>447749</v>
       </c>
       <c r="R36" t="n">
-        <v>6814842</v>
+        <v>6815028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,6 +4134,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4160,7 +4165,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605867</v>
+        <v>128605866</v>
       </c>
       <c r="B37" t="n">
         <v>79124</v>
@@ -4195,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447749</v>
+        <v>447839</v>
       </c>
       <c r="R37" t="n">
-        <v>6815028</v>
+        <v>6815058</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4235,7 +4240,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4262,7 +4267,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128605866</v>
+        <v>128605878</v>
       </c>
       <c r="B38" t="n">
         <v>79124</v>
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447839</v>
+        <v>447619</v>
       </c>
       <c r="R38" t="n">
-        <v>6815058</v>
+        <v>6814842</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4333,11 +4338,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4655,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605856</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4666,21 +4666,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447950</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6814974</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605856</v>
+        <v>128605893</v>
       </c>
       <c r="B43" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4763,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447950</v>
+        <v>447907</v>
       </c>
       <c r="R43" t="n">
-        <v>6814974</v>
+        <v>6815150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,6 +4823,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R45" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B46" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5059,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R46" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5124,6 +5119,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605838</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5748,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447770</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5842,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605890</v>
+        <v>128605871</v>
       </c>
       <c r="B54" t="n">
         <v>79124</v>
@@ -5869,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448003</v>
+        <v>447606</v>
       </c>
       <c r="R54" t="n">
-        <v>6814939</v>
+        <v>6814958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605851</v>
+        <v>128605890</v>
       </c>
       <c r="B55" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,21 +5950,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5966,10 +5974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447628</v>
+        <v>448003</v>
       </c>
       <c r="R55" t="n">
-        <v>6814833</v>
+        <v>6814939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,10 +6036,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605884</v>
+        <v>128605851</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447831</v>
+        <v>447628</v>
       </c>
       <c r="R56" t="n">
-        <v>6815067</v>
+        <v>6814833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605870</v>
+        <v>128605884</v>
       </c>
       <c r="B57" t="n">
         <v>79124</v>
@@ -6160,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447670</v>
+        <v>447831</v>
       </c>
       <c r="R57" t="n">
-        <v>6814996</v>
+        <v>6815067</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,7 +6230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605872</v>
+        <v>128605870</v>
       </c>
       <c r="B58" t="n">
         <v>79124</v>
@@ -6257,10 +6265,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447594</v>
+        <v>447670</v>
       </c>
       <c r="R58" t="n">
-        <v>6814977</v>
+        <v>6814996</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6319,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605838</v>
+        <v>128605872</v>
       </c>
       <c r="B59" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6330,42 +6338,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447770</v>
+        <v>447594</v>
       </c>
       <c r="R59" t="n">
-        <v>6814909</v>
+        <v>6814977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605841</v>
+        <v>128605881</v>
       </c>
       <c r="B60" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447636</v>
+        <v>447753</v>
       </c>
       <c r="R60" t="n">
-        <v>6814937</v>
+        <v>6814819</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605843</v>
+        <v>128605882</v>
       </c>
       <c r="B61" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447744</v>
+        <v>447789</v>
       </c>
       <c r="R61" t="n">
-        <v>6814896</v>
+        <v>6814910</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,6 +6592,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6618,7 +6623,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605881</v>
+        <v>128605880</v>
       </c>
       <c r="B62" t="n">
         <v>79124</v>
@@ -6653,10 +6658,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447753</v>
+        <v>447716</v>
       </c>
       <c r="R62" t="n">
-        <v>6814819</v>
+        <v>6814847</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6715,10 +6720,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605880</v>
+        <v>128605841</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,21 +6731,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447716</v>
+        <v>447636</v>
       </c>
       <c r="R63" t="n">
-        <v>6814847</v>
+        <v>6814937</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6812,10 +6817,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605882</v>
+        <v>128605843</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6823,21 +6828,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447789</v>
+        <v>447744</v>
       </c>
       <c r="R64" t="n">
-        <v>6814910</v>
+        <v>6814896</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6883,11 +6888,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605892</v>
+        <v>128605855</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447931</v>
+        <v>447946</v>
       </c>
       <c r="R6" t="n">
-        <v>6815092</v>
+        <v>6814990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1173,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605876</v>
+        <v>128605892</v>
       </c>
       <c r="B7" t="n">
         <v>79124</v>
@@ -1213,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447585</v>
+        <v>447931</v>
       </c>
       <c r="R7" t="n">
-        <v>6814852</v>
+        <v>6815092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1244,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R8" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R9" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605886</v>
+        <v>128605887</v>
       </c>
       <c r="B10" t="n">
         <v>79124</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447905</v>
+        <v>447907</v>
       </c>
       <c r="R10" t="n">
-        <v>6815066</v>
+        <v>6815070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605887</v>
+        <v>128605829</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447907</v>
+        <v>447634</v>
       </c>
       <c r="R12" t="n">
-        <v>6815070</v>
+        <v>6814941</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128605852</v>
+        <v>128605833</v>
       </c>
       <c r="B13" t="n">
-        <v>78881</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,34 +1771,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447783</v>
+        <v>447771</v>
       </c>
       <c r="R13" t="n">
-        <v>6814852</v>
+        <v>6814844</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1865,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605833</v>
+        <v>128605837</v>
       </c>
       <c r="B14" t="n">
         <v>57717</v>
@@ -1890,7 +1898,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1900,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447771</v>
+        <v>447740</v>
       </c>
       <c r="R14" t="n">
-        <v>6814844</v>
+        <v>6814822</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,10 +1970,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605837</v>
+        <v>128605852</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,42 +1981,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447740</v>
+        <v>447783</v>
       </c>
       <c r="R15" t="n">
-        <v>6814822</v>
+        <v>6814852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605885</v>
+        <v>128605853</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447840</v>
+        <v>447773</v>
       </c>
       <c r="R16" t="n">
-        <v>6815104</v>
+        <v>6814906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605853</v>
+        <v>128605885</v>
       </c>
       <c r="B18" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447773</v>
+        <v>447840</v>
       </c>
       <c r="R18" t="n">
-        <v>6814906</v>
+        <v>6815104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128605868</v>
+        <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,34 +2479,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447751</v>
+        <v>447610</v>
       </c>
       <c r="R20" t="n">
-        <v>6815024</v>
+        <v>6814943</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,8 +2550,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2565,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B21" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2576,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2600,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R21" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2662,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605840</v>
+        <v>128605854</v>
       </c>
       <c r="B22" t="n">
-        <v>80230</v>
+        <v>78881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2673,37 +2692,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447610</v>
+        <v>447840</v>
       </c>
       <c r="R22" t="n">
-        <v>6814943</v>
+        <v>6815042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2744,24 +2760,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2875,7 +2875,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605861</v>
+        <v>128605873</v>
       </c>
       <c r="B24" t="n">
         <v>79124</v>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448113</v>
+        <v>447570</v>
       </c>
       <c r="R24" t="n">
-        <v>6815152</v>
+        <v>6814915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,11 +2946,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,7 +3069,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605873</v>
+        <v>128605861</v>
       </c>
       <c r="B26" t="n">
         <v>79124</v>
@@ -3109,10 +3104,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447570</v>
+        <v>448113</v>
       </c>
       <c r="R26" t="n">
-        <v>6814915</v>
+        <v>6815152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,6 +3140,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605862</v>
+        <v>128605835</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,34 +3182,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448085</v>
+        <v>447581</v>
       </c>
       <c r="R27" t="n">
-        <v>6815187</v>
+        <v>6814933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,10 +3276,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605879</v>
+        <v>128605844</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3279,21 +3287,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3311,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447664</v>
+        <v>447771</v>
       </c>
       <c r="R28" t="n">
-        <v>6814830</v>
+        <v>6814896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605835</v>
+        <v>128605879</v>
       </c>
       <c r="B29" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,42 +3384,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447581</v>
+        <v>447664</v>
       </c>
       <c r="R29" t="n">
-        <v>6814933</v>
+        <v>6814830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605844</v>
+        <v>128605862</v>
       </c>
       <c r="B30" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447771</v>
+        <v>448085</v>
       </c>
       <c r="R30" t="n">
-        <v>6814896</v>
+        <v>6815187</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605889</v>
+        <v>128605846</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447989</v>
+        <v>448039</v>
       </c>
       <c r="R32" t="n">
-        <v>6814944</v>
+        <v>6814941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3869,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605830</v>
+        <v>128605889</v>
       </c>
       <c r="B34" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3875,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447941</v>
+        <v>447989</v>
       </c>
       <c r="R34" t="n">
-        <v>6814981</v>
+        <v>6814944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,6 +3935,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128605846</v>
+        <v>128605830</v>
       </c>
       <c r="B35" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448039</v>
+        <v>447941</v>
       </c>
       <c r="R35" t="n">
-        <v>6814941</v>
+        <v>6814981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605866</v>
+        <v>128605878</v>
       </c>
       <c r="B37" t="n">
         <v>79124</v>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447839</v>
+        <v>447619</v>
       </c>
       <c r="R37" t="n">
-        <v>6815058</v>
+        <v>6814842</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4236,11 +4236,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4267,7 +4262,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128605878</v>
+        <v>128605866</v>
       </c>
       <c r="B38" t="n">
         <v>79124</v>
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447619</v>
+        <v>447839</v>
       </c>
       <c r="R38" t="n">
-        <v>6814842</v>
+        <v>6815058</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4338,6 +4333,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128605850</v>
+        <v>128605874</v>
       </c>
       <c r="B39" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447632</v>
+        <v>447564</v>
       </c>
       <c r="R39" t="n">
-        <v>6814941</v>
+        <v>6814901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128605874</v>
+        <v>128605850</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447564</v>
+        <v>447632</v>
       </c>
       <c r="R40" t="n">
-        <v>6814901</v>
+        <v>6814941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605894</v>
+        <v>128605856</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447910</v>
+        <v>447950</v>
       </c>
       <c r="R41" t="n">
-        <v>6815145</v>
+        <v>6814974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605856</v>
+        <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4666,21 +4666,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447950</v>
+        <v>447907</v>
       </c>
       <c r="R42" t="n">
-        <v>6814974</v>
+        <v>6815150</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,6 +4726,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4752,7 +4757,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B43" t="n">
         <v>79124</v>
@@ -4787,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R43" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,11 +4828,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R45" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,6 +5022,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R46" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5119,11 +5124,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5150,7 +5150,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605883</v>
+        <v>128605877</v>
       </c>
       <c r="B47" t="n">
         <v>79124</v>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447840</v>
+        <v>447607</v>
       </c>
       <c r="R47" t="n">
-        <v>6815052</v>
+        <v>6814835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5221,11 +5221,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5252,7 +5247,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128605877</v>
+        <v>128605883</v>
       </c>
       <c r="B48" t="n">
         <v>79124</v>
@@ -5287,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447607</v>
+        <v>447840</v>
       </c>
       <c r="R48" t="n">
-        <v>6814835</v>
+        <v>6815052</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5323,6 +5318,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i grangrenarna inom en radie av 20 m.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605838</v>
+        <v>128605851</v>
       </c>
       <c r="B53" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447770</v>
+        <v>447628</v>
       </c>
       <c r="R53" t="n">
-        <v>6814909</v>
+        <v>6814833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,7 +5834,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605871</v>
+        <v>128605872</v>
       </c>
       <c r="B54" t="n">
         <v>79124</v>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447606</v>
+        <v>447594</v>
       </c>
       <c r="R54" t="n">
-        <v>6814958</v>
+        <v>6814977</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,7 +5931,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605890</v>
+        <v>128605870</v>
       </c>
       <c r="B55" t="n">
         <v>79124</v>
@@ -5974,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>448003</v>
+        <v>447670</v>
       </c>
       <c r="R55" t="n">
-        <v>6814939</v>
+        <v>6814996</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6036,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605851</v>
+        <v>128605884</v>
       </c>
       <c r="B56" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6047,21 +6039,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6071,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447628</v>
+        <v>447831</v>
       </c>
       <c r="R56" t="n">
-        <v>6814833</v>
+        <v>6815067</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6133,7 +6125,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605884</v>
+        <v>128605871</v>
       </c>
       <c r="B57" t="n">
         <v>79124</v>
@@ -6168,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447831</v>
+        <v>447606</v>
       </c>
       <c r="R57" t="n">
-        <v>6815067</v>
+        <v>6814958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,7 +6222,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605870</v>
+        <v>128605890</v>
       </c>
       <c r="B58" t="n">
         <v>79124</v>
@@ -6265,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447670</v>
+        <v>448003</v>
       </c>
       <c r="R58" t="n">
-        <v>6814996</v>
+        <v>6814939</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605872</v>
+        <v>128605838</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,34 +6330,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447594</v>
+        <v>447770</v>
       </c>
       <c r="R59" t="n">
-        <v>6814977</v>
+        <v>6814909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605839</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,34 +885,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>447574</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6814884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605839</v>
+        <v>128605869</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447574</v>
+        <v>447681</v>
       </c>
       <c r="R5" t="n">
-        <v>6814884</v>
+        <v>6815015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R6" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605892</v>
+        <v>128605855</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447931</v>
+        <v>447946</v>
       </c>
       <c r="R7" t="n">
-        <v>6815092</v>
+        <v>6814990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605876</v>
+        <v>128605892</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447585</v>
+        <v>447931</v>
       </c>
       <c r="R8" t="n">
-        <v>6814852</v>
+        <v>6815092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1341,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,7 +1375,7 @@
         <v>128605886</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605887</v>
+        <v>128605829</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447907</v>
+        <v>447634</v>
       </c>
       <c r="R10" t="n">
-        <v>6815070</v>
+        <v>6814941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,7 +1569,7 @@
         <v>128605849</v>
       </c>
       <c r="B11" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605829</v>
+        <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447634</v>
+        <v>447907</v>
       </c>
       <c r="R12" t="n">
-        <v>6814941</v>
+        <v>6815070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128605833</v>
+        <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,42 +1771,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447771</v>
+        <v>447783</v>
       </c>
       <c r="R13" t="n">
-        <v>6814844</v>
+        <v>6814852</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,10 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605837</v>
+        <v>128605833</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,7 +1890,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1908,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447740</v>
+        <v>447771</v>
       </c>
       <c r="R14" t="n">
-        <v>6814822</v>
+        <v>6814844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,10 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605852</v>
+        <v>128605837</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,34 +1973,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447783</v>
+        <v>447740</v>
       </c>
       <c r="R15" t="n">
-        <v>6814852</v>
+        <v>6814822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605853</v>
+        <v>128605888</v>
       </c>
       <c r="B16" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447773</v>
+        <v>447929</v>
       </c>
       <c r="R16" t="n">
-        <v>6814906</v>
+        <v>6815007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,6 +2138,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2164,10 +2169,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605888</v>
+        <v>128605853</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,21 +2180,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2199,10 +2204,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447929</v>
+        <v>447773</v>
       </c>
       <c r="R17" t="n">
-        <v>6815007</v>
+        <v>6814906</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,11 +2240,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605885</v>
+        <v>128605832</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,34 +2277,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447840</v>
+        <v>448062</v>
       </c>
       <c r="R18" t="n">
-        <v>6815104</v>
+        <v>6815199</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605832</v>
+        <v>128605885</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,42 +2382,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448062</v>
+        <v>447840</v>
       </c>
       <c r="R19" t="n">
-        <v>6815199</v>
+        <v>6815104</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
         <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R22" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605863</v>
+        <v>128605861</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448048</v>
+        <v>448113</v>
       </c>
       <c r="R23" t="n">
-        <v>6815201</v>
+        <v>6815152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2878,7 +2883,7 @@
         <v>128605873</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,7 +2980,7 @@
         <v>128605865</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3069,10 +3074,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R26" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,11 +3145,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605835</v>
+        <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,42 +3182,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447581</v>
+        <v>447771</v>
       </c>
       <c r="R27" t="n">
-        <v>6814933</v>
+        <v>6814896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605844</v>
+        <v>128605862</v>
       </c>
       <c r="B28" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,21 +3279,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447771</v>
+        <v>448085</v>
       </c>
       <c r="R28" t="n">
-        <v>6814896</v>
+        <v>6815187</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,7 +3368,7 @@
         <v>128605879</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,10 +3462,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605862</v>
+        <v>128605835</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,34 +3473,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448085</v>
+        <v>447581</v>
       </c>
       <c r="R30" t="n">
-        <v>6815187</v>
+        <v>6814933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605846</v>
+        <v>128605889</v>
       </c>
       <c r="B32" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448039</v>
+        <v>447989</v>
       </c>
       <c r="R32" t="n">
-        <v>6814941</v>
+        <v>6814944</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3765,7 +3770,7 @@
         <v>128605891</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3875,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R34" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3935,11 +3940,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128605830</v>
+        <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>79743</v>
+        <v>78787</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447941</v>
+        <v>448039</v>
       </c>
       <c r="R35" t="n">
-        <v>6814981</v>
+        <v>6814941</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605867</v>
+        <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447749</v>
+        <v>447619</v>
       </c>
       <c r="R36" t="n">
-        <v>6815028</v>
+        <v>6814842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,11 +4134,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4165,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605878</v>
+        <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4200,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447619</v>
+        <v>447749</v>
       </c>
       <c r="R37" t="n">
-        <v>6814842</v>
+        <v>6815028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4236,6 +4231,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4265,7 +4265,7 @@
         <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>128605874</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>128605850</v>
       </c>
       <c r="B40" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605856</v>
+        <v>128605894</v>
       </c>
       <c r="B41" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447950</v>
+        <v>447910</v>
       </c>
       <c r="R41" t="n">
-        <v>6814974</v>
+        <v>6815145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4658,7 +4658,7 @@
         <v>128605893</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605894</v>
+        <v>128605856</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,21 +4768,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447910</v>
+        <v>447950</v>
       </c>
       <c r="R43" t="n">
-        <v>6815145</v>
+        <v>6814974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
         <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>128605877</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>128605883</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>128605857</v>
       </c>
       <c r="B49" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605851</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447628</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814833</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605872</v>
+        <v>128605890</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447594</v>
+        <v>448003</v>
       </c>
       <c r="R54" t="n">
-        <v>6814977</v>
+        <v>6814939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
         <v>128605870</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605884</v>
+        <v>128605872</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447831</v>
+        <v>447594</v>
       </c>
       <c r="R56" t="n">
-        <v>6815067</v>
+        <v>6814977</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,21 +6136,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R57" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605890</v>
+        <v>128605884</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>448003</v>
+        <v>447831</v>
       </c>
       <c r="R58" t="n">
-        <v>6814939</v>
+        <v>6815067</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
         <v>128605838</v>
       </c>
       <c r="B59" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>128605881</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605882</v>
+        <v>128605880</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447789</v>
+        <v>447716</v>
       </c>
       <c r="R61" t="n">
-        <v>6814910</v>
+        <v>6814847</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,11 +6592,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6623,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605880</v>
+        <v>128605882</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6658,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447716</v>
+        <v>447789</v>
       </c>
       <c r="R62" t="n">
-        <v>6814847</v>
+        <v>6814910</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6694,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6723,7 +6723,7 @@
         <v>128605841</v>
       </c>
       <c r="B63" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128605843</v>
       </c>
       <c r="B64" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>128629773</v>
       </c>
       <c r="B65" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605839</v>
+        <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447574</v>
+        <v>448020</v>
       </c>
       <c r="R2" t="n">
-        <v>6814884</v>
+        <v>6815080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605860</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448020</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6815080</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605869</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447681</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815015</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605858</v>
+        <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +982,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448017</v>
+        <v>447574</v>
       </c>
       <c r="R5" t="n">
-        <v>6814944</v>
+        <v>6814884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>128605855</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605892</v>
+        <v>128605876</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447931</v>
+        <v>447585</v>
       </c>
       <c r="R7" t="n">
-        <v>6815092</v>
+        <v>6814852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128605876</v>
+        <v>128605892</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447585</v>
+        <v>447931</v>
       </c>
       <c r="R8" t="n">
-        <v>6814852</v>
+        <v>6815092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1341,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605887</v>
+        <v>128605849</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447907</v>
+        <v>447655</v>
       </c>
       <c r="R10" t="n">
-        <v>6815070</v>
+        <v>6814988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605829</v>
+        <v>128605886</v>
       </c>
       <c r="B11" t="n">
-        <v>79648</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447634</v>
+        <v>447905</v>
       </c>
       <c r="R11" t="n">
-        <v>6814941</v>
+        <v>6815066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R12" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605832</v>
+        <v>128605853</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>78791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,42 +2078,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448062</v>
+        <v>447773</v>
       </c>
       <c r="R16" t="n">
-        <v>6815199</v>
+        <v>6814906</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2207,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R17" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,11 +2235,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2274,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605885</v>
+        <v>128605888</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2309,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447840</v>
+        <v>447929</v>
       </c>
       <c r="R18" t="n">
-        <v>6815104</v>
+        <v>6815007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2371,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605853</v>
+        <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2382,34 +2374,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447773</v>
+        <v>448062</v>
       </c>
       <c r="R19" t="n">
-        <v>6814906</v>
+        <v>6815199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
         <v>128605840</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R22" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128605863</v>
+        <v>128605861</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448048</v>
+        <v>448113</v>
       </c>
       <c r="R23" t="n">
-        <v>6815201</v>
+        <v>6815152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,6 +2849,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2875,10 +2880,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,10 +2915,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R24" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2972,10 +2977,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605865</v>
+        <v>128605873</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447930</v>
+        <v>447570</v>
       </c>
       <c r="R25" t="n">
-        <v>6815173</v>
+        <v>6814915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,10 +3074,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605861</v>
+        <v>128605863</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448113</v>
+        <v>448048</v>
       </c>
       <c r="R26" t="n">
-        <v>6815152</v>
+        <v>6815201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,11 +3145,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605835</v>
+        <v>128605879</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,42 +3182,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447581</v>
+        <v>447664</v>
       </c>
       <c r="R27" t="n">
-        <v>6814933</v>
+        <v>6814830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605844</v>
+        <v>128605862</v>
       </c>
       <c r="B28" t="n">
-        <v>78787</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,21 +3279,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3311,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447771</v>
+        <v>448085</v>
       </c>
       <c r="R28" t="n">
-        <v>6814896</v>
+        <v>6815187</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128605879</v>
+        <v>128605835</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447664</v>
+        <v>447581</v>
       </c>
       <c r="R29" t="n">
-        <v>6814830</v>
+        <v>6814933</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128605862</v>
+        <v>128605844</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>78792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448085</v>
+        <v>447771</v>
       </c>
       <c r="R30" t="n">
-        <v>6815187</v>
+        <v>6814896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3570,7 +3570,7 @@
         <v>128605859</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605846</v>
+        <v>128605830</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>79653</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448039</v>
+        <v>447941</v>
       </c>
       <c r="R32" t="n">
-        <v>6814941</v>
+        <v>6814981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605891</v>
+        <v>128605889</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447935</v>
+        <v>447989</v>
       </c>
       <c r="R33" t="n">
-        <v>6815088</v>
+        <v>6814944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605889</v>
+        <v>128605891</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447989</v>
+        <v>447935</v>
       </c>
       <c r="R34" t="n">
-        <v>6814944</v>
+        <v>6815088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128605830</v>
+        <v>128605846</v>
       </c>
       <c r="B35" t="n">
-        <v>79648</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447941</v>
+        <v>448039</v>
       </c>
       <c r="R35" t="n">
-        <v>6814981</v>
+        <v>6814941</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128605867</v>
+        <v>128605878</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447749</v>
+        <v>447619</v>
       </c>
       <c r="R36" t="n">
-        <v>6815028</v>
+        <v>6814842</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4134,11 +4134,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4165,10 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128605878</v>
+        <v>128605867</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4200,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447619</v>
+        <v>447749</v>
       </c>
       <c r="R37" t="n">
-        <v>6814842</v>
+        <v>6815028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4236,6 +4231,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4265,7 +4265,7 @@
         <v>128605866</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605847</v>
+        <v>128605856</v>
       </c>
       <c r="B41" t="n">
-        <v>78787</v>
+        <v>78791</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448022</v>
+        <v>447950</v>
       </c>
       <c r="R41" t="n">
-        <v>6814932</v>
+        <v>6814974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R43" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,6 +4823,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B44" t="n">
-        <v>78786</v>
+        <v>78792</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R44" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>128605842</v>
       </c>
       <c r="B45" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>128605864</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128605877</v>
+        <v>128605857</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447607</v>
+        <v>447992</v>
       </c>
       <c r="R47" t="n">
-        <v>6814835</v>
+        <v>6814945</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5250,7 +5250,7 @@
         <v>128605883</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128605857</v>
+        <v>128605877</v>
       </c>
       <c r="B49" t="n">
-        <v>78786</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447992</v>
+        <v>447607</v>
       </c>
       <c r="R49" t="n">
-        <v>6814945</v>
+        <v>6814835</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>79653</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79648</v>
+        <v>79034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
         <v>128605845</v>
       </c>
       <c r="B52" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605838</v>
+        <v>128605851</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>78791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447770</v>
+        <v>447628</v>
       </c>
       <c r="R53" t="n">
-        <v>6814909</v>
+        <v>6814833</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,10 +5834,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605872</v>
+        <v>128605871</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5877,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447594</v>
+        <v>447606</v>
       </c>
       <c r="R54" t="n">
-        <v>6814977</v>
+        <v>6814958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5939,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605870</v>
+        <v>128605890</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5974,10 +5966,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447670</v>
+        <v>448003</v>
       </c>
       <c r="R55" t="n">
-        <v>6814996</v>
+        <v>6814939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6039,7 +6031,7 @@
         <v>128605884</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6133,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605871</v>
+        <v>128605870</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6168,10 +6160,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447606</v>
+        <v>447670</v>
       </c>
       <c r="R57" t="n">
-        <v>6814958</v>
+        <v>6814996</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6230,10 +6222,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605890</v>
+        <v>128605872</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6265,10 +6257,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>448003</v>
+        <v>447594</v>
       </c>
       <c r="R58" t="n">
-        <v>6814939</v>
+        <v>6814977</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605851</v>
+        <v>128605838</v>
       </c>
       <c r="B59" t="n">
-        <v>78786</v>
+        <v>57720</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,34 +6330,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447628</v>
+        <v>447770</v>
       </c>
       <c r="R59" t="n">
-        <v>6814833</v>
+        <v>6814909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6427,7 +6427,7 @@
         <v>128605881</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605882</v>
+        <v>128605880</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447789</v>
+        <v>447716</v>
       </c>
       <c r="R61" t="n">
-        <v>6814910</v>
+        <v>6814847</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6592,11 +6592,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6623,10 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605880</v>
+        <v>128605882</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6658,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447716</v>
+        <v>447789</v>
       </c>
       <c r="R62" t="n">
-        <v>6814847</v>
+        <v>6814910</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6694,6 +6689,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6723,7 +6723,7 @@
         <v>128605841</v>
       </c>
       <c r="B63" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>128605843</v>
       </c>
       <c r="B64" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -20065,10 +20065,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125793</v>
+        <v>129125725</v>
       </c>
       <c r="B187" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20076,21 +20076,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>447819</v>
+        <v>448124</v>
       </c>
       <c r="R187" t="n">
-        <v>6814842</v>
+        <v>6815167</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20172,7 +20172,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129125783</v>
+        <v>129125793</v>
       </c>
       <c r="B188" t="n">
         <v>79034</v>
@@ -20207,10 +20207,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>447952</v>
+        <v>447819</v>
       </c>
       <c r="R188" t="n">
-        <v>6814960</v>
+        <v>6814842</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20279,10 +20279,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125896</v>
+        <v>129125784</v>
       </c>
       <c r="B189" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20290,39 +20290,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>447925</v>
+        <v>447943</v>
       </c>
       <c r="R189" t="n">
-        <v>6815105</v>
+        <v>6814947</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20354,7 +20349,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20364,7 +20359,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20391,7 +20386,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129125815</v>
+        <v>129125783</v>
       </c>
       <c r="B190" t="n">
         <v>79034</v>
@@ -20426,10 +20421,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>447586</v>
+        <v>447952</v>
       </c>
       <c r="R190" t="n">
-        <v>6814809</v>
+        <v>6814960</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20461,7 +20456,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20471,7 +20466,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20498,10 +20493,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129125829</v>
+        <v>129125896</v>
       </c>
       <c r="B191" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20509,34 +20504,39 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>447771</v>
+        <v>447925</v>
       </c>
       <c r="R191" t="n">
-        <v>6815000</v>
+        <v>6815105</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20568,7 +20568,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20605,32 +20605,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129125736</v>
+        <v>129125815</v>
       </c>
       <c r="B192" t="n">
-        <v>80043</v>
+        <v>79034</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20640,10 +20640,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>447803</v>
+        <v>447586</v>
       </c>
       <c r="R192" t="n">
-        <v>6815004</v>
+        <v>6814809</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20685,7 +20685,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20712,10 +20712,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129125725</v>
+        <v>129125829</v>
       </c>
       <c r="B193" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20723,21 +20723,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20747,10 +20747,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>448124</v>
+        <v>447771</v>
       </c>
       <c r="R193" t="n">
-        <v>6815167</v>
+        <v>6815000</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20782,7 +20782,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20819,32 +20819,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129125784</v>
+        <v>129125736</v>
       </c>
       <c r="B194" t="n">
-        <v>79034</v>
+        <v>80043</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20854,10 +20854,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>447943</v>
+        <v>447803</v>
       </c>
       <c r="R194" t="n">
-        <v>6814947</v>
+        <v>6815004</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20926,7 +20926,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125893</v>
+        <v>129125857</v>
       </c>
       <c r="B195" t="n">
         <v>79034</v>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447992</v>
+        <v>447909</v>
       </c>
       <c r="R195" t="n">
-        <v>6815102</v>
+        <v>6815011</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21033,32 +21033,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129125866</v>
+        <v>129125898</v>
       </c>
       <c r="B196" t="n">
-        <v>79034</v>
+        <v>92811</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>448062</v>
+        <v>447585</v>
       </c>
       <c r="R196" t="n">
-        <v>6815224</v>
+        <v>6814810</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21140,7 +21140,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125890</v>
+        <v>129125834</v>
       </c>
       <c r="B197" t="n">
         <v>79034</v>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>448015</v>
+        <v>447788</v>
       </c>
       <c r="R197" t="n">
-        <v>6815065</v>
+        <v>6814995</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,7 +21247,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125857</v>
+        <v>129125847</v>
       </c>
       <c r="B198" t="n">
         <v>79034</v>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>447909</v>
+        <v>447814</v>
       </c>
       <c r="R198" t="n">
-        <v>6815011</v>
+        <v>6815081</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,32 +21354,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125898</v>
+        <v>129125819</v>
       </c>
       <c r="B199" t="n">
-        <v>92811</v>
+        <v>79034</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>447585</v>
+        <v>447647</v>
       </c>
       <c r="R199" t="n">
-        <v>6814810</v>
+        <v>6815013</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,7 +21461,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125834</v>
+        <v>129125893</v>
       </c>
       <c r="B200" t="n">
         <v>79034</v>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447788</v>
+        <v>447992</v>
       </c>
       <c r="R200" t="n">
-        <v>6814995</v>
+        <v>6815102</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21568,7 +21568,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129125847</v>
+        <v>129125866</v>
       </c>
       <c r="B201" t="n">
         <v>79034</v>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>447814</v>
+        <v>448062</v>
       </c>
       <c r="R201" t="n">
-        <v>6815081</v>
+        <v>6815224</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21675,7 +21675,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129125819</v>
+        <v>129125890</v>
       </c>
       <c r="B202" t="n">
         <v>79034</v>
@@ -21710,10 +21710,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>447647</v>
+        <v>448015</v>
       </c>
       <c r="R202" t="n">
-        <v>6815013</v>
+        <v>6815065</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21782,7 +21782,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129125881</v>
+        <v>129125856</v>
       </c>
       <c r="B203" t="n">
         <v>79034</v>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>448111</v>
+        <v>447906</v>
       </c>
       <c r="R203" t="n">
-        <v>6815099</v>
+        <v>6814985</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21889,7 +21889,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129125788</v>
+        <v>129125864</v>
       </c>
       <c r="B204" t="n">
         <v>79034</v>
@@ -21924,10 +21924,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>447870</v>
+        <v>448025</v>
       </c>
       <c r="R204" t="n">
-        <v>6814898</v>
+        <v>6815228</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21996,7 +21996,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129125875</v>
+        <v>129125881</v>
       </c>
       <c r="B205" t="n">
         <v>79034</v>
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>448141</v>
+        <v>448111</v>
       </c>
       <c r="R205" t="n">
-        <v>6815210</v>
+        <v>6815099</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22103,7 +22103,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129125892</v>
+        <v>129125788</v>
       </c>
       <c r="B206" t="n">
         <v>79034</v>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>448002</v>
+        <v>447870</v>
       </c>
       <c r="R206" t="n">
-        <v>6815094</v>
+        <v>6814898</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22210,7 +22210,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129125856</v>
+        <v>129125875</v>
       </c>
       <c r="B207" t="n">
         <v>79034</v>
@@ -22245,10 +22245,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>447906</v>
+        <v>448141</v>
       </c>
       <c r="R207" t="n">
-        <v>6814985</v>
+        <v>6815210</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22317,7 +22317,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129125864</v>
+        <v>129125892</v>
       </c>
       <c r="B208" t="n">
         <v>79034</v>
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>448025</v>
+        <v>448002</v>
       </c>
       <c r="R208" t="n">
-        <v>6815228</v>
+        <v>6815094</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22387,7 +22387,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23173,10 +23173,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129125789</v>
+        <v>129125733</v>
       </c>
       <c r="B216" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23184,34 +23184,39 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>447869</v>
+        <v>447785</v>
       </c>
       <c r="R216" t="n">
-        <v>6814887</v>
+        <v>6814977</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23243,7 +23248,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23253,7 +23258,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23280,10 +23285,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129125733</v>
+        <v>129125848</v>
       </c>
       <c r="B217" t="n">
-        <v>57883</v>
+        <v>79034</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23291,39 +23296,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>447785</v>
+        <v>447816</v>
       </c>
       <c r="R217" t="n">
-        <v>6814977</v>
+        <v>6815066</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23355,7 +23355,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23392,7 +23392,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129125848</v>
+        <v>129125871</v>
       </c>
       <c r="B218" t="n">
         <v>79034</v>
@@ -23427,10 +23427,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>447816</v>
+        <v>448138</v>
       </c>
       <c r="R218" t="n">
-        <v>6815066</v>
+        <v>6815238</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23499,7 +23499,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129125871</v>
+        <v>129125782</v>
       </c>
       <c r="B219" t="n">
         <v>79034</v>
@@ -23534,10 +23534,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>448138</v>
+        <v>447951</v>
       </c>
       <c r="R219" t="n">
-        <v>6815238</v>
+        <v>6814973</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23569,7 +23569,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23606,7 +23606,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129125782</v>
+        <v>129125774</v>
       </c>
       <c r="B220" t="n">
         <v>79034</v>
@@ -23641,10 +23641,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>447951</v>
+        <v>447907</v>
       </c>
       <c r="R220" t="n">
-        <v>6814973</v>
+        <v>6815056</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23676,7 +23676,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23713,7 +23713,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129125774</v>
+        <v>129125838</v>
       </c>
       <c r="B221" t="n">
         <v>79034</v>
@@ -23748,10 +23748,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>447907</v>
+        <v>447808</v>
       </c>
       <c r="R221" t="n">
-        <v>6815056</v>
+        <v>6815019</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23783,7 +23783,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23793,7 +23793,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23820,7 +23820,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129125838</v>
+        <v>129125822</v>
       </c>
       <c r="B222" t="n">
         <v>79034</v>
@@ -23855,10 +23855,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>447808</v>
+        <v>447745</v>
       </c>
       <c r="R222" t="n">
-        <v>6815019</v>
+        <v>6815055</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23900,7 +23900,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23927,7 +23927,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129125822</v>
+        <v>129125789</v>
       </c>
       <c r="B223" t="n">
         <v>79034</v>
@@ -23962,10 +23962,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>447745</v>
+        <v>447869</v>
       </c>
       <c r="R223" t="n">
-        <v>6815055</v>
+        <v>6814887</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD223" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605860</v>
+        <v>128605858</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448020</v>
+        <v>448017</v>
       </c>
       <c r="R2" t="n">
-        <v>6815080</v>
+        <v>6814944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605860</v>
       </c>
       <c r="B3" t="n">
         <v>79034</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>448020</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6815080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605869</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>447681</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6815015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605833</v>
+        <v>128605837</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -1890,7 +1890,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447771</v>
+        <v>447740</v>
       </c>
       <c r="R14" t="n">
-        <v>6814844</v>
+        <v>6814822</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605837</v>
+        <v>128605833</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -1995,7 +1995,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447740</v>
+        <v>447771</v>
       </c>
       <c r="R15" t="n">
-        <v>6814822</v>
+        <v>6814844</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605885</v>
+        <v>128605832</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2175,34 +2175,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447840</v>
+        <v>448062</v>
       </c>
       <c r="R17" t="n">
-        <v>6815104</v>
+        <v>6815199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,7 +2269,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B18" t="n">
         <v>79034</v>
@@ -2296,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R18" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2340,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605832</v>
+        <v>128605888</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,42 +2377,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448062</v>
+        <v>447929</v>
       </c>
       <c r="R19" t="n">
-        <v>6815199</v>
+        <v>6815007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,6 +2437,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2468,10 +2468,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128605840</v>
+        <v>128605868</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,37 +2479,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447610</v>
+        <v>447751</v>
       </c>
       <c r="R20" t="n">
-        <v>6814943</v>
+        <v>6815024</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,24 +2547,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2584,10 +2565,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605854</v>
+        <v>128605840</v>
       </c>
       <c r="B21" t="n">
-        <v>78791</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,34 +2576,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447840</v>
+        <v>447610</v>
       </c>
       <c r="R21" t="n">
-        <v>6815042</v>
+        <v>6814943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2663,8 +2647,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R22" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B45" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R45" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,6 +5022,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R46" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5119,11 +5124,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B50" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R50" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R51" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605881</v>
+        <v>128605843</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447753</v>
+        <v>447744</v>
       </c>
       <c r="R60" t="n">
-        <v>6814819</v>
+        <v>6814896</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605880</v>
+        <v>128605881</v>
       </c>
       <c r="B61" t="n">
         <v>79034</v>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447716</v>
+        <v>447753</v>
       </c>
       <c r="R61" t="n">
-        <v>6814847</v>
+        <v>6814819</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605882</v>
+        <v>128605880</v>
       </c>
       <c r="B62" t="n">
         <v>79034</v>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447789</v>
+        <v>447716</v>
       </c>
       <c r="R62" t="n">
-        <v>6814910</v>
+        <v>6814847</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6689,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605841</v>
+        <v>128605882</v>
       </c>
       <c r="B63" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447636</v>
+        <v>447789</v>
       </c>
       <c r="R63" t="n">
-        <v>6814937</v>
+        <v>6814910</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6791,6 +6786,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6817,7 +6817,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605843</v>
+        <v>128605841</v>
       </c>
       <c r="B64" t="n">
         <v>78792</v>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447744</v>
+        <v>447636</v>
       </c>
       <c r="R64" t="n">
-        <v>6814896</v>
+        <v>6814937</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129125764</v>
+        <v>129125766</v>
       </c>
       <c r="B66" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447872</v>
+        <v>447807</v>
       </c>
       <c r="R66" t="n">
-        <v>6814907</v>
+        <v>6814825</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7095,7 +7095,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På minst 250-årig tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7229,10 +7234,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129125766</v>
+        <v>129125764</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7240,21 +7245,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7264,10 +7269,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447807</v>
+        <v>447872</v>
       </c>
       <c r="R68" t="n">
-        <v>6814825</v>
+        <v>6814907</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7299,7 +7304,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7309,12 +7314,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På minst 250-årig tall</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129125843</v>
+        <v>129125755</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,21 +7352,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447812</v>
+        <v>447756</v>
       </c>
       <c r="R69" t="n">
-        <v>6815055</v>
+        <v>6814990</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7430,6 +7430,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7448,10 +7449,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129125755</v>
+        <v>129125798</v>
       </c>
       <c r="B70" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7459,21 +7460,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7483,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447756</v>
+        <v>447786</v>
       </c>
       <c r="R70" t="n">
-        <v>6814990</v>
+        <v>6814897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7518,7 +7519,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7528,7 +7529,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7537,7 +7538,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125798</v>
+        <v>129125821</v>
       </c>
       <c r="B71" t="n">
         <v>79034</v>
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447786</v>
+        <v>447754</v>
       </c>
       <c r="R71" t="n">
-        <v>6814897</v>
+        <v>6815052</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7663,7 +7663,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125821</v>
+        <v>129125787</v>
       </c>
       <c r="B72" t="n">
         <v>79034</v>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447754</v>
+        <v>447908</v>
       </c>
       <c r="R72" t="n">
-        <v>6815052</v>
+        <v>6814933</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7770,10 +7770,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125738</v>
+        <v>129125812</v>
       </c>
       <c r="B73" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7781,39 +7781,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447735</v>
+        <v>447682</v>
       </c>
       <c r="R73" t="n">
-        <v>6814890</v>
+        <v>6814779</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7845,7 +7840,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7855,12 +7850,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7887,7 +7877,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129125787</v>
+        <v>129125843</v>
       </c>
       <c r="B74" t="n">
         <v>79034</v>
@@ -7922,10 +7912,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447908</v>
+        <v>447812</v>
       </c>
       <c r="R74" t="n">
-        <v>6814933</v>
+        <v>6815055</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7957,7 +7947,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7967,7 +7957,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8101,50 +8091,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129125732</v>
+        <v>129125752</v>
       </c>
       <c r="B76" t="n">
-        <v>56913</v>
+        <v>81019</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447785</v>
+        <v>447893</v>
       </c>
       <c r="R76" t="n">
-        <v>6814990</v>
+        <v>6814914</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8176,7 +8161,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8186,7 +8171,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8213,10 +8198,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129125752</v>
+        <v>129125738</v>
       </c>
       <c r="B77" t="n">
-        <v>81019</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8224,34 +8209,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447893</v>
+        <v>447735</v>
       </c>
       <c r="R77" t="n">
-        <v>6814914</v>
+        <v>6814890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8283,7 +8273,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8293,7 +8283,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8320,45 +8315,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129125812</v>
+        <v>129125732</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>56913</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447682</v>
+        <v>447785</v>
       </c>
       <c r="R78" t="n">
-        <v>6814779</v>
+        <v>6814990</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8427,10 +8427,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125873</v>
+        <v>129125751</v>
       </c>
       <c r="B79" t="n">
-        <v>79034</v>
+        <v>81019</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448163</v>
+        <v>447952</v>
       </c>
       <c r="R79" t="n">
-        <v>6815302</v>
+        <v>6814974</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129125729</v>
+        <v>129125873</v>
       </c>
       <c r="B80" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>448039</v>
+        <v>448163</v>
       </c>
       <c r="R80" t="n">
-        <v>6815229</v>
+        <v>6815302</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125751</v>
+        <v>129125824</v>
       </c>
       <c r="B84" t="n">
-        <v>81019</v>
+        <v>79034</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8973,21 +8973,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447952</v>
+        <v>447761</v>
       </c>
       <c r="R84" t="n">
-        <v>6814974</v>
+        <v>6815045</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125730</v>
+        <v>129125808</v>
       </c>
       <c r="B85" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448098</v>
+        <v>447782</v>
       </c>
       <c r="R85" t="n">
-        <v>6815212</v>
+        <v>6814944</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9176,10 +9176,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125824</v>
+        <v>129125729</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9187,21 +9187,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447761</v>
+        <v>448039</v>
       </c>
       <c r="R86" t="n">
-        <v>6815045</v>
+        <v>6815229</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9283,54 +9283,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129125759</v>
+        <v>129125730</v>
       </c>
       <c r="B87" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447640</v>
+        <v>448098</v>
       </c>
       <c r="R87" t="n">
-        <v>6814923</v>
+        <v>6815212</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9372,7 +9363,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9399,7 +9390,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129125808</v>
+        <v>129125895</v>
       </c>
       <c r="B88" t="n">
         <v>79034</v>
@@ -9434,10 +9425,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447782</v>
+        <v>447963</v>
       </c>
       <c r="R88" t="n">
-        <v>6814944</v>
+        <v>6815131</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9469,7 +9460,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9479,7 +9470,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9506,7 +9497,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129125895</v>
+        <v>129125767</v>
       </c>
       <c r="B89" t="n">
         <v>79034</v>
@@ -9541,10 +9532,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447963</v>
+        <v>447915</v>
       </c>
       <c r="R89" t="n">
-        <v>6815131</v>
+        <v>6815140</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9576,7 +9567,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9586,7 +9577,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9613,45 +9604,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129125767</v>
+        <v>129125759</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447915</v>
+        <v>447640</v>
       </c>
       <c r="R90" t="n">
-        <v>6815140</v>
+        <v>6814923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125874</v>
+        <v>129125753</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448182</v>
+        <v>447766</v>
       </c>
       <c r="R91" t="n">
-        <v>6815308</v>
+        <v>6814899</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9809,6 +9814,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9827,7 +9833,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125809</v>
+        <v>129125795</v>
       </c>
       <c r="B92" t="n">
         <v>79034</v>
@@ -9862,10 +9868,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447763</v>
+        <v>447790</v>
       </c>
       <c r="R92" t="n">
-        <v>6814923</v>
+        <v>6814834</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9903,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9913,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,7 +9940,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125831</v>
+        <v>129125874</v>
       </c>
       <c r="B93" t="n">
         <v>79034</v>
@@ -9969,10 +9975,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447755</v>
+        <v>448182</v>
       </c>
       <c r="R93" t="n">
-        <v>6814973</v>
+        <v>6815308</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10010,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10020,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10041,7 +10047,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125772</v>
+        <v>129125809</v>
       </c>
       <c r="B94" t="n">
         <v>79034</v>
@@ -10076,10 +10082,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447920</v>
+        <v>447763</v>
       </c>
       <c r="R94" t="n">
-        <v>6815082</v>
+        <v>6814923</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10117,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10127,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,10 +10154,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125753</v>
+        <v>129125831</v>
       </c>
       <c r="B95" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,21 +10165,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10189,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447766</v>
+        <v>447755</v>
       </c>
       <c r="R95" t="n">
-        <v>6814899</v>
+        <v>6814973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10224,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,12 +10234,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10242,7 +10243,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125722</v>
+        <v>129125772</v>
       </c>
       <c r="B96" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10272,21 +10272,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447757</v>
+        <v>447920</v>
       </c>
       <c r="R96" t="n">
-        <v>6814906</v>
+        <v>6815082</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10368,10 +10368,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125795</v>
+        <v>129125722</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447790</v>
+        <v>447757</v>
       </c>
       <c r="R97" t="n">
-        <v>6814834</v>
+        <v>6814906</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10475,10 +10475,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129125872</v>
+        <v>129125741</v>
       </c>
       <c r="B98" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10486,34 +10486,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>448159</v>
+        <v>447902</v>
       </c>
       <c r="R98" t="n">
-        <v>6815277</v>
+        <v>6814922</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,7 +10550,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10555,7 +10560,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10582,32 +10587,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129125746</v>
+        <v>129125719</v>
       </c>
       <c r="B99" t="n">
-        <v>97528</v>
+        <v>79066</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10617,10 +10622,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>448129</v>
+        <v>447855</v>
       </c>
       <c r="R99" t="n">
-        <v>6815200</v>
+        <v>6814877</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10657,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10662,7 +10667,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10689,10 +10694,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129125741</v>
+        <v>129125872</v>
       </c>
       <c r="B100" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10700,39 +10705,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447902</v>
+        <v>448159</v>
       </c>
       <c r="R100" t="n">
-        <v>6814922</v>
+        <v>6815277</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10801,7 +10801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129125820</v>
+        <v>129125836</v>
       </c>
       <c r="B101" t="n">
         <v>79034</v>
@@ -10836,10 +10836,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447706</v>
+        <v>447789</v>
       </c>
       <c r="R101" t="n">
-        <v>6815025</v>
+        <v>6815016</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10908,7 +10908,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129125888</v>
+        <v>129125820</v>
       </c>
       <c r="B102" t="n">
         <v>79034</v>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448042</v>
+        <v>447706</v>
       </c>
       <c r="R102" t="n">
-        <v>6815053</v>
+        <v>6815025</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11015,10 +11015,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129125719</v>
+        <v>129125888</v>
       </c>
       <c r="B103" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11026,21 +11026,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11050,10 +11050,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447855</v>
+        <v>448042</v>
       </c>
       <c r="R103" t="n">
-        <v>6814877</v>
+        <v>6815053</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11229,32 +11229,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125836</v>
+        <v>129125746</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>97533</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447789</v>
+        <v>448129</v>
       </c>
       <c r="R105" t="n">
-        <v>6815016</v>
+        <v>6815200</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11443,7 +11443,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129125814</v>
+        <v>129125886</v>
       </c>
       <c r="B107" t="n">
         <v>79034</v>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447611</v>
+        <v>448097</v>
       </c>
       <c r="R107" t="n">
-        <v>6814782</v>
+        <v>6815025</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11550,7 +11550,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129125868</v>
+        <v>129125814</v>
       </c>
       <c r="B108" t="n">
         <v>79034</v>
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448101</v>
+        <v>447611</v>
       </c>
       <c r="R108" t="n">
-        <v>6815213</v>
+        <v>6814782</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129125886</v>
+        <v>129125868</v>
       </c>
       <c r="B109" t="n">
         <v>79034</v>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448097</v>
+        <v>448101</v>
       </c>
       <c r="R109" t="n">
-        <v>6815025</v>
+        <v>6815213</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11871,10 +11871,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129125721</v>
+        <v>129125807</v>
       </c>
       <c r="B111" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11882,21 +11882,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447943</v>
+        <v>447797</v>
       </c>
       <c r="R111" t="n">
-        <v>6814947</v>
+        <v>6814950</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11978,7 +11978,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125807</v>
+        <v>129125863</v>
       </c>
       <c r="B112" t="n">
         <v>79034</v>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447797</v>
+        <v>447878</v>
       </c>
       <c r="R112" t="n">
-        <v>6814950</v>
+        <v>6815153</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,7 +12085,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125863</v>
+        <v>129125779</v>
       </c>
       <c r="B113" t="n">
         <v>79034</v>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447878</v>
+        <v>447936</v>
       </c>
       <c r="R113" t="n">
-        <v>6815153</v>
+        <v>6814995</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,7 +12192,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125891</v>
+        <v>129125841</v>
       </c>
       <c r="B114" t="n">
         <v>79034</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>448003</v>
+        <v>447812</v>
       </c>
       <c r="R114" t="n">
-        <v>6815088</v>
+        <v>6815036</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12299,32 +12299,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129125779</v>
+        <v>129125728</v>
       </c>
       <c r="B115" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447936</v>
+        <v>447872</v>
       </c>
       <c r="R115" t="n">
-        <v>6814995</v>
+        <v>6815131</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12406,7 +12406,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125841</v>
+        <v>129125891</v>
       </c>
       <c r="B116" t="n">
         <v>79034</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447812</v>
+        <v>448003</v>
       </c>
       <c r="R116" t="n">
-        <v>6815036</v>
+        <v>6815088</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,32 +12513,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125728</v>
+        <v>129125851</v>
       </c>
       <c r="B117" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447872</v>
+        <v>447834</v>
       </c>
       <c r="R117" t="n">
-        <v>6815131</v>
+        <v>6815005</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12620,10 +12620,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129125851</v>
+        <v>129125721</v>
       </c>
       <c r="B118" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,21 +12631,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447834</v>
+        <v>447943</v>
       </c>
       <c r="R118" t="n">
-        <v>6815005</v>
+        <v>6814947</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12834,7 +12834,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125894</v>
+        <v>129125850</v>
       </c>
       <c r="B120" t="n">
         <v>79034</v>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447978</v>
+        <v>447844</v>
       </c>
       <c r="R120" t="n">
-        <v>6815111</v>
+        <v>6815026</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125850</v>
+        <v>129125827</v>
       </c>
       <c r="B121" t="n">
         <v>79034</v>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447844</v>
+        <v>447767</v>
       </c>
       <c r="R121" t="n">
-        <v>6815026</v>
+        <v>6815014</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13048,32 +13048,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129125827</v>
+        <v>129125750</v>
       </c>
       <c r="B122" t="n">
-        <v>79034</v>
+        <v>80175</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447767</v>
+        <v>447714</v>
       </c>
       <c r="R122" t="n">
-        <v>6815014</v>
+        <v>6815023</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13155,32 +13155,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125750</v>
+        <v>129125811</v>
       </c>
       <c r="B123" t="n">
-        <v>80175</v>
+        <v>79034</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447714</v>
+        <v>447716</v>
       </c>
       <c r="R123" t="n">
-        <v>6815023</v>
+        <v>6814829</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,7 +13262,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125811</v>
+        <v>129125882</v>
       </c>
       <c r="B124" t="n">
         <v>79034</v>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447716</v>
+        <v>448089</v>
       </c>
       <c r="R124" t="n">
-        <v>6814829</v>
+        <v>6815086</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,7 +13369,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125865</v>
+        <v>129125791</v>
       </c>
       <c r="B125" t="n">
         <v>79034</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448049</v>
+        <v>447839</v>
       </c>
       <c r="R125" t="n">
-        <v>6815224</v>
+        <v>6814871</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,7 +13476,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125859</v>
+        <v>129125894</v>
       </c>
       <c r="B126" t="n">
         <v>79034</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447887</v>
+        <v>447978</v>
       </c>
       <c r="R126" t="n">
-        <v>6815043</v>
+        <v>6815111</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125852</v>
+        <v>129125865</v>
       </c>
       <c r="B127" t="n">
         <v>79034</v>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447839</v>
+        <v>448049</v>
       </c>
       <c r="R127" t="n">
-        <v>6814995</v>
+        <v>6815224</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13690,7 +13690,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129125882</v>
+        <v>129125859</v>
       </c>
       <c r="B128" t="n">
         <v>79034</v>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>448089</v>
+        <v>447887</v>
       </c>
       <c r="R128" t="n">
-        <v>6815086</v>
+        <v>6815043</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13797,7 +13797,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125845</v>
+        <v>129125852</v>
       </c>
       <c r="B129" t="n">
         <v>79034</v>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447801</v>
+        <v>447839</v>
       </c>
       <c r="R129" t="n">
-        <v>6815082</v>
+        <v>6814995</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,7 +13904,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125791</v>
+        <v>129125845</v>
       </c>
       <c r="B130" t="n">
         <v>79034</v>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447839</v>
+        <v>447801</v>
       </c>
       <c r="R130" t="n">
-        <v>6814871</v>
+        <v>6815082</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,7 +14011,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125770</v>
+        <v>129125844</v>
       </c>
       <c r="B131" t="n">
         <v>79034</v>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447916</v>
+        <v>447808</v>
       </c>
       <c r="R131" t="n">
-        <v>6815113</v>
+        <v>6815078</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14118,32 +14118,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125844</v>
+        <v>129125743</v>
       </c>
       <c r="B132" t="n">
-        <v>79034</v>
+        <v>80043</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14153,10 +14153,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447808</v>
+        <v>447735</v>
       </c>
       <c r="R132" t="n">
-        <v>6815078</v>
+        <v>6814890</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14198,7 +14198,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14225,32 +14230,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125743</v>
+        <v>129125770</v>
       </c>
       <c r="B133" t="n">
-        <v>80043</v>
+        <v>79034</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14260,10 +14265,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447735</v>
+        <v>447916</v>
       </c>
       <c r="R133" t="n">
-        <v>6814890</v>
+        <v>6815113</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14295,7 +14300,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14305,12 +14310,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14551,7 +14551,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129125781</v>
+        <v>129125818</v>
       </c>
       <c r="B136" t="n">
         <v>79034</v>
@@ -14586,10 +14586,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>447968</v>
+        <v>447641</v>
       </c>
       <c r="R136" t="n">
-        <v>6814977</v>
+        <v>6814924</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14658,7 +14658,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125885</v>
+        <v>129125805</v>
       </c>
       <c r="B137" t="n">
         <v>79034</v>
@@ -14693,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>448080</v>
+        <v>447826</v>
       </c>
       <c r="R137" t="n">
-        <v>6815037</v>
+        <v>6814982</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14765,7 +14765,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125797</v>
+        <v>129125781</v>
       </c>
       <c r="B138" t="n">
         <v>79034</v>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>447781</v>
+        <v>447968</v>
       </c>
       <c r="R138" t="n">
-        <v>6814894</v>
+        <v>6814977</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14872,7 +14872,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125818</v>
+        <v>129125885</v>
       </c>
       <c r="B139" t="n">
         <v>79034</v>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>447641</v>
+        <v>448080</v>
       </c>
       <c r="R139" t="n">
-        <v>6814924</v>
+        <v>6815037</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14979,7 +14979,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125805</v>
+        <v>129125797</v>
       </c>
       <c r="B140" t="n">
         <v>79034</v>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>447826</v>
+        <v>447781</v>
       </c>
       <c r="R140" t="n">
-        <v>6814982</v>
+        <v>6814894</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15086,10 +15086,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125737</v>
+        <v>129125887</v>
       </c>
       <c r="B141" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15097,39 +15097,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>447735</v>
+        <v>448080</v>
       </c>
       <c r="R141" t="n">
-        <v>6815036</v>
+        <v>6815039</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15161,7 +15156,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15171,7 +15166,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15198,10 +15193,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129125887</v>
+        <v>129125737</v>
       </c>
       <c r="B142" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15209,34 +15204,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>448080</v>
+        <v>447735</v>
       </c>
       <c r="R142" t="n">
-        <v>6815039</v>
+        <v>6815036</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15305,7 +15305,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125775</v>
+        <v>129125828</v>
       </c>
       <c r="B143" t="n">
         <v>79034</v>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447916</v>
+        <v>447781</v>
       </c>
       <c r="R143" t="n">
-        <v>6815021</v>
+        <v>6815009</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,27 +15412,27 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125828</v>
+        <v>129125899</v>
       </c>
       <c r="B144" t="n">
-        <v>79034</v>
+        <v>80174</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447781</v>
+        <v>447580</v>
       </c>
       <c r="R144" t="n">
-        <v>6815009</v>
+        <v>6814868</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,27 +15519,27 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125899</v>
+        <v>129125839</v>
       </c>
       <c r="B145" t="n">
-        <v>80174</v>
+        <v>79034</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447580</v>
+        <v>447805</v>
       </c>
       <c r="R145" t="n">
-        <v>6814868</v>
+        <v>6815025</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15626,7 +15626,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125839</v>
+        <v>129125796</v>
       </c>
       <c r="B146" t="n">
         <v>79034</v>
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447805</v>
+        <v>447749</v>
       </c>
       <c r="R146" t="n">
-        <v>6815025</v>
+        <v>6814850</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,7 +15733,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125792</v>
+        <v>129125775</v>
       </c>
       <c r="B147" t="n">
         <v>79034</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447812</v>
+        <v>447916</v>
       </c>
       <c r="R147" t="n">
-        <v>6814852</v>
+        <v>6815021</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,7 +15840,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125796</v>
+        <v>129125792</v>
       </c>
       <c r="B148" t="n">
         <v>79034</v>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447749</v>
+        <v>447812</v>
       </c>
       <c r="R148" t="n">
-        <v>6814850</v>
+        <v>6814852</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16054,7 +16054,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129125802</v>
+        <v>129125806</v>
       </c>
       <c r="B150" t="n">
         <v>79034</v>
@@ -16089,10 +16089,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>447821</v>
+        <v>447816</v>
       </c>
       <c r="R150" t="n">
-        <v>6814955</v>
+        <v>6814979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16161,7 +16161,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129125806</v>
+        <v>129125830</v>
       </c>
       <c r="B151" t="n">
         <v>79034</v>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>447816</v>
+        <v>447767</v>
       </c>
       <c r="R151" t="n">
-        <v>6814979</v>
+        <v>6814993</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16268,7 +16268,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125830</v>
+        <v>129125799</v>
       </c>
       <c r="B152" t="n">
         <v>79034</v>
@@ -16303,10 +16303,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447767</v>
+        <v>447804</v>
       </c>
       <c r="R152" t="n">
-        <v>6814993</v>
+        <v>6814911</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,10 +16375,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125731</v>
+        <v>129125749</v>
       </c>
       <c r="B153" t="n">
-        <v>56913</v>
+        <v>80175</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16386,39 +16386,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>6464</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>448128</v>
+        <v>447581</v>
       </c>
       <c r="R153" t="n">
-        <v>6815234</v>
+        <v>6814869</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16450,7 +16445,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16460,7 +16455,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16487,7 +16482,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125799</v>
+        <v>129125769</v>
       </c>
       <c r="B154" t="n">
         <v>79034</v>
@@ -16522,10 +16517,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>447804</v>
+        <v>447912</v>
       </c>
       <c r="R154" t="n">
-        <v>6814911</v>
+        <v>6815110</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16557,7 +16552,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16567,7 +16562,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16594,7 +16589,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125769</v>
+        <v>129125768</v>
       </c>
       <c r="B155" t="n">
         <v>79034</v>
@@ -16629,10 +16624,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447912</v>
+        <v>447909</v>
       </c>
       <c r="R155" t="n">
-        <v>6815110</v>
+        <v>6815119</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16701,7 +16696,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125768</v>
+        <v>129125804</v>
       </c>
       <c r="B156" t="n">
         <v>79034</v>
@@ -16736,10 +16731,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447909</v>
+        <v>447840</v>
       </c>
       <c r="R156" t="n">
-        <v>6815119</v>
+        <v>6814978</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16771,7 +16766,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16781,7 +16776,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16808,10 +16803,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125720</v>
+        <v>129125801</v>
       </c>
       <c r="B157" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16819,21 +16814,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16843,10 +16838,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447936</v>
+        <v>447814</v>
       </c>
       <c r="R157" t="n">
-        <v>6814995</v>
+        <v>6814948</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16878,7 +16873,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16888,7 +16883,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16915,32 +16910,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125749</v>
+        <v>129125878</v>
       </c>
       <c r="B158" t="n">
-        <v>80175</v>
+        <v>79034</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16950,10 +16945,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>447581</v>
+        <v>448121</v>
       </c>
       <c r="R158" t="n">
-        <v>6814869</v>
+        <v>6815175</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16985,7 +16980,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16995,7 +16990,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17022,7 +17017,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129125804</v>
+        <v>129125869</v>
       </c>
       <c r="B159" t="n">
         <v>79034</v>
@@ -17057,10 +17052,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>447840</v>
+        <v>448114</v>
       </c>
       <c r="R159" t="n">
-        <v>6814978</v>
+        <v>6815209</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17092,7 +17087,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17102,7 +17097,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17129,7 +17124,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125801</v>
+        <v>129125849</v>
       </c>
       <c r="B160" t="n">
         <v>79034</v>
@@ -17164,10 +17159,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>447814</v>
+        <v>447825</v>
       </c>
       <c r="R160" t="n">
-        <v>6814948</v>
+        <v>6815056</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17199,7 +17194,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17209,7 +17204,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17236,45 +17231,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125878</v>
+        <v>129125758</v>
       </c>
       <c r="B161" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>448121</v>
+        <v>447571</v>
       </c>
       <c r="R161" t="n">
-        <v>6815175</v>
+        <v>6814831</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17306,7 +17310,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17316,7 +17320,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17343,45 +17347,54 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125869</v>
+        <v>129125757</v>
       </c>
       <c r="B162" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>448114</v>
+        <v>447746</v>
       </c>
       <c r="R162" t="n">
-        <v>6815209</v>
+        <v>6814851</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17413,7 +17426,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17423,7 +17436,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17450,54 +17463,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125758</v>
+        <v>129125802</v>
       </c>
       <c r="B163" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>447571</v>
+        <v>447821</v>
       </c>
       <c r="R163" t="n">
-        <v>6814831</v>
+        <v>6814955</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17529,7 +17533,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17539,7 +17543,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17566,42 +17570,38 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129125757</v>
+        <v>129125731</v>
       </c>
       <c r="B164" t="n">
-        <v>98651</v>
+        <v>56913</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -17610,10 +17610,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>447746</v>
+        <v>448128</v>
       </c>
       <c r="R164" t="n">
-        <v>6814851</v>
+        <v>6815234</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17682,10 +17682,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129125849</v>
+        <v>129125720</v>
       </c>
       <c r="B165" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17693,21 +17693,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>447825</v>
+        <v>447936</v>
       </c>
       <c r="R165" t="n">
-        <v>6815056</v>
+        <v>6814995</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17896,10 +17896,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129125734</v>
+        <v>129125855</v>
       </c>
       <c r="B167" t="n">
-        <v>57883</v>
+        <v>79034</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17907,48 +17907,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>447913</v>
+        <v>447895</v>
       </c>
       <c r="R167" t="n">
-        <v>6815128</v>
+        <v>6814968</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17980,7 +17966,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17990,7 +17976,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18017,7 +18003,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129125855</v>
+        <v>129125816</v>
       </c>
       <c r="B168" t="n">
         <v>79034</v>
@@ -18052,10 +18038,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>447895</v>
+        <v>447568</v>
       </c>
       <c r="R168" t="n">
-        <v>6814968</v>
+        <v>6814828</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18087,7 +18073,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18097,7 +18083,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18124,10 +18110,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129125816</v>
+        <v>129125734</v>
       </c>
       <c r="B169" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18135,34 +18121,48 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>447568</v>
+        <v>447913</v>
       </c>
       <c r="R169" t="n">
-        <v>6814828</v>
+        <v>6815128</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18338,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125739</v>
+        <v>129125880</v>
       </c>
       <c r="B171" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18349,39 +18349,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>448089</v>
+        <v>448107</v>
       </c>
       <c r="R171" t="n">
-        <v>6815093</v>
+        <v>6815120</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18413,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18423,12 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18562,32 +18552,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125745</v>
+        <v>129125718</v>
       </c>
       <c r="B173" t="n">
-        <v>97522</v>
+        <v>83010</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18597,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>448023</v>
+        <v>447772</v>
       </c>
       <c r="R173" t="n">
-        <v>6815221</v>
+        <v>6815035</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18632,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18642,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18669,10 +18659,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125724</v>
+        <v>129125861</v>
       </c>
       <c r="B174" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18680,21 +18670,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18704,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>447803</v>
+        <v>447887</v>
       </c>
       <c r="R174" t="n">
-        <v>6815095</v>
+        <v>6815067</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18739,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18749,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18776,10 +18766,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125740</v>
+        <v>129125862</v>
       </c>
       <c r="B175" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18787,39 +18777,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447580</v>
+        <v>447867</v>
       </c>
       <c r="R175" t="n">
-        <v>6814929</v>
+        <v>6815109</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18851,7 +18836,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18861,7 +18846,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18888,32 +18873,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125861</v>
+        <v>129125763</v>
       </c>
       <c r="B176" t="n">
-        <v>79034</v>
+        <v>82993</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18923,10 +18908,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>447887</v>
+        <v>447801</v>
       </c>
       <c r="R176" t="n">
-        <v>6815067</v>
+        <v>6814957</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18958,7 +18943,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18968,7 +18953,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18995,10 +18980,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125832</v>
+        <v>129125724</v>
       </c>
       <c r="B177" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19006,21 +18991,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19030,10 +19015,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>447762</v>
+        <v>447803</v>
       </c>
       <c r="R177" t="n">
-        <v>6814968</v>
+        <v>6815095</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19065,7 +19050,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19075,7 +19060,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19102,32 +19087,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129125763</v>
+        <v>129125723</v>
       </c>
       <c r="B178" t="n">
-        <v>82993</v>
+        <v>79066</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6439</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19137,10 +19122,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>447801</v>
+        <v>447751</v>
       </c>
       <c r="R178" t="n">
-        <v>6814957</v>
+        <v>6814901</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19172,7 +19157,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19182,7 +19167,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19209,10 +19194,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129125842</v>
+        <v>129125727</v>
       </c>
       <c r="B179" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19220,21 +19205,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19244,10 +19229,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>447813</v>
+        <v>448008</v>
       </c>
       <c r="R179" t="n">
-        <v>6815044</v>
+        <v>6815080</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19279,7 +19264,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19289,7 +19274,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19316,32 +19301,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129125880</v>
+        <v>129125745</v>
       </c>
       <c r="B180" t="n">
-        <v>79034</v>
+        <v>97527</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19351,10 +19336,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>448107</v>
+        <v>448023</v>
       </c>
       <c r="R180" t="n">
-        <v>6815120</v>
+        <v>6815221</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19386,7 +19371,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19396,7 +19381,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19423,10 +19408,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129125723</v>
+        <v>129125832</v>
       </c>
       <c r="B181" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19434,21 +19419,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19458,10 +19443,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>447751</v>
+        <v>447762</v>
       </c>
       <c r="R181" t="n">
-        <v>6814901</v>
+        <v>6814968</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19493,7 +19478,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19503,7 +19488,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19530,10 +19515,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125718</v>
+        <v>129125842</v>
       </c>
       <c r="B182" t="n">
-        <v>83010</v>
+        <v>79034</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19541,21 +19526,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19565,10 +19550,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>447772</v>
+        <v>447813</v>
       </c>
       <c r="R182" t="n">
-        <v>6815035</v>
+        <v>6815044</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19600,7 +19585,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19610,7 +19595,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19637,10 +19622,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125727</v>
+        <v>129125739</v>
       </c>
       <c r="B183" t="n">
-        <v>79066</v>
+        <v>57720</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19648,34 +19633,39 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>448008</v>
+        <v>448089</v>
       </c>
       <c r="R183" t="n">
-        <v>6815080</v>
+        <v>6815093</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,7 +19697,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19717,7 +19707,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19744,10 +19739,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129125862</v>
+        <v>129125740</v>
       </c>
       <c r="B184" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19755,34 +19750,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>447867</v>
+        <v>447580</v>
       </c>
       <c r="R184" t="n">
-        <v>6815109</v>
+        <v>6814929</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19851,7 +19851,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129125876</v>
+        <v>129125780</v>
       </c>
       <c r="B185" t="n">
         <v>79034</v>
@@ -19886,10 +19886,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>448131</v>
+        <v>447958</v>
       </c>
       <c r="R185" t="n">
-        <v>6815201</v>
+        <v>6814987</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19958,7 +19958,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129125780</v>
+        <v>129125793</v>
       </c>
       <c r="B186" t="n">
         <v>79034</v>
@@ -19993,10 +19993,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>447958</v>
+        <v>447819</v>
       </c>
       <c r="R186" t="n">
-        <v>6814987</v>
+        <v>6814842</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20065,10 +20065,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125725</v>
+        <v>129125815</v>
       </c>
       <c r="B187" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20076,21 +20076,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>448124</v>
+        <v>447586</v>
       </c>
       <c r="R187" t="n">
-        <v>6815167</v>
+        <v>6814809</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20172,10 +20172,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129125793</v>
+        <v>129125725</v>
       </c>
       <c r="B188" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20183,21 +20183,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20207,10 +20207,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>447819</v>
+        <v>448124</v>
       </c>
       <c r="R188" t="n">
-        <v>6814842</v>
+        <v>6815167</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20279,10 +20279,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125784</v>
+        <v>129125896</v>
       </c>
       <c r="B189" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20290,34 +20290,39 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>447943</v>
+        <v>447925</v>
       </c>
       <c r="R189" t="n">
-        <v>6814947</v>
+        <v>6815105</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20349,7 +20354,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20359,7 +20364,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20386,7 +20391,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129125783</v>
+        <v>129125876</v>
       </c>
       <c r="B190" t="n">
         <v>79034</v>
@@ -20421,10 +20426,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>447952</v>
+        <v>448131</v>
       </c>
       <c r="R190" t="n">
-        <v>6814960</v>
+        <v>6815201</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20456,7 +20461,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20466,7 +20471,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20493,10 +20498,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129125896</v>
+        <v>129125784</v>
       </c>
       <c r="B191" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20504,39 +20509,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>447925</v>
+        <v>447943</v>
       </c>
       <c r="R191" t="n">
-        <v>6815105</v>
+        <v>6814947</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20568,7 +20568,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20605,7 +20605,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129125815</v>
+        <v>129125783</v>
       </c>
       <c r="B192" t="n">
         <v>79034</v>
@@ -20640,10 +20640,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>447586</v>
+        <v>447952</v>
       </c>
       <c r="R192" t="n">
-        <v>6814809</v>
+        <v>6814960</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20685,7 +20685,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20926,7 +20926,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125857</v>
+        <v>129125893</v>
       </c>
       <c r="B195" t="n">
         <v>79034</v>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447909</v>
+        <v>447992</v>
       </c>
       <c r="R195" t="n">
-        <v>6815011</v>
+        <v>6815102</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21033,32 +21033,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129125898</v>
+        <v>129125890</v>
       </c>
       <c r="B196" t="n">
-        <v>92811</v>
+        <v>79034</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>447585</v>
+        <v>448015</v>
       </c>
       <c r="R196" t="n">
-        <v>6814810</v>
+        <v>6815065</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21140,7 +21140,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125834</v>
+        <v>129125857</v>
       </c>
       <c r="B197" t="n">
         <v>79034</v>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>447788</v>
+        <v>447909</v>
       </c>
       <c r="R197" t="n">
-        <v>6814995</v>
+        <v>6815011</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,7 +21247,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125847</v>
+        <v>129125834</v>
       </c>
       <c r="B198" t="n">
         <v>79034</v>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>447814</v>
+        <v>447788</v>
       </c>
       <c r="R198" t="n">
-        <v>6815081</v>
+        <v>6814995</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,7 +21354,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125819</v>
+        <v>129125847</v>
       </c>
       <c r="B199" t="n">
         <v>79034</v>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>447647</v>
+        <v>447814</v>
       </c>
       <c r="R199" t="n">
-        <v>6815013</v>
+        <v>6815081</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,7 +21461,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125893</v>
+        <v>129125819</v>
       </c>
       <c r="B200" t="n">
         <v>79034</v>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447992</v>
+        <v>447647</v>
       </c>
       <c r="R200" t="n">
-        <v>6815102</v>
+        <v>6815013</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21568,32 +21568,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129125866</v>
+        <v>129125898</v>
       </c>
       <c r="B201" t="n">
-        <v>79034</v>
+        <v>92816</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>448062</v>
+        <v>447585</v>
       </c>
       <c r="R201" t="n">
-        <v>6815224</v>
+        <v>6814810</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21675,7 +21675,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129125890</v>
+        <v>129125866</v>
       </c>
       <c r="B202" t="n">
         <v>79034</v>
@@ -21710,10 +21710,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>448015</v>
+        <v>448062</v>
       </c>
       <c r="R202" t="n">
-        <v>6815065</v>
+        <v>6815224</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21782,7 +21782,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129125856</v>
+        <v>129125864</v>
       </c>
       <c r="B203" t="n">
         <v>79034</v>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>447906</v>
+        <v>448025</v>
       </c>
       <c r="R203" t="n">
-        <v>6814985</v>
+        <v>6815228</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21889,7 +21889,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129125864</v>
+        <v>129125881</v>
       </c>
       <c r="B204" t="n">
         <v>79034</v>
@@ -21924,10 +21924,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>448025</v>
+        <v>448111</v>
       </c>
       <c r="R204" t="n">
-        <v>6815228</v>
+        <v>6815099</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21996,7 +21996,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129125881</v>
+        <v>129125875</v>
       </c>
       <c r="B205" t="n">
         <v>79034</v>
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>448111</v>
+        <v>448141</v>
       </c>
       <c r="R205" t="n">
-        <v>6815099</v>
+        <v>6815210</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22103,7 +22103,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129125788</v>
+        <v>129125856</v>
       </c>
       <c r="B206" t="n">
         <v>79034</v>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>447870</v>
+        <v>447906</v>
       </c>
       <c r="R206" t="n">
-        <v>6814898</v>
+        <v>6814985</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22210,7 +22210,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129125875</v>
+        <v>129125788</v>
       </c>
       <c r="B207" t="n">
         <v>79034</v>
@@ -22245,10 +22245,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>448141</v>
+        <v>447870</v>
       </c>
       <c r="R207" t="n">
-        <v>6815210</v>
+        <v>6814898</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22531,32 +22531,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129125735</v>
+        <v>129125762</v>
       </c>
       <c r="B210" t="n">
-        <v>80168</v>
+        <v>79034</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22566,10 +22566,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>447805</v>
+        <v>448058</v>
       </c>
       <c r="R210" t="n">
-        <v>6815002</v>
+        <v>6815046</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22638,7 +22638,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129125884</v>
+        <v>129125883</v>
       </c>
       <c r="B211" t="n">
         <v>79034</v>
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>448089</v>
+        <v>448080</v>
       </c>
       <c r="R211" t="n">
-        <v>6815055</v>
+        <v>6815060</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22745,32 +22745,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129125825</v>
+        <v>129125735</v>
       </c>
       <c r="B212" t="n">
-        <v>79034</v>
+        <v>80168</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>447766</v>
+        <v>447805</v>
       </c>
       <c r="R212" t="n">
-        <v>6815038</v>
+        <v>6815002</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22852,7 +22852,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129125762</v>
+        <v>129125884</v>
       </c>
       <c r="B213" t="n">
         <v>79034</v>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>448058</v>
+        <v>448089</v>
       </c>
       <c r="R213" t="n">
-        <v>6815046</v>
+        <v>6815055</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22959,7 +22959,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129125883</v>
+        <v>129125825</v>
       </c>
       <c r="B214" t="n">
         <v>79034</v>
@@ -22994,10 +22994,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>448080</v>
+        <v>447766</v>
       </c>
       <c r="R214" t="n">
-        <v>6815060</v>
+        <v>6815038</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23066,7 +23066,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129125785</v>
+        <v>129125822</v>
       </c>
       <c r="B215" t="n">
         <v>79034</v>
@@ -23101,10 +23101,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>447935</v>
+        <v>447745</v>
       </c>
       <c r="R215" t="n">
-        <v>6814942</v>
+        <v>6815055</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23136,7 +23136,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23173,10 +23173,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129125733</v>
+        <v>129125785</v>
       </c>
       <c r="B216" t="n">
-        <v>57883</v>
+        <v>79034</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23184,39 +23184,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>447785</v>
+        <v>447935</v>
       </c>
       <c r="R216" t="n">
-        <v>6814977</v>
+        <v>6814942</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23248,7 +23243,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23258,7 +23253,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23285,7 +23280,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129125848</v>
+        <v>129125789</v>
       </c>
       <c r="B217" t="n">
         <v>79034</v>
@@ -23320,10 +23315,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>447816</v>
+        <v>447869</v>
       </c>
       <c r="R217" t="n">
-        <v>6815066</v>
+        <v>6814887</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23355,7 +23350,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23365,7 +23360,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23392,7 +23387,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129125871</v>
+        <v>129125848</v>
       </c>
       <c r="B218" t="n">
         <v>79034</v>
@@ -23427,10 +23422,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>448138</v>
+        <v>447816</v>
       </c>
       <c r="R218" t="n">
-        <v>6815238</v>
+        <v>6815066</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23462,7 +23457,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23472,7 +23467,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23499,7 +23494,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129125782</v>
+        <v>129125871</v>
       </c>
       <c r="B219" t="n">
         <v>79034</v>
@@ -23534,10 +23529,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>447951</v>
+        <v>448138</v>
       </c>
       <c r="R219" t="n">
-        <v>6814973</v>
+        <v>6815238</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23569,7 +23564,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23579,7 +23574,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23606,7 +23601,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129125774</v>
+        <v>129125782</v>
       </c>
       <c r="B220" t="n">
         <v>79034</v>
@@ -23641,10 +23636,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>447907</v>
+        <v>447951</v>
       </c>
       <c r="R220" t="n">
-        <v>6815056</v>
+        <v>6814973</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23676,7 +23671,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23686,7 +23681,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23713,7 +23708,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129125838</v>
+        <v>129125774</v>
       </c>
       <c r="B221" t="n">
         <v>79034</v>
@@ -23748,10 +23743,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>447808</v>
+        <v>447907</v>
       </c>
       <c r="R221" t="n">
-        <v>6815019</v>
+        <v>6815056</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23783,7 +23778,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23793,7 +23788,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23820,7 +23815,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129125822</v>
+        <v>129125838</v>
       </c>
       <c r="B222" t="n">
         <v>79034</v>
@@ -23855,10 +23850,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>447745</v>
+        <v>447808</v>
       </c>
       <c r="R222" t="n">
-        <v>6815055</v>
+        <v>6815019</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23890,7 +23885,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23900,7 +23895,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23927,10 +23922,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129125789</v>
+        <v>129125733</v>
       </c>
       <c r="B223" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23938,34 +23933,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>447869</v>
+        <v>447785</v>
       </c>
       <c r="R223" t="n">
-        <v>6814887</v>
+        <v>6814977</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24034,10 +24034,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129125726</v>
+        <v>129125776</v>
       </c>
       <c r="B224" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24045,21 +24045,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24069,10 +24069,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>448080</v>
+        <v>447923</v>
       </c>
       <c r="R224" t="n">
-        <v>6815060</v>
+        <v>6814998</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24141,7 +24141,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125776</v>
+        <v>129125794</v>
       </c>
       <c r="B225" t="n">
         <v>79034</v>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447923</v>
+        <v>447798</v>
       </c>
       <c r="R225" t="n">
-        <v>6814998</v>
+        <v>6814819</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,7 +24248,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125790</v>
+        <v>129125817</v>
       </c>
       <c r="B226" t="n">
         <v>79034</v>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447855</v>
+        <v>447580</v>
       </c>
       <c r="R226" t="n">
-        <v>6814877</v>
+        <v>6814929</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,10 +24355,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125817</v>
+        <v>129125754</v>
       </c>
       <c r="B227" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24366,21 +24366,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447580</v>
+        <v>447877</v>
       </c>
       <c r="R227" t="n">
-        <v>6814929</v>
+        <v>6814908</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24444,6 +24444,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -24462,7 +24463,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129125794</v>
+        <v>129125889</v>
       </c>
       <c r="B228" t="n">
         <v>79034</v>
@@ -24497,10 +24498,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>447798</v>
+        <v>448024</v>
       </c>
       <c r="R228" t="n">
-        <v>6814819</v>
+        <v>6815046</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24532,7 +24533,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24542,7 +24543,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24569,10 +24570,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129125754</v>
+        <v>129125773</v>
       </c>
       <c r="B229" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24580,21 +24581,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24604,10 +24605,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>447877</v>
+        <v>447907</v>
       </c>
       <c r="R229" t="n">
-        <v>6814908</v>
+        <v>6815075</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24639,7 +24640,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24649,7 +24650,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24658,7 +24659,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -24677,7 +24677,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125889</v>
+        <v>129125823</v>
       </c>
       <c r="B230" t="n">
         <v>79034</v>
@@ -24712,10 +24712,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>448024</v>
+        <v>447754</v>
       </c>
       <c r="R230" t="n">
-        <v>6815046</v>
+        <v>6815045</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24747,7 +24747,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24757,7 +24757,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24784,7 +24784,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129125854</v>
+        <v>129125790</v>
       </c>
       <c r="B231" t="n">
         <v>79034</v>
@@ -24819,10 +24819,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>447876</v>
+        <v>447855</v>
       </c>
       <c r="R231" t="n">
-        <v>6814962</v>
+        <v>6814877</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24891,7 +24891,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129125773</v>
+        <v>129125854</v>
       </c>
       <c r="B232" t="n">
         <v>79034</v>
@@ -24926,10 +24926,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>447907</v>
+        <v>447876</v>
       </c>
       <c r="R232" t="n">
-        <v>6815075</v>
+        <v>6814962</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24961,7 +24961,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24998,10 +24998,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129125823</v>
+        <v>129125726</v>
       </c>
       <c r="B233" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25009,21 +25009,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -25033,10 +25033,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>447754</v>
+        <v>448080</v>
       </c>
       <c r="R233" t="n">
-        <v>6815045</v>
+        <v>6815060</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605860</v>
+        <v>128605858</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448020</v>
+        <v>448017</v>
       </c>
       <c r="R2" t="n">
-        <v>6815080</v>
+        <v>6814944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605869</v>
+        <v>128605839</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447681</v>
+        <v>447574</v>
       </c>
       <c r="R3" t="n">
-        <v>6815015</v>
+        <v>6814884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605858</v>
+        <v>128605860</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448017</v>
+        <v>448020</v>
       </c>
       <c r="R4" t="n">
-        <v>6814944</v>
+        <v>6815080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +948,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605839</v>
+        <v>128605869</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447574</v>
+        <v>447681</v>
       </c>
       <c r="R5" t="n">
-        <v>6814884</v>
+        <v>6815015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128605833</v>
+        <v>128605852</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1771,42 +1771,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447771</v>
+        <v>447783</v>
       </c>
       <c r="R13" t="n">
-        <v>6814844</v>
+        <v>6814852</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,7 +1857,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128605837</v>
+        <v>128605833</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -1898,7 +1890,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1908,10 +1900,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447740</v>
+        <v>447771</v>
       </c>
       <c r="R14" t="n">
-        <v>6814822</v>
+        <v>6814844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,10 +1962,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128605852</v>
+        <v>128605837</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,34 +1973,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447783</v>
+        <v>447740</v>
       </c>
       <c r="R15" t="n">
-        <v>6814852</v>
+        <v>6814822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605885</v>
+        <v>128605832</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,34 +2078,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447840</v>
+        <v>448062</v>
       </c>
       <c r="R16" t="n">
-        <v>6815104</v>
+        <v>6815199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,7 +2172,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605888</v>
+        <v>128605885</v>
       </c>
       <c r="B17" t="n">
         <v>79035</v>
@@ -2199,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447929</v>
+        <v>447840</v>
       </c>
       <c r="R17" t="n">
-        <v>6815007</v>
+        <v>6815104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,11 +2243,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,10 +2269,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605853</v>
+        <v>128605888</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,21 +2280,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2301,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447773</v>
+        <v>447929</v>
       </c>
       <c r="R18" t="n">
-        <v>6814906</v>
+        <v>6815007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,6 +2340,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2371,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605832</v>
+        <v>128605853</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,42 +2382,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448062</v>
+        <v>447773</v>
       </c>
       <c r="R19" t="n">
-        <v>6815199</v>
+        <v>6814906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605890</v>
+        <v>128605871</v>
       </c>
       <c r="B53" t="n">
         <v>79035</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448003</v>
+        <v>447606</v>
       </c>
       <c r="R53" t="n">
-        <v>6814939</v>
+        <v>6814958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605870</v>
+        <v>128605884</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447670</v>
+        <v>447831</v>
       </c>
       <c r="R54" t="n">
-        <v>6814996</v>
+        <v>6815067</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605872</v>
+        <v>128605838</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,34 +5942,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447594</v>
+        <v>447770</v>
       </c>
       <c r="R55" t="n">
-        <v>6814977</v>
+        <v>6814909</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,10 +6036,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128605871</v>
+        <v>128605851</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,21 +6047,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6063,10 +6071,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447606</v>
+        <v>447628</v>
       </c>
       <c r="R56" t="n">
-        <v>6814958</v>
+        <v>6814833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605884</v>
+        <v>128605890</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6160,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447831</v>
+        <v>448003</v>
       </c>
       <c r="R57" t="n">
-        <v>6815067</v>
+        <v>6814939</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128605838</v>
+        <v>128605870</v>
       </c>
       <c r="B58" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,42 +6241,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447770</v>
+        <v>447670</v>
       </c>
       <c r="R58" t="n">
-        <v>6814909</v>
+        <v>6814996</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6327,10 +6327,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128605851</v>
+        <v>128605872</v>
       </c>
       <c r="B59" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,21 +6338,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447628</v>
+        <v>447594</v>
       </c>
       <c r="R59" t="n">
-        <v>6814833</v>
+        <v>6814977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129125764</v>
+        <v>129125786</v>
       </c>
       <c r="B66" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447872</v>
+        <v>447922</v>
       </c>
       <c r="R66" t="n">
-        <v>6814907</v>
+        <v>6814934</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7122,7 +7122,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129125786</v>
+        <v>129125766</v>
       </c>
       <c r="B67" t="n">
         <v>79035</v>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447922</v>
+        <v>447807</v>
       </c>
       <c r="R67" t="n">
-        <v>6814934</v>
+        <v>6814825</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7202,7 +7202,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På minst 250-årig tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7229,10 +7234,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129125766</v>
+        <v>129125764</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7240,21 +7245,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7264,10 +7269,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447807</v>
+        <v>447872</v>
       </c>
       <c r="R68" t="n">
-        <v>6814825</v>
+        <v>6814907</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7299,7 +7304,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7309,12 +7314,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På minst 250-årig tall</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125798</v>
+        <v>129125755</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447786</v>
+        <v>447756</v>
       </c>
       <c r="R71" t="n">
-        <v>6814897</v>
+        <v>6814990</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7644,6 +7644,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7662,7 +7663,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125821</v>
+        <v>129125798</v>
       </c>
       <c r="B72" t="n">
         <v>79035</v>
@@ -7697,10 +7698,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447754</v>
+        <v>447786</v>
       </c>
       <c r="R72" t="n">
-        <v>6815052</v>
+        <v>6814897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,7 +7733,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7742,7 +7743,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7769,7 +7770,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125787</v>
+        <v>129125821</v>
       </c>
       <c r="B73" t="n">
         <v>79035</v>
@@ -7804,10 +7805,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447908</v>
+        <v>447754</v>
       </c>
       <c r="R73" t="n">
-        <v>6814933</v>
+        <v>6815052</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7839,7 +7840,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7849,7 +7850,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7876,7 +7877,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129125835</v>
+        <v>129125787</v>
       </c>
       <c r="B74" t="n">
         <v>79035</v>
@@ -7911,10 +7912,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447793</v>
+        <v>447908</v>
       </c>
       <c r="R74" t="n">
-        <v>6815007</v>
+        <v>6814933</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7946,7 +7947,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7956,7 +7957,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7983,7 +7984,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129125812</v>
+        <v>129125835</v>
       </c>
       <c r="B75" t="n">
         <v>79035</v>
@@ -8018,10 +8019,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447682</v>
+        <v>447793</v>
       </c>
       <c r="R75" t="n">
-        <v>6814779</v>
+        <v>6815007</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8053,7 +8054,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8063,7 +8064,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8090,10 +8091,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129125738</v>
+        <v>129125812</v>
       </c>
       <c r="B76" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8101,39 +8102,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447735</v>
+        <v>447682</v>
       </c>
       <c r="R76" t="n">
-        <v>6814890</v>
+        <v>6814779</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8165,7 +8161,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8175,12 +8171,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8207,10 +8198,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129125755</v>
+        <v>129125738</v>
       </c>
       <c r="B77" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8218,34 +8209,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447756</v>
+        <v>447735</v>
       </c>
       <c r="R77" t="n">
-        <v>6814990</v>
+        <v>6814890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8277,7 +8273,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8287,7 +8283,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8296,7 +8297,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125771</v>
+        <v>129125729</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447925</v>
+        <v>448039</v>
       </c>
       <c r="R79" t="n">
-        <v>6815103</v>
+        <v>6815229</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129125867</v>
+        <v>129125751</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>81020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>448088</v>
+        <v>447952</v>
       </c>
       <c r="R80" t="n">
-        <v>6815222</v>
+        <v>6814974</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129125824</v>
+        <v>129125730</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8652,21 +8652,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447761</v>
+        <v>448098</v>
       </c>
       <c r="R81" t="n">
-        <v>6815045</v>
+        <v>6815212</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8748,10 +8748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129125729</v>
+        <v>129125873</v>
       </c>
       <c r="B82" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,21 +8759,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448039</v>
+        <v>448163</v>
       </c>
       <c r="R82" t="n">
-        <v>6815229</v>
+        <v>6815302</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8855,10 +8855,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129125751</v>
+        <v>129125771</v>
       </c>
       <c r="B83" t="n">
-        <v>81020</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8866,21 +8866,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447952</v>
+        <v>447925</v>
       </c>
       <c r="R83" t="n">
-        <v>6814974</v>
+        <v>6815103</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125730</v>
+        <v>129125853</v>
       </c>
       <c r="B84" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8973,21 +8973,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448098</v>
+        <v>447853</v>
       </c>
       <c r="R84" t="n">
-        <v>6815212</v>
+        <v>6814972</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125873</v>
+        <v>129125867</v>
       </c>
       <c r="B85" t="n">
         <v>79035</v>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448163</v>
+        <v>448088</v>
       </c>
       <c r="R85" t="n">
-        <v>6815302</v>
+        <v>6815222</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9176,7 +9176,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125853</v>
+        <v>129125824</v>
       </c>
       <c r="B86" t="n">
         <v>79035</v>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447853</v>
+        <v>447761</v>
       </c>
       <c r="R86" t="n">
-        <v>6814972</v>
+        <v>6815045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125753</v>
+        <v>129125874</v>
       </c>
       <c r="B91" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447766</v>
+        <v>448182</v>
       </c>
       <c r="R91" t="n">
-        <v>6814899</v>
+        <v>6815308</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,12 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9814,7 +9809,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9833,7 +9827,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125874</v>
+        <v>129125809</v>
       </c>
       <c r="B92" t="n">
         <v>79035</v>
@@ -9868,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>448182</v>
+        <v>447763</v>
       </c>
       <c r="R92" t="n">
-        <v>6815308</v>
+        <v>6814923</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9903,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9913,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9940,7 +9934,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125809</v>
+        <v>129125831</v>
       </c>
       <c r="B93" t="n">
         <v>79035</v>
@@ -9975,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447763</v>
+        <v>447755</v>
       </c>
       <c r="R93" t="n">
-        <v>6814923</v>
+        <v>6814973</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10010,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10020,7 +10014,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10047,7 +10041,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125831</v>
+        <v>129125772</v>
       </c>
       <c r="B94" t="n">
         <v>79035</v>
@@ -10082,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447755</v>
+        <v>447920</v>
       </c>
       <c r="R94" t="n">
-        <v>6814973</v>
+        <v>6815082</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10117,7 +10111,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10127,7 +10121,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10154,10 +10148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125772</v>
+        <v>129125753</v>
       </c>
       <c r="B95" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10165,21 +10159,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10189,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447920</v>
+        <v>447766</v>
       </c>
       <c r="R95" t="n">
-        <v>6815082</v>
+        <v>6814899</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10224,7 +10218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10234,7 +10228,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10243,6 +10242,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10689,7 +10689,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129125888</v>
+        <v>129125858</v>
       </c>
       <c r="B100" t="n">
         <v>79035</v>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>448042</v>
+        <v>447914</v>
       </c>
       <c r="R100" t="n">
-        <v>6815053</v>
+        <v>6815024</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10796,7 +10796,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129125858</v>
+        <v>129125836</v>
       </c>
       <c r="B101" t="n">
         <v>79035</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447914</v>
+        <v>447789</v>
       </c>
       <c r="R101" t="n">
-        <v>6815024</v>
+        <v>6815016</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10903,32 +10903,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129125836</v>
+        <v>129125746</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447789</v>
+        <v>448129</v>
       </c>
       <c r="R102" t="n">
-        <v>6815016</v>
+        <v>6815200</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11010,10 +11010,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129125741</v>
+        <v>129125719</v>
       </c>
       <c r="B103" t="n">
-        <v>57720</v>
+        <v>79067</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11021,39 +11021,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447902</v>
+        <v>447855</v>
       </c>
       <c r="R103" t="n">
-        <v>6814922</v>
+        <v>6814877</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11085,7 +11080,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11095,7 +11090,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11122,32 +11117,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129125746</v>
+        <v>129125888</v>
       </c>
       <c r="B104" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11157,10 +11152,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448129</v>
+        <v>448042</v>
       </c>
       <c r="R104" t="n">
-        <v>6815200</v>
+        <v>6815053</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11192,7 +11187,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11202,7 +11197,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11229,10 +11224,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125719</v>
+        <v>129125741</v>
       </c>
       <c r="B105" t="n">
-        <v>79067</v>
+        <v>57720</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11240,34 +11235,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447855</v>
+        <v>447902</v>
       </c>
       <c r="R105" t="n">
-        <v>6814877</v>
+        <v>6814922</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11871,32 +11871,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129125728</v>
+        <v>129125721</v>
       </c>
       <c r="B111" t="n">
-        <v>91491</v>
+        <v>79067</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447872</v>
+        <v>447943</v>
       </c>
       <c r="R111" t="n">
-        <v>6815131</v>
+        <v>6814947</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11978,32 +11978,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125891</v>
+        <v>129125728</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>91491</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>448003</v>
+        <v>447872</v>
       </c>
       <c r="R112" t="n">
-        <v>6815088</v>
+        <v>6815131</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,10 +12085,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125721</v>
+        <v>129125807</v>
       </c>
       <c r="B113" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12096,21 +12096,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447943</v>
+        <v>447797</v>
       </c>
       <c r="R113" t="n">
-        <v>6814947</v>
+        <v>6814950</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,7 +12192,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125807</v>
+        <v>129125863</v>
       </c>
       <c r="B114" t="n">
         <v>79035</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447797</v>
+        <v>447878</v>
       </c>
       <c r="R114" t="n">
-        <v>6814950</v>
+        <v>6815153</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12299,7 +12299,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129125863</v>
+        <v>129125891</v>
       </c>
       <c r="B115" t="n">
         <v>79035</v>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447878</v>
+        <v>448003</v>
       </c>
       <c r="R115" t="n">
-        <v>6815153</v>
+        <v>6815088</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12727,32 +12727,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129125750</v>
+        <v>129125877</v>
       </c>
       <c r="B119" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447714</v>
+        <v>448126</v>
       </c>
       <c r="R119" t="n">
-        <v>6815023</v>
+        <v>6815198</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12834,7 +12834,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125877</v>
+        <v>129125894</v>
       </c>
       <c r="B120" t="n">
         <v>79035</v>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448126</v>
+        <v>447978</v>
       </c>
       <c r="R120" t="n">
-        <v>6815198</v>
+        <v>6815111</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125894</v>
+        <v>129125850</v>
       </c>
       <c r="B121" t="n">
         <v>79035</v>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447978</v>
+        <v>447844</v>
       </c>
       <c r="R121" t="n">
-        <v>6815111</v>
+        <v>6815026</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13048,7 +13048,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129125850</v>
+        <v>129125827</v>
       </c>
       <c r="B122" t="n">
         <v>79035</v>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447844</v>
+        <v>447767</v>
       </c>
       <c r="R122" t="n">
-        <v>6815026</v>
+        <v>6815014</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13155,7 +13155,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125827</v>
+        <v>129125811</v>
       </c>
       <c r="B123" t="n">
         <v>79035</v>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447767</v>
+        <v>447716</v>
       </c>
       <c r="R123" t="n">
-        <v>6815014</v>
+        <v>6814829</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,7 +13262,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125811</v>
+        <v>129125865</v>
       </c>
       <c r="B124" t="n">
         <v>79035</v>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447716</v>
+        <v>448049</v>
       </c>
       <c r="R124" t="n">
-        <v>6814829</v>
+        <v>6815224</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,7 +13369,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125865</v>
+        <v>129125859</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448049</v>
+        <v>447887</v>
       </c>
       <c r="R125" t="n">
-        <v>6815224</v>
+        <v>6815043</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,7 +13476,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125859</v>
+        <v>129125852</v>
       </c>
       <c r="B126" t="n">
         <v>79035</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447887</v>
+        <v>447839</v>
       </c>
       <c r="R126" t="n">
-        <v>6815043</v>
+        <v>6814995</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125852</v>
+        <v>129125882</v>
       </c>
       <c r="B127" t="n">
         <v>79035</v>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447839</v>
+        <v>448089</v>
       </c>
       <c r="R127" t="n">
-        <v>6814995</v>
+        <v>6815086</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13690,7 +13690,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129125882</v>
+        <v>129125845</v>
       </c>
       <c r="B128" t="n">
         <v>79035</v>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>448089</v>
+        <v>447801</v>
       </c>
       <c r="R128" t="n">
-        <v>6815086</v>
+        <v>6815082</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13797,7 +13797,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125845</v>
+        <v>129125791</v>
       </c>
       <c r="B129" t="n">
         <v>79035</v>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447801</v>
+        <v>447839</v>
       </c>
       <c r="R129" t="n">
-        <v>6815082</v>
+        <v>6814871</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,32 +13904,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125791</v>
+        <v>129125750</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447839</v>
+        <v>447714</v>
       </c>
       <c r="R130" t="n">
-        <v>6814871</v>
+        <v>6815023</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,32 +14011,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125743</v>
+        <v>129125770</v>
       </c>
       <c r="B131" t="n">
-        <v>80044</v>
+        <v>79035</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447735</v>
+        <v>447916</v>
       </c>
       <c r="R131" t="n">
-        <v>6814890</v>
+        <v>6815113</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,12 +14091,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14123,7 +14118,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125770</v>
+        <v>129125844</v>
       </c>
       <c r="B132" t="n">
         <v>79035</v>
@@ -14158,10 +14153,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447916</v>
+        <v>447808</v>
       </c>
       <c r="R132" t="n">
-        <v>6815113</v>
+        <v>6815078</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14193,7 +14188,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14203,7 +14198,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14230,32 +14225,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125844</v>
+        <v>129125743</v>
       </c>
       <c r="B133" t="n">
-        <v>79035</v>
+        <v>80044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14265,10 +14260,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447808</v>
+        <v>447735</v>
       </c>
       <c r="R133" t="n">
-        <v>6815078</v>
+        <v>6814890</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14300,7 +14295,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14310,7 +14305,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15305,27 +15305,27 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125899</v>
+        <v>129125775</v>
       </c>
       <c r="B143" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447580</v>
+        <v>447916</v>
       </c>
       <c r="R143" t="n">
-        <v>6814868</v>
+        <v>6815021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,7 +15412,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125775</v>
+        <v>129125828</v>
       </c>
       <c r="B144" t="n">
         <v>79035</v>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447916</v>
+        <v>447781</v>
       </c>
       <c r="R144" t="n">
-        <v>6815021</v>
+        <v>6815009</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,7 +15519,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125828</v>
+        <v>129125839</v>
       </c>
       <c r="B145" t="n">
         <v>79035</v>
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447781</v>
+        <v>447805</v>
       </c>
       <c r="R145" t="n">
-        <v>6815009</v>
+        <v>6815025</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15626,7 +15626,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125839</v>
+        <v>129125792</v>
       </c>
       <c r="B146" t="n">
         <v>79035</v>
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447805</v>
+        <v>447812</v>
       </c>
       <c r="R146" t="n">
-        <v>6815025</v>
+        <v>6814852</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,7 +15733,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125792</v>
+        <v>129125796</v>
       </c>
       <c r="B147" t="n">
         <v>79035</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447812</v>
+        <v>447749</v>
       </c>
       <c r="R147" t="n">
-        <v>6814852</v>
+        <v>6814850</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,7 +15840,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125796</v>
+        <v>129125826</v>
       </c>
       <c r="B148" t="n">
         <v>79035</v>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447749</v>
+        <v>447765</v>
       </c>
       <c r="R148" t="n">
-        <v>6814850</v>
+        <v>6815023</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15947,27 +15947,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129125826</v>
+        <v>129125899</v>
       </c>
       <c r="B149" t="n">
-        <v>79035</v>
+        <v>80175</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>447765</v>
+        <v>447580</v>
       </c>
       <c r="R149" t="n">
-        <v>6815023</v>
+        <v>6814868</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16054,32 +16054,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129125749</v>
+        <v>129125720</v>
       </c>
       <c r="B150" t="n">
-        <v>80176</v>
+        <v>79067</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16089,10 +16089,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>447581</v>
+        <v>447936</v>
       </c>
       <c r="R150" t="n">
-        <v>6814869</v>
+        <v>6814995</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16268,7 +16268,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125830</v>
+        <v>129125806</v>
       </c>
       <c r="B152" t="n">
         <v>79035</v>
@@ -16303,10 +16303,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447767</v>
+        <v>447816</v>
       </c>
       <c r="R152" t="n">
-        <v>6814993</v>
+        <v>6814979</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,7 +16375,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125799</v>
+        <v>129125830</v>
       </c>
       <c r="B153" t="n">
         <v>79035</v>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>447804</v>
+        <v>447767</v>
       </c>
       <c r="R153" t="n">
-        <v>6814911</v>
+        <v>6814993</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16482,7 +16482,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125769</v>
+        <v>129125799</v>
       </c>
       <c r="B154" t="n">
         <v>79035</v>
@@ -16517,10 +16517,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>447912</v>
+        <v>447804</v>
       </c>
       <c r="R154" t="n">
-        <v>6815110</v>
+        <v>6814911</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16589,7 +16589,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125768</v>
+        <v>129125769</v>
       </c>
       <c r="B155" t="n">
         <v>79035</v>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447909</v>
+        <v>447912</v>
       </c>
       <c r="R155" t="n">
-        <v>6815119</v>
+        <v>6815110</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16696,7 +16696,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125804</v>
+        <v>129125768</v>
       </c>
       <c r="B156" t="n">
         <v>79035</v>
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447840</v>
+        <v>447909</v>
       </c>
       <c r="R156" t="n">
-        <v>6814978</v>
+        <v>6815119</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16803,7 +16803,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125801</v>
+        <v>129125804</v>
       </c>
       <c r="B157" t="n">
         <v>79035</v>
@@ -16838,10 +16838,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447814</v>
+        <v>447840</v>
       </c>
       <c r="R157" t="n">
-        <v>6814948</v>
+        <v>6814978</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16910,7 +16910,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125878</v>
+        <v>129125801</v>
       </c>
       <c r="B158" t="n">
         <v>79035</v>
@@ -16945,10 +16945,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>448121</v>
+        <v>447814</v>
       </c>
       <c r="R158" t="n">
-        <v>6815175</v>
+        <v>6814948</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17017,7 +17017,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129125869</v>
+        <v>129125878</v>
       </c>
       <c r="B159" t="n">
         <v>79035</v>
@@ -17052,10 +17052,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>448114</v>
+        <v>448121</v>
       </c>
       <c r="R159" t="n">
-        <v>6815209</v>
+        <v>6815175</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17087,7 +17087,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17097,7 +17097,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17124,7 +17124,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125849</v>
+        <v>129125869</v>
       </c>
       <c r="B160" t="n">
         <v>79035</v>
@@ -17159,10 +17159,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>447825</v>
+        <v>448114</v>
       </c>
       <c r="R160" t="n">
-        <v>6815056</v>
+        <v>6815209</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17231,50 +17231,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125731</v>
+        <v>129125849</v>
       </c>
       <c r="B161" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>448128</v>
+        <v>447825</v>
       </c>
       <c r="R161" t="n">
-        <v>6815234</v>
+        <v>6815056</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17306,7 +17301,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17316,7 +17311,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17343,32 +17338,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125720</v>
+        <v>129125749</v>
       </c>
       <c r="B162" t="n">
-        <v>79067</v>
+        <v>80176</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17378,10 +17373,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>447936</v>
+        <v>447581</v>
       </c>
       <c r="R162" t="n">
-        <v>6814995</v>
+        <v>6814869</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17413,7 +17408,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17423,7 +17418,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17450,45 +17445,50 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125806</v>
+        <v>129125731</v>
       </c>
       <c r="B163" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>447816</v>
+        <v>448128</v>
       </c>
       <c r="R163" t="n">
-        <v>6814979</v>
+        <v>6815234</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17520,7 +17520,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17530,7 +17530,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18231,10 +18231,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129125739</v>
+        <v>129125724</v>
       </c>
       <c r="B170" t="n">
-        <v>57720</v>
+        <v>79067</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18242,39 +18242,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>448089</v>
+        <v>447803</v>
       </c>
       <c r="R170" t="n">
-        <v>6815093</v>
+        <v>6815095</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18306,7 +18301,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18316,12 +18311,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18348,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125740</v>
+        <v>129125723</v>
       </c>
       <c r="B171" t="n">
-        <v>57720</v>
+        <v>79067</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18359,39 +18349,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>447580</v>
+        <v>447751</v>
       </c>
       <c r="R171" t="n">
-        <v>6814929</v>
+        <v>6814901</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18423,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18433,7 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18460,7 +18445,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129125724</v>
+        <v>129125727</v>
       </c>
       <c r="B172" t="n">
         <v>79067</v>
@@ -18495,10 +18480,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>447803</v>
+        <v>448008</v>
       </c>
       <c r="R172" t="n">
-        <v>6815095</v>
+        <v>6815080</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18530,7 +18515,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18540,7 +18525,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18567,10 +18552,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125723</v>
+        <v>129125833</v>
       </c>
       <c r="B173" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18578,21 +18563,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18602,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>447751</v>
+        <v>447772</v>
       </c>
       <c r="R173" t="n">
-        <v>6814901</v>
+        <v>6814969</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18637,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18647,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18674,10 +18659,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125727</v>
+        <v>129125880</v>
       </c>
       <c r="B174" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18685,21 +18670,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18709,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>448008</v>
+        <v>448107</v>
       </c>
       <c r="R174" t="n">
-        <v>6815080</v>
+        <v>6815120</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18744,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18754,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18781,10 +18766,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125718</v>
+        <v>129125810</v>
       </c>
       <c r="B175" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18792,21 +18777,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18816,10 +18801,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447772</v>
+        <v>447736</v>
       </c>
       <c r="R175" t="n">
-        <v>6815035</v>
+        <v>6814886</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18851,7 +18836,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18861,7 +18846,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18888,32 +18873,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125763</v>
+        <v>129125718</v>
       </c>
       <c r="B176" t="n">
-        <v>82994</v>
+        <v>83011</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18923,10 +18908,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>447801</v>
+        <v>447772</v>
       </c>
       <c r="R176" t="n">
-        <v>6814957</v>
+        <v>6815035</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18958,7 +18943,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18968,7 +18953,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18995,7 +18980,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125833</v>
+        <v>129125861</v>
       </c>
       <c r="B177" t="n">
         <v>79035</v>
@@ -19030,10 +19015,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>447772</v>
+        <v>447887</v>
       </c>
       <c r="R177" t="n">
-        <v>6814969</v>
+        <v>6815067</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19065,7 +19050,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19075,7 +19060,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19102,7 +19087,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129125880</v>
+        <v>129125832</v>
       </c>
       <c r="B178" t="n">
         <v>79035</v>
@@ -19137,10 +19122,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>448107</v>
+        <v>447762</v>
       </c>
       <c r="R178" t="n">
-        <v>6815120</v>
+        <v>6814968</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19172,7 +19157,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19182,7 +19167,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19209,7 +19194,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129125810</v>
+        <v>129125862</v>
       </c>
       <c r="B179" t="n">
         <v>79035</v>
@@ -19244,10 +19229,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>447736</v>
+        <v>447867</v>
       </c>
       <c r="R179" t="n">
-        <v>6814886</v>
+        <v>6815109</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19279,7 +19264,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19289,7 +19274,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19316,32 +19301,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129125861</v>
+        <v>129125763</v>
       </c>
       <c r="B180" t="n">
-        <v>79035</v>
+        <v>82994</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19351,10 +19336,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>447887</v>
+        <v>447801</v>
       </c>
       <c r="R180" t="n">
-        <v>6815067</v>
+        <v>6814957</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19386,7 +19371,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19396,7 +19381,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19423,7 +19408,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129125832</v>
+        <v>129125842</v>
       </c>
       <c r="B181" t="n">
         <v>79035</v>
@@ -19458,10 +19443,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>447762</v>
+        <v>447813</v>
       </c>
       <c r="R181" t="n">
-        <v>6814968</v>
+        <v>6815044</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19493,7 +19478,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19503,7 +19488,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19530,10 +19515,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125862</v>
+        <v>129125739</v>
       </c>
       <c r="B182" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19541,34 +19526,39 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>447867</v>
+        <v>448089</v>
       </c>
       <c r="R182" t="n">
-        <v>6815109</v>
+        <v>6815093</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19600,7 +19590,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19610,7 +19600,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19637,10 +19632,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125842</v>
+        <v>129125740</v>
       </c>
       <c r="B183" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19648,34 +19643,39 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>447813</v>
+        <v>447580</v>
       </c>
       <c r="R183" t="n">
-        <v>6815044</v>
+        <v>6814929</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19851,10 +19851,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129125876</v>
+        <v>129125725</v>
       </c>
       <c r="B185" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19862,21 +19862,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19886,10 +19886,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>448131</v>
+        <v>448124</v>
       </c>
       <c r="R185" t="n">
-        <v>6815201</v>
+        <v>6815167</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19958,7 +19958,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129125780</v>
+        <v>129125876</v>
       </c>
       <c r="B186" t="n">
         <v>79035</v>
@@ -19993,10 +19993,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>447958</v>
+        <v>448131</v>
       </c>
       <c r="R186" t="n">
-        <v>6814987</v>
+        <v>6815201</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20065,7 +20065,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125793</v>
+        <v>129125780</v>
       </c>
       <c r="B187" t="n">
         <v>79035</v>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>447819</v>
+        <v>447958</v>
       </c>
       <c r="R187" t="n">
-        <v>6814842</v>
+        <v>6814987</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20172,7 +20172,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129125784</v>
+        <v>129125793</v>
       </c>
       <c r="B188" t="n">
         <v>79035</v>
@@ -20207,10 +20207,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>447943</v>
+        <v>447819</v>
       </c>
       <c r="R188" t="n">
-        <v>6814947</v>
+        <v>6814842</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20279,7 +20279,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125783</v>
+        <v>129125784</v>
       </c>
       <c r="B189" t="n">
         <v>79035</v>
@@ -20314,10 +20314,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>447952</v>
+        <v>447943</v>
       </c>
       <c r="R189" t="n">
-        <v>6814960</v>
+        <v>6814947</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20386,7 +20386,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129125815</v>
+        <v>129125783</v>
       </c>
       <c r="B190" t="n">
         <v>79035</v>
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>447586</v>
+        <v>447952</v>
       </c>
       <c r="R190" t="n">
-        <v>6814809</v>
+        <v>6814960</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20493,7 +20493,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129125829</v>
+        <v>129125815</v>
       </c>
       <c r="B191" t="n">
         <v>79035</v>
@@ -20528,10 +20528,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>447771</v>
+        <v>447586</v>
       </c>
       <c r="R191" t="n">
-        <v>6815000</v>
+        <v>6814809</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20600,10 +20600,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129125896</v>
+        <v>129125829</v>
       </c>
       <c r="B192" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20611,39 +20611,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>447925</v>
+        <v>447771</v>
       </c>
       <c r="R192" t="n">
-        <v>6815105</v>
+        <v>6815000</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20675,7 +20670,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20685,7 +20680,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20819,10 +20814,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129125725</v>
+        <v>129125896</v>
       </c>
       <c r="B194" t="n">
-        <v>79067</v>
+        <v>57723</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20830,34 +20825,39 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>448124</v>
+        <v>447925</v>
       </c>
       <c r="R194" t="n">
-        <v>6815167</v>
+        <v>6815105</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20926,32 +20926,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125893</v>
+        <v>129125898</v>
       </c>
       <c r="B195" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447992</v>
+        <v>447585</v>
       </c>
       <c r="R195" t="n">
-        <v>6815102</v>
+        <v>6814810</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21033,7 +21033,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129125866</v>
+        <v>129125893</v>
       </c>
       <c r="B196" t="n">
         <v>79035</v>
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>448062</v>
+        <v>447992</v>
       </c>
       <c r="R196" t="n">
-        <v>6815224</v>
+        <v>6815102</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21140,7 +21140,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125890</v>
+        <v>129125866</v>
       </c>
       <c r="B197" t="n">
         <v>79035</v>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>448015</v>
+        <v>448062</v>
       </c>
       <c r="R197" t="n">
-        <v>6815065</v>
+        <v>6815224</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,7 +21247,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125857</v>
+        <v>129125890</v>
       </c>
       <c r="B198" t="n">
         <v>79035</v>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>447909</v>
+        <v>448015</v>
       </c>
       <c r="R198" t="n">
-        <v>6815011</v>
+        <v>6815065</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,7 +21354,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125834</v>
+        <v>129125857</v>
       </c>
       <c r="B199" t="n">
         <v>79035</v>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>447788</v>
+        <v>447909</v>
       </c>
       <c r="R199" t="n">
-        <v>6814995</v>
+        <v>6815011</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,7 +21461,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125847</v>
+        <v>129125834</v>
       </c>
       <c r="B200" t="n">
         <v>79035</v>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447814</v>
+        <v>447788</v>
       </c>
       <c r="R200" t="n">
-        <v>6815081</v>
+        <v>6814995</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21568,32 +21568,32 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129125898</v>
+        <v>129125847</v>
       </c>
       <c r="B201" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>447585</v>
+        <v>447814</v>
       </c>
       <c r="R201" t="n">
-        <v>6814810</v>
+        <v>6815081</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21889,7 +21889,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129125864</v>
+        <v>129125788</v>
       </c>
       <c r="B204" t="n">
         <v>79035</v>
@@ -21924,10 +21924,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>448025</v>
+        <v>447870</v>
       </c>
       <c r="R204" t="n">
-        <v>6815228</v>
+        <v>6814898</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21996,7 +21996,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129125881</v>
+        <v>129125875</v>
       </c>
       <c r="B205" t="n">
         <v>79035</v>
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>448111</v>
+        <v>448141</v>
       </c>
       <c r="R205" t="n">
-        <v>6815099</v>
+        <v>6815210</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22103,7 +22103,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129125788</v>
+        <v>129125892</v>
       </c>
       <c r="B206" t="n">
         <v>79035</v>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>447870</v>
+        <v>448002</v>
       </c>
       <c r="R206" t="n">
-        <v>6814898</v>
+        <v>6815094</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22210,7 +22210,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129125875</v>
+        <v>129125864</v>
       </c>
       <c r="B207" t="n">
         <v>79035</v>
@@ -22245,10 +22245,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>448141</v>
+        <v>448025</v>
       </c>
       <c r="R207" t="n">
-        <v>6815210</v>
+        <v>6815228</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22317,7 +22317,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129125892</v>
+        <v>129125881</v>
       </c>
       <c r="B208" t="n">
         <v>79035</v>
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>448002</v>
+        <v>448111</v>
       </c>
       <c r="R208" t="n">
-        <v>6815094</v>
+        <v>6815099</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22387,7 +22387,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22424,32 +22424,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129125735</v>
+        <v>129125803</v>
       </c>
       <c r="B209" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22459,10 +22459,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>447805</v>
+        <v>447837</v>
       </c>
       <c r="R209" t="n">
-        <v>6815002</v>
+        <v>6814958</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22531,7 +22531,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129125803</v>
+        <v>129125884</v>
       </c>
       <c r="B210" t="n">
         <v>79035</v>
@@ -22566,10 +22566,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>447837</v>
+        <v>448089</v>
       </c>
       <c r="R210" t="n">
-        <v>6814958</v>
+        <v>6815055</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22638,7 +22638,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129125884</v>
+        <v>129125825</v>
       </c>
       <c r="B211" t="n">
         <v>79035</v>
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>448089</v>
+        <v>447766</v>
       </c>
       <c r="R211" t="n">
-        <v>6815055</v>
+        <v>6815038</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22745,7 +22745,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129125825</v>
+        <v>129125762</v>
       </c>
       <c r="B212" t="n">
         <v>79035</v>
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>447766</v>
+        <v>448058</v>
       </c>
       <c r="R212" t="n">
-        <v>6815038</v>
+        <v>6815046</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22852,7 +22852,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129125762</v>
+        <v>129125883</v>
       </c>
       <c r="B213" t="n">
         <v>79035</v>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>448058</v>
+        <v>448080</v>
       </c>
       <c r="R213" t="n">
-        <v>6815046</v>
+        <v>6815060</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22959,32 +22959,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129125883</v>
+        <v>129125735</v>
       </c>
       <c r="B214" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22994,10 +22994,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>448080</v>
+        <v>447805</v>
       </c>
       <c r="R214" t="n">
-        <v>6815060</v>
+        <v>6815002</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24141,7 +24141,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125790</v>
+        <v>129125776</v>
       </c>
       <c r="B225" t="n">
         <v>79035</v>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447855</v>
+        <v>447923</v>
       </c>
       <c r="R225" t="n">
-        <v>6814877</v>
+        <v>6814998</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,7 +24248,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125817</v>
+        <v>129125790</v>
       </c>
       <c r="B226" t="n">
         <v>79035</v>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447580</v>
+        <v>447855</v>
       </c>
       <c r="R226" t="n">
-        <v>6814929</v>
+        <v>6814877</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,7 +24355,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125794</v>
+        <v>129125817</v>
       </c>
       <c r="B227" t="n">
         <v>79035</v>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447798</v>
+        <v>447580</v>
       </c>
       <c r="R227" t="n">
-        <v>6814819</v>
+        <v>6814929</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24462,7 +24462,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129125889</v>
+        <v>129125794</v>
       </c>
       <c r="B228" t="n">
         <v>79035</v>
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>448024</v>
+        <v>447798</v>
       </c>
       <c r="R228" t="n">
-        <v>6815046</v>
+        <v>6814819</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24677,7 +24677,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125776</v>
+        <v>129125889</v>
       </c>
       <c r="B230" t="n">
         <v>79035</v>
@@ -24712,10 +24712,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>447923</v>
+        <v>448024</v>
       </c>
       <c r="R230" t="n">
-        <v>6814998</v>
+        <v>6815046</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24747,7 +24747,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24757,7 +24757,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD230" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128605858</v>
+        <v>128605860</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448017</v>
+        <v>448020</v>
       </c>
       <c r="R2" t="n">
-        <v>6814944</v>
+        <v>6815080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128605839</v>
+        <v>128605869</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447574</v>
+        <v>447681</v>
       </c>
       <c r="R3" t="n">
-        <v>6814884</v>
+        <v>6815015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128605860</v>
+        <v>128605858</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448020</v>
+        <v>448017</v>
       </c>
       <c r="R4" t="n">
-        <v>6815080</v>
+        <v>6814944</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128605869</v>
+        <v>128605839</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +982,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447681</v>
+        <v>447574</v>
       </c>
       <c r="R5" t="n">
-        <v>6815015</v>
+        <v>6814884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128605855</v>
+        <v>128605876</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447946</v>
+        <v>447585</v>
       </c>
       <c r="R6" t="n">
-        <v>6814990</v>
+        <v>6814852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128605876</v>
+        <v>128605855</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447585</v>
+        <v>447946</v>
       </c>
       <c r="R7" t="n">
-        <v>6814852</v>
+        <v>6814990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128605886</v>
+        <v>128605829</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447905</v>
+        <v>447634</v>
       </c>
       <c r="R9" t="n">
-        <v>6815066</v>
+        <v>6814941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128605887</v>
+        <v>128605886</v>
       </c>
       <c r="B10" t="n">
         <v>79035</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447907</v>
+        <v>447905</v>
       </c>
       <c r="R10" t="n">
-        <v>6815070</v>
+        <v>6815066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128605829</v>
+        <v>128605849</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447634</v>
+        <v>447655</v>
       </c>
       <c r="R11" t="n">
-        <v>6814941</v>
+        <v>6814988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128605849</v>
+        <v>128605887</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,21 +1674,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447655</v>
+        <v>447907</v>
       </c>
       <c r="R12" t="n">
-        <v>6814988</v>
+        <v>6815070</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128605832</v>
+        <v>128605885</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,42 +2078,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448062</v>
+        <v>447840</v>
       </c>
       <c r="R16" t="n">
-        <v>6815199</v>
+        <v>6815104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128605885</v>
+        <v>128605888</v>
       </c>
       <c r="B17" t="n">
         <v>79035</v>
@@ -2207,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447840</v>
+        <v>447929</v>
       </c>
       <c r="R17" t="n">
-        <v>6815104</v>
+        <v>6815007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,6 +2235,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,10 +2266,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128605888</v>
+        <v>128605853</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2280,21 +2277,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2301,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447929</v>
+        <v>447773</v>
       </c>
       <c r="R18" t="n">
-        <v>6815007</v>
+        <v>6814906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,11 +2337,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2371,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128605853</v>
+        <v>128605832</v>
       </c>
       <c r="B19" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2382,34 +2374,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447773</v>
+        <v>448062</v>
       </c>
       <c r="R19" t="n">
-        <v>6814906</v>
+        <v>6815199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128605868</v>
+        <v>128605854</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447751</v>
+        <v>447840</v>
       </c>
       <c r="R21" t="n">
-        <v>6815024</v>
+        <v>6815042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128605854</v>
+        <v>128605868</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447840</v>
+        <v>447751</v>
       </c>
       <c r="R22" t="n">
-        <v>6815042</v>
+        <v>6815024</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128605873</v>
+        <v>128605865</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447570</v>
+        <v>447930</v>
       </c>
       <c r="R24" t="n">
-        <v>6814915</v>
+        <v>6815173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128605863</v>
+        <v>128605873</v>
       </c>
       <c r="B25" t="n">
         <v>79035</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448048</v>
+        <v>447570</v>
       </c>
       <c r="R25" t="n">
-        <v>6815201</v>
+        <v>6814915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128605865</v>
+        <v>128605863</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447930</v>
+        <v>448048</v>
       </c>
       <c r="R26" t="n">
-        <v>6815173</v>
+        <v>6815201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128605835</v>
+        <v>128605844</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3182,42 +3182,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447581</v>
+        <v>447771</v>
       </c>
       <c r="R27" t="n">
-        <v>6814933</v>
+        <v>6814896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3276,10 +3268,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128605844</v>
+        <v>128605835</v>
       </c>
       <c r="B28" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,34 +3279,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447771</v>
+        <v>447581</v>
       </c>
       <c r="R28" t="n">
-        <v>6814896</v>
+        <v>6814933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128605889</v>
+        <v>128605830</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447989</v>
+        <v>447941</v>
       </c>
       <c r="R32" t="n">
-        <v>6814944</v>
+        <v>6814981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3767,7 +3762,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128605891</v>
+        <v>128605889</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447935</v>
+        <v>447989</v>
       </c>
       <c r="R33" t="n">
-        <v>6815088</v>
+        <v>6814944</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3842,7 +3837,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
+          <t>Rikligt med garnlav inom en radie av 30 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128605830</v>
+        <v>128605891</v>
       </c>
       <c r="B34" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3875,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447941</v>
+        <v>447935</v>
       </c>
       <c r="R34" t="n">
-        <v>6814981</v>
+        <v>6815088</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,6 +3935,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30 m. Tallstammarna är draperade!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128605874</v>
+        <v>128605850</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4375,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447564</v>
+        <v>447632</v>
       </c>
       <c r="R39" t="n">
-        <v>6814901</v>
+        <v>6814941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128605850</v>
+        <v>128605874</v>
       </c>
       <c r="B40" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447632</v>
+        <v>447564</v>
       </c>
       <c r="R40" t="n">
-        <v>6814941</v>
+        <v>6814901</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128605856</v>
+        <v>128605847</v>
       </c>
       <c r="B41" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447950</v>
+        <v>448022</v>
       </c>
       <c r="R41" t="n">
-        <v>6814974</v>
+        <v>6814932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128605893</v>
+        <v>128605894</v>
       </c>
       <c r="B42" t="n">
         <v>79035</v>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447907</v>
+        <v>447910</v>
       </c>
       <c r="R42" t="n">
-        <v>6815150</v>
+        <v>6815145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4726,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4757,7 +4752,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128605894</v>
+        <v>128605893</v>
       </c>
       <c r="B43" t="n">
         <v>79035</v>
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447910</v>
+        <v>447907</v>
       </c>
       <c r="R43" t="n">
-        <v>6815145</v>
+        <v>6815150</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4828,6 +4823,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en  radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4854,10 +4854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128605847</v>
+        <v>128605856</v>
       </c>
       <c r="B44" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448022</v>
+        <v>447950</v>
       </c>
       <c r="R44" t="n">
-        <v>6814932</v>
+        <v>6814974</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4951,10 +4951,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128605864</v>
+        <v>128605842</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4962,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448027</v>
+        <v>447628</v>
       </c>
       <c r="R45" t="n">
-        <v>6815200</v>
+        <v>6814833</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5022,11 +5022,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5048,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128605842</v>
+        <v>128605864</v>
       </c>
       <c r="B46" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5059,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447628</v>
+        <v>448027</v>
       </c>
       <c r="R46" t="n">
-        <v>6814833</v>
+        <v>6815200</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5124,6 +5119,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128605875</v>
+        <v>128605831</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,21 +5457,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447577</v>
+        <v>447976</v>
       </c>
       <c r="R50" t="n">
-        <v>6814894</v>
+        <v>6814958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128605831</v>
+        <v>128605875</v>
       </c>
       <c r="B51" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447976</v>
+        <v>447577</v>
       </c>
       <c r="R51" t="n">
-        <v>6814958</v>
+        <v>6814894</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128605871</v>
+        <v>128605838</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5748,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447606</v>
+        <v>447770</v>
       </c>
       <c r="R53" t="n">
-        <v>6814958</v>
+        <v>6814909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,7 +5842,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128605884</v>
+        <v>128605871</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -5869,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447831</v>
+        <v>447606</v>
       </c>
       <c r="R54" t="n">
-        <v>6815067</v>
+        <v>6814958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5931,10 +5939,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128605838</v>
+        <v>128605890</v>
       </c>
       <c r="B55" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,42 +5950,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skrikberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447770</v>
+        <v>448003</v>
       </c>
       <c r="R55" t="n">
-        <v>6814909</v>
+        <v>6814939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128605890</v>
+        <v>128605884</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>448003</v>
+        <v>447831</v>
       </c>
       <c r="R57" t="n">
-        <v>6814939</v>
+        <v>6815067</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128605881</v>
+        <v>128605841</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6435,21 +6435,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447753</v>
+        <v>447636</v>
       </c>
       <c r="R60" t="n">
-        <v>6814819</v>
+        <v>6814937</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6521,10 +6521,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128605880</v>
+        <v>128605843</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447716</v>
+        <v>447744</v>
       </c>
       <c r="R61" t="n">
-        <v>6814847</v>
+        <v>6814896</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128605882</v>
+        <v>128605881</v>
       </c>
       <c r="B62" t="n">
         <v>79035</v>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447789</v>
+        <v>447753</v>
       </c>
       <c r="R62" t="n">
-        <v>6814910</v>
+        <v>6814819</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6689,11 +6689,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6720,10 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128605841</v>
+        <v>128605880</v>
       </c>
       <c r="B63" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6731,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447636</v>
+        <v>447716</v>
       </c>
       <c r="R63" t="n">
-        <v>6814937</v>
+        <v>6814847</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6817,10 +6812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128605843</v>
+        <v>128605882</v>
       </c>
       <c r="B64" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6828,21 +6823,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447744</v>
+        <v>447789</v>
       </c>
       <c r="R64" t="n">
-        <v>6814896</v>
+        <v>6814910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6888,6 +6883,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7015,7 +7015,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129125786</v>
+        <v>129125766</v>
       </c>
       <c r="B66" t="n">
         <v>79035</v>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447922</v>
+        <v>447807</v>
       </c>
       <c r="R66" t="n">
-        <v>6814934</v>
+        <v>6814825</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7095,7 +7095,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På minst 250-årig tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7122,7 +7127,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129125766</v>
+        <v>129125786</v>
       </c>
       <c r="B67" t="n">
         <v>79035</v>
@@ -7157,10 +7162,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447807</v>
+        <v>447922</v>
       </c>
       <c r="R67" t="n">
-        <v>6814825</v>
+        <v>6814934</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7192,7 +7197,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7202,12 +7207,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På minst 250-årig tall</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125874</v>
+        <v>129125722</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448182</v>
+        <v>447757</v>
       </c>
       <c r="R91" t="n">
-        <v>6815308</v>
+        <v>6814906</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9827,7 +9827,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125809</v>
+        <v>129125874</v>
       </c>
       <c r="B92" t="n">
         <v>79035</v>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447763</v>
+        <v>448182</v>
       </c>
       <c r="R92" t="n">
-        <v>6814923</v>
+        <v>6815308</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,7 +9934,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125831</v>
+        <v>129125809</v>
       </c>
       <c r="B93" t="n">
         <v>79035</v>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447755</v>
+        <v>447763</v>
       </c>
       <c r="R93" t="n">
-        <v>6814973</v>
+        <v>6814923</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10041,7 +10041,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125772</v>
+        <v>129125831</v>
       </c>
       <c r="B94" t="n">
         <v>79035</v>
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447920</v>
+        <v>447755</v>
       </c>
       <c r="R94" t="n">
-        <v>6815082</v>
+        <v>6814973</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,10 +10148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125753</v>
+        <v>129125772</v>
       </c>
       <c r="B95" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,21 +10159,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447766</v>
+        <v>447920</v>
       </c>
       <c r="R95" t="n">
-        <v>6814899</v>
+        <v>6815082</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,12 +10228,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10242,7 +10237,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10261,10 +10255,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125795</v>
+        <v>129125753</v>
       </c>
       <c r="B96" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10272,21 +10266,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10296,10 +10290,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447790</v>
+        <v>447766</v>
       </c>
       <c r="R96" t="n">
-        <v>6814834</v>
+        <v>6814899</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10331,7 +10325,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10341,7 +10335,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,6 +10349,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125722</v>
+        <v>129125795</v>
       </c>
       <c r="B97" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447757</v>
+        <v>447790</v>
       </c>
       <c r="R97" t="n">
-        <v>6814906</v>
+        <v>6814834</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12727,32 +12727,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129125877</v>
+        <v>129125750</v>
       </c>
       <c r="B119" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>448126</v>
+        <v>447714</v>
       </c>
       <c r="R119" t="n">
-        <v>6815198</v>
+        <v>6815023</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12834,7 +12834,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125894</v>
+        <v>129125877</v>
       </c>
       <c r="B120" t="n">
         <v>79035</v>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447978</v>
+        <v>448126</v>
       </c>
       <c r="R120" t="n">
-        <v>6815111</v>
+        <v>6815198</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125850</v>
+        <v>129125894</v>
       </c>
       <c r="B121" t="n">
         <v>79035</v>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447844</v>
+        <v>447978</v>
       </c>
       <c r="R121" t="n">
-        <v>6815026</v>
+        <v>6815111</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13048,7 +13048,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129125827</v>
+        <v>129125850</v>
       </c>
       <c r="B122" t="n">
         <v>79035</v>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447767</v>
+        <v>447844</v>
       </c>
       <c r="R122" t="n">
-        <v>6815014</v>
+        <v>6815026</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13155,7 +13155,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125811</v>
+        <v>129125827</v>
       </c>
       <c r="B123" t="n">
         <v>79035</v>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447716</v>
+        <v>447767</v>
       </c>
       <c r="R123" t="n">
-        <v>6814829</v>
+        <v>6815014</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,7 +13262,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125865</v>
+        <v>129125811</v>
       </c>
       <c r="B124" t="n">
         <v>79035</v>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>448049</v>
+        <v>447716</v>
       </c>
       <c r="R124" t="n">
-        <v>6815224</v>
+        <v>6814829</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,7 +13369,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125859</v>
+        <v>129125865</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447887</v>
+        <v>448049</v>
       </c>
       <c r="R125" t="n">
-        <v>6815043</v>
+        <v>6815224</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,7 +13476,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125852</v>
+        <v>129125859</v>
       </c>
       <c r="B126" t="n">
         <v>79035</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447839</v>
+        <v>447887</v>
       </c>
       <c r="R126" t="n">
-        <v>6814995</v>
+        <v>6815043</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125882</v>
+        <v>129125852</v>
       </c>
       <c r="B127" t="n">
         <v>79035</v>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>448089</v>
+        <v>447839</v>
       </c>
       <c r="R127" t="n">
-        <v>6815086</v>
+        <v>6814995</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13690,7 +13690,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129125845</v>
+        <v>129125882</v>
       </c>
       <c r="B128" t="n">
         <v>79035</v>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447801</v>
+        <v>448089</v>
       </c>
       <c r="R128" t="n">
-        <v>6815082</v>
+        <v>6815086</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13797,7 +13797,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125791</v>
+        <v>129125845</v>
       </c>
       <c r="B129" t="n">
         <v>79035</v>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447839</v>
+        <v>447801</v>
       </c>
       <c r="R129" t="n">
-        <v>6814871</v>
+        <v>6815082</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,32 +13904,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125750</v>
+        <v>129125791</v>
       </c>
       <c r="B130" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447714</v>
+        <v>447839</v>
       </c>
       <c r="R130" t="n">
-        <v>6815023</v>
+        <v>6814871</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14551,10 +14551,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129125737</v>
+        <v>129125781</v>
       </c>
       <c r="B136" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14562,39 +14562,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>447735</v>
+        <v>447968</v>
       </c>
       <c r="R136" t="n">
-        <v>6815036</v>
+        <v>6814977</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14626,7 +14621,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14636,7 +14631,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14663,7 +14658,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125781</v>
+        <v>129125885</v>
       </c>
       <c r="B137" t="n">
         <v>79035</v>
@@ -14698,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>447968</v>
+        <v>448080</v>
       </c>
       <c r="R137" t="n">
-        <v>6814977</v>
+        <v>6815037</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14733,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14743,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14770,7 +14765,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125885</v>
+        <v>129125797</v>
       </c>
       <c r="B138" t="n">
         <v>79035</v>
@@ -14805,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>448080</v>
+        <v>447781</v>
       </c>
       <c r="R138" t="n">
-        <v>6815037</v>
+        <v>6814894</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14840,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14850,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14877,7 +14872,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125797</v>
+        <v>129125818</v>
       </c>
       <c r="B139" t="n">
         <v>79035</v>
@@ -14912,10 +14907,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>447781</v>
+        <v>447641</v>
       </c>
       <c r="R139" t="n">
-        <v>6814894</v>
+        <v>6814924</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14947,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14957,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14984,7 +14979,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125818</v>
+        <v>129125805</v>
       </c>
       <c r="B140" t="n">
         <v>79035</v>
@@ -15019,10 +15014,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>447641</v>
+        <v>447826</v>
       </c>
       <c r="R140" t="n">
-        <v>6814924</v>
+        <v>6814982</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15054,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15064,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15091,7 +15086,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125805</v>
+        <v>129125887</v>
       </c>
       <c r="B141" t="n">
         <v>79035</v>
@@ -15126,10 +15121,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>447826</v>
+        <v>448080</v>
       </c>
       <c r="R141" t="n">
-        <v>6814982</v>
+        <v>6815039</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15161,7 +15156,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15171,7 +15166,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15198,10 +15193,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129125887</v>
+        <v>129125737</v>
       </c>
       <c r="B142" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15209,34 +15204,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>448080</v>
+        <v>447735</v>
       </c>
       <c r="R142" t="n">
-        <v>6815039</v>
+        <v>6815036</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16054,45 +16054,54 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129125720</v>
+        <v>129125758</v>
       </c>
       <c r="B150" t="n">
-        <v>79067</v>
+        <v>98659</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>447936</v>
+        <v>447571</v>
       </c>
       <c r="R150" t="n">
-        <v>6814995</v>
+        <v>6814831</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16124,7 +16133,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16134,7 +16143,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16161,45 +16170,54 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129125802</v>
+        <v>129125757</v>
       </c>
       <c r="B151" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>447821</v>
+        <v>447746</v>
       </c>
       <c r="R151" t="n">
-        <v>6814955</v>
+        <v>6814851</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16231,7 +16249,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16241,7 +16259,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16268,10 +16286,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125806</v>
+        <v>129125720</v>
       </c>
       <c r="B152" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16279,21 +16297,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16303,10 +16321,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447816</v>
+        <v>447936</v>
       </c>
       <c r="R152" t="n">
-        <v>6814979</v>
+        <v>6814995</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16338,7 +16356,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16348,7 +16366,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,7 +16393,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125830</v>
+        <v>129125802</v>
       </c>
       <c r="B153" t="n">
         <v>79035</v>
@@ -16410,10 +16428,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>447767</v>
+        <v>447821</v>
       </c>
       <c r="R153" t="n">
-        <v>6814993</v>
+        <v>6814955</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16445,7 +16463,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16455,7 +16473,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16482,7 +16500,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125799</v>
+        <v>129125806</v>
       </c>
       <c r="B154" t="n">
         <v>79035</v>
@@ -16517,10 +16535,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>447804</v>
+        <v>447816</v>
       </c>
       <c r="R154" t="n">
-        <v>6814911</v>
+        <v>6814979</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16552,7 +16570,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16562,7 +16580,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16589,7 +16607,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125769</v>
+        <v>129125830</v>
       </c>
       <c r="B155" t="n">
         <v>79035</v>
@@ -16624,10 +16642,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447912</v>
+        <v>447767</v>
       </c>
       <c r="R155" t="n">
-        <v>6815110</v>
+        <v>6814993</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16659,7 +16677,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16669,7 +16687,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16696,7 +16714,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125768</v>
+        <v>129125799</v>
       </c>
       <c r="B156" t="n">
         <v>79035</v>
@@ -16731,10 +16749,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447909</v>
+        <v>447804</v>
       </c>
       <c r="R156" t="n">
-        <v>6815119</v>
+        <v>6814911</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16766,7 +16784,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16776,7 +16794,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16803,7 +16821,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125804</v>
+        <v>129125769</v>
       </c>
       <c r="B157" t="n">
         <v>79035</v>
@@ -16838,10 +16856,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447840</v>
+        <v>447912</v>
       </c>
       <c r="R157" t="n">
-        <v>6814978</v>
+        <v>6815110</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16873,7 +16891,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16883,7 +16901,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16910,7 +16928,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125801</v>
+        <v>129125768</v>
       </c>
       <c r="B158" t="n">
         <v>79035</v>
@@ -16945,10 +16963,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>447814</v>
+        <v>447909</v>
       </c>
       <c r="R158" t="n">
-        <v>6814948</v>
+        <v>6815119</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16980,7 +16998,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16990,7 +17008,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17017,7 +17035,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129125878</v>
+        <v>129125804</v>
       </c>
       <c r="B159" t="n">
         <v>79035</v>
@@ -17052,10 +17070,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>448121</v>
+        <v>447840</v>
       </c>
       <c r="R159" t="n">
-        <v>6815175</v>
+        <v>6814978</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17087,7 +17105,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17097,7 +17115,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17124,7 +17142,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125869</v>
+        <v>129125801</v>
       </c>
       <c r="B160" t="n">
         <v>79035</v>
@@ -17159,10 +17177,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>448114</v>
+        <v>447814</v>
       </c>
       <c r="R160" t="n">
-        <v>6815209</v>
+        <v>6814948</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17194,7 +17212,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17204,7 +17222,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17231,7 +17249,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125849</v>
+        <v>129125878</v>
       </c>
       <c r="B161" t="n">
         <v>79035</v>
@@ -17266,10 +17284,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>447825</v>
+        <v>448121</v>
       </c>
       <c r="R161" t="n">
-        <v>6815056</v>
+        <v>6815175</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17301,7 +17319,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17311,7 +17329,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17338,32 +17356,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125749</v>
+        <v>129125869</v>
       </c>
       <c r="B162" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17373,10 +17391,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>447581</v>
+        <v>448114</v>
       </c>
       <c r="R162" t="n">
-        <v>6814869</v>
+        <v>6815209</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17408,7 +17426,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17418,7 +17436,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17445,50 +17463,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125731</v>
+        <v>129125849</v>
       </c>
       <c r="B163" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>448128</v>
+        <v>447825</v>
       </c>
       <c r="R163" t="n">
-        <v>6815234</v>
+        <v>6815056</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17520,7 +17533,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17530,7 +17543,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17557,54 +17570,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129125758</v>
+        <v>129125749</v>
       </c>
       <c r="B164" t="n">
-        <v>98659</v>
+        <v>80176</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>447571</v>
+        <v>447581</v>
       </c>
       <c r="R164" t="n">
-        <v>6814831</v>
+        <v>6814869</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17636,7 +17640,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17646,7 +17650,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17673,42 +17677,38 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129125757</v>
+        <v>129125731</v>
       </c>
       <c r="B165" t="n">
-        <v>98659</v>
+        <v>56913</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>447746</v>
+        <v>448128</v>
       </c>
       <c r="R165" t="n">
-        <v>6814851</v>
+        <v>6815234</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129125766</v>
+        <v>129125764</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447807</v>
+        <v>447872</v>
       </c>
       <c r="R66" t="n">
-        <v>6814825</v>
+        <v>6814907</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7095,12 +7095,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På minst 250-årig tall</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7127,7 +7122,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129125786</v>
+        <v>129125766</v>
       </c>
       <c r="B67" t="n">
         <v>79035</v>
@@ -7162,10 +7157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447922</v>
+        <v>447807</v>
       </c>
       <c r="R67" t="n">
-        <v>6814934</v>
+        <v>6814825</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7197,7 +7192,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7207,7 +7202,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På minst 250-årig tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7234,10 +7234,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129125764</v>
+        <v>129125786</v>
       </c>
       <c r="B68" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447872</v>
+        <v>447922</v>
       </c>
       <c r="R68" t="n">
-        <v>6814907</v>
+        <v>6814934</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129125752</v>
+        <v>129125738</v>
       </c>
       <c r="B69" t="n">
-        <v>81020</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,34 +7352,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447893</v>
+        <v>447735</v>
       </c>
       <c r="R69" t="n">
-        <v>6814914</v>
+        <v>6814890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,7 +7416,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7421,7 +7426,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7448,10 +7458,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129125843</v>
+        <v>129125752</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>81020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7459,21 +7469,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447812</v>
+        <v>447893</v>
       </c>
       <c r="R70" t="n">
-        <v>6815055</v>
+        <v>6814914</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7518,7 +7528,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7528,7 +7538,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7555,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125755</v>
+        <v>129125821</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7566,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7590,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447756</v>
+        <v>447754</v>
       </c>
       <c r="R71" t="n">
-        <v>6814990</v>
+        <v>6815052</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7625,7 +7635,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7635,7 +7645,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7644,7 +7654,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7663,7 +7672,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125798</v>
+        <v>129125787</v>
       </c>
       <c r="B72" t="n">
         <v>79035</v>
@@ -7698,10 +7707,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447786</v>
+        <v>447908</v>
       </c>
       <c r="R72" t="n">
-        <v>6814897</v>
+        <v>6814933</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7733,7 +7742,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7743,7 +7752,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7770,7 +7779,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125821</v>
+        <v>129125843</v>
       </c>
       <c r="B73" t="n">
         <v>79035</v>
@@ -7805,10 +7814,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447754</v>
+        <v>447812</v>
       </c>
       <c r="R73" t="n">
-        <v>6815052</v>
+        <v>6815055</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7840,7 +7849,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7850,7 +7859,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7877,7 +7886,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129125787</v>
+        <v>129125812</v>
       </c>
       <c r="B74" t="n">
         <v>79035</v>
@@ -7912,10 +7921,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447908</v>
+        <v>447682</v>
       </c>
       <c r="R74" t="n">
-        <v>6814933</v>
+        <v>6814779</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7947,7 +7956,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7957,7 +7966,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7984,10 +7993,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129125835</v>
+        <v>129125755</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7995,21 +8004,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8019,10 +8028,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447793</v>
+        <v>447756</v>
       </c>
       <c r="R75" t="n">
-        <v>6815007</v>
+        <v>6814990</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8054,7 +8063,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8064,7 +8073,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8073,6 +8082,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8091,7 +8101,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129125812</v>
+        <v>129125798</v>
       </c>
       <c r="B76" t="n">
         <v>79035</v>
@@ -8126,10 +8136,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447682</v>
+        <v>447786</v>
       </c>
       <c r="R76" t="n">
-        <v>6814779</v>
+        <v>6814897</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8161,7 +8171,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8171,7 +8181,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8198,10 +8208,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129125738</v>
+        <v>129125835</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8209,39 +8219,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447735</v>
+        <v>447793</v>
       </c>
       <c r="R77" t="n">
-        <v>6814890</v>
+        <v>6815007</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8273,7 +8278,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8283,12 +8288,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8427,45 +8427,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125729</v>
+        <v>129125759</v>
       </c>
       <c r="B79" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448039</v>
+        <v>447640</v>
       </c>
       <c r="R79" t="n">
-        <v>6815229</v>
+        <v>6814923</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,7 +8506,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8507,7 +8516,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8641,10 +8650,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129125730</v>
+        <v>129125853</v>
       </c>
       <c r="B81" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8652,21 +8661,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8676,10 +8685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448098</v>
+        <v>447853</v>
       </c>
       <c r="R81" t="n">
-        <v>6815212</v>
+        <v>6814972</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8711,7 +8720,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8721,7 +8730,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8748,7 +8757,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129125873</v>
+        <v>129125867</v>
       </c>
       <c r="B82" t="n">
         <v>79035</v>
@@ -8783,10 +8792,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448163</v>
+        <v>448088</v>
       </c>
       <c r="R82" t="n">
-        <v>6815302</v>
+        <v>6815222</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,7 +8827,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8828,7 +8837,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8855,7 +8864,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129125771</v>
+        <v>129125824</v>
       </c>
       <c r="B83" t="n">
         <v>79035</v>
@@ -8890,10 +8899,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447925</v>
+        <v>447761</v>
       </c>
       <c r="R83" t="n">
-        <v>6815103</v>
+        <v>6815045</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8925,7 +8934,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8935,7 +8944,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8962,7 +8971,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125853</v>
+        <v>129125767</v>
       </c>
       <c r="B84" t="n">
         <v>79035</v>
@@ -8997,10 +9006,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447853</v>
+        <v>447915</v>
       </c>
       <c r="R84" t="n">
-        <v>6814972</v>
+        <v>6815140</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,7 +9041,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9042,7 +9051,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9069,10 +9078,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125867</v>
+        <v>129125729</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9080,21 +9089,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9104,10 +9113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448088</v>
+        <v>448039</v>
       </c>
       <c r="R85" t="n">
-        <v>6815222</v>
+        <v>6815229</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9139,7 +9148,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9149,7 +9158,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9176,10 +9185,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125824</v>
+        <v>129125730</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9187,21 +9196,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9211,10 +9220,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447761</v>
+        <v>448098</v>
       </c>
       <c r="R86" t="n">
-        <v>6815045</v>
+        <v>6815212</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,7 +9255,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9256,7 +9265,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9283,7 +9292,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129125808</v>
+        <v>129125771</v>
       </c>
       <c r="B87" t="n">
         <v>79035</v>
@@ -9318,10 +9327,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447782</v>
+        <v>447925</v>
       </c>
       <c r="R87" t="n">
-        <v>6814944</v>
+        <v>6815103</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9353,7 +9362,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9363,7 +9372,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9390,7 +9399,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129125895</v>
+        <v>129125873</v>
       </c>
       <c r="B88" t="n">
         <v>79035</v>
@@ -9425,10 +9434,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447963</v>
+        <v>448163</v>
       </c>
       <c r="R88" t="n">
-        <v>6815131</v>
+        <v>6815302</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9460,7 +9469,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9470,7 +9479,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9497,7 +9506,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129125767</v>
+        <v>129125808</v>
       </c>
       <c r="B89" t="n">
         <v>79035</v>
@@ -9532,10 +9541,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447915</v>
+        <v>447782</v>
       </c>
       <c r="R89" t="n">
-        <v>6815140</v>
+        <v>6814944</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9567,7 +9576,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9577,7 +9586,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9604,54 +9613,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129125759</v>
+        <v>129125895</v>
       </c>
       <c r="B90" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447640</v>
+        <v>447963</v>
       </c>
       <c r="R90" t="n">
-        <v>6814923</v>
+        <v>6815131</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125722</v>
+        <v>129125753</v>
       </c>
       <c r="B91" t="n">
-        <v>79067</v>
+        <v>78792</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447757</v>
+        <v>447766</v>
       </c>
       <c r="R91" t="n">
-        <v>6814906</v>
+        <v>6814899</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9809,6 +9814,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9827,7 +9833,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125874</v>
+        <v>129125831</v>
       </c>
       <c r="B92" t="n">
         <v>79035</v>
@@ -9862,10 +9868,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>448182</v>
+        <v>447755</v>
       </c>
       <c r="R92" t="n">
-        <v>6815308</v>
+        <v>6814973</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9903,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9913,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,10 +9940,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125809</v>
+        <v>129125722</v>
       </c>
       <c r="B93" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9945,21 +9951,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9969,10 +9975,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447763</v>
+        <v>447757</v>
       </c>
       <c r="R93" t="n">
-        <v>6814923</v>
+        <v>6814906</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10010,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10020,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10041,7 +10047,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125831</v>
+        <v>129125874</v>
       </c>
       <c r="B94" t="n">
         <v>79035</v>
@@ -10076,10 +10082,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447755</v>
+        <v>448182</v>
       </c>
       <c r="R94" t="n">
-        <v>6814973</v>
+        <v>6815308</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10117,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10127,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,7 +10154,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125772</v>
+        <v>129125795</v>
       </c>
       <c r="B95" t="n">
         <v>79035</v>
@@ -10183,10 +10189,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447920</v>
+        <v>447790</v>
       </c>
       <c r="R95" t="n">
-        <v>6815082</v>
+        <v>6814834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10224,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,7 +10234,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10255,10 +10261,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125753</v>
+        <v>129125809</v>
       </c>
       <c r="B96" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10266,21 +10272,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10290,10 +10296,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447766</v>
+        <v>447763</v>
       </c>
       <c r="R96" t="n">
-        <v>6814899</v>
+        <v>6814923</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10325,7 +10331,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10335,12 +10341,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10349,7 +10350,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125795</v>
+        <v>129125772</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447790</v>
+        <v>447920</v>
       </c>
       <c r="R97" t="n">
-        <v>6814834</v>
+        <v>6815082</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10475,7 +10475,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129125872</v>
+        <v>129125820</v>
       </c>
       <c r="B98" t="n">
         <v>79035</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>448159</v>
+        <v>447706</v>
       </c>
       <c r="R98" t="n">
-        <v>6815277</v>
+        <v>6815025</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10582,10 +10582,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129125820</v>
+        <v>129125741</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10593,34 +10593,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447706</v>
+        <v>447902</v>
       </c>
       <c r="R99" t="n">
-        <v>6815025</v>
+        <v>6814922</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10657,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10662,7 +10667,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10689,32 +10694,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129125858</v>
+        <v>129125746</v>
       </c>
       <c r="B100" t="n">
-        <v>79035</v>
+        <v>97536</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10724,10 +10729,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447914</v>
+        <v>448129</v>
       </c>
       <c r="R100" t="n">
-        <v>6815024</v>
+        <v>6815200</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10759,7 +10764,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10769,7 +10774,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10796,10 +10801,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129125836</v>
+        <v>129125719</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10807,21 +10812,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10831,10 +10836,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447789</v>
+        <v>447855</v>
       </c>
       <c r="R101" t="n">
-        <v>6815016</v>
+        <v>6814877</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10866,7 +10871,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10876,7 +10881,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10903,32 +10908,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129125746</v>
+        <v>129125872</v>
       </c>
       <c r="B102" t="n">
-        <v>97536</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10938,10 +10943,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448129</v>
+        <v>448159</v>
       </c>
       <c r="R102" t="n">
-        <v>6815200</v>
+        <v>6815277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10973,7 +10978,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10983,7 +10988,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11010,10 +11015,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129125719</v>
+        <v>129125836</v>
       </c>
       <c r="B103" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11021,21 +11026,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11045,10 +11050,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447855</v>
+        <v>447789</v>
       </c>
       <c r="R103" t="n">
-        <v>6814877</v>
+        <v>6815016</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11080,7 +11085,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11090,7 +11095,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11224,10 +11229,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125741</v>
+        <v>129125858</v>
       </c>
       <c r="B105" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11235,39 +11240,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447902</v>
+        <v>447914</v>
       </c>
       <c r="R105" t="n">
-        <v>6814922</v>
+        <v>6815024</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129125886</v>
+        <v>129125813</v>
       </c>
       <c r="B109" t="n">
         <v>79035</v>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448097</v>
+        <v>447617</v>
       </c>
       <c r="R109" t="n">
-        <v>6815025</v>
+        <v>6814828</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11764,7 +11764,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129125813</v>
+        <v>129125886</v>
       </c>
       <c r="B110" t="n">
         <v>79035</v>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447617</v>
+        <v>448097</v>
       </c>
       <c r="R110" t="n">
-        <v>6814828</v>
+        <v>6815025</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11978,32 +11978,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125728</v>
+        <v>129125807</v>
       </c>
       <c r="B112" t="n">
-        <v>91491</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447872</v>
+        <v>447797</v>
       </c>
       <c r="R112" t="n">
-        <v>6815131</v>
+        <v>6814950</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,7 +12085,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125807</v>
+        <v>129125779</v>
       </c>
       <c r="B113" t="n">
         <v>79035</v>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447797</v>
+        <v>447936</v>
       </c>
       <c r="R113" t="n">
-        <v>6814950</v>
+        <v>6814995</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,7 +12192,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125863</v>
+        <v>129125841</v>
       </c>
       <c r="B114" t="n">
         <v>79035</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447878</v>
+        <v>447812</v>
       </c>
       <c r="R114" t="n">
-        <v>6815153</v>
+        <v>6815036</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12406,32 +12406,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125779</v>
+        <v>129125728</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>91491</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447936</v>
+        <v>447872</v>
       </c>
       <c r="R116" t="n">
-        <v>6814995</v>
+        <v>6815131</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,7 +12513,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125841</v>
+        <v>129125863</v>
       </c>
       <c r="B117" t="n">
         <v>79035</v>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447812</v>
+        <v>447878</v>
       </c>
       <c r="R117" t="n">
-        <v>6815036</v>
+        <v>6815153</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12727,32 +12727,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129125750</v>
+        <v>129125865</v>
       </c>
       <c r="B119" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447714</v>
+        <v>448049</v>
       </c>
       <c r="R119" t="n">
-        <v>6815023</v>
+        <v>6815224</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12834,32 +12834,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125877</v>
+        <v>129125750</v>
       </c>
       <c r="B120" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448126</v>
+        <v>447714</v>
       </c>
       <c r="R120" t="n">
-        <v>6815198</v>
+        <v>6815023</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125894</v>
+        <v>129125877</v>
       </c>
       <c r="B121" t="n">
         <v>79035</v>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447978</v>
+        <v>448126</v>
       </c>
       <c r="R121" t="n">
-        <v>6815111</v>
+        <v>6815198</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13155,7 +13155,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125827</v>
+        <v>129125811</v>
       </c>
       <c r="B123" t="n">
         <v>79035</v>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447767</v>
+        <v>447716</v>
       </c>
       <c r="R123" t="n">
-        <v>6815014</v>
+        <v>6814829</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,7 +13262,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125811</v>
+        <v>129125852</v>
       </c>
       <c r="B124" t="n">
         <v>79035</v>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447716</v>
+        <v>447839</v>
       </c>
       <c r="R124" t="n">
-        <v>6814829</v>
+        <v>6814995</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,7 +13369,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125865</v>
+        <v>129125791</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448049</v>
+        <v>447839</v>
       </c>
       <c r="R125" t="n">
-        <v>6815224</v>
+        <v>6814871</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,7 +13476,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125859</v>
+        <v>129125894</v>
       </c>
       <c r="B126" t="n">
         <v>79035</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447887</v>
+        <v>447978</v>
       </c>
       <c r="R126" t="n">
-        <v>6815043</v>
+        <v>6815111</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125852</v>
+        <v>129125827</v>
       </c>
       <c r="B127" t="n">
         <v>79035</v>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447839</v>
+        <v>447767</v>
       </c>
       <c r="R127" t="n">
-        <v>6814995</v>
+        <v>6815014</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13690,7 +13690,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129125882</v>
+        <v>129125859</v>
       </c>
       <c r="B128" t="n">
         <v>79035</v>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>448089</v>
+        <v>447887</v>
       </c>
       <c r="R128" t="n">
-        <v>6815086</v>
+        <v>6815043</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13797,7 +13797,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125845</v>
+        <v>129125882</v>
       </c>
       <c r="B129" t="n">
         <v>79035</v>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447801</v>
+        <v>448089</v>
       </c>
       <c r="R129" t="n">
-        <v>6815082</v>
+        <v>6815086</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,7 +13904,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125791</v>
+        <v>129125845</v>
       </c>
       <c r="B130" t="n">
         <v>79035</v>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447839</v>
+        <v>447801</v>
       </c>
       <c r="R130" t="n">
-        <v>6814871</v>
+        <v>6815082</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,7 +14011,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125770</v>
+        <v>129125844</v>
       </c>
       <c r="B131" t="n">
         <v>79035</v>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447916</v>
+        <v>447808</v>
       </c>
       <c r="R131" t="n">
-        <v>6815113</v>
+        <v>6815078</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14118,32 +14118,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125844</v>
+        <v>129125743</v>
       </c>
       <c r="B132" t="n">
-        <v>79035</v>
+        <v>80044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14153,10 +14153,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447808</v>
+        <v>447735</v>
       </c>
       <c r="R132" t="n">
-        <v>6815078</v>
+        <v>6814890</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14198,7 +14198,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14225,32 +14230,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125743</v>
+        <v>129125770</v>
       </c>
       <c r="B133" t="n">
-        <v>80044</v>
+        <v>79035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14260,10 +14265,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447735</v>
+        <v>447916</v>
       </c>
       <c r="R133" t="n">
-        <v>6814890</v>
+        <v>6815113</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14295,7 +14300,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14305,12 +14310,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14658,7 +14658,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125885</v>
+        <v>129125797</v>
       </c>
       <c r="B137" t="n">
         <v>79035</v>
@@ -14693,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>448080</v>
+        <v>447781</v>
       </c>
       <c r="R137" t="n">
-        <v>6815037</v>
+        <v>6814894</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14765,7 +14765,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125797</v>
+        <v>129125805</v>
       </c>
       <c r="B138" t="n">
         <v>79035</v>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>447781</v>
+        <v>447826</v>
       </c>
       <c r="R138" t="n">
-        <v>6814894</v>
+        <v>6814982</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14872,7 +14872,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125818</v>
+        <v>129125887</v>
       </c>
       <c r="B139" t="n">
         <v>79035</v>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>447641</v>
+        <v>448080</v>
       </c>
       <c r="R139" t="n">
-        <v>6814924</v>
+        <v>6815039</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14979,7 +14979,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125805</v>
+        <v>129125885</v>
       </c>
       <c r="B140" t="n">
         <v>79035</v>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>447826</v>
+        <v>448080</v>
       </c>
       <c r="R140" t="n">
-        <v>6814982</v>
+        <v>6815037</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15086,7 +15086,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125887</v>
+        <v>129125818</v>
       </c>
       <c r="B141" t="n">
         <v>79035</v>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>448080</v>
+        <v>447641</v>
       </c>
       <c r="R141" t="n">
-        <v>6815039</v>
+        <v>6814924</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15305,27 +15305,27 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125775</v>
+        <v>129125899</v>
       </c>
       <c r="B143" t="n">
-        <v>79035</v>
+        <v>80175</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447916</v>
+        <v>447580</v>
       </c>
       <c r="R143" t="n">
-        <v>6815021</v>
+        <v>6814868</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,7 +15412,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125828</v>
+        <v>129125775</v>
       </c>
       <c r="B144" t="n">
         <v>79035</v>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447781</v>
+        <v>447916</v>
       </c>
       <c r="R144" t="n">
-        <v>6815009</v>
+        <v>6815021</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,7 +15519,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125839</v>
+        <v>129125792</v>
       </c>
       <c r="B145" t="n">
         <v>79035</v>
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447805</v>
+        <v>447812</v>
       </c>
       <c r="R145" t="n">
-        <v>6815025</v>
+        <v>6814852</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15626,7 +15626,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125792</v>
+        <v>129125796</v>
       </c>
       <c r="B146" t="n">
         <v>79035</v>
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447812</v>
+        <v>447749</v>
       </c>
       <c r="R146" t="n">
-        <v>6814852</v>
+        <v>6814850</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,7 +15733,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125796</v>
+        <v>129125826</v>
       </c>
       <c r="B147" t="n">
         <v>79035</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447749</v>
+        <v>447765</v>
       </c>
       <c r="R147" t="n">
-        <v>6814850</v>
+        <v>6815023</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,7 +15840,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125826</v>
+        <v>129125828</v>
       </c>
       <c r="B148" t="n">
         <v>79035</v>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447765</v>
+        <v>447781</v>
       </c>
       <c r="R148" t="n">
-        <v>6815023</v>
+        <v>6815009</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15947,27 +15947,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129125899</v>
+        <v>129125839</v>
       </c>
       <c r="B149" t="n">
-        <v>80175</v>
+        <v>79035</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>447580</v>
+        <v>447805</v>
       </c>
       <c r="R149" t="n">
-        <v>6814868</v>
+        <v>6815025</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16054,54 +16054,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129125758</v>
+        <v>129125720</v>
       </c>
       <c r="B150" t="n">
-        <v>98659</v>
+        <v>79067</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>447571</v>
+        <v>447936</v>
       </c>
       <c r="R150" t="n">
-        <v>6814831</v>
+        <v>6814995</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16133,7 +16124,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16143,7 +16134,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16170,54 +16161,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129125757</v>
+        <v>129125802</v>
       </c>
       <c r="B151" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>447746</v>
+        <v>447821</v>
       </c>
       <c r="R151" t="n">
-        <v>6814851</v>
+        <v>6814955</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16249,7 +16231,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16259,7 +16241,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16286,10 +16268,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125720</v>
+        <v>129125768</v>
       </c>
       <c r="B152" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16297,21 +16279,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16321,10 +16303,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447936</v>
+        <v>447909</v>
       </c>
       <c r="R152" t="n">
-        <v>6814995</v>
+        <v>6815119</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16356,7 +16338,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16366,7 +16348,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16393,7 +16375,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125802</v>
+        <v>129125801</v>
       </c>
       <c r="B153" t="n">
         <v>79035</v>
@@ -16428,10 +16410,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>447821</v>
+        <v>447814</v>
       </c>
       <c r="R153" t="n">
-        <v>6814955</v>
+        <v>6814948</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16500,45 +16482,54 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125806</v>
+        <v>129125758</v>
       </c>
       <c r="B154" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>447816</v>
+        <v>447571</v>
       </c>
       <c r="R154" t="n">
-        <v>6814979</v>
+        <v>6814831</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16570,7 +16561,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16580,7 +16571,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16607,45 +16598,54 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125830</v>
+        <v>129125757</v>
       </c>
       <c r="B155" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447767</v>
+        <v>447746</v>
       </c>
       <c r="R155" t="n">
-        <v>6814993</v>
+        <v>6814851</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16714,32 +16714,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125799</v>
+        <v>129125749</v>
       </c>
       <c r="B156" t="n">
-        <v>79035</v>
+        <v>80176</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447804</v>
+        <v>447581</v>
       </c>
       <c r="R156" t="n">
-        <v>6814911</v>
+        <v>6814869</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16821,7 +16821,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125769</v>
+        <v>129125806</v>
       </c>
       <c r="B157" t="n">
         <v>79035</v>
@@ -16856,10 +16856,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447912</v>
+        <v>447816</v>
       </c>
       <c r="R157" t="n">
-        <v>6815110</v>
+        <v>6814979</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16928,7 +16928,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125768</v>
+        <v>129125799</v>
       </c>
       <c r="B158" t="n">
         <v>79035</v>
@@ -16963,10 +16963,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>447909</v>
+        <v>447804</v>
       </c>
       <c r="R158" t="n">
-        <v>6815119</v>
+        <v>6814911</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16998,7 +16998,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17142,7 +17142,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125801</v>
+        <v>129125878</v>
       </c>
       <c r="B160" t="n">
         <v>79035</v>
@@ -17177,10 +17177,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>447814</v>
+        <v>448121</v>
       </c>
       <c r="R160" t="n">
-        <v>6814948</v>
+        <v>6815175</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,7 +17249,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125878</v>
+        <v>129125849</v>
       </c>
       <c r="B161" t="n">
         <v>79035</v>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>448121</v>
+        <v>447825</v>
       </c>
       <c r="R161" t="n">
-        <v>6815175</v>
+        <v>6815056</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,7 +17356,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125869</v>
+        <v>129125830</v>
       </c>
       <c r="B162" t="n">
         <v>79035</v>
@@ -17391,10 +17391,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>448114</v>
+        <v>447767</v>
       </c>
       <c r="R162" t="n">
-        <v>6815209</v>
+        <v>6814993</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17463,7 +17463,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125849</v>
+        <v>129125769</v>
       </c>
       <c r="B163" t="n">
         <v>79035</v>
@@ -17498,10 +17498,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>447825</v>
+        <v>447912</v>
       </c>
       <c r="R163" t="n">
-        <v>6815056</v>
+        <v>6815110</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17570,32 +17570,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129125749</v>
+        <v>129125869</v>
       </c>
       <c r="B164" t="n">
-        <v>80176</v>
+        <v>79035</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17605,10 +17605,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>447581</v>
+        <v>448114</v>
       </c>
       <c r="R164" t="n">
-        <v>6814869</v>
+        <v>6815209</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18231,10 +18231,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129125724</v>
+        <v>129125833</v>
       </c>
       <c r="B170" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18242,21 +18242,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18266,10 +18266,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>447803</v>
+        <v>447772</v>
       </c>
       <c r="R170" t="n">
-        <v>6815095</v>
+        <v>6814969</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18338,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125723</v>
+        <v>129125832</v>
       </c>
       <c r="B171" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18349,21 +18349,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18373,10 +18373,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>447751</v>
+        <v>447762</v>
       </c>
       <c r="R171" t="n">
-        <v>6814901</v>
+        <v>6814968</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18445,10 +18445,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129125727</v>
+        <v>129125718</v>
       </c>
       <c r="B172" t="n">
-        <v>79067</v>
+        <v>83011</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18456,21 +18456,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18480,10 +18480,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>448008</v>
+        <v>447772</v>
       </c>
       <c r="R172" t="n">
-        <v>6815080</v>
+        <v>6815035</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18552,32 +18552,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125833</v>
+        <v>129125763</v>
       </c>
       <c r="B173" t="n">
-        <v>79035</v>
+        <v>82994</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18587,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>447772</v>
+        <v>447801</v>
       </c>
       <c r="R173" t="n">
-        <v>6814969</v>
+        <v>6814957</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18659,10 +18659,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125880</v>
+        <v>129125724</v>
       </c>
       <c r="B174" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18670,21 +18670,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>448107</v>
+        <v>447803</v>
       </c>
       <c r="R174" t="n">
-        <v>6815120</v>
+        <v>6815095</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18766,10 +18766,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125810</v>
+        <v>129125723</v>
       </c>
       <c r="B175" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18777,21 +18777,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18801,10 +18801,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447736</v>
+        <v>447751</v>
       </c>
       <c r="R175" t="n">
-        <v>6814886</v>
+        <v>6814901</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18873,10 +18873,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125718</v>
+        <v>129125727</v>
       </c>
       <c r="B176" t="n">
-        <v>83011</v>
+        <v>79067</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18884,21 +18884,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18908,10 +18908,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>447772</v>
+        <v>448008</v>
       </c>
       <c r="R176" t="n">
-        <v>6815035</v>
+        <v>6815080</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18980,7 +18980,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125861</v>
+        <v>129125880</v>
       </c>
       <c r="B177" t="n">
         <v>79035</v>
@@ -19015,10 +19015,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>447887</v>
+        <v>448107</v>
       </c>
       <c r="R177" t="n">
-        <v>6815067</v>
+        <v>6815120</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19050,7 +19050,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19087,7 +19087,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129125832</v>
+        <v>129125810</v>
       </c>
       <c r="B178" t="n">
         <v>79035</v>
@@ -19122,10 +19122,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>447762</v>
+        <v>447736</v>
       </c>
       <c r="R178" t="n">
-        <v>6814968</v>
+        <v>6814886</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19157,7 +19157,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19301,32 +19301,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129125763</v>
+        <v>129125861</v>
       </c>
       <c r="B180" t="n">
-        <v>82994</v>
+        <v>79035</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19336,10 +19336,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>447801</v>
+        <v>447887</v>
       </c>
       <c r="R180" t="n">
-        <v>6814957</v>
+        <v>6815067</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19515,7 +19515,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125739</v>
+        <v>129125740</v>
       </c>
       <c r="B182" t="n">
         <v>57720</v>
@@ -19555,10 +19555,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>448089</v>
+        <v>447580</v>
       </c>
       <c r="R182" t="n">
-        <v>6815093</v>
+        <v>6814929</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19600,12 +19600,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19632,7 +19627,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125740</v>
+        <v>129125739</v>
       </c>
       <c r="B183" t="n">
         <v>57720</v>
@@ -19672,10 +19667,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>447580</v>
+        <v>448089</v>
       </c>
       <c r="R183" t="n">
-        <v>6814929</v>
+        <v>6815093</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,7 +19702,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19717,7 +19712,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19958,7 +19958,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129125876</v>
+        <v>129125793</v>
       </c>
       <c r="B186" t="n">
         <v>79035</v>
@@ -19993,10 +19993,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>448131</v>
+        <v>447819</v>
       </c>
       <c r="R186" t="n">
-        <v>6815201</v>
+        <v>6814842</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20065,7 +20065,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125780</v>
+        <v>129125783</v>
       </c>
       <c r="B187" t="n">
         <v>79035</v>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>447958</v>
+        <v>447952</v>
       </c>
       <c r="R187" t="n">
-        <v>6814987</v>
+        <v>6814960</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20172,32 +20172,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129125793</v>
+        <v>129125736</v>
       </c>
       <c r="B188" t="n">
-        <v>79035</v>
+        <v>80044</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20207,10 +20207,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>447819</v>
+        <v>447803</v>
       </c>
       <c r="R188" t="n">
-        <v>6814842</v>
+        <v>6815004</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20279,7 +20279,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125784</v>
+        <v>129125876</v>
       </c>
       <c r="B189" t="n">
         <v>79035</v>
@@ -20314,10 +20314,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>447943</v>
+        <v>448131</v>
       </c>
       <c r="R189" t="n">
-        <v>6814947</v>
+        <v>6815201</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20386,7 +20386,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129125783</v>
+        <v>129125780</v>
       </c>
       <c r="B190" t="n">
         <v>79035</v>
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>447952</v>
+        <v>447958</v>
       </c>
       <c r="R190" t="n">
-        <v>6814960</v>
+        <v>6814987</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20493,7 +20493,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129125815</v>
+        <v>129125784</v>
       </c>
       <c r="B191" t="n">
         <v>79035</v>
@@ -20528,10 +20528,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>447586</v>
+        <v>447943</v>
       </c>
       <c r="R191" t="n">
-        <v>6814809</v>
+        <v>6814947</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20600,7 +20600,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129125829</v>
+        <v>129125815</v>
       </c>
       <c r="B192" t="n">
         <v>79035</v>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>447771</v>
+        <v>447586</v>
       </c>
       <c r="R192" t="n">
-        <v>6815000</v>
+        <v>6814809</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20670,7 +20670,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20707,32 +20707,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129125736</v>
+        <v>129125829</v>
       </c>
       <c r="B193" t="n">
-        <v>80044</v>
+        <v>79035</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20742,10 +20742,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>447803</v>
+        <v>447771</v>
       </c>
       <c r="R193" t="n">
-        <v>6815004</v>
+        <v>6815000</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20926,32 +20926,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125898</v>
+        <v>129125893</v>
       </c>
       <c r="B195" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447585</v>
+        <v>447992</v>
       </c>
       <c r="R195" t="n">
-        <v>6814810</v>
+        <v>6815102</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21033,7 +21033,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129125893</v>
+        <v>129125866</v>
       </c>
       <c r="B196" t="n">
         <v>79035</v>
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>447992</v>
+        <v>448062</v>
       </c>
       <c r="R196" t="n">
-        <v>6815102</v>
+        <v>6815224</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21140,7 +21140,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125866</v>
+        <v>129125890</v>
       </c>
       <c r="B197" t="n">
         <v>79035</v>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>448062</v>
+        <v>448015</v>
       </c>
       <c r="R197" t="n">
-        <v>6815224</v>
+        <v>6815065</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,7 +21247,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125890</v>
+        <v>129125834</v>
       </c>
       <c r="B198" t="n">
         <v>79035</v>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>448015</v>
+        <v>447788</v>
       </c>
       <c r="R198" t="n">
-        <v>6815065</v>
+        <v>6814995</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,7 +21354,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125857</v>
+        <v>129125819</v>
       </c>
       <c r="B199" t="n">
         <v>79035</v>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>447909</v>
+        <v>447647</v>
       </c>
       <c r="R199" t="n">
-        <v>6815011</v>
+        <v>6815013</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,7 +21461,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125834</v>
+        <v>129125857</v>
       </c>
       <c r="B200" t="n">
         <v>79035</v>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447788</v>
+        <v>447909</v>
       </c>
       <c r="R200" t="n">
-        <v>6814995</v>
+        <v>6815011</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21675,32 +21675,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129125819</v>
+        <v>129125898</v>
       </c>
       <c r="B202" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21710,10 +21710,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>447647</v>
+        <v>447585</v>
       </c>
       <c r="R202" t="n">
-        <v>6815013</v>
+        <v>6814810</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21782,7 +21782,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129125856</v>
+        <v>129125881</v>
       </c>
       <c r="B203" t="n">
         <v>79035</v>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>447906</v>
+        <v>448111</v>
       </c>
       <c r="R203" t="n">
-        <v>6814985</v>
+        <v>6815099</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21996,7 +21996,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129125875</v>
+        <v>129125864</v>
       </c>
       <c r="B205" t="n">
         <v>79035</v>
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>448141</v>
+        <v>448025</v>
       </c>
       <c r="R205" t="n">
-        <v>6815210</v>
+        <v>6815228</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22103,7 +22103,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129125892</v>
+        <v>129125875</v>
       </c>
       <c r="B206" t="n">
         <v>79035</v>
@@ -22138,10 +22138,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>448002</v>
+        <v>448141</v>
       </c>
       <c r="R206" t="n">
-        <v>6815094</v>
+        <v>6815210</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22210,7 +22210,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129125864</v>
+        <v>129125892</v>
       </c>
       <c r="B207" t="n">
         <v>79035</v>
@@ -22245,10 +22245,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>448025</v>
+        <v>448002</v>
       </c>
       <c r="R207" t="n">
-        <v>6815228</v>
+        <v>6815094</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22317,7 +22317,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129125881</v>
+        <v>129125856</v>
       </c>
       <c r="B208" t="n">
         <v>79035</v>
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>448111</v>
+        <v>447906</v>
       </c>
       <c r="R208" t="n">
-        <v>6815099</v>
+        <v>6814985</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22387,7 +22387,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22424,7 +22424,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129125803</v>
+        <v>129125825</v>
       </c>
       <c r="B209" t="n">
         <v>79035</v>
@@ -22459,10 +22459,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>447837</v>
+        <v>447766</v>
       </c>
       <c r="R209" t="n">
-        <v>6814958</v>
+        <v>6815038</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22531,7 +22531,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129125884</v>
+        <v>129125883</v>
       </c>
       <c r="B210" t="n">
         <v>79035</v>
@@ -22566,10 +22566,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>448089</v>
+        <v>448080</v>
       </c>
       <c r="R210" t="n">
-        <v>6815055</v>
+        <v>6815060</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22638,7 +22638,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129125825</v>
+        <v>129125803</v>
       </c>
       <c r="B211" t="n">
         <v>79035</v>
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>447766</v>
+        <v>447837</v>
       </c>
       <c r="R211" t="n">
-        <v>6815038</v>
+        <v>6814958</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22745,32 +22745,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129125762</v>
+        <v>129125735</v>
       </c>
       <c r="B212" t="n">
-        <v>79035</v>
+        <v>80169</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>448058</v>
+        <v>447805</v>
       </c>
       <c r="R212" t="n">
-        <v>6815046</v>
+        <v>6815002</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22852,7 +22852,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129125883</v>
+        <v>129125884</v>
       </c>
       <c r="B213" t="n">
         <v>79035</v>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>448080</v>
+        <v>448089</v>
       </c>
       <c r="R213" t="n">
-        <v>6815060</v>
+        <v>6815055</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22959,32 +22959,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129125735</v>
+        <v>129125762</v>
       </c>
       <c r="B214" t="n">
-        <v>80169</v>
+        <v>79035</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22994,10 +22994,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>447805</v>
+        <v>448058</v>
       </c>
       <c r="R214" t="n">
-        <v>6815002</v>
+        <v>6815046</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23601,7 +23601,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129125774</v>
+        <v>129125838</v>
       </c>
       <c r="B220" t="n">
         <v>79035</v>
@@ -23636,10 +23636,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>447907</v>
+        <v>447808</v>
       </c>
       <c r="R220" t="n">
-        <v>6815056</v>
+        <v>6815019</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23708,7 +23708,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129125838</v>
+        <v>129125774</v>
       </c>
       <c r="B221" t="n">
         <v>79035</v>
@@ -23743,10 +23743,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>447808</v>
+        <v>447907</v>
       </c>
       <c r="R221" t="n">
-        <v>6815019</v>
+        <v>6815056</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24141,7 +24141,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125776</v>
+        <v>129125817</v>
       </c>
       <c r="B225" t="n">
         <v>79035</v>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447923</v>
+        <v>447580</v>
       </c>
       <c r="R225" t="n">
-        <v>6814998</v>
+        <v>6814929</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,7 +24248,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125790</v>
+        <v>129125794</v>
       </c>
       <c r="B226" t="n">
         <v>79035</v>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447855</v>
+        <v>447798</v>
       </c>
       <c r="R226" t="n">
-        <v>6814877</v>
+        <v>6814819</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,7 +24355,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125817</v>
+        <v>129125823</v>
       </c>
       <c r="B227" t="n">
         <v>79035</v>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447580</v>
+        <v>447754</v>
       </c>
       <c r="R227" t="n">
-        <v>6814929</v>
+        <v>6815045</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24462,7 +24462,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129125794</v>
+        <v>129125776</v>
       </c>
       <c r="B228" t="n">
         <v>79035</v>
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>447798</v>
+        <v>447923</v>
       </c>
       <c r="R228" t="n">
-        <v>6814819</v>
+        <v>6814998</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24569,10 +24569,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129125754</v>
+        <v>129125889</v>
       </c>
       <c r="B229" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24580,21 +24580,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24604,10 +24604,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>447877</v>
+        <v>448024</v>
       </c>
       <c r="R229" t="n">
-        <v>6814908</v>
+        <v>6815046</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24658,7 +24658,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -24677,7 +24676,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125889</v>
+        <v>129125773</v>
       </c>
       <c r="B230" t="n">
         <v>79035</v>
@@ -24712,10 +24711,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>448024</v>
+        <v>447907</v>
       </c>
       <c r="R230" t="n">
-        <v>6815046</v>
+        <v>6815075</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24747,7 +24746,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24757,7 +24756,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24784,10 +24783,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129125854</v>
+        <v>129125754</v>
       </c>
       <c r="B231" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24795,21 +24794,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24819,10 +24818,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>447876</v>
+        <v>447877</v>
       </c>
       <c r="R231" t="n">
-        <v>6814962</v>
+        <v>6814908</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24854,7 +24853,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24864,7 +24863,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24873,6 +24872,7 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -24891,7 +24891,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129125773</v>
+        <v>129125790</v>
       </c>
       <c r="B232" t="n">
         <v>79035</v>
@@ -24926,10 +24926,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>447907</v>
+        <v>447855</v>
       </c>
       <c r="R232" t="n">
-        <v>6815075</v>
+        <v>6814877</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24961,7 +24961,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24998,7 +24998,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129125823</v>
+        <v>129125854</v>
       </c>
       <c r="B233" t="n">
         <v>79035</v>
@@ -25033,10 +25033,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>447754</v>
+        <v>447876</v>
       </c>
       <c r="R233" t="n">
-        <v>6815045</v>
+        <v>6814962</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -6917,7 +6917,7 @@
         <v>128629773</v>
       </c>
       <c r="B65" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>129125764</v>
       </c>
       <c r="B66" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>129125766</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>129125786</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129125738</v>
+        <v>129125752</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>81024</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,39 +7352,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447735</v>
+        <v>447893</v>
       </c>
       <c r="R69" t="n">
-        <v>6814890</v>
+        <v>6814914</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7416,7 +7411,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7426,12 +7421,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,10 +7448,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129125752</v>
+        <v>129125821</v>
       </c>
       <c r="B70" t="n">
-        <v>81020</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7469,21 +7459,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447893</v>
+        <v>447754</v>
       </c>
       <c r="R70" t="n">
-        <v>6814914</v>
+        <v>6815052</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,7 +7518,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7538,7 +7528,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7555,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125821</v>
+        <v>129125787</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7600,10 +7590,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447754</v>
+        <v>447908</v>
       </c>
       <c r="R71" t="n">
-        <v>6815052</v>
+        <v>6814933</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,7 +7625,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7645,7 +7635,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7672,10 +7662,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125787</v>
+        <v>129125835</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7707,10 +7697,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447908</v>
+        <v>447793</v>
       </c>
       <c r="R72" t="n">
-        <v>6814933</v>
+        <v>6815007</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7742,7 +7732,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7752,7 +7742,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7779,10 +7769,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125843</v>
+        <v>129125812</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7814,10 +7804,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447812</v>
+        <v>447682</v>
       </c>
       <c r="R73" t="n">
-        <v>6815055</v>
+        <v>6814779</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7849,7 +7839,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7859,7 +7849,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7886,10 +7876,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129125812</v>
+        <v>129125843</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7921,10 +7911,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447682</v>
+        <v>447812</v>
       </c>
       <c r="R74" t="n">
-        <v>6814779</v>
+        <v>6815055</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7956,7 +7946,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7966,7 +7956,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7996,7 +7986,7 @@
         <v>129125755</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8104,7 +8094,7 @@
         <v>129125798</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8208,10 +8198,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129125835</v>
+        <v>129125738</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8219,34 +8209,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447793</v>
+        <v>447735</v>
       </c>
       <c r="R77" t="n">
-        <v>6815007</v>
+        <v>6814890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8278,7 +8273,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8288,7 +8283,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8318,7 +8318,7 @@
         <v>129125732</v>
       </c>
       <c r="B78" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,54 +8427,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125759</v>
+        <v>129125729</v>
       </c>
       <c r="B79" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447640</v>
+        <v>448039</v>
       </c>
       <c r="R79" t="n">
-        <v>6814923</v>
+        <v>6815229</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,7 +8497,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8516,7 +8507,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8546,7 +8537,7 @@
         <v>129125751</v>
       </c>
       <c r="B80" t="n">
-        <v>81020</v>
+        <v>81024</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8650,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129125853</v>
+        <v>129125730</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8661,21 +8652,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8685,10 +8676,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447853</v>
+        <v>448098</v>
       </c>
       <c r="R81" t="n">
-        <v>6814972</v>
+        <v>6815212</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8720,7 +8711,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8730,7 +8721,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8760,7 +8751,7 @@
         <v>129125867</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8867,7 +8858,7 @@
         <v>129125824</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8971,10 +8962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125767</v>
+        <v>129125873</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9006,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447915</v>
+        <v>448163</v>
       </c>
       <c r="R84" t="n">
-        <v>6815140</v>
+        <v>6815302</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9041,7 +9032,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9051,7 +9042,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9078,10 +9069,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125729</v>
+        <v>129125771</v>
       </c>
       <c r="B85" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9089,21 +9080,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9113,10 +9104,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448039</v>
+        <v>447925</v>
       </c>
       <c r="R85" t="n">
-        <v>6815229</v>
+        <v>6815103</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9148,7 +9139,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9158,7 +9149,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9185,10 +9176,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125730</v>
+        <v>129125853</v>
       </c>
       <c r="B86" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9196,21 +9187,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9220,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>448098</v>
+        <v>447853</v>
       </c>
       <c r="R86" t="n">
-        <v>6815212</v>
+        <v>6814972</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9255,7 +9246,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9265,7 +9256,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9292,10 +9283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129125771</v>
+        <v>129125808</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9327,10 +9318,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447925</v>
+        <v>447782</v>
       </c>
       <c r="R87" t="n">
-        <v>6815103</v>
+        <v>6814944</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9362,7 +9353,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9372,7 +9363,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9399,10 +9390,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129125873</v>
+        <v>129125895</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9434,10 +9425,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>448163</v>
+        <v>447963</v>
       </c>
       <c r="R88" t="n">
-        <v>6815302</v>
+        <v>6815131</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9469,7 +9460,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9479,7 +9470,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9506,10 +9497,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129125808</v>
+        <v>129125767</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9541,10 +9532,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447782</v>
+        <v>447915</v>
       </c>
       <c r="R89" t="n">
-        <v>6814944</v>
+        <v>6815140</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9576,7 +9567,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9586,7 +9577,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9613,45 +9604,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129125895</v>
+        <v>129125759</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447963</v>
+        <v>447640</v>
       </c>
       <c r="R90" t="n">
-        <v>6815131</v>
+        <v>6814923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125753</v>
+        <v>129125831</v>
       </c>
       <c r="B91" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447766</v>
+        <v>447755</v>
       </c>
       <c r="R91" t="n">
-        <v>6814899</v>
+        <v>6814973</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,12 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9814,7 +9809,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9833,10 +9827,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125831</v>
+        <v>129125809</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9868,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447755</v>
+        <v>447763</v>
       </c>
       <c r="R92" t="n">
-        <v>6814973</v>
+        <v>6814923</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9903,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9913,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9940,10 +9934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125722</v>
+        <v>129125772</v>
       </c>
       <c r="B93" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9951,21 +9945,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9975,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447757</v>
+        <v>447920</v>
       </c>
       <c r="R93" t="n">
-        <v>6814906</v>
+        <v>6815082</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10010,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10020,7 +10014,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10047,10 +10041,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125874</v>
+        <v>129125795</v>
       </c>
       <c r="B94" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10082,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>448182</v>
+        <v>447790</v>
       </c>
       <c r="R94" t="n">
-        <v>6815308</v>
+        <v>6814834</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10117,7 +10111,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10127,7 +10121,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10154,10 +10148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125795</v>
+        <v>129125722</v>
       </c>
       <c r="B95" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10165,21 +10159,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10189,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447790</v>
+        <v>447757</v>
       </c>
       <c r="R95" t="n">
-        <v>6814834</v>
+        <v>6814906</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10224,7 +10218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10234,7 +10228,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10261,10 +10255,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125809</v>
+        <v>129125874</v>
       </c>
       <c r="B96" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10296,10 +10290,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447763</v>
+        <v>448182</v>
       </c>
       <c r="R96" t="n">
-        <v>6814923</v>
+        <v>6815308</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10331,7 +10325,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10341,7 +10335,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10368,10 +10362,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125772</v>
+        <v>129125753</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10379,21 +10373,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10403,10 +10397,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447920</v>
+        <v>447766</v>
       </c>
       <c r="R97" t="n">
-        <v>6815082</v>
+        <v>6814899</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,7 +10432,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10448,7 +10442,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10457,6 +10456,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10475,10 +10475,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129125820</v>
+        <v>129125719</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10486,21 +10486,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447706</v>
+        <v>447855</v>
       </c>
       <c r="R98" t="n">
-        <v>6815025</v>
+        <v>6814877</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10582,10 +10582,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129125741</v>
+        <v>129125858</v>
       </c>
       <c r="B99" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10593,39 +10593,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447902</v>
+        <v>447914</v>
       </c>
       <c r="R99" t="n">
-        <v>6814922</v>
+        <v>6815024</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10657,7 +10652,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10667,7 +10662,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10694,32 +10689,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129125746</v>
+        <v>129125872</v>
       </c>
       <c r="B100" t="n">
-        <v>97536</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10729,10 +10724,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>448129</v>
+        <v>448159</v>
       </c>
       <c r="R100" t="n">
-        <v>6815200</v>
+        <v>6815277</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10764,7 +10759,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10774,7 +10769,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10801,10 +10796,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129125719</v>
+        <v>129125820</v>
       </c>
       <c r="B101" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10812,21 +10807,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10836,10 +10831,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447855</v>
+        <v>447706</v>
       </c>
       <c r="R101" t="n">
-        <v>6814877</v>
+        <v>6815025</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10871,7 +10866,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10881,7 +10876,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10908,10 +10903,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129125872</v>
+        <v>129125888</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10943,10 +10938,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448159</v>
+        <v>448042</v>
       </c>
       <c r="R102" t="n">
-        <v>6815277</v>
+        <v>6815053</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10978,7 +10973,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10988,7 +10983,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11018,7 +11013,7 @@
         <v>129125836</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11122,10 +11117,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129125888</v>
+        <v>129125741</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11133,34 +11128,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448042</v>
+        <v>447902</v>
       </c>
       <c r="R104" t="n">
-        <v>6815053</v>
+        <v>6814922</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11229,32 +11229,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125858</v>
+        <v>129125746</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>97546</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447914</v>
+        <v>448129</v>
       </c>
       <c r="R105" t="n">
-        <v>6815024</v>
+        <v>6815200</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11339,7 +11339,7 @@
         <v>129125837</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11443,10 +11443,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129125814</v>
+        <v>129125886</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447611</v>
+        <v>448097</v>
       </c>
       <c r="R107" t="n">
-        <v>6814782</v>
+        <v>6815025</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11550,10 +11550,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129125868</v>
+        <v>129125814</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448101</v>
+        <v>447611</v>
       </c>
       <c r="R108" t="n">
-        <v>6815213</v>
+        <v>6814782</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11657,10 +11657,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129125813</v>
+        <v>129125868</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447617</v>
+        <v>448101</v>
       </c>
       <c r="R109" t="n">
-        <v>6814828</v>
+        <v>6815213</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11764,10 +11764,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129125886</v>
+        <v>129125813</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>448097</v>
+        <v>447617</v>
       </c>
       <c r="R110" t="n">
-        <v>6815025</v>
+        <v>6814828</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11874,7 +11874,7 @@
         <v>129125721</v>
       </c>
       <c r="B111" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11978,10 +11978,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125807</v>
+        <v>129125863</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447797</v>
+        <v>447878</v>
       </c>
       <c r="R112" t="n">
-        <v>6814950</v>
+        <v>6815153</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,10 +12085,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125779</v>
+        <v>129125807</v>
       </c>
       <c r="B113" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447936</v>
+        <v>447797</v>
       </c>
       <c r="R113" t="n">
-        <v>6814995</v>
+        <v>6814950</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,32 +12192,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125841</v>
+        <v>129125728</v>
       </c>
       <c r="B114" t="n">
-        <v>79035</v>
+        <v>91497</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447812</v>
+        <v>447872</v>
       </c>
       <c r="R114" t="n">
-        <v>6815036</v>
+        <v>6815131</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12302,7 +12302,7 @@
         <v>129125891</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12406,32 +12406,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125728</v>
+        <v>129125779</v>
       </c>
       <c r="B116" t="n">
-        <v>91491</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447872</v>
+        <v>447936</v>
       </c>
       <c r="R116" t="n">
-        <v>6815131</v>
+        <v>6814995</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,10 +12513,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125863</v>
+        <v>129125841</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447878</v>
+        <v>447812</v>
       </c>
       <c r="R117" t="n">
-        <v>6815153</v>
+        <v>6815036</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12623,7 +12623,7 @@
         <v>129125851</v>
       </c>
       <c r="B118" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12727,10 +12727,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129125865</v>
+        <v>129125827</v>
       </c>
       <c r="B119" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>448049</v>
+        <v>447767</v>
       </c>
       <c r="R119" t="n">
-        <v>6815224</v>
+        <v>6815014</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12834,32 +12834,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125750</v>
+        <v>129125850</v>
       </c>
       <c r="B120" t="n">
-        <v>80176</v>
+        <v>79039</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447714</v>
+        <v>447844</v>
       </c>
       <c r="R120" t="n">
-        <v>6815023</v>
+        <v>6815026</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,10 +12941,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125877</v>
+        <v>129125811</v>
       </c>
       <c r="B121" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>448126</v>
+        <v>447716</v>
       </c>
       <c r="R121" t="n">
-        <v>6815198</v>
+        <v>6814829</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13048,10 +13048,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129125850</v>
+        <v>129125865</v>
       </c>
       <c r="B122" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447844</v>
+        <v>448049</v>
       </c>
       <c r="R122" t="n">
-        <v>6815026</v>
+        <v>6815224</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13155,10 +13155,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125811</v>
+        <v>129125882</v>
       </c>
       <c r="B123" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447716</v>
+        <v>448089</v>
       </c>
       <c r="R123" t="n">
-        <v>6814829</v>
+        <v>6815086</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,10 +13262,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125852</v>
+        <v>129125791</v>
       </c>
       <c r="B124" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>447839</v>
       </c>
       <c r="R124" t="n">
-        <v>6814995</v>
+        <v>6814871</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,10 +13369,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125791</v>
+        <v>129125852</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>447839</v>
       </c>
       <c r="R125" t="n">
-        <v>6814871</v>
+        <v>6814995</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,10 +13476,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125894</v>
+        <v>129125877</v>
       </c>
       <c r="B126" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447978</v>
+        <v>448126</v>
       </c>
       <c r="R126" t="n">
-        <v>6815111</v>
+        <v>6815198</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,10 +13583,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125827</v>
+        <v>129125894</v>
       </c>
       <c r="B127" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447767</v>
+        <v>447978</v>
       </c>
       <c r="R127" t="n">
-        <v>6815014</v>
+        <v>6815111</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13693,7 +13693,7 @@
         <v>129125859</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13797,10 +13797,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125882</v>
+        <v>129125845</v>
       </c>
       <c r="B129" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>448089</v>
+        <v>447801</v>
       </c>
       <c r="R129" t="n">
-        <v>6815086</v>
+        <v>6815082</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,32 +13904,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125845</v>
+        <v>129125750</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>80180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447801</v>
+        <v>447714</v>
       </c>
       <c r="R130" t="n">
-        <v>6815082</v>
+        <v>6815023</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,10 +14011,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125844</v>
+        <v>129125770</v>
       </c>
       <c r="B131" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447808</v>
+        <v>447916</v>
       </c>
       <c r="R131" t="n">
-        <v>6815078</v>
+        <v>6815113</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14118,32 +14118,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125743</v>
+        <v>129125846</v>
       </c>
       <c r="B132" t="n">
-        <v>80044</v>
+        <v>79039</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14153,10 +14153,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447735</v>
+        <v>447815</v>
       </c>
       <c r="R132" t="n">
-        <v>6814890</v>
+        <v>6815100</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14198,12 +14198,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14230,10 +14225,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125770</v>
+        <v>129125879</v>
       </c>
       <c r="B133" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14265,10 +14260,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447916</v>
+        <v>448114</v>
       </c>
       <c r="R133" t="n">
-        <v>6815113</v>
+        <v>6815160</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14300,7 +14295,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14310,7 +14305,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14337,32 +14332,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129125879</v>
+        <v>129125743</v>
       </c>
       <c r="B134" t="n">
-        <v>79035</v>
+        <v>80048</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14372,10 +14367,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>448114</v>
+        <v>447735</v>
       </c>
       <c r="R134" t="n">
-        <v>6815160</v>
+        <v>6814890</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14407,7 +14402,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14417,7 +14412,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14444,10 +14444,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129125846</v>
+        <v>129125844</v>
       </c>
       <c r="B135" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>447815</v>
+        <v>447808</v>
       </c>
       <c r="R135" t="n">
-        <v>6815100</v>
+        <v>6815078</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14551,10 +14551,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129125781</v>
+        <v>129125805</v>
       </c>
       <c r="B136" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14586,10 +14586,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>447968</v>
+        <v>447826</v>
       </c>
       <c r="R136" t="n">
-        <v>6814977</v>
+        <v>6814982</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14658,10 +14658,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125797</v>
+        <v>129125781</v>
       </c>
       <c r="B137" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14693,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>447781</v>
+        <v>447968</v>
       </c>
       <c r="R137" t="n">
-        <v>6814894</v>
+        <v>6814977</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14765,10 +14765,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125805</v>
+        <v>129125818</v>
       </c>
       <c r="B138" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>447826</v>
+        <v>447641</v>
       </c>
       <c r="R138" t="n">
-        <v>6814982</v>
+        <v>6814924</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14872,10 +14872,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125887</v>
+        <v>129125885</v>
       </c>
       <c r="B139" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>448080</v>
       </c>
       <c r="R139" t="n">
-        <v>6815039</v>
+        <v>6815037</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14979,10 +14979,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125885</v>
+        <v>129125797</v>
       </c>
       <c r="B140" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>448080</v>
+        <v>447781</v>
       </c>
       <c r="R140" t="n">
-        <v>6815037</v>
+        <v>6814894</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15086,10 +15086,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125818</v>
+        <v>129125887</v>
       </c>
       <c r="B141" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>447641</v>
+        <v>448080</v>
       </c>
       <c r="R141" t="n">
-        <v>6814924</v>
+        <v>6815039</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15196,7 +15196,7 @@
         <v>129125737</v>
       </c>
       <c r="B142" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>129125899</v>
       </c>
       <c r="B143" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15412,10 +15412,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125775</v>
+        <v>129125839</v>
       </c>
       <c r="B144" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447916</v>
+        <v>447805</v>
       </c>
       <c r="R144" t="n">
-        <v>6815021</v>
+        <v>6815025</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15522,7 +15522,7 @@
         <v>129125792</v>
       </c>
       <c r="B145" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15626,10 +15626,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125796</v>
+        <v>129125826</v>
       </c>
       <c r="B146" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447749</v>
+        <v>447765</v>
       </c>
       <c r="R146" t="n">
-        <v>6814850</v>
+        <v>6815023</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,10 +15733,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125826</v>
+        <v>129125828</v>
       </c>
       <c r="B147" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447765</v>
+        <v>447781</v>
       </c>
       <c r="R147" t="n">
-        <v>6815023</v>
+        <v>6815009</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,10 +15840,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125828</v>
+        <v>129125775</v>
       </c>
       <c r="B148" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447781</v>
+        <v>447916</v>
       </c>
       <c r="R148" t="n">
-        <v>6815009</v>
+        <v>6815021</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15947,10 +15947,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129125839</v>
+        <v>129125796</v>
       </c>
       <c r="B149" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>447805</v>
+        <v>447749</v>
       </c>
       <c r="R149" t="n">
-        <v>6815025</v>
+        <v>6814850</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16057,7 +16057,7 @@
         <v>129125720</v>
       </c>
       <c r="B150" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16161,10 +16161,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129125802</v>
+        <v>129125806</v>
       </c>
       <c r="B151" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>447821</v>
+        <v>447816</v>
       </c>
       <c r="R151" t="n">
-        <v>6814955</v>
+        <v>6814979</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16268,10 +16268,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125768</v>
+        <v>129125830</v>
       </c>
       <c r="B152" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16303,10 +16303,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447909</v>
+        <v>447767</v>
       </c>
       <c r="R152" t="n">
-        <v>6815119</v>
+        <v>6814993</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,10 +16375,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125801</v>
+        <v>129125799</v>
       </c>
       <c r="B153" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>447814</v>
+        <v>447804</v>
       </c>
       <c r="R153" t="n">
-        <v>6814948</v>
+        <v>6814911</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16482,54 +16482,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125758</v>
+        <v>129125804</v>
       </c>
       <c r="B154" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>447571</v>
+        <v>447840</v>
       </c>
       <c r="R154" t="n">
-        <v>6814831</v>
+        <v>6814978</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16561,7 +16552,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16571,7 +16562,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16598,54 +16589,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125757</v>
+        <v>129125801</v>
       </c>
       <c r="B155" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447746</v>
+        <v>447814</v>
       </c>
       <c r="R155" t="n">
-        <v>6814851</v>
+        <v>6814948</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16677,7 +16659,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16687,7 +16669,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16714,45 +16696,54 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125749</v>
+        <v>129125757</v>
       </c>
       <c r="B156" t="n">
-        <v>80176</v>
+        <v>98669</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447581</v>
+        <v>447746</v>
       </c>
       <c r="R156" t="n">
-        <v>6814869</v>
+        <v>6814851</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16784,7 +16775,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16794,7 +16785,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16821,45 +16812,54 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125806</v>
+        <v>129125758</v>
       </c>
       <c r="B157" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447816</v>
+        <v>447571</v>
       </c>
       <c r="R157" t="n">
-        <v>6814979</v>
+        <v>6814831</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16928,10 +16928,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125799</v>
+        <v>129125769</v>
       </c>
       <c r="B158" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16963,10 +16963,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>447804</v>
+        <v>447912</v>
       </c>
       <c r="R158" t="n">
-        <v>6814911</v>
+        <v>6815110</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16998,7 +16998,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17035,10 +17035,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129125804</v>
+        <v>129125869</v>
       </c>
       <c r="B159" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17070,10 +17070,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>447840</v>
+        <v>448114</v>
       </c>
       <c r="R159" t="n">
-        <v>6814978</v>
+        <v>6815209</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17105,7 +17105,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17142,10 +17142,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125878</v>
+        <v>129125849</v>
       </c>
       <c r="B160" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17177,10 +17177,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>448121</v>
+        <v>447825</v>
       </c>
       <c r="R160" t="n">
-        <v>6815175</v>
+        <v>6815056</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,10 +17249,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125849</v>
+        <v>129125768</v>
       </c>
       <c r="B161" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17284,10 +17284,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>447825</v>
+        <v>447909</v>
       </c>
       <c r="R161" t="n">
-        <v>6815056</v>
+        <v>6815119</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,10 +17356,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125830</v>
+        <v>129125878</v>
       </c>
       <c r="B162" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17391,10 +17391,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>447767</v>
+        <v>448121</v>
       </c>
       <c r="R162" t="n">
-        <v>6814993</v>
+        <v>6815175</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17463,10 +17463,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125769</v>
+        <v>129125802</v>
       </c>
       <c r="B163" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17498,10 +17498,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>447912</v>
+        <v>447821</v>
       </c>
       <c r="R163" t="n">
-        <v>6815110</v>
+        <v>6814955</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17570,32 +17570,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129125869</v>
+        <v>129125749</v>
       </c>
       <c r="B164" t="n">
-        <v>79035</v>
+        <v>80180</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17605,10 +17605,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>448114</v>
+        <v>447581</v>
       </c>
       <c r="R164" t="n">
-        <v>6815209</v>
+        <v>6814869</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17680,7 +17680,7 @@
         <v>129125731</v>
       </c>
       <c r="B165" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129125860</v>
+        <v>129125816</v>
       </c>
       <c r="B166" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17824,10 +17824,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>447887</v>
+        <v>447568</v>
       </c>
       <c r="R166" t="n">
-        <v>6815042</v>
+        <v>6814828</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17869,7 +17869,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17896,10 +17896,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129125855</v>
+        <v>129125860</v>
       </c>
       <c r="B167" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17931,10 +17931,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>447895</v>
+        <v>447887</v>
       </c>
       <c r="R167" t="n">
-        <v>6814968</v>
+        <v>6815042</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18003,10 +18003,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129125816</v>
+        <v>129125855</v>
       </c>
       <c r="B168" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18038,10 +18038,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>447568</v>
+        <v>447895</v>
       </c>
       <c r="R168" t="n">
-        <v>6814828</v>
+        <v>6814968</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18113,7 +18113,7 @@
         <v>129125734</v>
       </c>
       <c r="B169" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18231,10 +18231,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129125833</v>
+        <v>129125724</v>
       </c>
       <c r="B170" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18242,21 +18242,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18266,10 +18266,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>447772</v>
+        <v>447803</v>
       </c>
       <c r="R170" t="n">
-        <v>6814969</v>
+        <v>6815095</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18338,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125832</v>
+        <v>129125723</v>
       </c>
       <c r="B171" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18349,21 +18349,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18373,10 +18373,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>447762</v>
+        <v>447751</v>
       </c>
       <c r="R171" t="n">
-        <v>6814968</v>
+        <v>6814901</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18445,10 +18445,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129125718</v>
+        <v>129125727</v>
       </c>
       <c r="B172" t="n">
-        <v>83011</v>
+        <v>79071</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18456,21 +18456,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18480,10 +18480,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>447772</v>
+        <v>448008</v>
       </c>
       <c r="R172" t="n">
-        <v>6815035</v>
+        <v>6815080</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18552,32 +18552,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125763</v>
+        <v>129125880</v>
       </c>
       <c r="B173" t="n">
-        <v>82994</v>
+        <v>79039</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18587,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>447801</v>
+        <v>448107</v>
       </c>
       <c r="R173" t="n">
-        <v>6814957</v>
+        <v>6815120</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18659,10 +18659,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125724</v>
+        <v>129125833</v>
       </c>
       <c r="B174" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18670,21 +18670,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>447803</v>
+        <v>447772</v>
       </c>
       <c r="R174" t="n">
-        <v>6815095</v>
+        <v>6814969</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18766,10 +18766,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125723</v>
+        <v>129125842</v>
       </c>
       <c r="B175" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18777,21 +18777,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18801,10 +18801,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447751</v>
+        <v>447813</v>
       </c>
       <c r="R175" t="n">
-        <v>6814901</v>
+        <v>6815044</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18873,10 +18873,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125727</v>
+        <v>129125739</v>
       </c>
       <c r="B176" t="n">
-        <v>79067</v>
+        <v>57722</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18884,34 +18884,39 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>448008</v>
+        <v>448089</v>
       </c>
       <c r="R176" t="n">
-        <v>6815080</v>
+        <v>6815093</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18943,7 +18948,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18953,7 +18958,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18980,32 +18990,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125880</v>
+        <v>129125745</v>
       </c>
       <c r="B177" t="n">
-        <v>79035</v>
+        <v>97540</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19015,10 +19025,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>448107</v>
+        <v>448023</v>
       </c>
       <c r="R177" t="n">
-        <v>6815120</v>
+        <v>6815221</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19050,7 +19060,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19060,7 +19070,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19090,7 +19100,7 @@
         <v>129125810</v>
       </c>
       <c r="B178" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19194,10 +19204,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129125862</v>
+        <v>129125718</v>
       </c>
       <c r="B179" t="n">
-        <v>79035</v>
+        <v>83015</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19205,21 +19215,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19229,10 +19239,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>447867</v>
+        <v>447772</v>
       </c>
       <c r="R179" t="n">
-        <v>6815109</v>
+        <v>6815035</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19264,7 +19274,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19274,7 +19284,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19304,7 +19314,7 @@
         <v>129125861</v>
       </c>
       <c r="B180" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19408,10 +19418,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129125842</v>
+        <v>129125832</v>
       </c>
       <c r="B181" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19443,10 +19453,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>447813</v>
+        <v>447762</v>
       </c>
       <c r="R181" t="n">
-        <v>6815044</v>
+        <v>6814968</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19478,7 +19488,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19488,7 +19498,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19515,10 +19525,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125740</v>
+        <v>129125862</v>
       </c>
       <c r="B182" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19526,39 +19536,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>447580</v>
+        <v>447867</v>
       </c>
       <c r="R182" t="n">
-        <v>6814929</v>
+        <v>6815109</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19590,7 +19595,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19600,7 +19605,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19627,50 +19632,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125739</v>
+        <v>129125763</v>
       </c>
       <c r="B183" t="n">
-        <v>57720</v>
+        <v>82998</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>448089</v>
+        <v>447801</v>
       </c>
       <c r="R183" t="n">
-        <v>6815093</v>
+        <v>6814957</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19712,12 +19712,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19744,45 +19739,50 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129125745</v>
+        <v>129125740</v>
       </c>
       <c r="B184" t="n">
-        <v>97530</v>
+        <v>57722</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>448023</v>
+        <v>447580</v>
       </c>
       <c r="R184" t="n">
-        <v>6815221</v>
+        <v>6814929</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19854,7 +19854,7 @@
         <v>129125725</v>
       </c>
       <c r="B185" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19958,10 +19958,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129125793</v>
+        <v>129125783</v>
       </c>
       <c r="B186" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19993,10 +19993,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>447819</v>
+        <v>447952</v>
       </c>
       <c r="R186" t="n">
-        <v>6814842</v>
+        <v>6814960</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20065,10 +20065,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125783</v>
+        <v>129125784</v>
       </c>
       <c r="B187" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>447952</v>
+        <v>447943</v>
       </c>
       <c r="R187" t="n">
-        <v>6814960</v>
+        <v>6814947</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20172,32 +20172,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129125736</v>
+        <v>129125793</v>
       </c>
       <c r="B188" t="n">
-        <v>80044</v>
+        <v>79039</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20207,10 +20207,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>447803</v>
+        <v>447819</v>
       </c>
       <c r="R188" t="n">
-        <v>6815004</v>
+        <v>6814842</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20242,7 +20242,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20279,10 +20279,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125876</v>
+        <v>129125815</v>
       </c>
       <c r="B189" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20314,10 +20314,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>448131</v>
+        <v>447586</v>
       </c>
       <c r="R189" t="n">
-        <v>6815201</v>
+        <v>6814809</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20389,7 +20389,7 @@
         <v>129125780</v>
       </c>
       <c r="B190" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20493,10 +20493,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129125784</v>
+        <v>129125876</v>
       </c>
       <c r="B191" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20528,10 +20528,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>447943</v>
+        <v>448131</v>
       </c>
       <c r="R191" t="n">
-        <v>6814947</v>
+        <v>6815201</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20600,10 +20600,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129125815</v>
+        <v>129125829</v>
       </c>
       <c r="B192" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>447586</v>
+        <v>447771</v>
       </c>
       <c r="R192" t="n">
-        <v>6814809</v>
+        <v>6815000</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20670,7 +20670,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20707,10 +20707,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129125829</v>
+        <v>129125896</v>
       </c>
       <c r="B193" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20718,34 +20718,39 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>447771</v>
+        <v>447925</v>
       </c>
       <c r="R193" t="n">
-        <v>6815000</v>
+        <v>6815105</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20777,7 +20782,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20787,7 +20792,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20814,50 +20819,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129125896</v>
+        <v>129125736</v>
       </c>
       <c r="B194" t="n">
-        <v>57723</v>
+        <v>80048</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>447925</v>
+        <v>447803</v>
       </c>
       <c r="R194" t="n">
-        <v>6815105</v>
+        <v>6815004</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20926,10 +20926,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125893</v>
+        <v>129125847</v>
       </c>
       <c r="B195" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447992</v>
+        <v>447814</v>
       </c>
       <c r="R195" t="n">
-        <v>6815102</v>
+        <v>6815081</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21033,10 +21033,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129125866</v>
+        <v>129125857</v>
       </c>
       <c r="B196" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>448062</v>
+        <v>447909</v>
       </c>
       <c r="R196" t="n">
-        <v>6815224</v>
+        <v>6815011</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21140,10 +21140,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125890</v>
+        <v>129125893</v>
       </c>
       <c r="B197" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>448015</v>
+        <v>447992</v>
       </c>
       <c r="R197" t="n">
-        <v>6815065</v>
+        <v>6815102</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,10 +21247,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125834</v>
+        <v>129125866</v>
       </c>
       <c r="B198" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>447788</v>
+        <v>448062</v>
       </c>
       <c r="R198" t="n">
-        <v>6814995</v>
+        <v>6815224</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,10 +21354,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125819</v>
+        <v>129125890</v>
       </c>
       <c r="B199" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>447647</v>
+        <v>448015</v>
       </c>
       <c r="R199" t="n">
-        <v>6815013</v>
+        <v>6815065</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,10 +21461,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125857</v>
+        <v>129125834</v>
       </c>
       <c r="B200" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447909</v>
+        <v>447788</v>
       </c>
       <c r="R200" t="n">
-        <v>6815011</v>
+        <v>6814995</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21568,10 +21568,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129125847</v>
+        <v>129125819</v>
       </c>
       <c r="B201" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>447814</v>
+        <v>447647</v>
       </c>
       <c r="R201" t="n">
-        <v>6815081</v>
+        <v>6815013</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21678,7 +21678,7 @@
         <v>129125898</v>
       </c>
       <c r="B202" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>129125881</v>
       </c>
       <c r="B203" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>129125788</v>
       </c>
       <c r="B204" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21996,10 +21996,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129125864</v>
+        <v>129125856</v>
       </c>
       <c r="B205" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>448025</v>
+        <v>447906</v>
       </c>
       <c r="R205" t="n">
-        <v>6815228</v>
+        <v>6814985</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22106,7 +22106,7 @@
         <v>129125875</v>
       </c>
       <c r="B206" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>129125892</v>
       </c>
       <c r="B207" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22317,10 +22317,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129125856</v>
+        <v>129125864</v>
       </c>
       <c r="B208" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>447906</v>
+        <v>448025</v>
       </c>
       <c r="R208" t="n">
-        <v>6814985</v>
+        <v>6815228</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22387,7 +22387,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22424,32 +22424,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129125825</v>
+        <v>129125735</v>
       </c>
       <c r="B209" t="n">
-        <v>79035</v>
+        <v>80173</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22459,10 +22459,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>447766</v>
+        <v>447805</v>
       </c>
       <c r="R209" t="n">
-        <v>6815038</v>
+        <v>6815002</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22531,10 +22531,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129125883</v>
+        <v>129125825</v>
       </c>
       <c r="B210" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22566,10 +22566,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>448080</v>
+        <v>447766</v>
       </c>
       <c r="R210" t="n">
-        <v>6815060</v>
+        <v>6815038</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22638,10 +22638,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129125803</v>
+        <v>129125884</v>
       </c>
       <c r="B211" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>447837</v>
+        <v>448089</v>
       </c>
       <c r="R211" t="n">
-        <v>6814958</v>
+        <v>6815055</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22745,32 +22745,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129125735</v>
+        <v>129125762</v>
       </c>
       <c r="B212" t="n">
-        <v>80169</v>
+        <v>79039</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>447805</v>
+        <v>448058</v>
       </c>
       <c r="R212" t="n">
-        <v>6815002</v>
+        <v>6815046</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22852,10 +22852,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129125884</v>
+        <v>129125883</v>
       </c>
       <c r="B213" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>448089</v>
+        <v>448080</v>
       </c>
       <c r="R213" t="n">
-        <v>6815055</v>
+        <v>6815060</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22959,10 +22959,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129125762</v>
+        <v>129125803</v>
       </c>
       <c r="B214" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22994,10 +22994,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>448058</v>
+        <v>447837</v>
       </c>
       <c r="R214" t="n">
-        <v>6815046</v>
+        <v>6814958</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23066,10 +23066,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129125785</v>
+        <v>129125733</v>
       </c>
       <c r="B215" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23077,34 +23077,39 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>447935</v>
+        <v>447785</v>
       </c>
       <c r="R215" t="n">
-        <v>6814942</v>
+        <v>6814977</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23136,7 +23141,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23146,7 +23151,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23173,10 +23178,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129125789</v>
+        <v>129125848</v>
       </c>
       <c r="B216" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23208,10 +23213,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>447869</v>
+        <v>447816</v>
       </c>
       <c r="R216" t="n">
-        <v>6814887</v>
+        <v>6815066</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23243,7 +23248,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23253,7 +23258,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23280,10 +23285,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129125848</v>
+        <v>129125838</v>
       </c>
       <c r="B217" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23315,10 +23320,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>447816</v>
+        <v>447808</v>
       </c>
       <c r="R217" t="n">
-        <v>6815066</v>
+        <v>6815019</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23350,7 +23355,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23360,7 +23365,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23387,10 +23392,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129125871</v>
+        <v>129125789</v>
       </c>
       <c r="B218" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23422,10 +23427,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>448138</v>
+        <v>447869</v>
       </c>
       <c r="R218" t="n">
-        <v>6815238</v>
+        <v>6814887</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23457,7 +23462,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23467,7 +23472,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23494,10 +23499,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129125782</v>
+        <v>129125785</v>
       </c>
       <c r="B219" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23529,10 +23534,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>447951</v>
+        <v>447935</v>
       </c>
       <c r="R219" t="n">
-        <v>6814973</v>
+        <v>6814942</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23564,7 +23569,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23574,7 +23579,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23601,10 +23606,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129125838</v>
+        <v>129125871</v>
       </c>
       <c r="B220" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23636,10 +23641,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>447808</v>
+        <v>448138</v>
       </c>
       <c r="R220" t="n">
-        <v>6815019</v>
+        <v>6815238</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23671,7 +23676,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23681,7 +23686,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23708,10 +23713,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129125774</v>
+        <v>129125782</v>
       </c>
       <c r="B221" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23743,10 +23748,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>447907</v>
+        <v>447951</v>
       </c>
       <c r="R221" t="n">
-        <v>6815056</v>
+        <v>6814973</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23778,7 +23783,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23788,7 +23793,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23815,10 +23820,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129125822</v>
+        <v>129125774</v>
       </c>
       <c r="B222" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23850,10 +23855,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>447745</v>
+        <v>447907</v>
       </c>
       <c r="R222" t="n">
-        <v>6815055</v>
+        <v>6815056</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23885,7 +23890,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23895,7 +23900,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23922,10 +23927,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129125733</v>
+        <v>129125822</v>
       </c>
       <c r="B223" t="n">
-        <v>57883</v>
+        <v>79039</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23933,39 +23938,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>447785</v>
+        <v>447745</v>
       </c>
       <c r="R223" t="n">
-        <v>6814977</v>
+        <v>6815055</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24034,10 +24034,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129125726</v>
+        <v>129125794</v>
       </c>
       <c r="B224" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24045,21 +24045,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24069,10 +24069,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>448080</v>
+        <v>447798</v>
       </c>
       <c r="R224" t="n">
-        <v>6815060</v>
+        <v>6814819</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24141,10 +24141,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125817</v>
+        <v>129125790</v>
       </c>
       <c r="B225" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447580</v>
+        <v>447855</v>
       </c>
       <c r="R225" t="n">
-        <v>6814929</v>
+        <v>6814877</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,10 +24248,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125794</v>
+        <v>129125823</v>
       </c>
       <c r="B226" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447798</v>
+        <v>447754</v>
       </c>
       <c r="R226" t="n">
-        <v>6814819</v>
+        <v>6815045</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,10 +24355,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125823</v>
+        <v>129125817</v>
       </c>
       <c r="B227" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447754</v>
+        <v>447580</v>
       </c>
       <c r="R227" t="n">
-        <v>6815045</v>
+        <v>6814929</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24462,10 +24462,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129125776</v>
+        <v>129125773</v>
       </c>
       <c r="B228" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>447923</v>
+        <v>447907</v>
       </c>
       <c r="R228" t="n">
-        <v>6814998</v>
+        <v>6815075</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24572,7 +24572,7 @@
         <v>129125889</v>
       </c>
       <c r="B229" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24676,10 +24676,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125773</v>
+        <v>129125726</v>
       </c>
       <c r="B230" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24687,21 +24687,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24711,10 +24711,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>447907</v>
+        <v>448080</v>
       </c>
       <c r="R230" t="n">
-        <v>6815075</v>
+        <v>6815060</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24746,7 +24746,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24783,10 +24783,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129125754</v>
+        <v>129125776</v>
       </c>
       <c r="B231" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24794,21 +24794,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24818,10 +24818,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>447877</v>
+        <v>447923</v>
       </c>
       <c r="R231" t="n">
-        <v>6814908</v>
+        <v>6814998</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24853,7 +24853,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24872,7 +24872,6 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -24891,10 +24890,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129125790</v>
+        <v>129125754</v>
       </c>
       <c r="B232" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24902,21 +24901,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24926,10 +24925,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>447855</v>
+        <v>447877</v>
       </c>
       <c r="R232" t="n">
-        <v>6814877</v>
+        <v>6814908</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24961,7 +24960,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24971,7 +24970,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24980,6 +24979,7 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
@@ -25001,7 +25001,7 @@
         <v>129125854</v>
       </c>
       <c r="B233" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125831</v>
+        <v>129125722</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447755</v>
+        <v>447757</v>
       </c>
       <c r="R91" t="n">
-        <v>6814973</v>
+        <v>6814906</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9827,7 +9827,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125809</v>
+        <v>129125831</v>
       </c>
       <c r="B92" t="n">
         <v>79039</v>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447763</v>
+        <v>447755</v>
       </c>
       <c r="R92" t="n">
-        <v>6814923</v>
+        <v>6814973</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,7 +9934,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125772</v>
+        <v>129125809</v>
       </c>
       <c r="B93" t="n">
         <v>79039</v>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447920</v>
+        <v>447763</v>
       </c>
       <c r="R93" t="n">
-        <v>6815082</v>
+        <v>6814923</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10041,7 +10041,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125795</v>
+        <v>129125772</v>
       </c>
       <c r="B94" t="n">
         <v>79039</v>
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447790</v>
+        <v>447920</v>
       </c>
       <c r="R94" t="n">
-        <v>6814834</v>
+        <v>6815082</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,10 +10148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125722</v>
+        <v>129125795</v>
       </c>
       <c r="B95" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,21 +10159,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447757</v>
+        <v>447790</v>
       </c>
       <c r="R95" t="n">
-        <v>6814906</v>
+        <v>6814834</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11336,7 +11336,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129125837</v>
+        <v>129125868</v>
       </c>
       <c r="B106" t="n">
         <v>79039</v>
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447806</v>
+        <v>448101</v>
       </c>
       <c r="R106" t="n">
-        <v>6815012</v>
+        <v>6815213</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11443,7 +11443,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129125886</v>
+        <v>129125813</v>
       </c>
       <c r="B107" t="n">
         <v>79039</v>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>448097</v>
+        <v>447617</v>
       </c>
       <c r="R107" t="n">
-        <v>6815025</v>
+        <v>6814828</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11550,7 +11550,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129125814</v>
+        <v>129125837</v>
       </c>
       <c r="B108" t="n">
         <v>79039</v>
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447611</v>
+        <v>447806</v>
       </c>
       <c r="R108" t="n">
-        <v>6814782</v>
+        <v>6815012</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129125868</v>
+        <v>129125886</v>
       </c>
       <c r="B109" t="n">
         <v>79039</v>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448101</v>
+        <v>448097</v>
       </c>
       <c r="R109" t="n">
-        <v>6815213</v>
+        <v>6815025</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11764,7 +11764,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129125813</v>
+        <v>129125814</v>
       </c>
       <c r="B110" t="n">
         <v>79039</v>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447617</v>
+        <v>447611</v>
       </c>
       <c r="R110" t="n">
-        <v>6814828</v>
+        <v>6814782</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11978,7 +11978,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125863</v>
+        <v>129125891</v>
       </c>
       <c r="B112" t="n">
         <v>79039</v>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447878</v>
+        <v>448003</v>
       </c>
       <c r="R112" t="n">
-        <v>6815153</v>
+        <v>6815088</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,7 +12085,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125807</v>
+        <v>129125779</v>
       </c>
       <c r="B113" t="n">
         <v>79039</v>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447797</v>
+        <v>447936</v>
       </c>
       <c r="R113" t="n">
-        <v>6814950</v>
+        <v>6814995</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,32 +12192,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125728</v>
+        <v>129125841</v>
       </c>
       <c r="B114" t="n">
-        <v>91497</v>
+        <v>79039</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447872</v>
+        <v>447812</v>
       </c>
       <c r="R114" t="n">
-        <v>6815131</v>
+        <v>6815036</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12299,7 +12299,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129125891</v>
+        <v>129125851</v>
       </c>
       <c r="B115" t="n">
         <v>79039</v>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448003</v>
+        <v>447834</v>
       </c>
       <c r="R115" t="n">
-        <v>6815088</v>
+        <v>6815005</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12406,7 +12406,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125779</v>
+        <v>129125863</v>
       </c>
       <c r="B116" t="n">
         <v>79039</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447936</v>
+        <v>447878</v>
       </c>
       <c r="R116" t="n">
-        <v>6814995</v>
+        <v>6815153</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,7 +12513,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125841</v>
+        <v>129125807</v>
       </c>
       <c r="B117" t="n">
         <v>79039</v>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447812</v>
+        <v>447797</v>
       </c>
       <c r="R117" t="n">
-        <v>6815036</v>
+        <v>6814950</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12620,32 +12620,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129125851</v>
+        <v>129125728</v>
       </c>
       <c r="B118" t="n">
-        <v>79039</v>
+        <v>91497</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447834</v>
+        <v>447872</v>
       </c>
       <c r="R118" t="n">
-        <v>6815005</v>
+        <v>6815131</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14011,32 +14011,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125770</v>
+        <v>129125743</v>
       </c>
       <c r="B131" t="n">
-        <v>79039</v>
+        <v>80048</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447916</v>
+        <v>447735</v>
       </c>
       <c r="R131" t="n">
-        <v>6815113</v>
+        <v>6814890</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,7 +14091,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14118,7 +14123,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125846</v>
+        <v>129125770</v>
       </c>
       <c r="B132" t="n">
         <v>79039</v>
@@ -14153,10 +14158,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447815</v>
+        <v>447916</v>
       </c>
       <c r="R132" t="n">
-        <v>6815100</v>
+        <v>6815113</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14188,7 +14193,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14198,7 +14203,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14225,7 +14230,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125879</v>
+        <v>129125846</v>
       </c>
       <c r="B133" t="n">
         <v>79039</v>
@@ -14260,10 +14265,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>448114</v>
+        <v>447815</v>
       </c>
       <c r="R133" t="n">
-        <v>6815160</v>
+        <v>6815100</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14295,7 +14300,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14305,7 +14310,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14332,32 +14337,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129125743</v>
+        <v>129125879</v>
       </c>
       <c r="B134" t="n">
-        <v>80048</v>
+        <v>79039</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14367,10 +14372,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>447735</v>
+        <v>448114</v>
       </c>
       <c r="R134" t="n">
-        <v>6814890</v>
+        <v>6815160</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14402,7 +14407,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14412,12 +14417,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15305,27 +15305,27 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125899</v>
+        <v>129125828</v>
       </c>
       <c r="B143" t="n">
-        <v>80179</v>
+        <v>79039</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447580</v>
+        <v>447781</v>
       </c>
       <c r="R143" t="n">
-        <v>6814868</v>
+        <v>6815009</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,7 +15412,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125839</v>
+        <v>129125775</v>
       </c>
       <c r="B144" t="n">
         <v>79039</v>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447805</v>
+        <v>447916</v>
       </c>
       <c r="R144" t="n">
-        <v>6815025</v>
+        <v>6815021</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,7 +15519,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125792</v>
+        <v>129125796</v>
       </c>
       <c r="B145" t="n">
         <v>79039</v>
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447812</v>
+        <v>447749</v>
       </c>
       <c r="R145" t="n">
-        <v>6814852</v>
+        <v>6814850</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15626,7 +15626,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125826</v>
+        <v>129125839</v>
       </c>
       <c r="B146" t="n">
         <v>79039</v>
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447765</v>
+        <v>447805</v>
       </c>
       <c r="R146" t="n">
-        <v>6815023</v>
+        <v>6815025</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,7 +15733,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125828</v>
+        <v>129125792</v>
       </c>
       <c r="B147" t="n">
         <v>79039</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447781</v>
+        <v>447812</v>
       </c>
       <c r="R147" t="n">
-        <v>6815009</v>
+        <v>6814852</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,7 +15840,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125775</v>
+        <v>129125826</v>
       </c>
       <c r="B148" t="n">
         <v>79039</v>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447916</v>
+        <v>447765</v>
       </c>
       <c r="R148" t="n">
-        <v>6815021</v>
+        <v>6815023</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15947,27 +15947,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129125796</v>
+        <v>129125899</v>
       </c>
       <c r="B149" t="n">
-        <v>79039</v>
+        <v>80179</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>447749</v>
+        <v>447580</v>
       </c>
       <c r="R149" t="n">
-        <v>6814850</v>
+        <v>6814868</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129125816</v>
+        <v>129125734</v>
       </c>
       <c r="B166" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,34 +17800,48 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>447568</v>
+        <v>447913</v>
       </c>
       <c r="R166" t="n">
-        <v>6814828</v>
+        <v>6815128</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17859,7 +17873,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17869,7 +17883,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17896,7 +17910,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129125860</v>
+        <v>129125816</v>
       </c>
       <c r="B167" t="n">
         <v>79039</v>
@@ -17931,10 +17945,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>447887</v>
+        <v>447568</v>
       </c>
       <c r="R167" t="n">
-        <v>6815042</v>
+        <v>6814828</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17966,7 +17980,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17976,7 +17990,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18003,7 +18017,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129125855</v>
+        <v>129125860</v>
       </c>
       <c r="B168" t="n">
         <v>79039</v>
@@ -18038,10 +18052,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>447895</v>
+        <v>447887</v>
       </c>
       <c r="R168" t="n">
-        <v>6814968</v>
+        <v>6815042</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18073,7 +18087,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18083,7 +18097,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18110,10 +18124,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129125734</v>
+        <v>129125855</v>
       </c>
       <c r="B169" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18121,48 +18135,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>447913</v>
+        <v>447895</v>
       </c>
       <c r="R169" t="n">
-        <v>6815128</v>
+        <v>6814968</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18231,10 +18231,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129125724</v>
+        <v>129125810</v>
       </c>
       <c r="B170" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18242,21 +18242,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18266,10 +18266,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>447803</v>
+        <v>447736</v>
       </c>
       <c r="R170" t="n">
-        <v>6815095</v>
+        <v>6814886</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18338,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125723</v>
+        <v>129125718</v>
       </c>
       <c r="B171" t="n">
-        <v>79071</v>
+        <v>83015</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18349,21 +18349,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18373,10 +18373,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>447751</v>
+        <v>447772</v>
       </c>
       <c r="R171" t="n">
-        <v>6814901</v>
+        <v>6815035</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18445,10 +18445,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129125727</v>
+        <v>129125861</v>
       </c>
       <c r="B172" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18456,21 +18456,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18480,10 +18480,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>448008</v>
+        <v>447887</v>
       </c>
       <c r="R172" t="n">
-        <v>6815080</v>
+        <v>6815067</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18552,7 +18552,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125880</v>
+        <v>129125832</v>
       </c>
       <c r="B173" t="n">
         <v>79039</v>
@@ -18587,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>448107</v>
+        <v>447762</v>
       </c>
       <c r="R173" t="n">
-        <v>6815120</v>
+        <v>6814968</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18659,7 +18659,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125833</v>
+        <v>129125862</v>
       </c>
       <c r="B174" t="n">
         <v>79039</v>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>447772</v>
+        <v>447867</v>
       </c>
       <c r="R174" t="n">
-        <v>6814969</v>
+        <v>6815109</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18766,32 +18766,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125842</v>
+        <v>129125763</v>
       </c>
       <c r="B175" t="n">
-        <v>79039</v>
+        <v>82998</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18801,10 +18801,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447813</v>
+        <v>447801</v>
       </c>
       <c r="R175" t="n">
-        <v>6815044</v>
+        <v>6814957</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18873,7 +18873,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125739</v>
+        <v>129125740</v>
       </c>
       <c r="B176" t="n">
         <v>57722</v>
@@ -18913,10 +18913,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>448089</v>
+        <v>447580</v>
       </c>
       <c r="R176" t="n">
-        <v>6815093</v>
+        <v>6814929</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18958,12 +18958,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18990,32 +18985,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125745</v>
+        <v>129125724</v>
       </c>
       <c r="B177" t="n">
-        <v>97540</v>
+        <v>79071</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19025,10 +19020,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>448023</v>
+        <v>447803</v>
       </c>
       <c r="R177" t="n">
-        <v>6815221</v>
+        <v>6815095</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19060,7 +19055,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19070,7 +19065,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19097,10 +19092,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129125810</v>
+        <v>129125723</v>
       </c>
       <c r="B178" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19108,21 +19103,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19132,10 +19127,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>447736</v>
+        <v>447751</v>
       </c>
       <c r="R178" t="n">
-        <v>6814886</v>
+        <v>6814901</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19167,7 +19162,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19177,7 +19172,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19204,10 +19199,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129125718</v>
+        <v>129125727</v>
       </c>
       <c r="B179" t="n">
-        <v>83015</v>
+        <v>79071</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19215,21 +19210,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19239,10 +19234,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>447772</v>
+        <v>448008</v>
       </c>
       <c r="R179" t="n">
-        <v>6815035</v>
+        <v>6815080</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19274,7 +19269,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19284,7 +19279,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19311,7 +19306,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129125861</v>
+        <v>129125880</v>
       </c>
       <c r="B180" t="n">
         <v>79039</v>
@@ -19346,10 +19341,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>447887</v>
+        <v>448107</v>
       </c>
       <c r="R180" t="n">
-        <v>6815067</v>
+        <v>6815120</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19381,7 +19376,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19391,7 +19386,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19418,7 +19413,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129125832</v>
+        <v>129125833</v>
       </c>
       <c r="B181" t="n">
         <v>79039</v>
@@ -19453,10 +19448,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>447762</v>
+        <v>447772</v>
       </c>
       <c r="R181" t="n">
-        <v>6814968</v>
+        <v>6814969</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19525,7 +19520,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125862</v>
+        <v>129125842</v>
       </c>
       <c r="B182" t="n">
         <v>79039</v>
@@ -19560,10 +19555,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>447867</v>
+        <v>447813</v>
       </c>
       <c r="R182" t="n">
-        <v>6815109</v>
+        <v>6815044</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19595,7 +19590,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19605,7 +19600,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19632,45 +19627,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125763</v>
+        <v>129125739</v>
       </c>
       <c r="B183" t="n">
-        <v>82998</v>
+        <v>57722</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>447801</v>
+        <v>448089</v>
       </c>
       <c r="R183" t="n">
-        <v>6814957</v>
+        <v>6815093</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19712,7 +19712,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19739,50 +19744,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129125740</v>
+        <v>129125745</v>
       </c>
       <c r="B184" t="n">
-        <v>57722</v>
+        <v>97540</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>447580</v>
+        <v>448023</v>
       </c>
       <c r="R184" t="n">
-        <v>6814929</v>
+        <v>6815221</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -24034,10 +24034,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129125794</v>
+        <v>129125726</v>
       </c>
       <c r="B224" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24045,21 +24045,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24069,10 +24069,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>447798</v>
+        <v>448080</v>
       </c>
       <c r="R224" t="n">
-        <v>6814819</v>
+        <v>6815060</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24141,7 +24141,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125790</v>
+        <v>129125794</v>
       </c>
       <c r="B225" t="n">
         <v>79039</v>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447855</v>
+        <v>447798</v>
       </c>
       <c r="R225" t="n">
-        <v>6814877</v>
+        <v>6814819</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,7 +24248,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125823</v>
+        <v>129125790</v>
       </c>
       <c r="B226" t="n">
         <v>79039</v>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447754</v>
+        <v>447855</v>
       </c>
       <c r="R226" t="n">
-        <v>6815045</v>
+        <v>6814877</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,7 +24355,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125817</v>
+        <v>129125823</v>
       </c>
       <c r="B227" t="n">
         <v>79039</v>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447580</v>
+        <v>447754</v>
       </c>
       <c r="R227" t="n">
-        <v>6814929</v>
+        <v>6815045</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24462,7 +24462,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129125773</v>
+        <v>129125817</v>
       </c>
       <c r="B228" t="n">
         <v>79039</v>
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>447907</v>
+        <v>447580</v>
       </c>
       <c r="R228" t="n">
-        <v>6815075</v>
+        <v>6814929</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24569,7 +24569,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129125889</v>
+        <v>129125773</v>
       </c>
       <c r="B229" t="n">
         <v>79039</v>
@@ -24604,10 +24604,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>448024</v>
+        <v>447907</v>
       </c>
       <c r="R229" t="n">
-        <v>6815046</v>
+        <v>6815075</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24676,10 +24676,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125726</v>
+        <v>129125889</v>
       </c>
       <c r="B230" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24687,21 +24687,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24711,10 +24711,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>448080</v>
+        <v>448024</v>
       </c>
       <c r="R230" t="n">
-        <v>6815060</v>
+        <v>6815046</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24746,7 +24746,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD230" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129125764</v>
+        <v>129125786</v>
       </c>
       <c r="B66" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447872</v>
+        <v>447922</v>
       </c>
       <c r="R66" t="n">
-        <v>6814907</v>
+        <v>6814934</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129125766</v>
+        <v>129125764</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7133,21 +7133,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447807</v>
+        <v>447872</v>
       </c>
       <c r="R67" t="n">
-        <v>6814825</v>
+        <v>6814907</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7202,12 +7202,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På minst 250-årig tall</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7234,7 +7229,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129125786</v>
+        <v>129125766</v>
       </c>
       <c r="B68" t="n">
         <v>79039</v>
@@ -7269,10 +7264,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447922</v>
+        <v>447807</v>
       </c>
       <c r="R68" t="n">
-        <v>6814934</v>
+        <v>6814825</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7304,7 +7299,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7314,7 +7309,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På minst 250-årig tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129125752</v>
+        <v>129125738</v>
       </c>
       <c r="B69" t="n">
-        <v>81024</v>
+        <v>57722</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,34 +7352,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447893</v>
+        <v>447735</v>
       </c>
       <c r="R69" t="n">
-        <v>6814914</v>
+        <v>6814890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,7 +7416,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7421,7 +7426,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7555,10 +7565,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125787</v>
+        <v>129125752</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>81024</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7566,21 +7576,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7590,10 +7600,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447908</v>
+        <v>447893</v>
       </c>
       <c r="R71" t="n">
-        <v>6814933</v>
+        <v>6814914</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7625,7 +7635,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7635,7 +7645,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7662,7 +7672,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125835</v>
+        <v>129125843</v>
       </c>
       <c r="B72" t="n">
         <v>79039</v>
@@ -7697,10 +7707,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447793</v>
+        <v>447812</v>
       </c>
       <c r="R72" t="n">
-        <v>6815007</v>
+        <v>6815055</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7732,7 +7742,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7742,7 +7752,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7769,10 +7779,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125812</v>
+        <v>129125755</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7780,21 +7790,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7804,10 +7814,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447682</v>
+        <v>447756</v>
       </c>
       <c r="R73" t="n">
-        <v>6814779</v>
+        <v>6814990</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7839,7 +7849,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7849,7 +7859,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7858,6 +7868,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7876,7 +7887,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129125843</v>
+        <v>129125798</v>
       </c>
       <c r="B74" t="n">
         <v>79039</v>
@@ -7911,10 +7922,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447812</v>
+        <v>447786</v>
       </c>
       <c r="R74" t="n">
-        <v>6815055</v>
+        <v>6814897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7946,7 +7957,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7956,7 +7967,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7983,10 +7994,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129125755</v>
+        <v>129125787</v>
       </c>
       <c r="B75" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7994,21 +8005,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8018,10 +8029,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447756</v>
+        <v>447908</v>
       </c>
       <c r="R75" t="n">
-        <v>6814990</v>
+        <v>6814933</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8053,7 +8064,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8063,7 +8074,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8072,7 +8083,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8091,7 +8101,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129125798</v>
+        <v>129125835</v>
       </c>
       <c r="B76" t="n">
         <v>79039</v>
@@ -8126,10 +8136,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447786</v>
+        <v>447793</v>
       </c>
       <c r="R76" t="n">
-        <v>6814897</v>
+        <v>6815007</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8161,7 +8171,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8171,7 +8181,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8198,10 +8208,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129125738</v>
+        <v>129125812</v>
       </c>
       <c r="B77" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8209,39 +8219,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447735</v>
+        <v>447682</v>
       </c>
       <c r="R77" t="n">
-        <v>6814890</v>
+        <v>6814779</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8273,7 +8278,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8283,12 +8288,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8427,10 +8427,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125729</v>
+        <v>129125895</v>
       </c>
       <c r="B79" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8438,21 +8438,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448039</v>
+        <v>447963</v>
       </c>
       <c r="R79" t="n">
-        <v>6815229</v>
+        <v>6815131</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129125751</v>
+        <v>129125730</v>
       </c>
       <c r="B80" t="n">
-        <v>81024</v>
+        <v>91540</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447952</v>
+        <v>448098</v>
       </c>
       <c r="R80" t="n">
-        <v>6814974</v>
+        <v>6815212</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129125730</v>
+        <v>129125729</v>
       </c>
       <c r="B81" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448098</v>
+        <v>448039</v>
       </c>
       <c r="R81" t="n">
-        <v>6815212</v>
+        <v>6815229</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8748,10 +8748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129125867</v>
+        <v>129125751</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>81024</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,21 +8759,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448088</v>
+        <v>447952</v>
       </c>
       <c r="R82" t="n">
-        <v>6815222</v>
+        <v>6814974</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129125824</v>
+        <v>129125873</v>
       </c>
       <c r="B83" t="n">
         <v>79039</v>
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447761</v>
+        <v>448163</v>
       </c>
       <c r="R83" t="n">
-        <v>6815045</v>
+        <v>6815302</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125873</v>
+        <v>129125771</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448163</v>
+        <v>447925</v>
       </c>
       <c r="R84" t="n">
-        <v>6815302</v>
+        <v>6815103</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125771</v>
+        <v>129125853</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447925</v>
+        <v>447853</v>
       </c>
       <c r="R85" t="n">
-        <v>6815103</v>
+        <v>6814972</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9176,7 +9176,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125853</v>
+        <v>129125867</v>
       </c>
       <c r="B86" t="n">
         <v>79039</v>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447853</v>
+        <v>448088</v>
       </c>
       <c r="R86" t="n">
-        <v>6814972</v>
+        <v>6815222</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9283,7 +9283,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129125808</v>
+        <v>129125824</v>
       </c>
       <c r="B87" t="n">
         <v>79039</v>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447782</v>
+        <v>447761</v>
       </c>
       <c r="R87" t="n">
-        <v>6814944</v>
+        <v>6815045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9390,7 +9390,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129125895</v>
+        <v>129125808</v>
       </c>
       <c r="B88" t="n">
         <v>79039</v>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447963</v>
+        <v>447782</v>
       </c>
       <c r="R88" t="n">
-        <v>6815131</v>
+        <v>6814944</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9607,7 +9607,7 @@
         <v>129125759</v>
       </c>
       <c r="B90" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125722</v>
+        <v>129125809</v>
       </c>
       <c r="B91" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447757</v>
+        <v>447763</v>
       </c>
       <c r="R91" t="n">
-        <v>6814906</v>
+        <v>6814923</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9827,10 +9827,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125831</v>
+        <v>129125722</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9838,21 +9838,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447755</v>
+        <v>447757</v>
       </c>
       <c r="R92" t="n">
-        <v>6814973</v>
+        <v>6814906</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,7 +9934,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125809</v>
+        <v>129125874</v>
       </c>
       <c r="B93" t="n">
         <v>79039</v>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447763</v>
+        <v>448182</v>
       </c>
       <c r="R93" t="n">
-        <v>6814923</v>
+        <v>6815308</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10041,7 +10041,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125772</v>
+        <v>129125831</v>
       </c>
       <c r="B94" t="n">
         <v>79039</v>
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447920</v>
+        <v>447755</v>
       </c>
       <c r="R94" t="n">
-        <v>6815082</v>
+        <v>6814973</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,7 +10148,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125795</v>
+        <v>129125772</v>
       </c>
       <c r="B95" t="n">
         <v>79039</v>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447790</v>
+        <v>447920</v>
       </c>
       <c r="R95" t="n">
-        <v>6814834</v>
+        <v>6815082</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10255,10 +10255,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125874</v>
+        <v>129125753</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10266,21 +10266,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>448182</v>
+        <v>447766</v>
       </c>
       <c r="R96" t="n">
-        <v>6815308</v>
+        <v>6814899</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10335,7 +10335,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10344,6 +10349,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10362,10 +10368,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125753</v>
+        <v>129125795</v>
       </c>
       <c r="B97" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10373,21 +10379,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10397,10 +10403,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447766</v>
+        <v>447790</v>
       </c>
       <c r="R97" t="n">
-        <v>6814899</v>
+        <v>6814834</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10432,7 +10438,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10442,12 +10448,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10456,7 +10457,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10475,32 +10475,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129125719</v>
+        <v>129125746</v>
       </c>
       <c r="B98" t="n">
-        <v>79071</v>
+        <v>97553</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447855</v>
+        <v>448129</v>
       </c>
       <c r="R98" t="n">
-        <v>6814877</v>
+        <v>6815200</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10582,10 +10582,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129125858</v>
+        <v>129125719</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447914</v>
+        <v>447855</v>
       </c>
       <c r="R99" t="n">
-        <v>6815024</v>
+        <v>6814877</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10689,7 +10689,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129125872</v>
+        <v>129125820</v>
       </c>
       <c r="B100" t="n">
         <v>79039</v>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>448159</v>
+        <v>447706</v>
       </c>
       <c r="R100" t="n">
-        <v>6815277</v>
+        <v>6815025</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10796,7 +10796,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129125820</v>
+        <v>129125858</v>
       </c>
       <c r="B101" t="n">
         <v>79039</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447706</v>
+        <v>447914</v>
       </c>
       <c r="R101" t="n">
-        <v>6815025</v>
+        <v>6815024</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129125888</v>
+        <v>129125741</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10914,34 +10914,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448042</v>
+        <v>447902</v>
       </c>
       <c r="R102" t="n">
-        <v>6815053</v>
+        <v>6814922</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10973,7 +10978,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10983,7 +10988,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11010,7 +11015,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129125836</v>
+        <v>129125872</v>
       </c>
       <c r="B103" t="n">
         <v>79039</v>
@@ -11045,10 +11050,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447789</v>
+        <v>448159</v>
       </c>
       <c r="R103" t="n">
-        <v>6815016</v>
+        <v>6815277</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11080,7 +11085,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11090,7 +11095,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11117,10 +11122,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129125741</v>
+        <v>129125888</v>
       </c>
       <c r="B104" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11128,39 +11133,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447902</v>
+        <v>448042</v>
       </c>
       <c r="R104" t="n">
-        <v>6814922</v>
+        <v>6815053</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11229,32 +11229,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125746</v>
+        <v>129125836</v>
       </c>
       <c r="B105" t="n">
-        <v>97546</v>
+        <v>79039</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11264,10 +11264,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>448129</v>
+        <v>447789</v>
       </c>
       <c r="R105" t="n">
-        <v>6815200</v>
+        <v>6815016</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11336,7 +11336,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129125868</v>
+        <v>129125814</v>
       </c>
       <c r="B106" t="n">
         <v>79039</v>
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448101</v>
+        <v>447611</v>
       </c>
       <c r="R106" t="n">
-        <v>6815213</v>
+        <v>6814782</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11443,7 +11443,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129125813</v>
+        <v>129125868</v>
       </c>
       <c r="B107" t="n">
         <v>79039</v>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447617</v>
+        <v>448101</v>
       </c>
       <c r="R107" t="n">
-        <v>6814828</v>
+        <v>6815213</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11550,7 +11550,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129125837</v>
+        <v>129125886</v>
       </c>
       <c r="B108" t="n">
         <v>79039</v>
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447806</v>
+        <v>448097</v>
       </c>
       <c r="R108" t="n">
-        <v>6815012</v>
+        <v>6815025</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11657,7 +11657,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129125886</v>
+        <v>129125813</v>
       </c>
       <c r="B109" t="n">
         <v>79039</v>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448097</v>
+        <v>447617</v>
       </c>
       <c r="R109" t="n">
-        <v>6815025</v>
+        <v>6814828</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11764,7 +11764,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129125814</v>
+        <v>129125837</v>
       </c>
       <c r="B110" t="n">
         <v>79039</v>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447611</v>
+        <v>447806</v>
       </c>
       <c r="R110" t="n">
-        <v>6814782</v>
+        <v>6815012</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11978,32 +11978,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125891</v>
+        <v>129125728</v>
       </c>
       <c r="B112" t="n">
-        <v>79039</v>
+        <v>91504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>448003</v>
+        <v>447872</v>
       </c>
       <c r="R112" t="n">
-        <v>6815088</v>
+        <v>6815131</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,7 +12085,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125779</v>
+        <v>129125863</v>
       </c>
       <c r="B113" t="n">
         <v>79039</v>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447936</v>
+        <v>447878</v>
       </c>
       <c r="R113" t="n">
-        <v>6814995</v>
+        <v>6815153</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,7 +12192,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125841</v>
+        <v>129125779</v>
       </c>
       <c r="B114" t="n">
         <v>79039</v>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447812</v>
+        <v>447936</v>
       </c>
       <c r="R114" t="n">
-        <v>6815036</v>
+        <v>6814995</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12406,7 +12406,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125863</v>
+        <v>129125807</v>
       </c>
       <c r="B116" t="n">
         <v>79039</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447878</v>
+        <v>447797</v>
       </c>
       <c r="R116" t="n">
-        <v>6815153</v>
+        <v>6814950</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,7 +12513,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125807</v>
+        <v>129125891</v>
       </c>
       <c r="B117" t="n">
         <v>79039</v>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447797</v>
+        <v>448003</v>
       </c>
       <c r="R117" t="n">
-        <v>6814950</v>
+        <v>6815088</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12620,32 +12620,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129125728</v>
+        <v>129125841</v>
       </c>
       <c r="B118" t="n">
-        <v>91497</v>
+        <v>79039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447872</v>
+        <v>447812</v>
       </c>
       <c r="R118" t="n">
-        <v>6815131</v>
+        <v>6815036</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12727,7 +12727,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129125827</v>
+        <v>129125894</v>
       </c>
       <c r="B119" t="n">
         <v>79039</v>
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447767</v>
+        <v>447978</v>
       </c>
       <c r="R119" t="n">
-        <v>6815014</v>
+        <v>6815111</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125811</v>
+        <v>129125827</v>
       </c>
       <c r="B121" t="n">
         <v>79039</v>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447716</v>
+        <v>447767</v>
       </c>
       <c r="R121" t="n">
-        <v>6814829</v>
+        <v>6815014</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13369,7 +13369,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125852</v>
+        <v>129125877</v>
       </c>
       <c r="B125" t="n">
         <v>79039</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447839</v>
+        <v>448126</v>
       </c>
       <c r="R125" t="n">
-        <v>6814995</v>
+        <v>6815198</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,32 +13476,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125877</v>
+        <v>129125750</v>
       </c>
       <c r="B126" t="n">
-        <v>79039</v>
+        <v>80180</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448126</v>
+        <v>447714</v>
       </c>
       <c r="R126" t="n">
-        <v>6815198</v>
+        <v>6815023</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125894</v>
+        <v>129125811</v>
       </c>
       <c r="B127" t="n">
         <v>79039</v>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447978</v>
+        <v>447716</v>
       </c>
       <c r="R127" t="n">
-        <v>6815111</v>
+        <v>6814829</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13797,7 +13797,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125845</v>
+        <v>129125852</v>
       </c>
       <c r="B129" t="n">
         <v>79039</v>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447801</v>
+        <v>447839</v>
       </c>
       <c r="R129" t="n">
-        <v>6815082</v>
+        <v>6814995</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,32 +13904,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125750</v>
+        <v>129125845</v>
       </c>
       <c r="B130" t="n">
-        <v>80180</v>
+        <v>79039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447714</v>
+        <v>447801</v>
       </c>
       <c r="R130" t="n">
-        <v>6815023</v>
+        <v>6815082</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,32 +14011,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125743</v>
+        <v>129125844</v>
       </c>
       <c r="B131" t="n">
-        <v>80048</v>
+        <v>79039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447735</v>
+        <v>447808</v>
       </c>
       <c r="R131" t="n">
-        <v>6814890</v>
+        <v>6815078</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,12 +14091,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14123,7 +14118,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125770</v>
+        <v>129125879</v>
       </c>
       <c r="B132" t="n">
         <v>79039</v>
@@ -14158,10 +14153,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447916</v>
+        <v>448114</v>
       </c>
       <c r="R132" t="n">
-        <v>6815113</v>
+        <v>6815160</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14193,7 +14188,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14203,7 +14198,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14230,7 +14225,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125846</v>
+        <v>129125770</v>
       </c>
       <c r="B133" t="n">
         <v>79039</v>
@@ -14265,10 +14260,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447815</v>
+        <v>447916</v>
       </c>
       <c r="R133" t="n">
-        <v>6815100</v>
+        <v>6815113</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14300,7 +14295,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14310,7 +14305,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14337,32 +14332,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129125879</v>
+        <v>129125743</v>
       </c>
       <c r="B134" t="n">
-        <v>79039</v>
+        <v>80048</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14372,10 +14367,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>448114</v>
+        <v>447735</v>
       </c>
       <c r="R134" t="n">
-        <v>6815160</v>
+        <v>6814890</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14407,7 +14402,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14417,7 +14412,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14444,7 +14444,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129125844</v>
+        <v>129125846</v>
       </c>
       <c r="B135" t="n">
         <v>79039</v>
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>447808</v>
+        <v>447815</v>
       </c>
       <c r="R135" t="n">
-        <v>6815078</v>
+        <v>6815100</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14551,7 +14551,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129125805</v>
+        <v>129125781</v>
       </c>
       <c r="B136" t="n">
         <v>79039</v>
@@ -14586,10 +14586,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>447826</v>
+        <v>447968</v>
       </c>
       <c r="R136" t="n">
-        <v>6814982</v>
+        <v>6814977</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14658,7 +14658,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125781</v>
+        <v>129125818</v>
       </c>
       <c r="B137" t="n">
         <v>79039</v>
@@ -14693,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>447968</v>
+        <v>447641</v>
       </c>
       <c r="R137" t="n">
-        <v>6814977</v>
+        <v>6814924</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14765,7 +14765,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125818</v>
+        <v>129125805</v>
       </c>
       <c r="B138" t="n">
         <v>79039</v>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>447641</v>
+        <v>447826</v>
       </c>
       <c r="R138" t="n">
-        <v>6814924</v>
+        <v>6814982</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14872,7 +14872,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125885</v>
+        <v>129125887</v>
       </c>
       <c r="B139" t="n">
         <v>79039</v>
@@ -14910,7 +14910,7 @@
         <v>448080</v>
       </c>
       <c r="R139" t="n">
-        <v>6815037</v>
+        <v>6815039</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14979,7 +14979,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125797</v>
+        <v>129125885</v>
       </c>
       <c r="B140" t="n">
         <v>79039</v>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>447781</v>
+        <v>448080</v>
       </c>
       <c r="R140" t="n">
-        <v>6814894</v>
+        <v>6815037</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15086,7 +15086,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125887</v>
+        <v>129125797</v>
       </c>
       <c r="B141" t="n">
         <v>79039</v>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>448080</v>
+        <v>447781</v>
       </c>
       <c r="R141" t="n">
-        <v>6815039</v>
+        <v>6814894</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15305,7 +15305,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125828</v>
+        <v>129125775</v>
       </c>
       <c r="B143" t="n">
         <v>79039</v>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447781</v>
+        <v>447916</v>
       </c>
       <c r="R143" t="n">
-        <v>6815009</v>
+        <v>6815021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,7 +15412,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125775</v>
+        <v>129125828</v>
       </c>
       <c r="B144" t="n">
         <v>79039</v>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447916</v>
+        <v>447781</v>
       </c>
       <c r="R144" t="n">
-        <v>6815021</v>
+        <v>6815009</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,7 +15519,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125796</v>
+        <v>129125826</v>
       </c>
       <c r="B145" t="n">
         <v>79039</v>
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447749</v>
+        <v>447765</v>
       </c>
       <c r="R145" t="n">
-        <v>6814850</v>
+        <v>6815023</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15626,27 +15626,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125839</v>
+        <v>129125899</v>
       </c>
       <c r="B146" t="n">
-        <v>79039</v>
+        <v>80179</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447805</v>
+        <v>447580</v>
       </c>
       <c r="R146" t="n">
-        <v>6815025</v>
+        <v>6814868</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,7 +15733,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125792</v>
+        <v>129125839</v>
       </c>
       <c r="B147" t="n">
         <v>79039</v>
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447812</v>
+        <v>447805</v>
       </c>
       <c r="R147" t="n">
-        <v>6814852</v>
+        <v>6815025</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,7 +15840,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125826</v>
+        <v>129125792</v>
       </c>
       <c r="B148" t="n">
         <v>79039</v>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447765</v>
+        <v>447812</v>
       </c>
       <c r="R148" t="n">
-        <v>6815023</v>
+        <v>6814852</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15947,27 +15947,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129125899</v>
+        <v>129125796</v>
       </c>
       <c r="B149" t="n">
-        <v>80179</v>
+        <v>79039</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -15982,10 +15982,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>447580</v>
+        <v>447749</v>
       </c>
       <c r="R149" t="n">
-        <v>6814868</v>
+        <v>6814850</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16054,10 +16054,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129125720</v>
+        <v>129125806</v>
       </c>
       <c r="B150" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16065,21 +16065,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16089,10 +16089,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>447936</v>
+        <v>447816</v>
       </c>
       <c r="R150" t="n">
-        <v>6814995</v>
+        <v>6814979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16161,7 +16161,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129125806</v>
+        <v>129125799</v>
       </c>
       <c r="B151" t="n">
         <v>79039</v>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>447816</v>
+        <v>447804</v>
       </c>
       <c r="R151" t="n">
-        <v>6814979</v>
+        <v>6814911</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16231,7 +16231,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16268,7 +16268,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125830</v>
+        <v>129125769</v>
       </c>
       <c r="B152" t="n">
         <v>79039</v>
@@ -16303,10 +16303,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447767</v>
+        <v>447912</v>
       </c>
       <c r="R152" t="n">
-        <v>6814993</v>
+        <v>6815110</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,7 +16375,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125799</v>
+        <v>129125804</v>
       </c>
       <c r="B153" t="n">
         <v>79039</v>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>447804</v>
+        <v>447840</v>
       </c>
       <c r="R153" t="n">
-        <v>6814911</v>
+        <v>6814978</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16482,7 +16482,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125804</v>
+        <v>129125878</v>
       </c>
       <c r="B154" t="n">
         <v>79039</v>
@@ -16517,10 +16517,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>447840</v>
+        <v>448121</v>
       </c>
       <c r="R154" t="n">
-        <v>6814978</v>
+        <v>6815175</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16589,7 +16589,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125801</v>
+        <v>129125849</v>
       </c>
       <c r="B155" t="n">
         <v>79039</v>
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447814</v>
+        <v>447825</v>
       </c>
       <c r="R155" t="n">
-        <v>6814948</v>
+        <v>6815056</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16696,54 +16696,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125757</v>
+        <v>129125802</v>
       </c>
       <c r="B156" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447746</v>
+        <v>447821</v>
       </c>
       <c r="R156" t="n">
-        <v>6814851</v>
+        <v>6814955</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16775,7 +16766,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16785,7 +16776,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16812,54 +16803,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125758</v>
+        <v>129125830</v>
       </c>
       <c r="B157" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447571</v>
+        <v>447767</v>
       </c>
       <c r="R157" t="n">
-        <v>6814831</v>
+        <v>6814993</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16891,7 +16873,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16901,7 +16883,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16928,7 +16910,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125769</v>
+        <v>129125768</v>
       </c>
       <c r="B158" t="n">
         <v>79039</v>
@@ -16963,10 +16945,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>447912</v>
+        <v>447909</v>
       </c>
       <c r="R158" t="n">
-        <v>6815110</v>
+        <v>6815119</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17035,32 +17017,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129125869</v>
+        <v>129125749</v>
       </c>
       <c r="B159" t="n">
-        <v>79039</v>
+        <v>80180</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17070,10 +17052,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>448114</v>
+        <v>447581</v>
       </c>
       <c r="R159" t="n">
-        <v>6815209</v>
+        <v>6814869</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17105,7 +17087,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17115,7 +17097,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17142,7 +17124,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125849</v>
+        <v>129125801</v>
       </c>
       <c r="B160" t="n">
         <v>79039</v>
@@ -17177,10 +17159,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>447825</v>
+        <v>447814</v>
       </c>
       <c r="R160" t="n">
-        <v>6815056</v>
+        <v>6814948</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17212,7 +17194,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17222,7 +17204,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17249,7 +17231,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125768</v>
+        <v>129125869</v>
       </c>
       <c r="B161" t="n">
         <v>79039</v>
@@ -17284,10 +17266,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>447909</v>
+        <v>448114</v>
       </c>
       <c r="R161" t="n">
-        <v>6815119</v>
+        <v>6815209</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17319,7 +17301,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17329,7 +17311,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17356,45 +17338,50 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125878</v>
+        <v>129125731</v>
       </c>
       <c r="B162" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>448121</v>
+        <v>448128</v>
       </c>
       <c r="R162" t="n">
-        <v>6815175</v>
+        <v>6815234</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17426,7 +17413,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17436,7 +17423,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17463,45 +17450,54 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125802</v>
+        <v>129125758</v>
       </c>
       <c r="B163" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>447821</v>
+        <v>447571</v>
       </c>
       <c r="R163" t="n">
-        <v>6814955</v>
+        <v>6814831</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17533,7 +17529,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17543,7 +17539,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17570,45 +17566,54 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129125749</v>
+        <v>129125757</v>
       </c>
       <c r="B164" t="n">
-        <v>80180</v>
+        <v>98676</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>447581</v>
+        <v>447746</v>
       </c>
       <c r="R164" t="n">
-        <v>6814869</v>
+        <v>6814851</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17640,7 +17645,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17650,7 +17655,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17677,50 +17682,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129125731</v>
+        <v>129125720</v>
       </c>
       <c r="B165" t="n">
-        <v>56915</v>
+        <v>79071</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>448128</v>
+        <v>447936</v>
       </c>
       <c r="R165" t="n">
-        <v>6815234</v>
+        <v>6814995</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129125734</v>
+        <v>129125816</v>
       </c>
       <c r="B166" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,48 +17800,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>447913</v>
+        <v>447568</v>
       </c>
       <c r="R166" t="n">
-        <v>6815128</v>
+        <v>6814828</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17873,7 +17859,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17883,7 +17869,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17910,7 +17896,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129125816</v>
+        <v>129125860</v>
       </c>
       <c r="B167" t="n">
         <v>79039</v>
@@ -17945,10 +17931,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>447568</v>
+        <v>447887</v>
       </c>
       <c r="R167" t="n">
-        <v>6814828</v>
+        <v>6815042</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17980,7 +17966,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17990,7 +17976,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18017,7 +18003,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129125860</v>
+        <v>129125855</v>
       </c>
       <c r="B168" t="n">
         <v>79039</v>
@@ -18052,10 +18038,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>447887</v>
+        <v>447895</v>
       </c>
       <c r="R168" t="n">
-        <v>6815042</v>
+        <v>6814968</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18087,7 +18073,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18097,7 +18083,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18124,10 +18110,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129125855</v>
+        <v>129125734</v>
       </c>
       <c r="B169" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18135,34 +18121,48 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>447895</v>
+        <v>447913</v>
       </c>
       <c r="R169" t="n">
-        <v>6814968</v>
+        <v>6815128</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18231,32 +18231,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129125810</v>
+        <v>129125745</v>
       </c>
       <c r="B170" t="n">
-        <v>79039</v>
+        <v>97547</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18266,10 +18266,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>447736</v>
+        <v>448023</v>
       </c>
       <c r="R170" t="n">
-        <v>6814886</v>
+        <v>6815221</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18338,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125718</v>
+        <v>129125724</v>
       </c>
       <c r="B171" t="n">
-        <v>83015</v>
+        <v>79071</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18349,21 +18349,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18373,10 +18373,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>447772</v>
+        <v>447803</v>
       </c>
       <c r="R171" t="n">
-        <v>6815035</v>
+        <v>6815095</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18445,10 +18445,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129125861</v>
+        <v>129125723</v>
       </c>
       <c r="B172" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18456,21 +18456,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18480,10 +18480,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>447887</v>
+        <v>447751</v>
       </c>
       <c r="R172" t="n">
-        <v>6815067</v>
+        <v>6814901</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18552,10 +18552,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125832</v>
+        <v>129125727</v>
       </c>
       <c r="B173" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18563,21 +18563,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18587,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>447762</v>
+        <v>448008</v>
       </c>
       <c r="R173" t="n">
-        <v>6814968</v>
+        <v>6815080</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18659,7 +18659,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125862</v>
+        <v>129125880</v>
       </c>
       <c r="B174" t="n">
         <v>79039</v>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>447867</v>
+        <v>448107</v>
       </c>
       <c r="R174" t="n">
-        <v>6815109</v>
+        <v>6815120</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18766,45 +18766,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125763</v>
+        <v>129125740</v>
       </c>
       <c r="B175" t="n">
-        <v>82998</v>
+        <v>57722</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447801</v>
+        <v>447580</v>
       </c>
       <c r="R175" t="n">
-        <v>6814957</v>
+        <v>6814929</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18836,7 +18841,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18846,7 +18851,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18873,7 +18878,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125740</v>
+        <v>129125739</v>
       </c>
       <c r="B176" t="n">
         <v>57722</v>
@@ -18913,10 +18918,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>447580</v>
+        <v>448089</v>
       </c>
       <c r="R176" t="n">
-        <v>6814929</v>
+        <v>6815093</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18948,7 +18953,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18958,7 +18963,12 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18985,10 +18995,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125724</v>
+        <v>129125833</v>
       </c>
       <c r="B177" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18996,21 +19006,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19020,10 +19030,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>447803</v>
+        <v>447772</v>
       </c>
       <c r="R177" t="n">
-        <v>6815095</v>
+        <v>6814969</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19055,7 +19065,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19065,7 +19075,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19092,10 +19102,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129125723</v>
+        <v>129125810</v>
       </c>
       <c r="B178" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19103,21 +19113,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19127,10 +19137,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>447751</v>
+        <v>447736</v>
       </c>
       <c r="R178" t="n">
-        <v>6814901</v>
+        <v>6814886</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19162,7 +19172,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19172,7 +19182,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19199,10 +19209,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129125727</v>
+        <v>129125718</v>
       </c>
       <c r="B179" t="n">
-        <v>79071</v>
+        <v>83005</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19210,21 +19220,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19234,10 +19244,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>448008</v>
+        <v>447772</v>
       </c>
       <c r="R179" t="n">
-        <v>6815080</v>
+        <v>6815035</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19269,7 +19279,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19279,7 +19289,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19306,7 +19316,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129125880</v>
+        <v>129125861</v>
       </c>
       <c r="B180" t="n">
         <v>79039</v>
@@ -19341,10 +19351,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>448107</v>
+        <v>447887</v>
       </c>
       <c r="R180" t="n">
-        <v>6815120</v>
+        <v>6815067</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19376,7 +19386,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19386,7 +19396,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19413,7 +19423,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129125833</v>
+        <v>129125832</v>
       </c>
       <c r="B181" t="n">
         <v>79039</v>
@@ -19448,10 +19458,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>447772</v>
+        <v>447762</v>
       </c>
       <c r="R181" t="n">
-        <v>6814969</v>
+        <v>6814968</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19520,7 +19530,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125842</v>
+        <v>129125862</v>
       </c>
       <c r="B182" t="n">
         <v>79039</v>
@@ -19555,10 +19565,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>447813</v>
+        <v>447867</v>
       </c>
       <c r="R182" t="n">
-        <v>6815044</v>
+        <v>6815109</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19590,7 +19600,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19600,7 +19610,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19627,50 +19637,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125739</v>
+        <v>129125763</v>
       </c>
       <c r="B183" t="n">
-        <v>57722</v>
+        <v>82988</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>448089</v>
+        <v>447801</v>
       </c>
       <c r="R183" t="n">
-        <v>6815093</v>
+        <v>6814957</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19702,7 +19707,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19712,12 +19717,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19744,32 +19744,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129125745</v>
+        <v>129125842</v>
       </c>
       <c r="B184" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19779,10 +19779,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>448023</v>
+        <v>447813</v>
       </c>
       <c r="R184" t="n">
-        <v>6815221</v>
+        <v>6815044</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19851,10 +19851,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129125725</v>
+        <v>129125876</v>
       </c>
       <c r="B185" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19862,21 +19862,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19886,10 +19886,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>448124</v>
+        <v>448131</v>
       </c>
       <c r="R185" t="n">
-        <v>6815167</v>
+        <v>6815201</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19958,7 +19958,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129125783</v>
+        <v>129125829</v>
       </c>
       <c r="B186" t="n">
         <v>79039</v>
@@ -19993,10 +19993,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>447952</v>
+        <v>447771</v>
       </c>
       <c r="R186" t="n">
-        <v>6814960</v>
+        <v>6815000</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20065,32 +20065,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125784</v>
+        <v>129125736</v>
       </c>
       <c r="B187" t="n">
-        <v>79039</v>
+        <v>80048</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>447943</v>
+        <v>447803</v>
       </c>
       <c r="R187" t="n">
-        <v>6814947</v>
+        <v>6815004</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20172,10 +20172,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129125793</v>
+        <v>129125896</v>
       </c>
       <c r="B188" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20183,34 +20183,39 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>447819</v>
+        <v>447925</v>
       </c>
       <c r="R188" t="n">
-        <v>6814842</v>
+        <v>6815105</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20242,7 +20247,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20252,7 +20257,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20279,10 +20284,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125815</v>
+        <v>129125725</v>
       </c>
       <c r="B189" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20290,21 +20295,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20314,10 +20319,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>447586</v>
+        <v>448124</v>
       </c>
       <c r="R189" t="n">
-        <v>6814809</v>
+        <v>6815167</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20349,7 +20354,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20359,7 +20364,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20493,7 +20498,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129125876</v>
+        <v>129125793</v>
       </c>
       <c r="B191" t="n">
         <v>79039</v>
@@ -20528,10 +20533,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>448131</v>
+        <v>447819</v>
       </c>
       <c r="R191" t="n">
-        <v>6815201</v>
+        <v>6814842</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20563,7 +20568,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20573,7 +20578,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20600,7 +20605,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129125829</v>
+        <v>129125784</v>
       </c>
       <c r="B192" t="n">
         <v>79039</v>
@@ -20635,10 +20640,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>447771</v>
+        <v>447943</v>
       </c>
       <c r="R192" t="n">
-        <v>6815000</v>
+        <v>6814947</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20670,7 +20675,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -20680,7 +20685,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20707,10 +20712,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129125896</v>
+        <v>129125783</v>
       </c>
       <c r="B193" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20718,39 +20723,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>447925</v>
+        <v>447952</v>
       </c>
       <c r="R193" t="n">
-        <v>6815105</v>
+        <v>6814960</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20782,7 +20782,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20819,32 +20819,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129125736</v>
+        <v>129125815</v>
       </c>
       <c r="B194" t="n">
-        <v>80048</v>
+        <v>79039</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20854,10 +20854,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>447803</v>
+        <v>447586</v>
       </c>
       <c r="R194" t="n">
-        <v>6815004</v>
+        <v>6814809</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20926,32 +20926,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125847</v>
+        <v>129125898</v>
       </c>
       <c r="B195" t="n">
-        <v>79039</v>
+        <v>92833</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447814</v>
+        <v>447585</v>
       </c>
       <c r="R195" t="n">
-        <v>6815081</v>
+        <v>6814810</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21033,7 +21033,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129125857</v>
+        <v>129125866</v>
       </c>
       <c r="B196" t="n">
         <v>79039</v>
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>447909</v>
+        <v>448062</v>
       </c>
       <c r="R196" t="n">
-        <v>6815011</v>
+        <v>6815224</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21140,7 +21140,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125893</v>
+        <v>129125834</v>
       </c>
       <c r="B197" t="n">
         <v>79039</v>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>447992</v>
+        <v>447788</v>
       </c>
       <c r="R197" t="n">
-        <v>6815102</v>
+        <v>6814995</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,7 +21247,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125866</v>
+        <v>129125847</v>
       </c>
       <c r="B198" t="n">
         <v>79039</v>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>448062</v>
+        <v>447814</v>
       </c>
       <c r="R198" t="n">
-        <v>6815224</v>
+        <v>6815081</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,7 +21354,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125890</v>
+        <v>129125819</v>
       </c>
       <c r="B199" t="n">
         <v>79039</v>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>448015</v>
+        <v>447647</v>
       </c>
       <c r="R199" t="n">
-        <v>6815065</v>
+        <v>6815013</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,7 +21461,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125834</v>
+        <v>129125893</v>
       </c>
       <c r="B200" t="n">
         <v>79039</v>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447788</v>
+        <v>447992</v>
       </c>
       <c r="R200" t="n">
-        <v>6814995</v>
+        <v>6815102</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21568,7 +21568,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129125819</v>
+        <v>129125890</v>
       </c>
       <c r="B201" t="n">
         <v>79039</v>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>447647</v>
+        <v>448015</v>
       </c>
       <c r="R201" t="n">
-        <v>6815013</v>
+        <v>6815065</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21675,32 +21675,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129125898</v>
+        <v>129125857</v>
       </c>
       <c r="B202" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21710,10 +21710,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>447585</v>
+        <v>447909</v>
       </c>
       <c r="R202" t="n">
-        <v>6814810</v>
+        <v>6815011</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21782,7 +21782,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129125881</v>
+        <v>129125856</v>
       </c>
       <c r="B203" t="n">
         <v>79039</v>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>448111</v>
+        <v>447906</v>
       </c>
       <c r="R203" t="n">
-        <v>6815099</v>
+        <v>6814985</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21889,7 +21889,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129125788</v>
+        <v>129125881</v>
       </c>
       <c r="B204" t="n">
         <v>79039</v>
@@ -21924,10 +21924,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>447870</v>
+        <v>448111</v>
       </c>
       <c r="R204" t="n">
-        <v>6814898</v>
+        <v>6815099</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21996,7 +21996,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129125856</v>
+        <v>129125788</v>
       </c>
       <c r="B205" t="n">
         <v>79039</v>
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>447906</v>
+        <v>447870</v>
       </c>
       <c r="R205" t="n">
-        <v>6814985</v>
+        <v>6814898</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22424,32 +22424,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129125735</v>
+        <v>129125884</v>
       </c>
       <c r="B209" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22459,10 +22459,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>447805</v>
+        <v>448089</v>
       </c>
       <c r="R209" t="n">
-        <v>6815002</v>
+        <v>6815055</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22638,7 +22638,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129125884</v>
+        <v>129125803</v>
       </c>
       <c r="B211" t="n">
         <v>79039</v>
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>448089</v>
+        <v>447837</v>
       </c>
       <c r="R211" t="n">
-        <v>6815055</v>
+        <v>6814958</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22745,32 +22745,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129125762</v>
+        <v>129125735</v>
       </c>
       <c r="B212" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>448058</v>
+        <v>447805</v>
       </c>
       <c r="R212" t="n">
-        <v>6815046</v>
+        <v>6815002</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22852,7 +22852,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129125883</v>
+        <v>129125762</v>
       </c>
       <c r="B213" t="n">
         <v>79039</v>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>448080</v>
+        <v>448058</v>
       </c>
       <c r="R213" t="n">
-        <v>6815060</v>
+        <v>6815046</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22959,7 +22959,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129125803</v>
+        <v>129125883</v>
       </c>
       <c r="B214" t="n">
         <v>79039</v>
@@ -22994,10 +22994,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>447837</v>
+        <v>448080</v>
       </c>
       <c r="R214" t="n">
-        <v>6814958</v>
+        <v>6815060</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23066,10 +23066,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129125733</v>
+        <v>129125785</v>
       </c>
       <c r="B215" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23077,39 +23077,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>447785</v>
+        <v>447935</v>
       </c>
       <c r="R215" t="n">
-        <v>6814977</v>
+        <v>6814942</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23141,7 +23136,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23151,7 +23146,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23178,7 +23173,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129125848</v>
+        <v>129125789</v>
       </c>
       <c r="B216" t="n">
         <v>79039</v>
@@ -23213,10 +23208,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>447816</v>
+        <v>447869</v>
       </c>
       <c r="R216" t="n">
-        <v>6815066</v>
+        <v>6814887</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23248,7 +23243,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23258,7 +23253,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23392,7 +23387,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129125789</v>
+        <v>129125822</v>
       </c>
       <c r="B218" t="n">
         <v>79039</v>
@@ -23427,10 +23422,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>447869</v>
+        <v>447745</v>
       </c>
       <c r="R218" t="n">
-        <v>6814887</v>
+        <v>6815055</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23462,7 +23457,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23472,7 +23467,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23499,7 +23494,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129125785</v>
+        <v>129125848</v>
       </c>
       <c r="B219" t="n">
         <v>79039</v>
@@ -23534,10 +23529,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>447935</v>
+        <v>447816</v>
       </c>
       <c r="R219" t="n">
-        <v>6814942</v>
+        <v>6815066</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23569,7 +23564,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23579,7 +23574,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23927,10 +23922,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129125822</v>
+        <v>129125733</v>
       </c>
       <c r="B223" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23938,34 +23933,39 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>447745</v>
+        <v>447785</v>
       </c>
       <c r="R223" t="n">
-        <v>6815055</v>
+        <v>6814977</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24141,7 +24141,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125794</v>
+        <v>129125790</v>
       </c>
       <c r="B225" t="n">
         <v>79039</v>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447798</v>
+        <v>447855</v>
       </c>
       <c r="R225" t="n">
-        <v>6814819</v>
+        <v>6814877</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,7 +24248,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125790</v>
+        <v>129125823</v>
       </c>
       <c r="B226" t="n">
         <v>79039</v>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447855</v>
+        <v>447754</v>
       </c>
       <c r="R226" t="n">
-        <v>6814877</v>
+        <v>6815045</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,7 +24355,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125823</v>
+        <v>129125776</v>
       </c>
       <c r="B227" t="n">
         <v>79039</v>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447754</v>
+        <v>447923</v>
       </c>
       <c r="R227" t="n">
-        <v>6815045</v>
+        <v>6814998</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24569,7 +24569,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129125773</v>
+        <v>129125794</v>
       </c>
       <c r="B229" t="n">
         <v>79039</v>
@@ -24604,10 +24604,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>447907</v>
+        <v>447798</v>
       </c>
       <c r="R229" t="n">
-        <v>6815075</v>
+        <v>6814819</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24676,10 +24676,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125889</v>
+        <v>129125754</v>
       </c>
       <c r="B230" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24687,21 +24687,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24711,10 +24711,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>448024</v>
+        <v>447877</v>
       </c>
       <c r="R230" t="n">
-        <v>6815046</v>
+        <v>6814908</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24746,7 +24746,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24765,6 +24765,7 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
+      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
@@ -24783,7 +24784,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129125776</v>
+        <v>129125889</v>
       </c>
       <c r="B231" t="n">
         <v>79039</v>
@@ -24818,10 +24819,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>447923</v>
+        <v>448024</v>
       </c>
       <c r="R231" t="n">
-        <v>6814998</v>
+        <v>6815046</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24853,7 +24854,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24863,7 +24864,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24890,10 +24891,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129125754</v>
+        <v>129125854</v>
       </c>
       <c r="B232" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24901,21 +24902,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24925,10 +24926,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>447877</v>
+        <v>447876</v>
       </c>
       <c r="R232" t="n">
-        <v>6814908</v>
+        <v>6814962</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24960,7 +24961,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24970,7 +24971,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24979,7 +24980,6 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
-      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
@@ -24998,7 +24998,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129125854</v>
+        <v>129125773</v>
       </c>
       <c r="B233" t="n">
         <v>79039</v>
@@ -25033,10 +25033,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>447876</v>
+        <v>447907</v>
       </c>
       <c r="R233" t="n">
-        <v>6814962</v>
+        <v>6815075</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -7015,10 +7015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129125786</v>
+        <v>129125764</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7026,21 +7026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447922</v>
+        <v>447872</v>
       </c>
       <c r="R66" t="n">
-        <v>6814934</v>
+        <v>6814907</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7122,10 +7122,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129125764</v>
+        <v>129125786</v>
       </c>
       <c r="B67" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7133,21 +7133,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447872</v>
+        <v>447922</v>
       </c>
       <c r="R67" t="n">
-        <v>6814907</v>
+        <v>6814934</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7232,7 +7232,7 @@
         <v>129125766</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129125738</v>
+        <v>129125752</v>
       </c>
       <c r="B69" t="n">
-        <v>57722</v>
+        <v>81026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,39 +7352,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447735</v>
+        <v>447893</v>
       </c>
       <c r="R69" t="n">
-        <v>6814890</v>
+        <v>6814914</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7416,7 +7411,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7426,12 +7421,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7458,45 +7448,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129125821</v>
+        <v>129125732</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>56917</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447754</v>
+        <v>447785</v>
       </c>
       <c r="R70" t="n">
-        <v>6815052</v>
+        <v>6814990</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7528,7 +7523,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7538,7 +7533,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7565,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125752</v>
+        <v>129125843</v>
       </c>
       <c r="B71" t="n">
-        <v>81024</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7576,21 +7571,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7600,10 +7595,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447893</v>
+        <v>447812</v>
       </c>
       <c r="R71" t="n">
-        <v>6814914</v>
+        <v>6815055</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7645,7 +7640,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7672,10 +7667,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125843</v>
+        <v>129125755</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7683,21 +7678,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7707,10 +7702,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447812</v>
+        <v>447756</v>
       </c>
       <c r="R72" t="n">
-        <v>6815055</v>
+        <v>6814990</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7742,7 +7737,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7752,7 +7747,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7761,6 +7756,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7779,10 +7775,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125755</v>
+        <v>129125798</v>
       </c>
       <c r="B73" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7790,21 +7786,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7814,10 +7810,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447756</v>
+        <v>447786</v>
       </c>
       <c r="R73" t="n">
-        <v>6814990</v>
+        <v>6814897</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7849,7 +7845,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7859,7 +7855,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7868,7 +7864,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7887,10 +7882,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129125798</v>
+        <v>129125787</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7922,10 +7917,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447786</v>
+        <v>447908</v>
       </c>
       <c r="R74" t="n">
-        <v>6814897</v>
+        <v>6814933</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7957,7 +7952,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -7967,7 +7962,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7994,10 +7989,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129125787</v>
+        <v>129125835</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8029,10 +8024,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447908</v>
+        <v>447793</v>
       </c>
       <c r="R75" t="n">
-        <v>6814933</v>
+        <v>6815007</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8064,7 +8059,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8074,7 +8069,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8101,10 +8096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129125835</v>
+        <v>129125812</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8136,10 +8131,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447793</v>
+        <v>447682</v>
       </c>
       <c r="R76" t="n">
-        <v>6815007</v>
+        <v>6814779</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8171,7 +8166,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8181,7 +8176,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8208,10 +8203,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129125812</v>
+        <v>129125738</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8219,34 +8214,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447682</v>
+        <v>447735</v>
       </c>
       <c r="R77" t="n">
-        <v>6814779</v>
+        <v>6814890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8288,7 +8288,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8315,50 +8320,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129125732</v>
+        <v>129125821</v>
       </c>
       <c r="B78" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447785</v>
+        <v>447754</v>
       </c>
       <c r="R78" t="n">
-        <v>6814990</v>
+        <v>6815052</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8427,10 +8427,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125895</v>
+        <v>129125873</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8462,10 +8462,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447963</v>
+        <v>448163</v>
       </c>
       <c r="R79" t="n">
-        <v>6815131</v>
+        <v>6815302</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129125730</v>
+        <v>129125771</v>
       </c>
       <c r="B80" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>448098</v>
+        <v>447925</v>
       </c>
       <c r="R80" t="n">
-        <v>6815212</v>
+        <v>6815103</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129125729</v>
+        <v>129125853</v>
       </c>
       <c r="B81" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8652,21 +8652,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448039</v>
+        <v>447853</v>
       </c>
       <c r="R81" t="n">
-        <v>6815229</v>
+        <v>6814972</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8748,10 +8748,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129125751</v>
+        <v>129125867</v>
       </c>
       <c r="B82" t="n">
-        <v>81024</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,21 +8759,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8783,10 +8783,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447952</v>
+        <v>448088</v>
       </c>
       <c r="R82" t="n">
-        <v>6814974</v>
+        <v>6815222</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8855,10 +8855,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129125873</v>
+        <v>129125824</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>448163</v>
+        <v>447761</v>
       </c>
       <c r="R83" t="n">
-        <v>6815302</v>
+        <v>6815045</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8962,10 +8962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125771</v>
+        <v>129125808</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447925</v>
+        <v>447782</v>
       </c>
       <c r="R84" t="n">
-        <v>6815103</v>
+        <v>6814944</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125853</v>
+        <v>129125895</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447853</v>
+        <v>447963</v>
       </c>
       <c r="R85" t="n">
-        <v>6814972</v>
+        <v>6815131</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9176,10 +9176,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125867</v>
+        <v>129125767</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>448088</v>
+        <v>447915</v>
       </c>
       <c r="R86" t="n">
-        <v>6815222</v>
+        <v>6815140</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9283,10 +9283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129125824</v>
+        <v>129125729</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,21 +9294,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447761</v>
+        <v>448039</v>
       </c>
       <c r="R87" t="n">
-        <v>6815045</v>
+        <v>6815229</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9390,10 +9390,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129125808</v>
+        <v>129125751</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>81026</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9401,21 +9401,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447782</v>
+        <v>447952</v>
       </c>
       <c r="R88" t="n">
-        <v>6814944</v>
+        <v>6814974</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9497,10 +9497,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129125767</v>
+        <v>129125730</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9508,21 +9508,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447915</v>
+        <v>448098</v>
       </c>
       <c r="R89" t="n">
-        <v>6815140</v>
+        <v>6815212</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9607,7 +9607,7 @@
         <v>129125759</v>
       </c>
       <c r="B90" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125809</v>
+        <v>129125874</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447763</v>
+        <v>448182</v>
       </c>
       <c r="R91" t="n">
-        <v>6814923</v>
+        <v>6815308</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9827,10 +9827,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125722</v>
+        <v>129125809</v>
       </c>
       <c r="B92" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9838,21 +9838,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447757</v>
+        <v>447763</v>
       </c>
       <c r="R92" t="n">
-        <v>6814906</v>
+        <v>6814923</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,10 +9934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125874</v>
+        <v>129125831</v>
       </c>
       <c r="B93" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>448182</v>
+        <v>447755</v>
       </c>
       <c r="R93" t="n">
-        <v>6815308</v>
+        <v>6814973</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10041,10 +10041,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125831</v>
+        <v>129125772</v>
       </c>
       <c r="B94" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447755</v>
+        <v>447920</v>
       </c>
       <c r="R94" t="n">
-        <v>6814973</v>
+        <v>6815082</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,10 +10148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125772</v>
+        <v>129125753</v>
       </c>
       <c r="B95" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,21 +10159,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447920</v>
+        <v>447766</v>
       </c>
       <c r="R95" t="n">
-        <v>6815082</v>
+        <v>6814899</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,7 +10228,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10237,6 +10242,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10255,10 +10261,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125753</v>
+        <v>129125795</v>
       </c>
       <c r="B96" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10266,21 +10272,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10290,10 +10296,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447766</v>
+        <v>447790</v>
       </c>
       <c r="R96" t="n">
-        <v>6814899</v>
+        <v>6814834</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10325,7 +10331,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10335,12 +10341,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10349,7 +10350,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125795</v>
+        <v>129125722</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447790</v>
+        <v>447757</v>
       </c>
       <c r="R97" t="n">
-        <v>6814834</v>
+        <v>6814906</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129125746</v>
+        <v>129125719</v>
       </c>
       <c r="B98" t="n">
-        <v>97553</v>
+        <v>79073</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>448129</v>
+        <v>447855</v>
       </c>
       <c r="R98" t="n">
-        <v>6815200</v>
+        <v>6814877</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10582,32 +10582,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129125719</v>
+        <v>129125746</v>
       </c>
       <c r="B99" t="n">
-        <v>79071</v>
+        <v>97555</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447855</v>
+        <v>448129</v>
       </c>
       <c r="R99" t="n">
-        <v>6814877</v>
+        <v>6815200</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10689,10 +10689,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129125820</v>
+        <v>129125872</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447706</v>
+        <v>448159</v>
       </c>
       <c r="R100" t="n">
-        <v>6815025</v>
+        <v>6815277</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10796,10 +10796,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129125858</v>
+        <v>129125820</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447914</v>
+        <v>447706</v>
       </c>
       <c r="R101" t="n">
-        <v>6815024</v>
+        <v>6815025</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10903,10 +10903,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129125741</v>
+        <v>129125888</v>
       </c>
       <c r="B102" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10914,39 +10914,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447902</v>
+        <v>448042</v>
       </c>
       <c r="R102" t="n">
-        <v>6814922</v>
+        <v>6815053</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10978,7 +10973,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10988,7 +10983,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11015,10 +11010,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129125872</v>
+        <v>129125858</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11050,10 +11045,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>448159</v>
+        <v>447914</v>
       </c>
       <c r="R103" t="n">
-        <v>6815277</v>
+        <v>6815024</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11085,7 +11080,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11095,7 +11090,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11122,10 +11117,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129125888</v>
+        <v>129125836</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11157,10 +11152,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448042</v>
+        <v>447789</v>
       </c>
       <c r="R104" t="n">
-        <v>6815053</v>
+        <v>6815016</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11192,7 +11187,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11202,7 +11197,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11229,10 +11224,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125836</v>
+        <v>129125741</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11240,34 +11235,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447789</v>
+        <v>447902</v>
       </c>
       <c r="R105" t="n">
-        <v>6815016</v>
+        <v>6814922</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11336,10 +11336,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129125814</v>
+        <v>129125868</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447611</v>
+        <v>448101</v>
       </c>
       <c r="R106" t="n">
-        <v>6814782</v>
+        <v>6815213</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11443,10 +11443,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129125868</v>
+        <v>129125837</v>
       </c>
       <c r="B107" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>448101</v>
+        <v>447806</v>
       </c>
       <c r="R107" t="n">
-        <v>6815213</v>
+        <v>6815012</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11550,10 +11550,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129125886</v>
+        <v>129125814</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448097</v>
+        <v>447611</v>
       </c>
       <c r="R108" t="n">
-        <v>6815025</v>
+        <v>6814782</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11657,10 +11657,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129125813</v>
+        <v>129125886</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447617</v>
+        <v>448097</v>
       </c>
       <c r="R109" t="n">
-        <v>6814828</v>
+        <v>6815025</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11764,10 +11764,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129125837</v>
+        <v>129125813</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447806</v>
+        <v>447617</v>
       </c>
       <c r="R110" t="n">
-        <v>6815012</v>
+        <v>6814828</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11871,10 +11871,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129125721</v>
+        <v>129125807</v>
       </c>
       <c r="B111" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11882,21 +11882,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447943</v>
+        <v>447797</v>
       </c>
       <c r="R111" t="n">
-        <v>6814947</v>
+        <v>6814950</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11978,32 +11978,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129125728</v>
+        <v>129125863</v>
       </c>
       <c r="B112" t="n">
-        <v>91504</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447872</v>
+        <v>447878</v>
       </c>
       <c r="R112" t="n">
-        <v>6815131</v>
+        <v>6815153</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12085,10 +12085,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125863</v>
+        <v>129125891</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447878</v>
+        <v>448003</v>
       </c>
       <c r="R113" t="n">
-        <v>6815153</v>
+        <v>6815088</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12195,7 +12195,7 @@
         <v>129125779</v>
       </c>
       <c r="B114" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12299,10 +12299,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129125851</v>
+        <v>129125841</v>
       </c>
       <c r="B115" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447834</v>
+        <v>447812</v>
       </c>
       <c r="R115" t="n">
-        <v>6815005</v>
+        <v>6815036</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12406,32 +12406,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125807</v>
+        <v>129125728</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>91506</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447797</v>
+        <v>447872</v>
       </c>
       <c r="R116" t="n">
-        <v>6814950</v>
+        <v>6815131</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,10 +12513,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125891</v>
+        <v>129125851</v>
       </c>
       <c r="B117" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448003</v>
+        <v>447834</v>
       </c>
       <c r="R117" t="n">
-        <v>6815088</v>
+        <v>6815005</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12620,10 +12620,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129125841</v>
+        <v>129125721</v>
       </c>
       <c r="B118" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,21 +12631,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447812</v>
+        <v>447943</v>
       </c>
       <c r="R118" t="n">
-        <v>6815036</v>
+        <v>6814947</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12727,10 +12727,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129125894</v>
+        <v>129125877</v>
       </c>
       <c r="B119" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447978</v>
+        <v>448126</v>
       </c>
       <c r="R119" t="n">
-        <v>6815111</v>
+        <v>6815198</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12834,10 +12834,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125850</v>
+        <v>129125894</v>
       </c>
       <c r="B120" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447844</v>
+        <v>447978</v>
       </c>
       <c r="R120" t="n">
-        <v>6815026</v>
+        <v>6815111</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,10 +12941,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125827</v>
+        <v>129125850</v>
       </c>
       <c r="B121" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447767</v>
+        <v>447844</v>
       </c>
       <c r="R121" t="n">
-        <v>6815014</v>
+        <v>6815026</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13048,10 +13048,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129125865</v>
+        <v>129125827</v>
       </c>
       <c r="B122" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>448049</v>
+        <v>447767</v>
       </c>
       <c r="R122" t="n">
-        <v>6815224</v>
+        <v>6815014</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13155,10 +13155,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125882</v>
+        <v>129125811</v>
       </c>
       <c r="B123" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>448089</v>
+        <v>447716</v>
       </c>
       <c r="R123" t="n">
-        <v>6815086</v>
+        <v>6814829</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,10 +13262,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125791</v>
+        <v>129125865</v>
       </c>
       <c r="B124" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447839</v>
+        <v>448049</v>
       </c>
       <c r="R124" t="n">
-        <v>6814871</v>
+        <v>6815224</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,10 +13369,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125877</v>
+        <v>129125859</v>
       </c>
       <c r="B125" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448126</v>
+        <v>447887</v>
       </c>
       <c r="R125" t="n">
-        <v>6815198</v>
+        <v>6815043</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,32 +13476,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125750</v>
+        <v>129125882</v>
       </c>
       <c r="B126" t="n">
-        <v>80180</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447714</v>
+        <v>448089</v>
       </c>
       <c r="R126" t="n">
-        <v>6815023</v>
+        <v>6815086</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,10 +13583,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125811</v>
+        <v>129125845</v>
       </c>
       <c r="B127" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447716</v>
+        <v>447801</v>
       </c>
       <c r="R127" t="n">
-        <v>6814829</v>
+        <v>6815082</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13690,10 +13690,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129125859</v>
+        <v>129125791</v>
       </c>
       <c r="B128" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447887</v>
+        <v>447839</v>
       </c>
       <c r="R128" t="n">
-        <v>6815043</v>
+        <v>6814871</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13797,32 +13797,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125852</v>
+        <v>129125750</v>
       </c>
       <c r="B129" t="n">
-        <v>79039</v>
+        <v>80182</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447839</v>
+        <v>447714</v>
       </c>
       <c r="R129" t="n">
-        <v>6814995</v>
+        <v>6815023</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,10 +13904,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125845</v>
+        <v>129125852</v>
       </c>
       <c r="B130" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447801</v>
+        <v>447839</v>
       </c>
       <c r="R130" t="n">
-        <v>6815082</v>
+        <v>6814995</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,32 +14011,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125844</v>
+        <v>129125743</v>
       </c>
       <c r="B131" t="n">
-        <v>79039</v>
+        <v>80050</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447808</v>
+        <v>447735</v>
       </c>
       <c r="R131" t="n">
-        <v>6815078</v>
+        <v>6814890</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,7 +14091,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14121,7 +14126,7 @@
         <v>129125879</v>
       </c>
       <c r="B132" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14228,7 +14233,7 @@
         <v>129125770</v>
       </c>
       <c r="B133" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14332,32 +14337,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129125743</v>
+        <v>129125844</v>
       </c>
       <c r="B134" t="n">
-        <v>80048</v>
+        <v>79041</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14367,10 +14372,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>447735</v>
+        <v>447808</v>
       </c>
       <c r="R134" t="n">
-        <v>6814890</v>
+        <v>6815078</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14402,7 +14407,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14412,12 +14417,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14447,7 +14447,7 @@
         <v>129125846</v>
       </c>
       <c r="B135" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>129125781</v>
       </c>
       <c r="B136" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14658,10 +14658,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125818</v>
+        <v>129125885</v>
       </c>
       <c r="B137" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14693,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>447641</v>
+        <v>448080</v>
       </c>
       <c r="R137" t="n">
-        <v>6814924</v>
+        <v>6815037</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14765,10 +14765,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125805</v>
+        <v>129125797</v>
       </c>
       <c r="B138" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>447826</v>
+        <v>447781</v>
       </c>
       <c r="R138" t="n">
-        <v>6814982</v>
+        <v>6814894</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14872,10 +14872,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125887</v>
+        <v>129125805</v>
       </c>
       <c r="B139" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>448080</v>
+        <v>447826</v>
       </c>
       <c r="R139" t="n">
-        <v>6815039</v>
+        <v>6814982</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14979,10 +14979,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125885</v>
+        <v>129125887</v>
       </c>
       <c r="B140" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>448080</v>
       </c>
       <c r="R140" t="n">
-        <v>6815037</v>
+        <v>6815039</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15086,10 +15086,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125797</v>
+        <v>129125737</v>
       </c>
       <c r="B141" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15097,34 +15097,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>447781</v>
+        <v>447735</v>
       </c>
       <c r="R141" t="n">
-        <v>6814894</v>
+        <v>6815036</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15156,7 +15161,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15166,7 +15171,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15193,10 +15198,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129125737</v>
+        <v>129125818</v>
       </c>
       <c r="B142" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15204,39 +15209,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>447735</v>
+        <v>447641</v>
       </c>
       <c r="R142" t="n">
-        <v>6815036</v>
+        <v>6814924</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15305,10 +15305,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125775</v>
+        <v>129125828</v>
       </c>
       <c r="B143" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447916</v>
+        <v>447781</v>
       </c>
       <c r="R143" t="n">
-        <v>6815021</v>
+        <v>6815009</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,10 +15412,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125828</v>
+        <v>129125839</v>
       </c>
       <c r="B144" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447781</v>
+        <v>447805</v>
       </c>
       <c r="R144" t="n">
-        <v>6815009</v>
+        <v>6815025</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,10 +15519,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125826</v>
+        <v>129125792</v>
       </c>
       <c r="B145" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447765</v>
+        <v>447812</v>
       </c>
       <c r="R145" t="n">
-        <v>6815023</v>
+        <v>6814852</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15626,27 +15626,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129125899</v>
+        <v>129125826</v>
       </c>
       <c r="B146" t="n">
-        <v>80179</v>
+        <v>79041</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -15661,10 +15661,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>447580</v>
+        <v>447765</v>
       </c>
       <c r="R146" t="n">
-        <v>6814868</v>
+        <v>6815023</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15733,27 +15733,27 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129125839</v>
+        <v>129125899</v>
       </c>
       <c r="B147" t="n">
-        <v>79039</v>
+        <v>80181</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -15768,10 +15768,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>447805</v>
+        <v>447580</v>
       </c>
       <c r="R147" t="n">
-        <v>6815025</v>
+        <v>6814868</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15840,10 +15840,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129125792</v>
+        <v>129125775</v>
       </c>
       <c r="B148" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15875,10 +15875,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>447812</v>
+        <v>447916</v>
       </c>
       <c r="R148" t="n">
-        <v>6814852</v>
+        <v>6815021</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15950,7 +15950,7 @@
         <v>129125796</v>
       </c>
       <c r="B149" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16054,10 +16054,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129125806</v>
+        <v>129125720</v>
       </c>
       <c r="B150" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16065,21 +16065,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16089,10 +16089,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>447816</v>
+        <v>447936</v>
       </c>
       <c r="R150" t="n">
-        <v>6814979</v>
+        <v>6814995</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16161,45 +16161,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129125799</v>
+        <v>129125731</v>
       </c>
       <c r="B151" t="n">
-        <v>79039</v>
+        <v>56917</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>447804</v>
+        <v>448128</v>
       </c>
       <c r="R151" t="n">
-        <v>6814911</v>
+        <v>6815234</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16231,7 +16236,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16241,7 +16246,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16268,10 +16273,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129125769</v>
+        <v>129125802</v>
       </c>
       <c r="B152" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16303,10 +16308,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>447912</v>
+        <v>447821</v>
       </c>
       <c r="R152" t="n">
-        <v>6815110</v>
+        <v>6814955</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16338,7 +16343,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16348,7 +16353,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,10 +16380,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129125804</v>
+        <v>129125806</v>
       </c>
       <c r="B153" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16410,10 +16415,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>447840</v>
+        <v>447816</v>
       </c>
       <c r="R153" t="n">
-        <v>6814978</v>
+        <v>6814979</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16445,7 +16450,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16455,7 +16460,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16482,10 +16487,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129125878</v>
+        <v>129125830</v>
       </c>
       <c r="B154" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16517,10 +16522,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>448121</v>
+        <v>447767</v>
       </c>
       <c r="R154" t="n">
-        <v>6815175</v>
+        <v>6814993</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16552,7 +16557,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16562,7 +16567,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16589,10 +16594,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129125849</v>
+        <v>129125769</v>
       </c>
       <c r="B155" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16624,10 +16629,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>447825</v>
+        <v>447912</v>
       </c>
       <c r="R155" t="n">
-        <v>6815056</v>
+        <v>6815110</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16659,7 +16664,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -16669,7 +16674,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16696,10 +16701,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129125802</v>
+        <v>129125768</v>
       </c>
       <c r="B156" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16731,10 +16736,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>447821</v>
+        <v>447909</v>
       </c>
       <c r="R156" t="n">
-        <v>6814955</v>
+        <v>6815119</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16766,7 +16771,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16776,7 +16781,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16803,10 +16808,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129125830</v>
+        <v>129125804</v>
       </c>
       <c r="B157" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16838,10 +16843,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>447767</v>
+        <v>447840</v>
       </c>
       <c r="R157" t="n">
-        <v>6814993</v>
+        <v>6814978</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16873,7 +16878,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16883,7 +16888,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16910,10 +16915,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129125768</v>
+        <v>129125801</v>
       </c>
       <c r="B158" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16945,10 +16950,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>447909</v>
+        <v>447814</v>
       </c>
       <c r="R158" t="n">
-        <v>6815119</v>
+        <v>6814948</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16980,7 +16985,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -16990,7 +16995,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17017,32 +17022,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129125749</v>
+        <v>129125849</v>
       </c>
       <c r="B159" t="n">
-        <v>80180</v>
+        <v>79041</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17052,10 +17057,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>447581</v>
+        <v>447825</v>
       </c>
       <c r="R159" t="n">
-        <v>6814869</v>
+        <v>6815056</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17087,7 +17092,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17097,7 +17102,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17124,32 +17129,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129125801</v>
+        <v>129125749</v>
       </c>
       <c r="B160" t="n">
-        <v>79039</v>
+        <v>80182</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17159,10 +17164,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>447814</v>
+        <v>447581</v>
       </c>
       <c r="R160" t="n">
-        <v>6814948</v>
+        <v>6814869</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17194,7 +17199,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17204,7 +17209,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17231,10 +17236,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129125869</v>
+        <v>129125799</v>
       </c>
       <c r="B161" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17266,10 +17271,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>448114</v>
+        <v>447804</v>
       </c>
       <c r="R161" t="n">
-        <v>6815209</v>
+        <v>6814911</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17301,7 +17306,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17311,7 +17316,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17338,50 +17343,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129125731</v>
+        <v>129125878</v>
       </c>
       <c r="B162" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>448128</v>
+        <v>448121</v>
       </c>
       <c r="R162" t="n">
-        <v>6815234</v>
+        <v>6815175</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17450,54 +17450,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129125758</v>
+        <v>129125869</v>
       </c>
       <c r="B163" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>447571</v>
+        <v>448114</v>
       </c>
       <c r="R163" t="n">
-        <v>6814831</v>
+        <v>6815209</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17529,7 +17520,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17539,7 +17530,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17566,10 +17557,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129125757</v>
+        <v>129125758</v>
       </c>
       <c r="B164" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17610,10 +17601,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>447746</v>
+        <v>447571</v>
       </c>
       <c r="R164" t="n">
-        <v>6814851</v>
+        <v>6814831</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17645,7 +17636,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17655,7 +17646,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17682,45 +17673,54 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129125720</v>
+        <v>129125757</v>
       </c>
       <c r="B165" t="n">
-        <v>79071</v>
+        <v>98678</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>447936</v>
+        <v>447746</v>
       </c>
       <c r="R165" t="n">
-        <v>6814995</v>
+        <v>6814851</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17789,10 +17789,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129125816</v>
+        <v>129125734</v>
       </c>
       <c r="B166" t="n">
-        <v>79039</v>
+        <v>57887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17800,34 +17800,48 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>447568</v>
+        <v>447913</v>
       </c>
       <c r="R166" t="n">
-        <v>6814828</v>
+        <v>6815128</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17859,7 +17873,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17869,7 +17883,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17899,7 +17913,7 @@
         <v>129125860</v>
       </c>
       <c r="B167" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18006,7 +18020,7 @@
         <v>129125855</v>
       </c>
       <c r="B168" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18110,10 +18124,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129125734</v>
+        <v>129125816</v>
       </c>
       <c r="B169" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18121,48 +18135,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>447913</v>
+        <v>447568</v>
       </c>
       <c r="R169" t="n">
-        <v>6815128</v>
+        <v>6814828</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18231,32 +18231,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129125745</v>
+        <v>129125880</v>
       </c>
       <c r="B170" t="n">
-        <v>97547</v>
+        <v>79041</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18266,10 +18266,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>448023</v>
+        <v>448107</v>
       </c>
       <c r="R170" t="n">
-        <v>6815221</v>
+        <v>6815120</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18338,10 +18338,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129125724</v>
+        <v>129125718</v>
       </c>
       <c r="B171" t="n">
-        <v>79071</v>
+        <v>83007</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18349,21 +18349,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18373,10 +18373,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>447803</v>
+        <v>447772</v>
       </c>
       <c r="R171" t="n">
-        <v>6815095</v>
+        <v>6815035</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18418,7 +18418,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18445,10 +18445,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129125723</v>
+        <v>129125832</v>
       </c>
       <c r="B172" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18456,21 +18456,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18480,10 +18480,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>447751</v>
+        <v>447762</v>
       </c>
       <c r="R172" t="n">
-        <v>6814901</v>
+        <v>6814968</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18552,10 +18552,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129125727</v>
+        <v>129125862</v>
       </c>
       <c r="B173" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18563,21 +18563,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18587,10 +18587,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>448008</v>
+        <v>447867</v>
       </c>
       <c r="R173" t="n">
-        <v>6815080</v>
+        <v>6815109</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18659,32 +18659,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129125880</v>
+        <v>129125763</v>
       </c>
       <c r="B174" t="n">
-        <v>79039</v>
+        <v>82990</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>448107</v>
+        <v>447801</v>
       </c>
       <c r="R174" t="n">
-        <v>6815120</v>
+        <v>6814957</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18766,10 +18766,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129125740</v>
+        <v>129125842</v>
       </c>
       <c r="B175" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18777,39 +18777,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>447580</v>
+        <v>447813</v>
       </c>
       <c r="R175" t="n">
-        <v>6814929</v>
+        <v>6815044</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18841,7 +18836,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18851,7 +18846,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18878,10 +18873,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129125739</v>
+        <v>129125724</v>
       </c>
       <c r="B176" t="n">
-        <v>57722</v>
+        <v>79073</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18889,39 +18884,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>448089</v>
+        <v>447803</v>
       </c>
       <c r="R176" t="n">
-        <v>6815093</v>
+        <v>6815095</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18953,7 +18943,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -18963,12 +18953,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>16:13</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>I gammal asp</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18995,10 +18980,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129125833</v>
+        <v>129125723</v>
       </c>
       <c r="B177" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19006,21 +18991,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19030,10 +19015,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>447772</v>
+        <v>447751</v>
       </c>
       <c r="R177" t="n">
-        <v>6814969</v>
+        <v>6814901</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19065,7 +19050,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19075,7 +19060,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19102,10 +19087,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129125810</v>
+        <v>129125727</v>
       </c>
       <c r="B178" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19113,21 +19098,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19137,10 +19122,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>447736</v>
+        <v>448008</v>
       </c>
       <c r="R178" t="n">
-        <v>6814886</v>
+        <v>6815080</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19172,7 +19157,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19182,7 +19167,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19209,10 +19194,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129125718</v>
+        <v>129125833</v>
       </c>
       <c r="B179" t="n">
-        <v>83005</v>
+        <v>79041</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19220,21 +19205,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19247,7 +19232,7 @@
         <v>447772</v>
       </c>
       <c r="R179" t="n">
-        <v>6815035</v>
+        <v>6814969</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19279,7 +19264,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19289,7 +19274,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19316,10 +19301,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129125861</v>
+        <v>129125810</v>
       </c>
       <c r="B180" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19351,10 +19336,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>447887</v>
+        <v>447736</v>
       </c>
       <c r="R180" t="n">
-        <v>6815067</v>
+        <v>6814886</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19386,7 +19371,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -19396,7 +19381,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19423,10 +19408,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129125832</v>
+        <v>129125861</v>
       </c>
       <c r="B181" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19458,10 +19443,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>447762</v>
+        <v>447887</v>
       </c>
       <c r="R181" t="n">
-        <v>6814968</v>
+        <v>6815067</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19493,7 +19478,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -19503,7 +19488,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19530,10 +19515,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129125862</v>
+        <v>129125739</v>
       </c>
       <c r="B182" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19541,34 +19526,39 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>447867</v>
+        <v>448089</v>
       </c>
       <c r="R182" t="n">
-        <v>6815109</v>
+        <v>6815093</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19600,7 +19590,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -19610,7 +19600,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>I gammal asp</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19637,45 +19632,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129125763</v>
+        <v>129125740</v>
       </c>
       <c r="B183" t="n">
-        <v>82988</v>
+        <v>57724</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6439</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>447801</v>
+        <v>447580</v>
       </c>
       <c r="R183" t="n">
-        <v>6814957</v>
+        <v>6814929</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19744,32 +19744,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129125842</v>
+        <v>129125745</v>
       </c>
       <c r="B184" t="n">
-        <v>79039</v>
+        <v>97549</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19779,10 +19779,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>447813</v>
+        <v>448023</v>
       </c>
       <c r="R184" t="n">
-        <v>6815044</v>
+        <v>6815221</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19851,10 +19851,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129125876</v>
+        <v>129125725</v>
       </c>
       <c r="B185" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19862,21 +19862,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19886,10 +19886,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>448131</v>
+        <v>448124</v>
       </c>
       <c r="R185" t="n">
-        <v>6815201</v>
+        <v>6815167</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19958,32 +19958,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129125829</v>
+        <v>129125736</v>
       </c>
       <c r="B186" t="n">
-        <v>79039</v>
+        <v>80050</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19993,10 +19993,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>447771</v>
+        <v>447803</v>
       </c>
       <c r="R186" t="n">
-        <v>6815000</v>
+        <v>6815004</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20065,32 +20065,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129125736</v>
+        <v>129125829</v>
       </c>
       <c r="B187" t="n">
-        <v>80048</v>
+        <v>79041</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20100,10 +20100,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>447803</v>
+        <v>447771</v>
       </c>
       <c r="R187" t="n">
-        <v>6815004</v>
+        <v>6815000</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20145,7 +20145,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20175,7 +20175,7 @@
         <v>129125896</v>
       </c>
       <c r="B188" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20284,10 +20284,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129125725</v>
+        <v>129125876</v>
       </c>
       <c r="B189" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20295,21 +20295,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20319,10 +20319,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>448124</v>
+        <v>448131</v>
       </c>
       <c r="R189" t="n">
-        <v>6815167</v>
+        <v>6815201</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20354,7 +20354,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20394,7 +20394,7 @@
         <v>129125780</v>
       </c>
       <c r="B190" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>129125793</v>
       </c>
       <c r="B191" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>129125784</v>
       </c>
       <c r="B192" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>129125783</v>
       </c>
       <c r="B193" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>129125815</v>
       </c>
       <c r="B194" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20926,32 +20926,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129125898</v>
+        <v>129125893</v>
       </c>
       <c r="B195" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>447585</v>
+        <v>447992</v>
       </c>
       <c r="R195" t="n">
-        <v>6814810</v>
+        <v>6815102</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21036,7 +21036,7 @@
         <v>129125866</v>
       </c>
       <c r="B196" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21140,10 +21140,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129125834</v>
+        <v>129125890</v>
       </c>
       <c r="B197" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21175,10 +21175,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>447788</v>
+        <v>448015</v>
       </c>
       <c r="R197" t="n">
-        <v>6814995</v>
+        <v>6815065</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21247,10 +21247,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129125847</v>
+        <v>129125857</v>
       </c>
       <c r="B198" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21282,10 +21282,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>447814</v>
+        <v>447909</v>
       </c>
       <c r="R198" t="n">
-        <v>6815081</v>
+        <v>6815011</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21354,10 +21354,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129125819</v>
+        <v>129125834</v>
       </c>
       <c r="B199" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21389,10 +21389,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>447647</v>
+        <v>447788</v>
       </c>
       <c r="R199" t="n">
-        <v>6815013</v>
+        <v>6814995</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21461,10 +21461,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129125893</v>
+        <v>129125847</v>
       </c>
       <c r="B200" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21496,10 +21496,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>447992</v>
+        <v>447814</v>
       </c>
       <c r="R200" t="n">
-        <v>6815102</v>
+        <v>6815081</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21568,10 +21568,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129125890</v>
+        <v>129125819</v>
       </c>
       <c r="B201" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21603,10 +21603,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>448015</v>
+        <v>447647</v>
       </c>
       <c r="R201" t="n">
-        <v>6815065</v>
+        <v>6815013</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21675,32 +21675,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129125857</v>
+        <v>129125898</v>
       </c>
       <c r="B202" t="n">
-        <v>79039</v>
+        <v>92835</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21710,10 +21710,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>447909</v>
+        <v>447585</v>
       </c>
       <c r="R202" t="n">
-        <v>6815011</v>
+        <v>6814810</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21782,10 +21782,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129125856</v>
+        <v>129125864</v>
       </c>
       <c r="B203" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>447906</v>
+        <v>448025</v>
       </c>
       <c r="R203" t="n">
-        <v>6814985</v>
+        <v>6815228</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21852,7 +21852,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21892,7 +21892,7 @@
         <v>129125881</v>
       </c>
       <c r="B204" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>129125788</v>
       </c>
       <c r="B205" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>129125875</v>
       </c>
       <c r="B206" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>129125892</v>
       </c>
       <c r="B207" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22317,10 +22317,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129125864</v>
+        <v>129125856</v>
       </c>
       <c r="B208" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>448025</v>
+        <v>447906</v>
       </c>
       <c r="R208" t="n">
-        <v>6815228</v>
+        <v>6814985</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22387,7 +22387,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22424,10 +22424,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129125884</v>
+        <v>129125803</v>
       </c>
       <c r="B209" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22459,10 +22459,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>448089</v>
+        <v>447837</v>
       </c>
       <c r="R209" t="n">
-        <v>6815055</v>
+        <v>6814958</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22531,10 +22531,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129125825</v>
+        <v>129125884</v>
       </c>
       <c r="B210" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22566,10 +22566,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>447766</v>
+        <v>448089</v>
       </c>
       <c r="R210" t="n">
-        <v>6815038</v>
+        <v>6815055</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22638,10 +22638,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129125803</v>
+        <v>129125825</v>
       </c>
       <c r="B211" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22673,10 +22673,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>447837</v>
+        <v>447766</v>
       </c>
       <c r="R211" t="n">
-        <v>6814958</v>
+        <v>6815038</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22708,7 +22708,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22745,32 +22745,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129125735</v>
+        <v>129125762</v>
       </c>
       <c r="B212" t="n">
-        <v>80173</v>
+        <v>79041</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22780,10 +22780,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>447805</v>
+        <v>448058</v>
       </c>
       <c r="R212" t="n">
-        <v>6815002</v>
+        <v>6815046</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22852,10 +22852,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129125762</v>
+        <v>129125883</v>
       </c>
       <c r="B213" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22887,10 +22887,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>448058</v>
+        <v>448080</v>
       </c>
       <c r="R213" t="n">
-        <v>6815046</v>
+        <v>6815060</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22922,7 +22922,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22959,32 +22959,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129125883</v>
+        <v>129125735</v>
       </c>
       <c r="B214" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22994,10 +22994,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>448080</v>
+        <v>447805</v>
       </c>
       <c r="R214" t="n">
-        <v>6815060</v>
+        <v>6815002</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23069,7 +23069,7 @@
         <v>129125785</v>
       </c>
       <c r="B215" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>129125789</v>
       </c>
       <c r="B216" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129125838</v>
+        <v>129125848</v>
       </c>
       <c r="B217" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23315,10 +23315,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>447808</v>
+        <v>447816</v>
       </c>
       <c r="R217" t="n">
-        <v>6815019</v>
+        <v>6815066</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -23360,7 +23360,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23387,10 +23387,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129125822</v>
+        <v>129125871</v>
       </c>
       <c r="B218" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23422,10 +23422,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>447745</v>
+        <v>448138</v>
       </c>
       <c r="R218" t="n">
-        <v>6815055</v>
+        <v>6815238</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23494,10 +23494,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129125848</v>
+        <v>129125782</v>
       </c>
       <c r="B219" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23529,10 +23529,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>447816</v>
+        <v>447951</v>
       </c>
       <c r="R219" t="n">
-        <v>6815066</v>
+        <v>6814973</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23564,7 +23564,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23601,10 +23601,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129125871</v>
+        <v>129125774</v>
       </c>
       <c r="B220" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23636,10 +23636,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>448138</v>
+        <v>447907</v>
       </c>
       <c r="R220" t="n">
-        <v>6815238</v>
+        <v>6815056</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23671,7 +23671,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23708,10 +23708,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129125782</v>
+        <v>129125838</v>
       </c>
       <c r="B221" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23743,10 +23743,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>447951</v>
+        <v>447808</v>
       </c>
       <c r="R221" t="n">
-        <v>6814973</v>
+        <v>6815019</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -23788,7 +23788,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23815,10 +23815,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129125774</v>
+        <v>129125822</v>
       </c>
       <c r="B222" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23850,10 +23850,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>447907</v>
+        <v>447745</v>
       </c>
       <c r="R222" t="n">
-        <v>6815056</v>
+        <v>6815055</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23925,7 +23925,7 @@
         <v>129125733</v>
       </c>
       <c r="B223" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>129125726</v>
       </c>
       <c r="B224" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24141,10 +24141,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129125790</v>
+        <v>129125776</v>
       </c>
       <c r="B225" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24176,10 +24176,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>447855</v>
+        <v>447923</v>
       </c>
       <c r="R225" t="n">
-        <v>6814877</v>
+        <v>6814998</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24248,10 +24248,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129125823</v>
+        <v>129125790</v>
       </c>
       <c r="B226" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24283,10 +24283,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>447754</v>
+        <v>447855</v>
       </c>
       <c r="R226" t="n">
-        <v>6815045</v>
+        <v>6814877</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24355,10 +24355,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129125776</v>
+        <v>129125817</v>
       </c>
       <c r="B227" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>447923</v>
+        <v>447580</v>
       </c>
       <c r="R227" t="n">
-        <v>6814998</v>
+        <v>6814929</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24462,10 +24462,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129125817</v>
+        <v>129125754</v>
       </c>
       <c r="B228" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24473,21 +24473,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>447580</v>
+        <v>447877</v>
       </c>
       <c r="R228" t="n">
-        <v>6814929</v>
+        <v>6814908</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24551,6 +24551,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -24569,10 +24570,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129125794</v>
+        <v>129125854</v>
       </c>
       <c r="B229" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24604,10 +24605,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>447798</v>
+        <v>447876</v>
       </c>
       <c r="R229" t="n">
-        <v>6814819</v>
+        <v>6814962</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24639,7 +24640,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24649,7 +24650,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24676,10 +24677,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129125754</v>
+        <v>129125823</v>
       </c>
       <c r="B230" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24687,21 +24688,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24711,10 +24712,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>447877</v>
+        <v>447754</v>
       </c>
       <c r="R230" t="n">
-        <v>6814908</v>
+        <v>6815045</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24746,7 +24747,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24756,7 +24757,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24765,7 +24766,6 @@
       <c r="AE230" t="b">
         <v>0</v>
       </c>
-      <c r="AF230" t="inlineStr"/>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
@@ -24784,10 +24784,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129125889</v>
+        <v>129125794</v>
       </c>
       <c r="B231" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24819,10 +24819,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>448024</v>
+        <v>447798</v>
       </c>
       <c r="R231" t="n">
-        <v>6815046</v>
+        <v>6814819</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24891,10 +24891,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129125854</v>
+        <v>129125889</v>
       </c>
       <c r="B232" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24926,10 +24926,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>447876</v>
+        <v>448024</v>
       </c>
       <c r="R232" t="n">
-        <v>6814962</v>
+        <v>6815046</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24961,7 +24961,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25001,7 +25001,7 @@
         <v>129125773</v>
       </c>
       <c r="B233" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>

--- a/artfynd/A 41585-2025 artfynd.xlsx
+++ b/artfynd/A 41585-2025 artfynd.xlsx
@@ -7448,50 +7448,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129125732</v>
+        <v>129125798</v>
       </c>
       <c r="B70" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447785</v>
+        <v>447786</v>
       </c>
       <c r="R70" t="n">
-        <v>6814990</v>
+        <v>6814897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7523,7 +7518,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7533,7 +7528,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7560,7 +7555,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129125843</v>
+        <v>129125835</v>
       </c>
       <c r="B71" t="n">
         <v>79041</v>
@@ -7595,10 +7590,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447812</v>
+        <v>447793</v>
       </c>
       <c r="R71" t="n">
-        <v>6815055</v>
+        <v>6815007</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7630,7 +7625,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7640,7 +7635,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7667,10 +7662,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129125755</v>
+        <v>129125843</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7678,21 +7673,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7702,10 +7697,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447756</v>
+        <v>447812</v>
       </c>
       <c r="R72" t="n">
-        <v>6814990</v>
+        <v>6815055</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7737,7 +7732,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7747,7 +7742,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7756,7 +7751,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7775,7 +7769,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129125798</v>
+        <v>129125821</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7810,10 +7804,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447786</v>
+        <v>447754</v>
       </c>
       <c r="R73" t="n">
-        <v>6814897</v>
+        <v>6815052</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7845,7 +7839,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7855,7 +7849,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7989,7 +7983,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129125835</v>
+        <v>129125812</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8024,10 +8018,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447793</v>
+        <v>447682</v>
       </c>
       <c r="R75" t="n">
-        <v>6815007</v>
+        <v>6814779</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8059,7 +8053,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8069,7 +8063,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8096,10 +8090,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129125812</v>
+        <v>129125755</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8107,21 +8101,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8131,10 +8125,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447682</v>
+        <v>447756</v>
       </c>
       <c r="R76" t="n">
-        <v>6814779</v>
+        <v>6814990</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8166,7 +8160,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8176,7 +8170,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,6 +8179,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8320,45 +8315,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129125821</v>
+        <v>129125732</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447754</v>
+        <v>447785</v>
       </c>
       <c r="R78" t="n">
-        <v>6815052</v>
+        <v>6814990</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8427,45 +8427,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129125873</v>
+        <v>129125759</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448163</v>
+        <v>447640</v>
       </c>
       <c r="R79" t="n">
-        <v>6815302</v>
+        <v>6814923</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,7 +8506,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8507,7 +8516,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,10 +8543,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129125771</v>
+        <v>129125729</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8545,21 +8554,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8569,10 +8578,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447925</v>
+        <v>448039</v>
       </c>
       <c r="R80" t="n">
-        <v>6815103</v>
+        <v>6815229</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8604,7 +8613,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8614,7 +8623,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8641,10 +8650,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129125853</v>
+        <v>129125751</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>81026</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8652,21 +8661,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8676,10 +8685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447853</v>
+        <v>447952</v>
       </c>
       <c r="R81" t="n">
-        <v>6814972</v>
+        <v>6814974</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8711,7 +8720,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8721,7 +8730,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8748,10 +8757,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129125867</v>
+        <v>129125730</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8759,21 +8768,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8783,10 +8792,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448088</v>
+        <v>448098</v>
       </c>
       <c r="R82" t="n">
-        <v>6815222</v>
+        <v>6815212</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,7 +8827,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8828,7 +8837,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8855,7 +8864,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129125824</v>
+        <v>129125873</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -8890,10 +8899,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447761</v>
+        <v>448163</v>
       </c>
       <c r="R83" t="n">
-        <v>6815045</v>
+        <v>6815302</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8925,7 +8934,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8935,7 +8944,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8962,7 +8971,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129125808</v>
+        <v>129125771</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -8997,10 +9006,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447782</v>
+        <v>447925</v>
       </c>
       <c r="R84" t="n">
-        <v>6814944</v>
+        <v>6815103</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9032,7 +9041,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9042,7 +9051,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9069,7 +9078,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129125895</v>
+        <v>129125853</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9104,10 +9113,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447963</v>
+        <v>447853</v>
       </c>
       <c r="R85" t="n">
-        <v>6815131</v>
+        <v>6814972</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9139,7 +9148,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9149,7 +9158,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9176,7 +9185,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129125767</v>
+        <v>129125867</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9211,10 +9220,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447915</v>
+        <v>448088</v>
       </c>
       <c r="R86" t="n">
-        <v>6815140</v>
+        <v>6815222</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9246,7 +9255,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9256,7 +9265,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9283,10 +9292,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129125729</v>
+        <v>129125824</v>
       </c>
       <c r="B87" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,21 +9303,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9318,10 +9327,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>448039</v>
+        <v>447761</v>
       </c>
       <c r="R87" t="n">
-        <v>6815229</v>
+        <v>6815045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9353,7 +9362,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9363,7 +9372,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9390,10 +9399,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129125751</v>
+        <v>129125808</v>
       </c>
       <c r="B88" t="n">
-        <v>81026</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9401,21 +9410,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9425,10 +9434,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447952</v>
+        <v>447782</v>
       </c>
       <c r="R88" t="n">
-        <v>6814974</v>
+        <v>6814944</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9460,7 +9469,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9470,7 +9479,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9497,10 +9506,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129125730</v>
+        <v>129125767</v>
       </c>
       <c r="B89" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9508,21 +9517,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9532,10 +9541,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>448098</v>
+        <v>447915</v>
       </c>
       <c r="R89" t="n">
-        <v>6815212</v>
+        <v>6815140</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9567,7 +9576,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9577,7 +9586,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9604,54 +9613,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129125759</v>
+        <v>129125895</v>
       </c>
       <c r="B90" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447640</v>
+        <v>447963</v>
       </c>
       <c r="R90" t="n">
-        <v>6814923</v>
+        <v>6815131</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9720,10 +9720,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129125874</v>
+        <v>129125722</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,21 +9731,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448182</v>
+        <v>447757</v>
       </c>
       <c r="R91" t="n">
-        <v>6815308</v>
+        <v>6814906</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9827,7 +9827,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129125809</v>
+        <v>129125772</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447763</v>
+        <v>447920</v>
       </c>
       <c r="R92" t="n">
-        <v>6814923</v>
+        <v>6815082</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9934,10 +9934,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129125831</v>
+        <v>129125753</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9945,21 +9945,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447755</v>
+        <v>447766</v>
       </c>
       <c r="R93" t="n">
-        <v>6814973</v>
+        <v>6814899</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10014,7 +10014,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På kolad högstubbe utan hänsynsmarkering</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10023,6 +10028,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10041,7 +10047,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129125772</v>
+        <v>129125874</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -10076,10 +10082,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447920</v>
+        <v>448182</v>
       </c>
       <c r="R94" t="n">
-        <v>6815082</v>
+        <v>6815308</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10111,7 +10117,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10121,7 +10127,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,10 +10154,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129125753</v>
+        <v>129125809</v>
       </c>
       <c r="B95" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,21 +10165,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10189,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447766</v>
+        <v>447763</v>
       </c>
       <c r="R95" t="n">
-        <v>6814899</v>
+        <v>6814923</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10218,7 +10224,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10228,12 +10234,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På kolad högstubbe utan hänsynsmarkering</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10242,7 +10243,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10261,7 +10261,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129125795</v>
+        <v>129125831</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447790</v>
+        <v>447755</v>
       </c>
       <c r="R96" t="n">
-        <v>6814834</v>
+        <v>6814973</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10368,10 +10368,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129125722</v>
+        <v>129125795</v>
       </c>
       <c r="B97" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10379,21 +10379,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447757</v>
+        <v>447790</v>
       </c>
       <c r="R97" t="n">
-        <v>6814906</v>
+        <v>6814834</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10475,10 +10475,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129125719</v>
+        <v>129125741</v>
       </c>
       <c r="B98" t="n">
-        <v>79073</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10486,34 +10486,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447855</v>
+        <v>447902</v>
       </c>
       <c r="R98" t="n">
-        <v>6814877</v>
+        <v>6814922</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10545,7 +10550,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10555,7 +10560,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10582,32 +10587,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129125746</v>
+        <v>129125719</v>
       </c>
       <c r="B99" t="n">
-        <v>97555</v>
+        <v>79073</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10617,10 +10622,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>448129</v>
+        <v>447855</v>
       </c>
       <c r="R99" t="n">
-        <v>6815200</v>
+        <v>6814877</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10652,7 +10657,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10662,7 +10667,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11224,50 +11229,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129125741</v>
+        <v>129125746</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>97555</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447902</v>
+        <v>448129</v>
       </c>
       <c r="R105" t="n">
-        <v>6814922</v>
+        <v>6815200</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11336,7 +11336,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129125868</v>
+        <v>129125837</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448101</v>
+        <v>447806</v>
       </c>
       <c r="R106" t="n">
-        <v>6815213</v>
+        <v>6815012</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11443,7 +11443,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129125837</v>
+        <v>129125814</v>
       </c>
       <c r="B107" t="n">
         <v>79041</v>
@@ -11478,10 +11478,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447806</v>
+        <v>447611</v>
       </c>
       <c r="R107" t="n">
-        <v>6815012</v>
+        <v>6814782</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11550,7 +11550,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129125814</v>
+        <v>129125868</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11585,10 +11585,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447611</v>
+        <v>448101</v>
       </c>
       <c r="R108" t="n">
-        <v>6814782</v>
+        <v>6815213</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12085,32 +12085,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129125891</v>
+        <v>129125728</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>91506</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>448003</v>
+        <v>447872</v>
       </c>
       <c r="R113" t="n">
-        <v>6815088</v>
+        <v>6815131</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12192,10 +12192,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129125779</v>
+        <v>129125721</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12203,21 +12203,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447936</v>
+        <v>447943</v>
       </c>
       <c r="R114" t="n">
-        <v>6814995</v>
+        <v>6814947</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12299,7 +12299,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129125841</v>
+        <v>129125891</v>
       </c>
       <c r="B115" t="n">
         <v>79041</v>
@@ -12334,10 +12334,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447812</v>
+        <v>448003</v>
       </c>
       <c r="R115" t="n">
-        <v>6815036</v>
+        <v>6815088</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12406,32 +12406,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129125728</v>
+        <v>129125779</v>
       </c>
       <c r="B116" t="n">
-        <v>91506</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447872</v>
+        <v>447936</v>
       </c>
       <c r="R116" t="n">
-        <v>6815131</v>
+        <v>6814995</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12513,7 +12513,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129125851</v>
+        <v>129125841</v>
       </c>
       <c r="B117" t="n">
         <v>79041</v>
@@ -12548,10 +12548,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447834</v>
+        <v>447812</v>
       </c>
       <c r="R117" t="n">
-        <v>6815005</v>
+        <v>6815036</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12620,10 +12620,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129125721</v>
+        <v>129125851</v>
       </c>
       <c r="B118" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,21 +12631,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447943</v>
+        <v>447834</v>
       </c>
       <c r="R118" t="n">
-        <v>6814947</v>
+        <v>6815005</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12834,7 +12834,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129125894</v>
+        <v>129125852</v>
       </c>
       <c r="B120" t="n">
         <v>79041</v>
@@ -12869,10 +12869,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447978</v>
+        <v>447839</v>
       </c>
       <c r="R120" t="n">
-        <v>6815111</v>
+        <v>6814995</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129125850</v>
+        <v>129125882</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447844</v>
+        <v>448089</v>
       </c>
       <c r="R121" t="n">
-        <v>6815026</v>
+        <v>6815086</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13048,7 +13048,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129125827</v>
+        <v>129125791</v>
       </c>
       <c r="B122" t="n">
         <v>79041</v>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447767</v>
+        <v>447839</v>
       </c>
       <c r="R122" t="n">
-        <v>6815014</v>
+        <v>6814871</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13155,7 +13155,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129125811</v>
+        <v>129125894</v>
       </c>
       <c r="B123" t="n">
         <v>79041</v>
@@ -13190,10 +13190,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447716</v>
+        <v>447978</v>
       </c>
       <c r="R123" t="n">
-        <v>6814829</v>
+        <v>6815111</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13262,7 +13262,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129125865</v>
+        <v>129125850</v>
       </c>
       <c r="B124" t="n">
         <v>79041</v>
@@ -13297,10 +13297,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>448049</v>
+        <v>447844</v>
       </c>
       <c r="R124" t="n">
-        <v>6815224</v>
+        <v>6815026</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13369,7 +13369,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129125859</v>
+        <v>129125827</v>
       </c>
       <c r="B125" t="n">
         <v>79041</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447887</v>
+        <v>447767</v>
       </c>
       <c r="R125" t="n">
-        <v>6815043</v>
+        <v>6815014</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13476,7 +13476,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129125882</v>
+        <v>129125811</v>
       </c>
       <c r="B126" t="n">
         <v>79041</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448089</v>
+        <v>447716</v>
       </c>
       <c r="R126" t="n">
-        <v>6815086</v>
+        <v>6814829</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13583,7 +13583,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129125845</v>
+        <v>129125865</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447801</v>
+        <v>448049</v>
       </c>
       <c r="R127" t="n">
-        <v>6815082</v>
+        <v>6815224</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13690,7 +13690,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129125791</v>
+        <v>129125859</v>
       </c>
       <c r="B128" t="n">
         <v>79041</v>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447839</v>
+        <v>447887</v>
       </c>
       <c r="R128" t="n">
-        <v>6814871</v>
+        <v>6815043</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13797,32 +13797,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129125750</v>
+        <v>129125845</v>
       </c>
       <c r="B129" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13832,10 +13832,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447714</v>
+        <v>447801</v>
       </c>
       <c r="R129" t="n">
-        <v>6815023</v>
+        <v>6815082</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13904,32 +13904,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129125852</v>
+        <v>129125750</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447839</v>
+        <v>447714</v>
       </c>
       <c r="R130" t="n">
-        <v>6814995</v>
+        <v>6815023</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14011,32 +14011,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129125743</v>
+        <v>129125770</v>
       </c>
       <c r="B131" t="n">
-        <v>80050</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14046,10 +14046,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447735</v>
+        <v>447916</v>
       </c>
       <c r="R131" t="n">
-        <v>6814890</v>
+        <v>6815113</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14091,12 +14091,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14123,7 +14118,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129125879</v>
+        <v>129125846</v>
       </c>
       <c r="B132" t="n">
         <v>79041</v>
@@ -14158,10 +14153,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>448114</v>
+        <v>447815</v>
       </c>
       <c r="R132" t="n">
-        <v>6815160</v>
+        <v>6815100</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14193,7 +14188,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14203,7 +14198,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14230,7 +14225,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129125770</v>
+        <v>129125844</v>
       </c>
       <c r="B133" t="n">
         <v>79041</v>
@@ -14265,10 +14260,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447916</v>
+        <v>447808</v>
       </c>
       <c r="R133" t="n">
-        <v>6815113</v>
+        <v>6815078</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14300,7 +14295,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14310,7 +14305,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14337,7 +14332,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129125844</v>
+        <v>129125879</v>
       </c>
       <c r="B134" t="n">
         <v>79041</v>
@@ -14372,10 +14367,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>447808</v>
+        <v>448114</v>
       </c>
       <c r="R134" t="n">
-        <v>6815078</v>
+        <v>6815160</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14407,7 +14402,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14417,7 +14412,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14444,32 +14439,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129125846</v>
+        <v>129125743</v>
       </c>
       <c r="B135" t="n">
-        <v>79041</v>
+        <v>80050</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14479,10 +14474,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>447815</v>
+        <v>447735</v>
       </c>
       <c r="R135" t="n">
-        <v>6815100</v>
+        <v>6814890</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14514,7 +14509,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14524,7 +14519,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14551,7 +14551,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129125781</v>
+        <v>129125818</v>
       </c>
       <c r="B136" t="n">
         <v>79041</v>
@@ -14586,10 +14586,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>447968</v>
+        <v>447641</v>
       </c>
       <c r="R136" t="n">
-        <v>6814977</v>
+        <v>6814924</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14658,7 +14658,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129125885</v>
+        <v>129125805</v>
       </c>
       <c r="B137" t="n">
         <v>79041</v>
@@ -14693,10 +14693,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>448080</v>
+        <v>447826</v>
       </c>
       <c r="R137" t="n">
-        <v>6815037</v>
+        <v>6814982</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14765,7 +14765,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129125797</v>
+        <v>129125781</v>
       </c>
       <c r="B138" t="n">
         <v>79041</v>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>447781</v>
+        <v>447968</v>
       </c>
       <c r="R138" t="n">
-        <v>6814894</v>
+        <v>6814977</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14872,7 +14872,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129125805</v>
+        <v>129125885</v>
       </c>
       <c r="B139" t="n">
         <v>79041</v>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>447826</v>
+        <v>448080</v>
       </c>
       <c r="R139" t="n">
-        <v>6814982</v>
+        <v>6815037</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14979,7 +14979,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129125887</v>
+        <v>129125797</v>
       </c>
       <c r="B140" t="n">
         <v>79041</v>
@@ -15014,10 +15014,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>448080</v>
+        <v>447781</v>
       </c>
       <c r="R140" t="n">
-        <v>6815039</v>
+        <v>6814894</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15086,10 +15086,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129125737</v>
+        <v>129125887</v>
       </c>
       <c r="B141" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15097,39 +15097,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>447735</v>
+        <v>448080</v>
       </c>
       <c r="R141" t="n">
-        <v>6815036</v>
+        <v>6815039</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15161,7 +15156,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15171,7 +15166,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15198,10 +15193,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129125818</v>
+        <v>129125737</v>
       </c>
       <c r="B142" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15209,34 +15204,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Skrikberget, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>447641</v>
+        <v>447735</v>
       </c>
       <c r="R142" t="n">
-        <v>6814924</v>
+        <v>6815036</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15305,7 +15305,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129125828</v>
+        <v>129125775</v>
       </c>
       <c r="B143" t="n">
         <v>79041</v>
@@ -15340,10 +15340,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>447781</v>
+        <v>447916</v>
       </c>
       <c r="R143" t="n">
-        <v>6815009</v>
+        <v>6815021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15412,7 +15412,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129125839</v>
+        <v>129125828</v>
       </c>
       <c r="B144" t="n">
         <v>79041</v>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>447805</v>
+        <v>447781</v>
       </c>
       <c r="R144" t="n">
-        <v>6815025</v>
+        <v>6815009</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15519,7 +15519,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129125792</v>
+        <v>129125839</v>
       </c>
       <c r="B145" t="n">
         <v>79041</v>
@@ -15554,10 +15554,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>447812</v>
+        <v>447805</v>
       </c>
       <c r="R145" t="n">
-        <v>6814852</v>
+        <v>6815025</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15589,7 +155